--- a/argus/kship/models/333430_model.xlsx
+++ b/argus/kship/models/333430_model.xlsx
@@ -666,43 +666,43 @@
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 87563억 × 비례계수 0.0076 × 계절비중 Q2 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 87836억 × 비례계수 0.0076 × 계절비중 Q2 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 87134억 × 비례계수 0.0076 × 계절비중 Q3 0.233(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 87401억 × 비례계수 0.0076 × 계절비중 Q3 0.233(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 86401억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 86661억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 85524억 × 비례계수 0.0076 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 85778억 × 비례계수 0.0076 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 84762억 × 비례계수 0.0076 × 계절비중 Q2 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 84735억 × 비례계수 0.0076 × 계절비중 Q2 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 83550억 × 비례계수 0.0076 × 계절비중 Q3 0.233(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 83524억 × 비례계수 0.0076 × 계절비중 Q3 0.233(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 81993억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 81967억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1815,43 +1815,43 @@
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 87563억 × 비례계수 0.0076 × 계절비중 Q2 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 87836억 × 비례계수 0.0076 × 계절비중 Q2 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 87134억 × 비례계수 0.0076 × 계절비중 Q3 0.233(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 87401억 × 비례계수 0.0076 × 계절비중 Q3 0.233(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 86401억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 86661억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 85524억 × 비례계수 0.0076 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 85778억 × 비례계수 0.0076 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 84762억 × 비례계수 0.0076 × 계절비중 Q2 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 84735억 × 비례계수 0.0076 × 계절비중 Q2 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 83550억 × 비례계수 0.0076 × 계절비중 Q3 0.233(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 83524억 × 비례계수 0.0076 × 계절비중 Q3 0.233(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 81993억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 81967억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -6545,26 +6545,26 @@
         <v>0.212456</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>-0.032645</v>
+        <v>-0.029626</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.08615299999999999</v>
+        <v>0.089467</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.017022</v>
+        <v>0.020067</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>-0.0183</v>
+        <v>-0.015364</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>-0.031977</v>
+        <v>-0.035306</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>-0.041153</v>
+        <v>-0.044393</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>-0.051045</v>
+        <v>-0.054172</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6694,29 +6694,29 @@
         <v>0.123114</v>
       </c>
       <c r="AG22" s="24" t="n">
-        <v>0.123129</v>
+        <v>0.123127</v>
       </c>
       <c r="AH22" s="24" t="n">
-        <v>0.123069</v>
+        <v>0.123083</v>
       </c>
       <c r="AI22" s="24" t="n">
-        <v>0.123098</v>
+        <v>0.123122</v>
       </c>
       <c r="AJ22" s="25">
         <f>IFERROR(subQ!AJ8/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK22" s="24" t="n">
-        <v>0.123113</v>
+        <v>0.123093</v>
       </c>
       <c r="AL22" s="24" t="n">
-        <v>0.123116</v>
+        <v>0.123091</v>
       </c>
       <c r="AM22" s="24" t="n">
-        <v>0.123071</v>
+        <v>0.123112</v>
       </c>
       <c r="AN22" s="24" t="n">
-        <v>0.123099</v>
+        <v>0.123086</v>
       </c>
       <c r="AO22" s="25">
         <f>IFERROR(subQ!AO8/subQ!AO5,"")</f>
@@ -6849,29 +6849,29 @@
         <v>0.19563</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.195618</v>
+        <v>0.195644</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.195638</v>
+        <v>0.195625</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.195642</v>
+        <v>0.195645</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.19566</v>
+        <v>0.195631</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.195631</v>
+        <v>0.195629</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.19564</v>
+        <v>0.195639</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.195666</v>
+        <v>0.195623</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7129,7 +7129,7 @@
         <v>2.98</v>
       </c>
       <c r="AI25" s="29" t="n">
-        <v>3.1</v>
+        <v>3.11</v>
       </c>
       <c r="AJ25" s="30">
         <f>subQ!AJ11</f>
@@ -7433,29 +7433,29 @@
         <v>0.050016</v>
       </c>
       <c r="AG27" s="24" t="n">
-        <v>0.050045</v>
+        <v>0.049896</v>
       </c>
       <c r="AH27" s="24" t="n">
-        <v>0.050121</v>
+        <v>0.04997</v>
       </c>
       <c r="AI27" s="24" t="n">
-        <v>0.050047</v>
+        <v>0.049896</v>
       </c>
       <c r="AJ27" s="25">
         <f>IFERROR(subQ!AJ14/subQ!AJ13,"")</f>
         <v/>
       </c>
       <c r="AK27" s="24" t="n">
-        <v>0.050016</v>
+        <v>0.049889</v>
       </c>
       <c r="AL27" s="24" t="n">
-        <v>0.050136</v>
+        <v>0.050151</v>
       </c>
       <c r="AM27" s="24" t="n">
-        <v>0.05</v>
+        <v>0.050015</v>
       </c>
       <c r="AN27" s="24" t="n">
-        <v>0.04994</v>
+        <v>0.049952</v>
       </c>
       <c r="AO27" s="25">
         <f>IFERROR(subQ!AO14/subQ!AO13,"")</f>
@@ -7588,29 +7588,29 @@
         <v>0.570567</v>
       </c>
       <c r="AG28" s="24" t="n">
-        <v>0.570712</v>
+        <v>0.5708029999999999</v>
       </c>
       <c r="AH28" s="24" t="n">
-        <v>0.570702</v>
+        <v>0.57084</v>
       </c>
       <c r="AI28" s="24" t="n">
-        <v>0.5707989999999999</v>
+        <v>0.570731</v>
       </c>
       <c r="AJ28" s="25">
         <f>IFERROR(subQ!AJ16/subQ!AJ15,"")</f>
         <v/>
       </c>
       <c r="AK28" s="24" t="n">
-        <v>0.570758</v>
+        <v>0.570903</v>
       </c>
       <c r="AL28" s="24" t="n">
         <v>0.570747</v>
       </c>
       <c r="AM28" s="24" t="n">
-        <v>0.570825</v>
+        <v>0.570686</v>
       </c>
       <c r="AN28" s="24" t="n">
-        <v>0.570739</v>
+        <v>0.5708839999999999</v>
       </c>
       <c r="AO28" s="25">
         <f>IFERROR(subQ!AO16/subQ!AO15,"")</f>
@@ -7850,13 +7850,13 @@
         <v>0</v>
       </c>
       <c r="AG30" s="29" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AH30" s="29" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="AI30" s="29" t="n">
         <v>0</v>
-      </c>
-      <c r="AH30" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI30" s="29" t="n">
-        <v>-0</v>
       </c>
       <c r="AJ30" s="30" t="n"/>
       <c r="AK30" s="29" t="n">
@@ -7869,7 +7869,7 @@
         <v>0</v>
       </c>
       <c r="AN30" s="29" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AO30" s="30" t="n"/>
     </row>
@@ -7978,20 +7978,20 @@
         <v>0</v>
       </c>
       <c r="AG31" s="29" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="AH31" s="29" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AI31" s="29" t="n">
         <v>0</v>
-      </c>
-      <c r="AI31" s="29" t="n">
-        <v>0.01</v>
       </c>
       <c r="AJ31" s="30" t="n"/>
       <c r="AK31" s="29" t="n">
         <v>0</v>
       </c>
       <c r="AL31" s="29" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="AM31" s="29" t="n">
         <v>0</v>
@@ -8231,29 +8231,29 @@
       </c>
       <c r="AE33" s="25" t="n"/>
       <c r="AF33" s="24" t="n">
-        <v>0.094596</v>
+        <v>0.094565</v>
       </c>
       <c r="AG33" s="24" t="n">
-        <v>0.092389</v>
+        <v>0.092682</v>
       </c>
       <c r="AH33" s="24" t="n">
-        <v>0.08346199999999999</v>
+        <v>0.08365400000000001</v>
       </c>
       <c r="AI33" s="24" t="n">
-        <v>0.099895</v>
+        <v>0.100171</v>
       </c>
       <c r="AJ33" s="25" t="n"/>
       <c r="AK33" s="24" t="n">
-        <v>0.06636400000000001</v>
+        <v>0.066498</v>
       </c>
       <c r="AL33" s="24" t="n">
-        <v>0.06565699999999999</v>
+        <v>0.065563</v>
       </c>
       <c r="AM33" s="24" t="n">
-        <v>0.06028</v>
+        <v>0.060237</v>
       </c>
       <c r="AN33" s="24" t="n">
-        <v>0.07271900000000001</v>
+        <v>0.07265199999999999</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -8362,26 +8362,26 @@
         <v>0.04213</v>
       </c>
       <c r="AG34" s="24" t="n">
-        <v>0.043247</v>
+        <v>0.043369</v>
       </c>
       <c r="AH34" s="24" t="n">
-        <v>0.040882</v>
+        <v>0.040994</v>
       </c>
       <c r="AI34" s="24" t="n">
-        <v>0.050962</v>
+        <v>0.051088</v>
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="24" t="n">
-        <v>0.035424</v>
+        <v>0.035518</v>
       </c>
       <c r="AL34" s="24" t="n">
-        <v>0.036093</v>
+        <v>0.036055</v>
       </c>
       <c r="AM34" s="24" t="n">
-        <v>0.034083</v>
+        <v>0.034069</v>
       </c>
       <c r="AN34" s="24" t="n">
-        <v>0.042158</v>
+        <v>0.042131</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -9014,26 +9014,26 @@
         <v>-0.434049</v>
       </c>
       <c r="AG40" s="24" t="n">
-        <v>0.322835</v>
+        <v>0.32196</v>
       </c>
       <c r="AH40" s="24" t="n">
-        <v>0.750591</v>
+        <v>0.748227</v>
       </c>
       <c r="AI40" s="24" t="n">
-        <v>0.431774</v>
+        <v>0.427875</v>
       </c>
       <c r="AJ40" s="25" t="n"/>
       <c r="AK40" s="24" t="n">
-        <v>0.32701</v>
+        <v>0.323397</v>
       </c>
       <c r="AL40" s="24" t="n">
-        <v>-0.025794</v>
+        <v>-0.027134</v>
       </c>
       <c r="AM40" s="24" t="n">
         <v>0</v>
       </c>
       <c r="AN40" s="24" t="n">
-        <v>0.019061</v>
+        <v>0.021843</v>
       </c>
       <c r="AO40" s="25" t="n"/>
     </row>
@@ -9149,7 +9149,7 @@
         <v>-0.112299</v>
       </c>
       <c r="AM41" s="24" t="n">
-        <v>-0.104972</v>
+        <v>-0.110497</v>
       </c>
       <c r="AN41" s="24" t="n">
         <v>-0.108571</v>
@@ -9437,29 +9437,29 @@
         <v>0.19563</v>
       </c>
       <c r="AG43" s="24" t="n">
-        <v>0.195618</v>
+        <v>0.195644</v>
       </c>
       <c r="AH43" s="24" t="n">
-        <v>0.195638</v>
+        <v>0.195625</v>
       </c>
       <c r="AI43" s="24" t="n">
-        <v>0.195642</v>
+        <v>0.195645</v>
       </c>
       <c r="AJ43" s="25">
         <f>IFERROR(subQ!AJ34/subQ!AJ33,"")</f>
         <v/>
       </c>
       <c r="AK43" s="24" t="n">
-        <v>0.19566</v>
+        <v>0.195631</v>
       </c>
       <c r="AL43" s="24" t="n">
-        <v>0.195631</v>
+        <v>0.195629</v>
       </c>
       <c r="AM43" s="24" t="n">
-        <v>0.19564</v>
+        <v>0.195639</v>
       </c>
       <c r="AN43" s="24" t="n">
-        <v>0.195666</v>
+        <v>0.195623</v>
       </c>
       <c r="AO43" s="25">
         <f>IFERROR(subQ!AO34/subQ!AO33,"")</f>
@@ -39654,7 +39654,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>242</v>
+        <v>242.2</v>
       </c>
     </row>
     <row r="30">
@@ -39674,7 +39674,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>15.12</v>
+        <v>15.11</v>
       </c>
     </row>
     <row r="32">
@@ -39694,7 +39694,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.1409</v>
+        <v>0.141</v>
       </c>
     </row>
     <row r="34">

--- a/argus/kship/models/333430_model.xlsx
+++ b/argus/kship/models/333430_model.xlsx
@@ -654,55 +654,55 @@
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 84957억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 85287억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 87118억 × 비례계수 0.0076 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 88687억 × 비례계수 0.0076 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 87836억 × 비례계수 0.0076 × 계절비중 Q2 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 92009억 × 비례계수 0.0076 × 계절비중 Q2 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 87401억 × 비례계수 0.0076 × 계절비중 Q3 0.233(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 95873억 × 비례계수 0.0076 × 계절비중 Q3 0.233(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 86661억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 101010억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 85778억 × 비례계수 0.0076 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 107090억 × 비례계수 0.0076 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 84735억 × 비례계수 0.0076 × 계절비중 Q2 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 113604억 × 비례계수 0.0076 × 계절비중 Q2 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 83524억 × 비례계수 0.0076 × 계절비중 Q3 0.233(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 120051억 × 비례계수 0.0076 × 계절비중 Q3 0.233(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 81967억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 125764억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -912,37 +912,37 @@
     <comment ref="AH25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 770억 × 1.55% − 총차입금 290억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 772억 × 1.55% − 총차입금 290억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AI25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 801억 × 1.55% − 총차입금 290억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 806억 × 1.55% − 총차입금 290억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AK25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 842억 × 1.55% − 총차입금 290억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 853억 × 1.55% − 총차입금 290억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AL25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 872억 × 1.55% − 총차입금 290억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 890억 × 1.55% − 총차입금 290억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AM25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 903억 × 1.55% − 총차입금 290억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 931억 × 1.55% − 총차입금 290억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AN25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 934억 × 1.55% − 총차입금 290억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 974억 × 1.55% − 총차입금 290억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AC26" authorId="0" shapeId="0">
@@ -1803,55 +1803,55 @@
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 84957억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 85287억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 87118억 × 비례계수 0.0076 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 88687억 × 비례계수 0.0076 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 87836억 × 비례계수 0.0076 × 계절비중 Q2 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 92009억 × 비례계수 0.0076 × 계절비중 Q2 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 87401억 × 비례계수 0.0076 × 계절비중 Q3 0.233(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 95873억 × 비례계수 0.0076 × 계절비중 Q3 0.233(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 86661억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 101010억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 85778억 × 비례계수 0.0076 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 107090억 × 비례계수 0.0076 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 84735억 × 비례계수 0.0076 × 계절비중 Q2 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 113604억 × 비례계수 0.0076 × 계절비중 Q2 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 83524억 × 비례계수 0.0076 × 계절비중 Q3 0.233(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 120051억 × 비례계수 0.0076 × 계절비중 Q3 0.233(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 81967억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 125764억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -2276,37 +2276,37 @@
     </comment>
     <comment ref="AH11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 770억 × 1.55% − 총차입금 290억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 772억 × 1.55% − 총차입금 290억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 801억 × 1.55% − 총차입금 290억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 806억 × 1.55% − 총차입금 290억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 842억 × 1.55% − 총차입금 290억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 853억 × 1.55% − 총차입금 290억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 872억 × 1.55% − 총차입금 290억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 890억 × 1.55% − 총차입금 290억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 903억 × 1.55% − 총차입금 290억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 931억 × 1.55% − 총차입금 290억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 934억 × 1.55% − 총차입금 290억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 974억 × 1.55% − 총차입금 290억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
@@ -4359,7 +4359,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-09-30</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-02</t>
         </is>
       </c>
     </row>
@@ -4487,7 +4487,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 11.1, "op_wape_pct": 63.9, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "customer_yard_revenue_weighted", "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식", "detail": [{"q": "2025Q3", "rev_pred": 135.46, "rev_act": 137.98, "op_pred": 13.53, "op_act": 33.43}, {"q": "2025Q4", "rev_pred": 178.85, "rev_act": 152.6, "op_pred": 17.86, "op_act": 55.32}, {"q": "2026Q1", "rev_pred": 148.81, "rev_act": 120.79, "op_pred": 14.86, "op_act": 23.04}, {"q": "2026Q2", "rev_pred": 155.17, "rev_act": 162.29, "op_pred": 15.5, "op_act": 59.33}]}</t>
+          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 11.1, "op_wape_pct": 63.9, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "customer_yard_revenue_weighted", "selection_oos_at_freeze": {"freeze": "2024Q2", "n": 4, "wape_link": 22.8, "wape_trend": 36.0, "adopted": true}, "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices·forecast_panel 신규수주 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식; 고객 연동 채택은 동결 모델 안에서도 자기 la−4분기 OOS 규칙(selection_oos_at_freeze)", "detail": [{"q": "2025Q3", "rev_pred": 135.46, "rev_act": 137.98, "op_pred": 13.53, "op_act": 33.43}, {"q": "2025Q4", "rev_pred": 178.85, "rev_act": 152.6, "op_pred": 17.86, "op_act": 55.32}, {"q": "2026Q1", "rev_pred": 148.81, "rev_act": 120.79, "op_pred": 14.86, "op_act": 23.04}, {"q": "2026Q2", "rev_pred": 155.17, "rev_act": 162.29, "op_pred": 15.5, "op_act": 59.33}]}</t>
         </is>
       </c>
     </row>
@@ -6538,33 +6538,33 @@
         <v>0.027993</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.312811</v>
+        <v>0.317923</v>
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.212456</v>
+        <v>0.23423</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>-0.029626</v>
+        <v>0.016465</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.089467</v>
+        <v>0.195079</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.020067</v>
+        <v>0.184377</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>-0.015364</v>
+        <v>0.20754</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>-0.035306</v>
+        <v>0.234724</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>-0.044393</v>
+        <v>0.252198</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>-0.054172</v>
+        <v>0.245056</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6684,39 +6684,39 @@
         <v>0.123096</v>
       </c>
       <c r="AD22" s="24" t="n">
-        <v>0.123097</v>
+        <v>0.123117</v>
       </c>
       <c r="AE22" s="25">
         <f>IFERROR(subQ!AE8/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF22" s="24" t="n">
-        <v>0.123114</v>
+        <v>0.123088</v>
       </c>
       <c r="AG22" s="24" t="n">
-        <v>0.123127</v>
+        <v>0.123121</v>
       </c>
       <c r="AH22" s="24" t="n">
-        <v>0.123083</v>
+        <v>0.12312</v>
       </c>
       <c r="AI22" s="24" t="n">
-        <v>0.123122</v>
+        <v>0.123095</v>
       </c>
       <c r="AJ22" s="25">
         <f>IFERROR(subQ!AJ8/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK22" s="24" t="n">
-        <v>0.123093</v>
+        <v>0.123097</v>
       </c>
       <c r="AL22" s="24" t="n">
-        <v>0.123091</v>
+        <v>0.123085</v>
       </c>
       <c r="AM22" s="24" t="n">
+        <v>0.123104</v>
+      </c>
+      <c r="AN22" s="24" t="n">
         <v>0.123112</v>
-      </c>
-      <c r="AN22" s="24" t="n">
-        <v>0.123086</v>
       </c>
       <c r="AO22" s="25">
         <f>IFERROR(subQ!AO8/subQ!AO5,"")</f>
@@ -6839,39 +6839,39 @@
         <v>0.195643</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>0.195627</v>
+        <v>0.195664</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.19563</v>
+        <v>0.195667</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.195644</v>
+        <v>0.195623</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.195625</v>
+        <v>0.195623</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.195645</v>
+        <v>0.195642</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.195631</v>
+        <v>0.195645</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.195629</v>
+        <v>0.19565</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.195639</v>
+        <v>0.195656</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.195623</v>
+        <v>0.195643</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7126,26 +7126,26 @@
         <v>2.86</v>
       </c>
       <c r="AH25" s="29" t="n">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="AI25" s="29" t="n">
-        <v>3.11</v>
+        <v>3.12</v>
       </c>
       <c r="AJ25" s="30">
         <f>subQ!AJ11</f>
         <v/>
       </c>
       <c r="AK25" s="29" t="n">
-        <v>3.26</v>
+        <v>3.31</v>
       </c>
       <c r="AL25" s="29" t="n">
-        <v>3.38</v>
+        <v>3.45</v>
       </c>
       <c r="AM25" s="29" t="n">
-        <v>3.5</v>
+        <v>3.61</v>
       </c>
       <c r="AN25" s="29" t="n">
-        <v>3.62</v>
+        <v>3.77</v>
       </c>
       <c r="AO25" s="30">
         <f>subQ!AO11</f>
@@ -7423,39 +7423,39 @@
         <v>0.04995</v>
       </c>
       <c r="AD27" s="24" t="n">
-        <v>0.050024</v>
+        <v>0.050072</v>
       </c>
       <c r="AE27" s="25">
         <f>IFERROR(subQ!AE14/subQ!AE13,"")</f>
         <v/>
       </c>
       <c r="AF27" s="24" t="n">
-        <v>0.050016</v>
+        <v>0.050141</v>
       </c>
       <c r="AG27" s="24" t="n">
-        <v>0.049896</v>
+        <v>0.0501</v>
       </c>
       <c r="AH27" s="24" t="n">
-        <v>0.04997</v>
+        <v>0.050069</v>
       </c>
       <c r="AI27" s="24" t="n">
-        <v>0.049896</v>
+        <v>0.05008</v>
       </c>
       <c r="AJ27" s="25">
         <f>IFERROR(subQ!AJ14/subQ!AJ13,"")</f>
         <v/>
       </c>
       <c r="AK27" s="24" t="n">
-        <v>0.049889</v>
+        <v>0.050091</v>
       </c>
       <c r="AL27" s="24" t="n">
-        <v>0.050151</v>
+        <v>0.049885</v>
       </c>
       <c r="AM27" s="24" t="n">
-        <v>0.050015</v>
+        <v>0.050078</v>
       </c>
       <c r="AN27" s="24" t="n">
-        <v>0.049952</v>
+        <v>0.050008</v>
       </c>
       <c r="AO27" s="25">
         <f>IFERROR(subQ!AO14/subQ!AO13,"")</f>
@@ -7578,39 +7578,39 @@
         <v>0.570682</v>
       </c>
       <c r="AD28" s="24" t="n">
-        <v>0.570925</v>
+        <v>0.570783</v>
       </c>
       <c r="AE28" s="25">
         <f>IFERROR(subQ!AE16/subQ!AE15,"")</f>
         <v/>
       </c>
       <c r="AF28" s="24" t="n">
-        <v>0.570567</v>
+        <v>0.57058</v>
       </c>
       <c r="AG28" s="24" t="n">
-        <v>0.5708029999999999</v>
+        <v>0.570701</v>
       </c>
       <c r="AH28" s="24" t="n">
-        <v>0.57084</v>
+        <v>0.570597</v>
       </c>
       <c r="AI28" s="24" t="n">
-        <v>0.570731</v>
+        <v>0.570703</v>
       </c>
       <c r="AJ28" s="25">
         <f>IFERROR(subQ!AJ16/subQ!AJ15,"")</f>
         <v/>
       </c>
       <c r="AK28" s="24" t="n">
-        <v>0.570903</v>
+        <v>0.570765</v>
       </c>
       <c r="AL28" s="24" t="n">
-        <v>0.570747</v>
+        <v>0.570873</v>
       </c>
       <c r="AM28" s="24" t="n">
-        <v>0.570686</v>
+        <v>0.570662</v>
       </c>
       <c r="AN28" s="24" t="n">
-        <v>0.5708839999999999</v>
+        <v>0.570869</v>
       </c>
       <c r="AO28" s="25">
         <f>IFERROR(subQ!AO16/subQ!AO15,"")</f>
@@ -7847,20 +7847,20 @@
       </c>
       <c r="AE30" s="30" t="n"/>
       <c r="AF30" s="29" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AG30" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="AG30" s="29" t="n">
-        <v>0.01</v>
-      </c>
       <c r="AH30" s="29" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="AI30" s="29" t="n">
         <v>0</v>
       </c>
       <c r="AJ30" s="30" t="n"/>
       <c r="AK30" s="29" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL30" s="29" t="n">
         <v>0</v>
@@ -7869,7 +7869,7 @@
         <v>0</v>
       </c>
       <c r="AN30" s="29" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO30" s="30" t="n"/>
     </row>
@@ -7975,13 +7975,13 @@
       </c>
       <c r="AE31" s="30" t="n"/>
       <c r="AF31" s="29" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="AG31" s="29" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AH31" s="29" t="n">
         <v>0</v>
-      </c>
-      <c r="AG31" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH31" s="29" t="n">
-        <v>-0</v>
       </c>
       <c r="AI31" s="29" t="n">
         <v>0</v>
@@ -8227,33 +8227,33 @@
         <v>0.116314</v>
       </c>
       <c r="AD33" s="24" t="n">
-        <v>0.143987</v>
+        <v>0.144495</v>
       </c>
       <c r="AE33" s="25" t="n"/>
       <c r="AF33" s="24" t="n">
-        <v>0.094565</v>
+        <v>0.096108</v>
       </c>
       <c r="AG33" s="24" t="n">
-        <v>0.092682</v>
+        <v>0.09653</v>
       </c>
       <c r="AH33" s="24" t="n">
-        <v>0.08365400000000001</v>
+        <v>0.09056400000000001</v>
       </c>
       <c r="AI33" s="24" t="n">
-        <v>0.100171</v>
+        <v>0.114239</v>
       </c>
       <c r="AJ33" s="25" t="n"/>
       <c r="AK33" s="24" t="n">
-        <v>0.066498</v>
+        <v>0.079434</v>
       </c>
       <c r="AL33" s="24" t="n">
-        <v>0.065563</v>
+        <v>0.08269700000000001</v>
       </c>
       <c r="AM33" s="24" t="n">
-        <v>0.060237</v>
+        <v>0.07963000000000001</v>
       </c>
       <c r="AN33" s="24" t="n">
-        <v>0.07265199999999999</v>
+        <v>0.100986</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -8355,33 +8355,33 @@
         <v>0.044906</v>
       </c>
       <c r="AD34" s="24" t="n">
-        <v>0.059421</v>
+        <v>0.059631</v>
       </c>
       <c r="AE34" s="25" t="n"/>
       <c r="AF34" s="24" t="n">
-        <v>0.04213</v>
+        <v>0.042828</v>
       </c>
       <c r="AG34" s="24" t="n">
-        <v>0.043369</v>
+        <v>0.045214</v>
       </c>
       <c r="AH34" s="24" t="n">
-        <v>0.040994</v>
+        <v>0.044502</v>
       </c>
       <c r="AI34" s="24" t="n">
-        <v>0.051088</v>
+        <v>0.058611</v>
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="24" t="n">
-        <v>0.035518</v>
+        <v>0.042896</v>
       </c>
       <c r="AL34" s="24" t="n">
-        <v>0.036055</v>
+        <v>0.046222</v>
       </c>
       <c r="AM34" s="24" t="n">
-        <v>0.034069</v>
+        <v>0.04606</v>
       </c>
       <c r="AN34" s="24" t="n">
-        <v>0.042131</v>
+        <v>0.060287</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -9007,33 +9007,33 @@
         <v>-0.758009</v>
       </c>
       <c r="AD40" s="24" t="n">
-        <v>-0.64176</v>
+        <v>-0.642109</v>
       </c>
       <c r="AE40" s="25" t="n"/>
       <c r="AF40" s="24" t="n">
-        <v>-0.434049</v>
+        <v>-0.436094</v>
       </c>
       <c r="AG40" s="24" t="n">
-        <v>0.32196</v>
+        <v>0.301837</v>
       </c>
       <c r="AH40" s="24" t="n">
-        <v>0.748227</v>
+        <v>0.686761</v>
       </c>
       <c r="AI40" s="24" t="n">
-        <v>0.427875</v>
+        <v>0.320976</v>
       </c>
       <c r="AJ40" s="25" t="n"/>
       <c r="AK40" s="24" t="n">
-        <v>0.323397</v>
+        <v>0.176791</v>
       </c>
       <c r="AL40" s="24" t="n">
-        <v>-0.027134</v>
+        <v>-0.170027</v>
       </c>
       <c r="AM40" s="24" t="n">
-        <v>0</v>
+        <v>-0.178697</v>
       </c>
       <c r="AN40" s="24" t="n">
-        <v>0.021843</v>
+        <v>-0.189808</v>
       </c>
       <c r="AO40" s="25" t="n"/>
     </row>
@@ -9130,29 +9130,29 @@
       </c>
       <c r="AE41" s="25" t="n"/>
       <c r="AF41" s="24" t="n">
-        <v>-0.481183</v>
+        <v>-0.483871</v>
       </c>
       <c r="AG41" s="24" t="n">
-        <v>-0.34386</v>
+        <v>-0.347368</v>
       </c>
       <c r="AH41" s="24" t="n">
-        <v>-0.125604</v>
+        <v>-0.130435</v>
       </c>
       <c r="AI41" s="24" t="n">
-        <v>-0.116162</v>
+        <v>-0.126263</v>
       </c>
       <c r="AJ41" s="25" t="n"/>
       <c r="AK41" s="24" t="n">
-        <v>-0.119171</v>
+        <v>-0.125</v>
       </c>
       <c r="AL41" s="24" t="n">
-        <v>-0.112299</v>
+        <v>-0.129032</v>
       </c>
       <c r="AM41" s="24" t="n">
-        <v>-0.110497</v>
+        <v>-0.133333</v>
       </c>
       <c r="AN41" s="24" t="n">
-        <v>-0.108571</v>
+        <v>-0.138728</v>
       </c>
       <c r="AO41" s="25" t="n"/>
     </row>
@@ -9427,39 +9427,39 @@
         <v>0.195643</v>
       </c>
       <c r="AD43" s="24" t="n">
-        <v>0.195627</v>
+        <v>0.195664</v>
       </c>
       <c r="AE43" s="25">
         <f>IFERROR(subQ!AE34/subQ!AE33,"")</f>
         <v/>
       </c>
       <c r="AF43" s="24" t="n">
-        <v>0.19563</v>
+        <v>0.195667</v>
       </c>
       <c r="AG43" s="24" t="n">
-        <v>0.195644</v>
+        <v>0.195623</v>
       </c>
       <c r="AH43" s="24" t="n">
-        <v>0.195625</v>
+        <v>0.195623</v>
       </c>
       <c r="AI43" s="24" t="n">
-        <v>0.195645</v>
+        <v>0.195642</v>
       </c>
       <c r="AJ43" s="25">
         <f>IFERROR(subQ!AJ34/subQ!AJ33,"")</f>
         <v/>
       </c>
       <c r="AK43" s="24" t="n">
-        <v>0.195631</v>
+        <v>0.195645</v>
       </c>
       <c r="AL43" s="24" t="n">
-        <v>0.195629</v>
+        <v>0.19565</v>
       </c>
       <c r="AM43" s="24" t="n">
-        <v>0.195639</v>
+        <v>0.195656</v>
       </c>
       <c r="AN43" s="24" t="n">
-        <v>0.195623</v>
+        <v>0.195643</v>
       </c>
       <c r="AO43" s="25">
         <f>IFERROR(subQ!AO34/subQ!AO33,"")</f>
@@ -10202,7 +10202,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18703,7 +18703,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -39654,7 +39654,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>242.2</v>
+        <v>246</v>
       </c>
     </row>
     <row r="30">
@@ -39674,7 +39674,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>15.11</v>
+        <v>14.88</v>
       </c>
     </row>
     <row r="32">
@@ -39694,7 +39694,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.141</v>
+        <v>0.1432</v>
       </c>
     </row>
     <row r="34">
@@ -39704,7 +39704,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="35">

--- a/argus/kship/models/333430_model.xlsx
+++ b/argus/kship/models/333430_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -663,55 +663,55 @@
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 84766억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 84761억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 87829억 × 비례계수 0.0076 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 87818억 × 비례계수 0.0076 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 90812억 × 비례계수 0.0076 × 계절비중 Q2 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 90794억 × 비례계수 0.0076 × 계절비중 Q2 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 94520억 × 비례계수 0.0076 × 계절비중 Q3 0.233(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 94496억 × 비례계수 0.0076 × 계절비중 Q3 0.233(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 99648억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 99624억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 105726억 × 비례계수 0.0076 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 105703억 × 비례계수 0.0076 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 112240억 × 비례계수 0.0076 × 계절비중 Q2 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 112218억 × 비례계수 0.0076 × 계절비중 Q2 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 118689억 × 비례계수 0.0076 × 계절비중 Q3 0.233(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 118668억 × 비례계수 0.0076 × 계절비중 Q3 0.233(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 124404억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 124385억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1590,55 +1590,55 @@
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 84766억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 84761억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 87829억 × 비례계수 0.0076 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 87818억 × 비례계수 0.0076 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 90812억 × 비례계수 0.0076 × 계절비중 Q2 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 90794억 × 비례계수 0.0076 × 계절비중 Q2 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 94520억 × 비례계수 0.0076 × 계절비중 Q3 0.233(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 94496억 × 비례계수 0.0076 × 계절비중 Q3 0.233(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 99648억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 99624억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 105726억 × 비례계수 0.0076 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 105703억 × 비례계수 0.0076 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 112240억 × 비례계수 0.0076 × 계절비중 Q2 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 112218억 × 비례계수 0.0076 × 계절비중 Q2 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 118689억 × 비례계수 0.0076 × 계절비중 Q3 0.233(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 118668억 × 비례계수 0.0076 × 계절비중 Q3 0.233(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 124404억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 124385억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -1986,7 +1986,7 @@
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 854억 × 1.66%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 290억 × 3.62%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 853억 × 1.66%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 290억 × 3.62%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2046,7 +2046,7 @@
     </comment>
     <comment ref="AL12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 854억 × 1.66%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 290억 × 3.62%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 853억 × 1.66%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 290억 × 3.62%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -4059,7 +4059,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-05</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
         </is>
       </c>
     </row>
@@ -4930,35 +4930,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1354.78</v>
+        <v>1351.18</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1460.21</v>
+        <v>1459.61</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5049,35 +5049,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5168,35 +5168,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>858.4</v>
+        <v>855.39</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>921.0599999999999</v>
+        <v>920.6900000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5287,35 +5287,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5406,35 +5406,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1525.7</v>
+        <v>1519.07</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1694.79</v>
+        <v>1693.81</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5525,35 +5525,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5644,35 +5644,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>202.07</v>
+        <v>201.53</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>214.1</v>
+        <v>214.03</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5763,35 +5763,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5898,7 +5898,7 @@
         <v>3790</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>3915</v>
+        <v>3890</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6171,7 +6171,7 @@
         <v>3675.7</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>3927.5</v>
+        <v>3915</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6326,33 +6326,33 @@
         <v>0.025601257</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.309862238</v>
+        <v>0.309796705</v>
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.222307864</v>
+        <v>0.222142284</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.003217122</v>
+        <v>0.003032265</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.180976609</v>
+        <v>0.180623278</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.175605363</v>
+        <v>0.175363987</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.203806556</v>
+        <v>0.203698686</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.235980591</v>
+        <v>0.235962649</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.255684538</v>
+        <v>0.255820913</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.248404119</v>
+        <v>0.248552699</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6637,39 +6637,39 @@
         <v>0.195675217</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>0.1956674</v>
+        <v>0.195627158</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.195678678</v>
+        <v>0.195637448</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.195626804</v>
+        <v>0.195662858</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.195667784</v>
+        <v>0.195666487</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.195633671</v>
+        <v>0.195641069</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.195633827</v>
+        <v>0.195621588</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.195646772</v>
+        <v>0.195635966</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.195663569</v>
+        <v>0.19565321</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.195636612</v>
+        <v>0.195629198</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7539,36 +7539,36 @@
         <v/>
       </c>
       <c r="AC29" s="30" t="n">
-        <v>0.009384876</v>
+        <v>0.008664824999999999</v>
       </c>
       <c r="AD29" s="30" t="n">
-        <v>-8.348e-06</v>
+        <v>-0.00978943</v>
       </c>
       <c r="AE29" s="31" t="n"/>
       <c r="AF29" s="30" t="n">
-        <v>0.005566254</v>
+        <v>-0.003937773</v>
       </c>
       <c r="AG29" s="30" t="n">
-        <v>-3.9693e-05</v>
+        <v>0.009146033</v>
       </c>
       <c r="AH29" s="30" t="n">
-        <v>0.000141802</v>
+        <v>0.00053521</v>
       </c>
       <c r="AI29" s="30" t="n">
-        <v>0.006650989</v>
+        <v>-0.003310662</v>
       </c>
       <c r="AJ29" s="31" t="n"/>
       <c r="AK29" s="30" t="n">
-        <v>-0.005285618</v>
+        <v>0.00502172</v>
       </c>
       <c r="AL29" s="30" t="n">
-        <v>0.000614183</v>
+        <v>0.00082303</v>
       </c>
       <c r="AM29" s="30" t="n">
-        <v>0.014715596</v>
+        <v>-0.005134902</v>
       </c>
       <c r="AN29" s="30" t="n">
-        <v>-0.001366393</v>
+        <v>-0.001644828</v>
       </c>
       <c r="AO29" s="31" t="n"/>
     </row>
@@ -7667,36 +7667,36 @@
         <v/>
       </c>
       <c r="AC30" s="30" t="n">
-        <v>0.004387226</v>
+        <v>0.003870905</v>
       </c>
       <c r="AD30" s="30" t="n">
-        <v>-2.6065e-05</v>
+        <v>-0.005757851</v>
       </c>
       <c r="AE30" s="31" t="n"/>
       <c r="AF30" s="30" t="n">
-        <v>0.006177437</v>
+        <v>0.000642079</v>
       </c>
       <c r="AG30" s="30" t="n">
-        <v>-0.005956624</v>
+        <v>0.003456135</v>
       </c>
       <c r="AH30" s="30" t="n">
-        <v>0.009297254</v>
+        <v>0.003688025</v>
       </c>
       <c r="AI30" s="30" t="n">
-        <v>-0.004790618</v>
+        <v>-0.000653392</v>
       </c>
       <c r="AJ30" s="31" t="n"/>
       <c r="AK30" s="30" t="n">
-        <v>0.003390764</v>
+        <v>-0.002276563</v>
       </c>
       <c r="AL30" s="30" t="n">
-        <v>-0.004566907</v>
+        <v>-0.000308422</v>
       </c>
       <c r="AM30" s="30" t="n">
-        <v>0.006705757</v>
+        <v>0.000923388</v>
       </c>
       <c r="AN30" s="30" t="n">
-        <v>0.00361985</v>
+        <v>-0.002469413</v>
       </c>
       <c r="AO30" s="31" t="n"/>
     </row>
@@ -7926,33 +7926,33 @@
         <v>0.098616281</v>
       </c>
       <c r="AD32" s="24" t="n">
-        <v>0.12710115</v>
+        <v>0.127064288</v>
       </c>
       <c r="AE32" s="25" t="n"/>
       <c r="AF32" s="24" t="n">
-        <v>0.08379120900000001</v>
+        <v>0.08379394900000001</v>
       </c>
       <c r="AG32" s="24" t="n">
-        <v>0.0854608</v>
+        <v>0.08546337900000001</v>
       </c>
       <c r="AH32" s="24" t="n">
-        <v>0.081067556</v>
+        <v>0.081042008</v>
       </c>
       <c r="AI32" s="24" t="n">
-        <v>0.105282107</v>
+        <v>0.105261804</v>
       </c>
       <c r="AJ32" s="25" t="n"/>
       <c r="AK32" s="24" t="n">
-        <v>0.07268497</v>
+        <v>0.072690044</v>
       </c>
       <c r="AL32" s="24" t="n">
-        <v>0.076782926</v>
+        <v>0.076766231</v>
       </c>
       <c r="AM32" s="24" t="n">
-        <v>0.074550802</v>
+        <v>0.074536664</v>
       </c>
       <c r="AN32" s="24" t="n">
-        <v>0.096541382</v>
+        <v>0.09653168400000001</v>
       </c>
       <c r="AO32" s="25" t="n"/>
     </row>
@@ -8058,29 +8058,29 @@
       </c>
       <c r="AE33" s="25" t="n"/>
       <c r="AF33" s="24" t="n">
-        <v>0.036707628</v>
+        <v>0.036693306</v>
       </c>
       <c r="AG33" s="24" t="n">
-        <v>0.039124128</v>
+        <v>0.039124668</v>
       </c>
       <c r="AH33" s="24" t="n">
-        <v>0.038767832</v>
+        <v>0.038755052</v>
       </c>
       <c r="AI33" s="24" t="n">
-        <v>0.052397834</v>
+        <v>0.052386377</v>
       </c>
       <c r="AJ33" s="25" t="n"/>
       <c r="AK33" s="24" t="n">
-        <v>0.037992387</v>
+        <v>0.037993773</v>
       </c>
       <c r="AL33" s="24" t="n">
-        <v>0.041475788</v>
+        <v>0.041465529</v>
       </c>
       <c r="AM33" s="24" t="n">
-        <v>0.041635261</v>
+        <v>0.041625885</v>
       </c>
       <c r="AN33" s="24" t="n">
-        <v>0.055620356</v>
+        <v>0.055612559</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -8743,7 +8743,7 @@
         </is>
       </c>
       <c r="D41" s="34" t="n">
-        <v>3915</v>
+        <v>3890</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
@@ -8783,7 +8783,7 @@
       </c>
       <c r="D42" s="35" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -9018,7 +9018,7 @@
         </is>
       </c>
       <c r="D48" s="36" t="n">
-        <v>0.121315310631661</v>
+        <v>0.121340543913473</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
@@ -9057,7 +9057,7 @@
         </is>
       </c>
       <c r="D49" s="36" t="n">
-        <v>0.1231031454986829</v>
+        <v>0.1231034678706665</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -9096,7 +9096,7 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.5707650434885511</v>
+        <v>0.5707607184069591</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -9135,7 +9135,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.01660472112379296</v>
+        <v>0.01660774121289423</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -9174,7 +9174,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.03620531794291023</v>
+        <v>0.03621230007694279</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -9611,7 +9611,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18840,7 +18840,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -33332,7 +33332,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -38209,7 +38209,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -40261,7 +40261,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>18.66</v>
+        <v>18.54</v>
       </c>
     </row>
     <row r="32">
@@ -40271,7 +40271,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/333430_model.xlsx
+++ b/argus/kship/models/333430_model.xlsx
@@ -663,55 +663,55 @@
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 84761억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 84757억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 87818억 × 비례계수 0.0076 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 87806억 × 비례계수 0.0076 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 90794억 × 비례계수 0.0076 × 계절비중 Q2 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 90775억 × 비례계수 0.0076 × 계절비중 Q2 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 94496억 × 비례계수 0.0076 × 계절비중 Q3 0.233(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 94470억 × 비례계수 0.0076 × 계절비중 Q3 0.233(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 99624억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 99596억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 105703억 × 비례계수 0.0076 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 105675억 × 비례계수 0.0076 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 112218억 × 비례계수 0.0076 × 계절비중 Q2 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 112192억 × 비례계수 0.0076 × 계절비중 Q2 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 118668억 × 비례계수 0.0076 × 계절비중 Q3 0.233(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 118643억 × 비례계수 0.0076 × 계절비중 Q3 0.233(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 124385억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 124361억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1590,55 +1590,55 @@
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 84761억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 84757억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 87818억 × 비례계수 0.0076 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 87806억 × 비례계수 0.0076 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 90794억 × 비례계수 0.0076 × 계절비중 Q2 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 90775억 × 비례계수 0.0076 × 계절비중 Q2 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 94496억 × 비례계수 0.0076 × 계절비중 Q3 0.233(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 94470억 × 비례계수 0.0076 × 계절비중 Q3 0.233(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 99624억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 99596억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 105703억 × 비례계수 0.0076 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 105675억 × 비례계수 0.0076 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 112218억 × 비례계수 0.0076 × 계절비중 Q2 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 112192억 × 비례계수 0.0076 × 계절비중 Q2 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 118668억 × 비례계수 0.0076 × 계절비중 Q3 0.233(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 118643억 × 비례계수 0.0076 × 계절비중 Q3 0.233(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 124385억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 124361억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -4059,7 +4059,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
         </is>
       </c>
     </row>
@@ -4930,35 +4930,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1351.18</v>
+        <v>1348.08</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1459.61</v>
+        <v>1458.99</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5049,35 +5049,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5168,35 +5168,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>855.39</v>
+        <v>853.26</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>920.6900000000001</v>
+        <v>920.3099999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5287,35 +5287,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5406,35 +5406,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1519.07</v>
+        <v>1516.47</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1693.81</v>
+        <v>1692.86</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5525,35 +5525,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5644,35 +5644,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>201.53</v>
+        <v>201.07</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>214.03</v>
+        <v>213.96</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5763,35 +5763,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5898,7 +5898,7 @@
         <v>3790</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>3890</v>
+        <v>3770</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6080,7 +6080,7 @@
         <v>2850</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>3795</v>
+        <v>3745</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6171,7 +6171,7 @@
         <v>3675.7</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>3915</v>
+        <v>3880</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6326,33 +6326,33 @@
         <v>0.025601257</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.309796705</v>
+        <v>0.309731173</v>
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.222142284</v>
+        <v>0.221976705</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.003032265</v>
+        <v>0.002847409</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.180623278</v>
+        <v>0.180340612</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.175363987</v>
+        <v>0.175072551</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.203698686</v>
+        <v>0.203523035</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.235962649</v>
+        <v>0.235883257</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.255820913</v>
+        <v>0.255882177</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.248552699</v>
+        <v>0.248669363</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6637,39 +6637,39 @@
         <v>0.195675217</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>0.195627158</v>
+        <v>0.195636946</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.195637448</v>
+        <v>0.195663957</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.195662858</v>
+        <v>0.195637481</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.195666487</v>
+        <v>0.195653475</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.195641069</v>
+        <v>0.195656802</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.195621588</v>
+        <v>0.195620356</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.195635966</v>
+        <v>0.195634881</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.19565321</v>
+        <v>0.195642847</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.195629198</v>
+        <v>0.195635124</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7539,36 +7539,36 @@
         <v/>
       </c>
       <c r="AC29" s="30" t="n">
-        <v>0.008664824999999999</v>
+        <v>0.008666256000000001</v>
       </c>
       <c r="AD29" s="30" t="n">
-        <v>-0.00978943</v>
+        <v>-0.009761298999999999</v>
       </c>
       <c r="AE29" s="31" t="n"/>
       <c r="AF29" s="30" t="n">
-        <v>-0.003937773</v>
+        <v>0.006108126</v>
       </c>
       <c r="AG29" s="30" t="n">
-        <v>0.009146033</v>
+        <v>0.000390112</v>
       </c>
       <c r="AH29" s="30" t="n">
-        <v>0.00053521</v>
+        <v>0.001764334</v>
       </c>
       <c r="AI29" s="30" t="n">
-        <v>-0.003310662</v>
+        <v>0.007950240000000001</v>
       </c>
       <c r="AJ29" s="31" t="n"/>
       <c r="AK29" s="30" t="n">
-        <v>0.00502172</v>
+        <v>-0.003732041</v>
       </c>
       <c r="AL29" s="30" t="n">
-        <v>0.00082303</v>
+        <v>-0.007940635</v>
       </c>
       <c r="AM29" s="30" t="n">
-        <v>-0.005134902</v>
+        <v>0.006092465</v>
       </c>
       <c r="AN29" s="30" t="n">
-        <v>-0.001644828</v>
+        <v>-0.000377625</v>
       </c>
       <c r="AO29" s="31" t="n"/>
     </row>
@@ -7667,36 +7667,36 @@
         <v/>
       </c>
       <c r="AC30" s="30" t="n">
-        <v>0.003870905</v>
+        <v>0.005000591</v>
       </c>
       <c r="AD30" s="30" t="n">
-        <v>-0.005757851</v>
+        <v>-0.004144135</v>
       </c>
       <c r="AE30" s="31" t="n"/>
       <c r="AF30" s="30" t="n">
-        <v>0.000642079</v>
+        <v>0.001855558</v>
       </c>
       <c r="AG30" s="30" t="n">
-        <v>0.003456135</v>
+        <v>0.009770756</v>
       </c>
       <c r="AH30" s="30" t="n">
-        <v>0.003688025</v>
+        <v>3.3109e-05</v>
       </c>
       <c r="AI30" s="30" t="n">
-        <v>-0.000653392</v>
+        <v>-0.00374482</v>
       </c>
       <c r="AJ30" s="31" t="n"/>
       <c r="AK30" s="30" t="n">
-        <v>-0.002276563</v>
+        <v>0.004174439</v>
       </c>
       <c r="AL30" s="30" t="n">
-        <v>-0.000308422</v>
+        <v>-0.003670455</v>
       </c>
       <c r="AM30" s="30" t="n">
-        <v>0.000923388</v>
+        <v>0.007631044</v>
       </c>
       <c r="AN30" s="30" t="n">
-        <v>-0.002469413</v>
+        <v>0.004932278</v>
       </c>
       <c r="AO30" s="31" t="n"/>
     </row>
@@ -7933,26 +7933,26 @@
         <v>0.08379394900000001</v>
       </c>
       <c r="AG32" s="24" t="n">
-        <v>0.08546337900000001</v>
+        <v>0.085433202</v>
       </c>
       <c r="AH32" s="24" t="n">
-        <v>0.081042008</v>
+        <v>0.08104426200000001</v>
       </c>
       <c r="AI32" s="24" t="n">
-        <v>0.105261804</v>
+        <v>0.105213075</v>
       </c>
       <c r="AJ32" s="25" t="n"/>
       <c r="AK32" s="24" t="n">
-        <v>0.072690044</v>
+        <v>0.072671848</v>
       </c>
       <c r="AL32" s="24" t="n">
-        <v>0.076766231</v>
+        <v>0.07675119900000001</v>
       </c>
       <c r="AM32" s="24" t="n">
-        <v>0.074536664</v>
+        <v>0.07454417200000001</v>
       </c>
       <c r="AN32" s="24" t="n">
-        <v>0.09653168400000001</v>
+        <v>0.09652198400000001</v>
       </c>
       <c r="AO32" s="25" t="n"/>
     </row>
@@ -8058,29 +8058,29 @@
       </c>
       <c r="AE33" s="25" t="n"/>
       <c r="AF33" s="24" t="n">
-        <v>0.036693306</v>
+        <v>0.036678984</v>
       </c>
       <c r="AG33" s="24" t="n">
-        <v>0.039124668</v>
+        <v>0.039111394</v>
       </c>
       <c r="AH33" s="24" t="n">
-        <v>0.038755052</v>
+        <v>0.038756083</v>
       </c>
       <c r="AI33" s="24" t="n">
-        <v>0.052386377</v>
+        <v>0.052374918</v>
       </c>
       <c r="AJ33" s="25" t="n"/>
       <c r="AK33" s="24" t="n">
-        <v>0.037993773</v>
+        <v>0.037982997</v>
       </c>
       <c r="AL33" s="24" t="n">
-        <v>0.041465529</v>
+        <v>0.041455756</v>
       </c>
       <c r="AM33" s="24" t="n">
-        <v>0.041625885</v>
+        <v>0.041628226</v>
       </c>
       <c r="AN33" s="24" t="n">
-        <v>0.055612559</v>
+        <v>0.055604761</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -8743,11 +8743,11 @@
         </is>
       </c>
       <c r="D41" s="34" t="n">
-        <v>3890</v>
+        <v>3770</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 3,905원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 3,900원)</t>
         </is>
       </c>
       <c r="F41" s="9" t="n"/>
@@ -8783,7 +8783,7 @@
       </c>
       <c r="D42" s="35" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -9018,7 +9018,7 @@
         </is>
       </c>
       <c r="D48" s="36" t="n">
-        <v>0.121340543913473</v>
+        <v>0.121339782597389</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
@@ -9057,7 +9057,7 @@
         </is>
       </c>
       <c r="D49" s="36" t="n">
-        <v>0.1231034678706665</v>
+        <v>0.1230960008267025</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -9096,7 +9096,7 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.5707607184069591</v>
+        <v>0.5708070673887952</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -9135,7 +9135,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.01660774121289423</v>
+        <v>0.01661109871829449</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -9174,7 +9174,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.03621230007694279</v>
+        <v>0.03622001156980006</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -9611,7 +9611,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18840,7 +18840,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -33332,7 +33332,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -38209,7 +38209,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -40261,7 +40261,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>18.54</v>
+        <v>17.97</v>
       </c>
     </row>
     <row r="32">
@@ -40271,7 +40271,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2.26</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/333430_model.xlsx
+++ b/argus/kship/models/333430_model.xlsx
@@ -4059,7 +4059,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-08</t>
         </is>
       </c>
     </row>
@@ -9611,7 +9611,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18840,7 +18840,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/333430_model.xlsx
+++ b/argus/kship/models/333430_model.xlsx
@@ -663,43 +663,43 @@
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 84757억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 84754억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 87806억 × 비례계수 0.0076 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 87803억 × 비례계수 0.0076 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 90775억 × 비례계수 0.0076 × 계절비중 Q2 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 90772억 × 비례계수 0.0076 × 계절비중 Q2 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 94470억 × 비례계수 0.0076 × 계절비중 Q3 0.233(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 94467억 × 비례계수 0.0076 × 계절비중 Q3 0.233(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 99596억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 99595억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 105675억 × 비례계수 0.0076 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 105674억 × 비례계수 0.0076 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 112192억 × 비례계수 0.0076 × 계절비중 Q2 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 112191억 × 비례계수 0.0076 × 계절비중 Q2 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
@@ -1590,43 +1590,43 @@
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 84757억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 84754억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 87806억 × 비례계수 0.0076 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 87803억 × 비례계수 0.0076 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 90775억 × 비례계수 0.0076 × 계절비중 Q2 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 90772억 × 비례계수 0.0076 × 계절비중 Q2 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 94470억 × 비례계수 0.0076 × 계절비중 Q3 0.233(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 94467억 × 비례계수 0.0076 × 계절비중 Q3 0.233(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 99596억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 99595억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 105675억 × 비례계수 0.0076 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 105674억 × 비례계수 0.0076 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 112192억 × 비례계수 0.0076 × 계절비중 Q2 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 112191억 × 비례계수 0.0076 × 계절비중 Q2 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -4930,35 +4930,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1348.08</v>
+        <v>1346.2</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1458.99</v>
+        <v>1458.38</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5049,35 +5049,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5168,35 +5168,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>853.26</v>
+        <v>851.8099999999999</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>920.3099999999999</v>
+        <v>919.9299999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5287,35 +5287,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5406,35 +5406,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1516.47</v>
+        <v>1512.43</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1692.86</v>
+        <v>1691.86</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5525,35 +5525,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5644,35 +5644,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>201.07</v>
+        <v>200.79</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.96</v>
+        <v>213.89</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5763,35 +5763,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5898,7 +5898,7 @@
         <v>3790</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>3770</v>
+        <v>3665</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6080,7 +6080,7 @@
         <v>2850</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>3745</v>
+        <v>3645</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6171,7 +6171,7 @@
         <v>3675.7</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>3880</v>
+        <v>3832</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6326,30 +6326,30 @@
         <v>0.025601257</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.309731173</v>
+        <v>0.30966564</v>
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
         <v>0.221976705</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.002847409</v>
+        <v>0.00278579</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.180340612</v>
+        <v>0.180269946</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.175072551</v>
+        <v>0.175131349</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
         <v>0.203523035</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.235883257</v>
+        <v>0.235959199</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.255882177</v>
+        <v>0.25595737</v>
       </c>
       <c r="AN21" s="24" t="n">
         <v>0.248669363</v>
@@ -6637,7 +6637,7 @@
         <v>0.195675217</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>0.195636946</v>
+        <v>0.195646735</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
@@ -6647,10 +6647,10 @@
         <v>0.195663957</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.195637481</v>
+        <v>0.195649502</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.195653475</v>
+        <v>0.19566519</v>
       </c>
       <c r="AI23" s="24" t="n">
         <v>0.195656802</v>
@@ -7539,36 +7539,36 @@
         <v/>
       </c>
       <c r="AC29" s="30" t="n">
-        <v>0.008666256000000001</v>
+        <v>0.008660961</v>
       </c>
       <c r="AD29" s="30" t="n">
-        <v>-0.009761298999999999</v>
+        <v>0.000236277</v>
       </c>
       <c r="AE29" s="31" t="n"/>
       <c r="AF29" s="30" t="n">
-        <v>0.006108126</v>
+        <v>-0.003890117</v>
       </c>
       <c r="AG29" s="30" t="n">
-        <v>0.000390112</v>
+        <v>0.000394867</v>
       </c>
       <c r="AH29" s="30" t="n">
-        <v>0.001764334</v>
+        <v>0.001772655</v>
       </c>
       <c r="AI29" s="30" t="n">
-        <v>0.007950240000000001</v>
+        <v>0.007961945999999999</v>
       </c>
       <c r="AJ29" s="31" t="n"/>
       <c r="AK29" s="30" t="n">
-        <v>-0.003732041</v>
+        <v>-0.003751911</v>
       </c>
       <c r="AL29" s="30" t="n">
-        <v>-0.007940635</v>
+        <v>0.00204323</v>
       </c>
       <c r="AM29" s="30" t="n">
-        <v>0.006092465</v>
+        <v>-0.003882935</v>
       </c>
       <c r="AN29" s="30" t="n">
-        <v>-0.000377625</v>
+        <v>-0.000385086</v>
       </c>
       <c r="AO29" s="31" t="n"/>
     </row>
@@ -7667,36 +7667,36 @@
         <v/>
       </c>
       <c r="AC30" s="30" t="n">
-        <v>0.005000591</v>
+        <v>0.004688188</v>
       </c>
       <c r="AD30" s="30" t="n">
-        <v>-0.004144135</v>
+        <v>-0.004583377</v>
       </c>
       <c r="AE30" s="31" t="n"/>
       <c r="AF30" s="30" t="n">
-        <v>0.001855558</v>
+        <v>0.00153117</v>
       </c>
       <c r="AG30" s="30" t="n">
-        <v>0.009770756</v>
+        <v>0.009413856999999999</v>
       </c>
       <c r="AH30" s="30" t="n">
-        <v>3.3109e-05</v>
+        <v>-0.000332442</v>
       </c>
       <c r="AI30" s="30" t="n">
-        <v>-0.00374482</v>
+        <v>0.0057421</v>
       </c>
       <c r="AJ30" s="31" t="n"/>
       <c r="AK30" s="30" t="n">
-        <v>0.004174439</v>
+        <v>-0.006233555</v>
       </c>
       <c r="AL30" s="30" t="n">
-        <v>-0.003670455</v>
+        <v>0.005870893</v>
       </c>
       <c r="AM30" s="30" t="n">
-        <v>0.007631044</v>
+        <v>-0.002824857</v>
       </c>
       <c r="AN30" s="30" t="n">
-        <v>0.004932278</v>
+        <v>0.004274098</v>
       </c>
       <c r="AO30" s="31" t="n"/>
     </row>
@@ -7930,16 +7930,16 @@
       </c>
       <c r="AE32" s="25" t="n"/>
       <c r="AF32" s="24" t="n">
-        <v>0.08379394900000001</v>
+        <v>0.083761243</v>
       </c>
       <c r="AG32" s="24" t="n">
-        <v>0.085433202</v>
+        <v>0.08543578</v>
       </c>
       <c r="AH32" s="24" t="n">
-        <v>0.08104426200000001</v>
+        <v>0.081046515</v>
       </c>
       <c r="AI32" s="24" t="n">
-        <v>0.105213075</v>
+        <v>0.1052415</v>
       </c>
       <c r="AJ32" s="25" t="n"/>
       <c r="AK32" s="24" t="n">
@@ -7949,10 +7949,10 @@
         <v>0.07675119900000001</v>
       </c>
       <c r="AM32" s="24" t="n">
-        <v>0.07454417200000001</v>
+        <v>0.07452402499999999</v>
       </c>
       <c r="AN32" s="24" t="n">
-        <v>0.09652198400000001</v>
+        <v>0.096523793</v>
       </c>
       <c r="AO32" s="25" t="n"/>
     </row>
@@ -8067,20 +8067,20 @@
         <v>0.038756083</v>
       </c>
       <c r="AI33" s="24" t="n">
-        <v>0.052374918</v>
+        <v>0.052362119</v>
       </c>
       <c r="AJ33" s="25" t="n"/>
       <c r="AK33" s="24" t="n">
-        <v>0.037982997</v>
+        <v>0.037983459</v>
       </c>
       <c r="AL33" s="24" t="n">
-        <v>0.041455756</v>
+        <v>0.041467959</v>
       </c>
       <c r="AM33" s="24" t="n">
-        <v>0.041628226</v>
+        <v>0.041616975</v>
       </c>
       <c r="AN33" s="24" t="n">
-        <v>0.055604761</v>
+        <v>0.055605362</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -8743,11 +8743,11 @@
         </is>
       </c>
       <c r="D41" s="34" t="n">
-        <v>3770</v>
+        <v>3665</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 3,900원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 3,860원)</t>
         </is>
       </c>
       <c r="F41" s="9" t="n"/>
@@ -8783,7 +8783,7 @@
       </c>
       <c r="D42" s="35" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -9057,7 +9057,7 @@
         </is>
       </c>
       <c r="D49" s="36" t="n">
-        <v>0.1230960008267025</v>
+        <v>0.1230979089269752</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -9096,7 +9096,7 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.5708070673887952</v>
+        <v>0.5707943648632651</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -9135,7 +9135,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.01661109871829449</v>
+        <v>0.0166116444159815</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -9174,7 +9174,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.03622001156980006</v>
+        <v>0.03622129785153237</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -33332,7 +33332,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -38209,7 +38209,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -40241,7 +40241,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>209.8</v>
+        <v>209.7</v>
       </c>
     </row>
     <row r="30">
@@ -40261,7 +40261,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>17.97</v>
+        <v>17.48</v>
       </c>
     </row>
     <row r="32">
@@ -40271,7 +40271,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2.19</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/333430_model.xlsx
+++ b/argus/kship/models/333430_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -23,7 +23,7 @@
     <definedName name="BS연결H">BS연결!$C$1:$AO$1</definedName>
     <definedName name="BS연결">BS연결!$C$5:$AO$102</definedName>
     <definedName name="BS별도H">BS별도!$C$1:$AO$1</definedName>
-    <definedName name="BS별도">BS별도!$C$5:$AO$92</definedName>
+    <definedName name="BS별도">BS별도!$C$5:$AO$101</definedName>
     <definedName name="SUBQH">subQ!$A$1:$AO$1</definedName>
     <definedName name="subQ">subQ!$A$5:$AO$40</definedName>
   </definedNames>
@@ -657,61 +657,61 @@
     <comment ref="AC21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 80037억 × 비례계수 0.0076 × 계절비중 Q3 0.233(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 80223억 × 비례계수 0.0076 × 계절비중 Q3 0.233(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 84754억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 85183억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 87803억 × 비례계수 0.0076 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 88307억 × 비례계수 0.0076 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 90772억 × 비례계수 0.0076 × 계절비중 Q2 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 91228억 × 비례계수 0.0076 × 계절비중 Q2 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 94467억 × 비례계수 0.0076 × 계절비중 Q3 0.233(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 94600억 × 비례계수 0.0076 × 계절비중 Q3 0.233(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 99595억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 99289억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 105674억 × 비례계수 0.0076 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 105070억 × 비례계수 0.0076 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 112191억 × 비례계수 0.0076 × 계절비중 Q2 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 111421억 × 비례계수 0.0076 × 계절비중 Q2 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 118643억 × 비례계수 0.0076 × 계절비중 Q3 0.233(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 117844억 × 비례계수 0.0076 × 계절비중 Q3 0.233(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 124361억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 123670억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1584,61 +1584,61 @@
   <commentList>
     <comment ref="AC5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 80037억 × 비례계수 0.0076 × 계절비중 Q3 0.233(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 80223억 × 비례계수 0.0076 × 계절비중 Q3 0.233(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 84754억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 85183억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 87803억 × 비례계수 0.0076 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 88307억 × 비례계수 0.0076 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 90772억 × 비례계수 0.0076 × 계절비중 Q2 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 91228억 × 비례계수 0.0076 × 계절비중 Q2 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 94467억 × 비례계수 0.0076 × 계절비중 Q3 0.233(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 94600억 × 비례계수 0.0076 × 계절비중 Q3 0.233(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 99595억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 99289억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 105674억 × 비례계수 0.0076 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 105070억 × 비례계수 0.0076 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 112191억 × 비례계수 0.0076 × 계절비중 Q2 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 111421억 × 비례계수 0.0076 × 계절비중 Q2 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 118643억 × 비례계수 0.0076 × 계절비중 Q3 0.233(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 117844억 × 비례계수 0.0076 × 계절비중 Q3 0.233(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 124361억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 123670억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -1968,25 +1968,25 @@
     </comment>
     <comment ref="AH11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 752억 × 1.66%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 290억 × 3.62%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 753억 × 1.66%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 290억 × 3.62%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 781억 × 1.66%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 290억 × 3.62%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 782억 × 1.66%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 290억 × 3.62%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 822억 × 1.66%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 290억 × 3.62%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 823억 × 1.66%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 290억 × 3.62%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 853억 × 1.66%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 290억 × 3.62%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 854억 × 1.66%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 290억 × 3.62%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2028,25 +2028,25 @@
     </comment>
     <comment ref="AH12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 752억 × 1.66%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 290억 × 3.62%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 753억 × 1.66%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 290억 × 3.62%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AI12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 781억 × 1.66%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 290억 × 3.62%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 782억 × 1.66%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 290억 × 3.62%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AK12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 822억 × 1.66%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 290억 × 3.62%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 823억 × 1.66%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 290억 × 3.62%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AL12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 853억 × 1.66%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 290억 × 3.62%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 854억 × 1.66%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 290억 × 3.62%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -4059,7 +4059,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-08</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
         </is>
       </c>
     </row>
@@ -4208,7 +4208,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>· 이자율 자산 1.66% / 부채 3.62% — 이자손익 = (전분기 이자발생자산 × 자산이자율 − 전분기 총차입금 × 부채이자율)/4, 최소자승 역산(모델 assumptions [0.0166, 0.0362] 는 4자리 반올림이라 그대로 쓰면 ±1억 어긋남) · 출처: {"asset": "주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)", "debt": "주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)"}</t>
+          <t>· 이자율 자산 1.66% / 부채 3.63% — 이자손익 = (전분기 이자발생자산 × 자산이자율 − 전분기 총차입금 × 부채이자율)/4, 최소자승 역산(모델 assumptions [0.0166, 0.0362] 는 4자리 반올림이라 그대로 쓰면 ±1억 어긋남) · 출처: {"asset": "주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)", "debt": "주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)"}</t>
         </is>
       </c>
     </row>
@@ -6323,36 +6323,36 @@
         <v/>
       </c>
       <c r="AC21" s="24" t="n">
-        <v>0.025601257</v>
+        <v>0.02799295</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.30966564</v>
+        <v>0.316349948</v>
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.221976705</v>
+        <v>0.229013833</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.00278579</v>
+        <v>0.007838539</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.180269946</v>
+        <v>0.179216018</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.175131349</v>
+        <v>0.165579728</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.203523035</v>
+        <v>0.189828225</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.235959199</v>
+        <v>0.221325507</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.25595737</v>
+        <v>0.245665431</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.248669363</v>
+        <v>0.245547345</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6634,42 +6634,42 @@
         <v/>
       </c>
       <c r="AC23" s="24" t="n">
-        <v>0.195675217</v>
+        <v>0.195642978</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>0.195646735</v>
+        <v>0.195648927</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.195663957</v>
+        <v>0.195621421</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.195649502</v>
+        <v>0.195646857</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.19566519</v>
+        <v>0.19562358</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.195656802</v>
+        <v>0.19566053</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.195620356</v>
+        <v>0.195663251</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.195634881</v>
+        <v>0.195634762</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.195642847</v>
+        <v>0.195632349</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.195635124</v>
+        <v>0.195631301</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7539,36 +7539,36 @@
         <v/>
       </c>
       <c r="AC29" s="30" t="n">
-        <v>0.008660961</v>
+        <v>0.001370794</v>
       </c>
       <c r="AD29" s="30" t="n">
-        <v>0.000236277</v>
+        <v>-0.003342852</v>
       </c>
       <c r="AE29" s="31" t="n"/>
       <c r="AF29" s="30" t="n">
-        <v>-0.003890117</v>
+        <v>0.007680666</v>
       </c>
       <c r="AG29" s="30" t="n">
-        <v>0.000394867</v>
+        <v>-0.007328564</v>
       </c>
       <c r="AH29" s="30" t="n">
-        <v>0.001772655</v>
+        <v>-0.000800383</v>
       </c>
       <c r="AI29" s="30" t="n">
-        <v>0.007961945999999999</v>
+        <v>0.007922452</v>
       </c>
       <c r="AJ29" s="31" t="n"/>
       <c r="AK29" s="30" t="n">
-        <v>-0.003751911</v>
+        <v>0.001487675</v>
       </c>
       <c r="AL29" s="30" t="n">
-        <v>0.00204323</v>
+        <v>0.006596532</v>
       </c>
       <c r="AM29" s="30" t="n">
-        <v>-0.003882935</v>
+        <v>0.001134992</v>
       </c>
       <c r="AN29" s="30" t="n">
-        <v>-0.000385086</v>
+        <v>-0.000708558</v>
       </c>
       <c r="AO29" s="31" t="n"/>
     </row>
@@ -7667,36 +7667,36 @@
         <v/>
       </c>
       <c r="AC30" s="30" t="n">
-        <v>0.004688188</v>
+        <v>0.00361582</v>
       </c>
       <c r="AD30" s="30" t="n">
-        <v>-0.004583377</v>
+        <v>-0.005528254</v>
       </c>
       <c r="AE30" s="31" t="n"/>
       <c r="AF30" s="30" t="n">
-        <v>0.00153117</v>
+        <v>0.001116082</v>
       </c>
       <c r="AG30" s="30" t="n">
-        <v>0.009413856999999999</v>
+        <v>-0.000726324</v>
       </c>
       <c r="AH30" s="30" t="n">
-        <v>-0.000332442</v>
+        <v>-0.000355157</v>
       </c>
       <c r="AI30" s="30" t="n">
-        <v>0.0057421</v>
+        <v>0.005287276</v>
       </c>
       <c r="AJ30" s="31" t="n"/>
       <c r="AK30" s="30" t="n">
-        <v>-0.006233555</v>
+        <v>-0.001752575</v>
       </c>
       <c r="AL30" s="30" t="n">
-        <v>0.005870893</v>
+        <v>-0.000189406</v>
       </c>
       <c r="AM30" s="30" t="n">
-        <v>-0.002824857</v>
+        <v>-0.004404074</v>
       </c>
       <c r="AN30" s="30" t="n">
-        <v>0.004274098</v>
+        <v>0.001836257</v>
       </c>
       <c r="AO30" s="31" t="n"/>
     </row>
@@ -7923,36 +7923,36 @@
         <v/>
       </c>
       <c r="AC32" s="24" t="n">
-        <v>0.098616281</v>
+        <v>0.098859266</v>
       </c>
       <c r="AD32" s="24" t="n">
-        <v>0.127064288</v>
+        <v>0.127662711</v>
       </c>
       <c r="AE32" s="25" t="n"/>
       <c r="AF32" s="24" t="n">
-        <v>0.083761243</v>
+        <v>0.08418850899999999</v>
       </c>
       <c r="AG32" s="24" t="n">
-        <v>0.08543578</v>
+        <v>0.085759932</v>
       </c>
       <c r="AH32" s="24" t="n">
-        <v>0.081046515</v>
+        <v>0.081040562</v>
       </c>
       <c r="AI32" s="24" t="n">
-        <v>0.1052415</v>
+        <v>0.104781961</v>
       </c>
       <c r="AJ32" s="25" t="n"/>
       <c r="AK32" s="24" t="n">
-        <v>0.072671848</v>
+        <v>0.072179088</v>
       </c>
       <c r="AL32" s="24" t="n">
-        <v>0.07675119900000001</v>
+        <v>0.076209267</v>
       </c>
       <c r="AM32" s="24" t="n">
-        <v>0.07452402499999999</v>
+        <v>0.07403602099999999</v>
       </c>
       <c r="AN32" s="24" t="n">
-        <v>0.096523793</v>
+        <v>0.09603661400000001</v>
       </c>
       <c r="AO32" s="25" t="n"/>
     </row>
@@ -8051,36 +8051,36 @@
         <v/>
       </c>
       <c r="AC33" s="24" t="n">
-        <v>0.038086636</v>
+        <v>0.038180475</v>
       </c>
       <c r="AD33" s="24" t="n">
-        <v>0.051932203</v>
+        <v>0.052183607</v>
       </c>
       <c r="AE33" s="25" t="n"/>
       <c r="AF33" s="24" t="n">
-        <v>0.036678984</v>
+        <v>0.036881667</v>
       </c>
       <c r="AG33" s="24" t="n">
-        <v>0.039111394</v>
+        <v>0.039284186</v>
       </c>
       <c r="AH33" s="24" t="n">
-        <v>0.038756083</v>
+        <v>0.038782452</v>
       </c>
       <c r="AI33" s="24" t="n">
-        <v>0.052362119</v>
+        <v>0.052171133</v>
       </c>
       <c r="AJ33" s="25" t="n"/>
       <c r="AK33" s="24" t="n">
-        <v>0.037983459</v>
+        <v>0.037756491</v>
       </c>
       <c r="AL33" s="24" t="n">
-        <v>0.041467959</v>
+        <v>0.041173714</v>
       </c>
       <c r="AM33" s="24" t="n">
-        <v>0.041616975</v>
+        <v>0.041345559</v>
       </c>
       <c r="AN33" s="24" t="n">
-        <v>0.055605362</v>
+        <v>0.055315471</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -9018,7 +9018,7 @@
         </is>
       </c>
       <c r="D48" s="36" t="n">
-        <v>0.121339782597389</v>
+        <v>0.1213020833333333</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
@@ -9057,7 +9057,7 @@
         </is>
       </c>
       <c r="D49" s="36" t="n">
-        <v>0.1230979089269752</v>
+        <v>0.1230963481968672</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -9096,7 +9096,7 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.5707943648632651</v>
+        <v>0.5707468879668049</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -9135,7 +9135,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.0166116444159815</v>
+        <v>0.01661919388857396</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -9174,7 +9174,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.03622129785153237</v>
+        <v>0.03625453639493557</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -9611,7 +9611,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-08</t>
+          <t>UPDATE: 26-10-09</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18592,7 +18592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO92"/>
+  <dimension ref="A1:AO101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -18840,7 +18840,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-08</t>
+          <t>UPDATE: 26-10-09</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -21248,7 +21248,7 @@
         <v>3686.21</v>
       </c>
       <c r="H27" s="18" t="n">
-        <v>3600</v>
+        <v>2000</v>
       </c>
       <c r="I27" s="18" t="n">
         <v>4300</v>
@@ -21342,9 +21342,6 @@
       <c r="G28" s="18" t="n">
         <v>3686.21</v>
       </c>
-      <c r="H28" s="18" t="n">
-        <v>3600</v>
-      </c>
       <c r="I28" s="18" t="n">
         <v>4300</v>
       </c>
@@ -21995,71 +21992,81 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>장기금융부채(face)</t>
+          <t>비유동리스부채</t>
         </is>
       </c>
       <c r="E35" s="18" t="n">
-        <v>5000</v>
+        <v>22.71</v>
       </c>
       <c r="F35" s="37" t="n">
-        <v>5000</v>
+        <v>22.71</v>
       </c>
       <c r="G35" s="18" t="n">
-        <v>13500</v>
+        <v>19.33</v>
       </c>
       <c r="H35" s="18" t="n">
-        <v>13500</v>
+        <v>59.32</v>
       </c>
       <c r="I35" s="18" t="n">
-        <v>13500</v>
+        <v>53.33</v>
       </c>
       <c r="J35" s="18" t="n">
-        <v>13500</v>
+        <v>47.18</v>
       </c>
       <c r="K35" s="37" t="n">
-        <v>13500</v>
+        <v>47.18</v>
       </c>
       <c r="L35" s="18" t="n">
-        <v>13291.59</v>
+        <v>40.85</v>
       </c>
       <c r="M35" s="18" t="n">
-        <v>12728.94</v>
+        <v>34.34</v>
       </c>
       <c r="N35" s="18" t="n">
-        <v>12166.45</v>
+        <v>30.99</v>
       </c>
       <c r="O35" s="18" t="n">
-        <v>11603.96</v>
+        <v>28.32</v>
       </c>
       <c r="P35" s="37" t="n">
-        <v>11603.96</v>
+        <v>28.32</v>
       </c>
       <c r="Q35" s="18" t="n">
-        <v>11041.47</v>
+        <v>25.58</v>
       </c>
       <c r="R35" s="18" t="n">
-        <v>10478.98</v>
+        <v>22.77</v>
       </c>
       <c r="S35" s="18" t="n">
-        <v>12874.88</v>
+        <v>19.91</v>
       </c>
       <c r="T35" s="18" t="n">
-        <v>14200</v>
+        <v>16.97</v>
       </c>
       <c r="U35" s="37" t="n">
-        <v>14200</v>
+        <v>16.97</v>
       </c>
       <c r="V35" s="18" t="n">
-        <v>14200</v>
+        <v>13.97</v>
       </c>
       <c r="W35" s="18" t="n">
-        <v>14200</v>
+        <v>10.89</v>
       </c>
       <c r="X35" s="18" t="n">
-        <v>15700</v>
-      </c>
-      <c r="Z35" s="9" t="n"/>
-      <c r="AB35" s="5" t="n"/>
+        <v>7.75</v>
+      </c>
+      <c r="Y35" s="18" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="Z35" s="37" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="AA35" s="18" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AB35" s="19" t="n">
+        <v>0</v>
+      </c>
       <c r="AC35" s="10" t="n"/>
       <c r="AD35" s="10" t="n"/>
       <c r="AE35" s="11" t="n"/>
@@ -22080,7 +22087,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>비유동리스부채</t>
+          <t>장기금융부채</t>
         </is>
       </c>
       <c r="E36" s="18" t="n">
@@ -22175,80 +22182,80 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>장기금융부채</t>
+          <t>확정급여부채</t>
         </is>
       </c>
       <c r="E37" s="18" t="n">
-        <v>22.71</v>
+        <v>225.15</v>
       </c>
       <c r="F37" s="37" t="n">
-        <v>22.71</v>
+        <v>225.15</v>
       </c>
       <c r="G37" s="18" t="n">
-        <v>19.33</v>
+        <v>221.68</v>
       </c>
       <c r="H37" s="18" t="n">
-        <v>59.32</v>
+        <v>193.02</v>
       </c>
       <c r="I37" s="18" t="n">
-        <v>53.33</v>
+        <v>308.8</v>
       </c>
       <c r="J37" s="18" t="n">
-        <v>47.18</v>
+        <v>466.97</v>
       </c>
       <c r="K37" s="37" t="n">
-        <v>47.18</v>
+        <v>466.97</v>
       </c>
       <c r="L37" s="18" t="n">
-        <v>40.85</v>
+        <v>523.5700000000001</v>
       </c>
       <c r="M37" s="18" t="n">
-        <v>34.34</v>
+        <v>408.56</v>
       </c>
       <c r="N37" s="18" t="n">
-        <v>30.99</v>
+        <v>402.9</v>
       </c>
       <c r="O37" s="18" t="n">
-        <v>28.32</v>
+        <v>86.92</v>
       </c>
       <c r="P37" s="37" t="n">
-        <v>28.32</v>
+        <v>86.92</v>
       </c>
       <c r="Q37" s="18" t="n">
-        <v>25.58</v>
+        <v>218.97</v>
       </c>
       <c r="R37" s="18" t="n">
-        <v>22.77</v>
+        <v>8.23</v>
       </c>
       <c r="S37" s="18" t="n">
-        <v>19.91</v>
+        <v>37.94</v>
       </c>
       <c r="T37" s="18" t="n">
-        <v>16.97</v>
+        <v>67.19</v>
       </c>
       <c r="U37" s="37" t="n">
-        <v>16.97</v>
+        <v>67.19</v>
       </c>
       <c r="V37" s="18" t="n">
-        <v>13.97</v>
+        <v>101.5</v>
       </c>
       <c r="W37" s="18" t="n">
-        <v>10.89</v>
+        <v>113.11</v>
       </c>
       <c r="X37" s="18" t="n">
-        <v>7.75</v>
+        <v>148.07</v>
       </c>
       <c r="Y37" s="18" t="n">
-        <v>4.53</v>
+        <v>58.2</v>
       </c>
       <c r="Z37" s="37" t="n">
-        <v>4.53</v>
+        <v>58.2</v>
       </c>
       <c r="AA37" s="18" t="n">
-        <v>1.23</v>
+        <v>75.34</v>
       </c>
       <c r="AB37" s="19" t="n">
-        <v>0</v>
+        <v>96.64</v>
       </c>
       <c r="AC37" s="10" t="n"/>
       <c r="AD37" s="10" t="n"/>
@@ -22270,80 +22277,80 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>확정급여부채</t>
+          <t>이연법인세부채</t>
         </is>
       </c>
       <c r="E38" s="18" t="n">
-        <v>225.15</v>
+        <v>875.28</v>
       </c>
       <c r="F38" s="37" t="n">
-        <v>225.15</v>
+        <v>875.28</v>
       </c>
       <c r="G38" s="18" t="n">
-        <v>221.68</v>
+        <v>1025.97</v>
       </c>
       <c r="H38" s="18" t="n">
-        <v>193.02</v>
+        <v>955.71</v>
       </c>
       <c r="I38" s="18" t="n">
-        <v>308.8</v>
+        <v>1042.35</v>
       </c>
       <c r="J38" s="18" t="n">
-        <v>466.97</v>
+        <v>841.13</v>
       </c>
       <c r="K38" s="37" t="n">
-        <v>466.97</v>
+        <v>841.13</v>
       </c>
       <c r="L38" s="18" t="n">
-        <v>523.5700000000001</v>
+        <v>877.73</v>
       </c>
       <c r="M38" s="18" t="n">
-        <v>408.56</v>
+        <v>1192.51</v>
       </c>
       <c r="N38" s="18" t="n">
-        <v>402.9</v>
+        <v>1035.1</v>
       </c>
       <c r="O38" s="18" t="n">
-        <v>86.92</v>
+        <v>831.08</v>
       </c>
       <c r="P38" s="37" t="n">
-        <v>86.92</v>
+        <v>831.08</v>
       </c>
       <c r="Q38" s="18" t="n">
-        <v>218.97</v>
+        <v>748.67</v>
       </c>
       <c r="R38" s="18" t="n">
-        <v>8.23</v>
+        <v>711.24</v>
       </c>
       <c r="S38" s="18" t="n">
-        <v>37.94</v>
+        <v>675.05</v>
       </c>
       <c r="T38" s="18" t="n">
-        <v>67.19</v>
+        <v>413.81</v>
       </c>
       <c r="U38" s="37" t="n">
-        <v>67.19</v>
+        <v>413.81</v>
       </c>
       <c r="V38" s="18" t="n">
-        <v>101.5</v>
+        <v>418.6</v>
       </c>
       <c r="W38" s="18" t="n">
-        <v>113.11</v>
+        <v>498.2</v>
       </c>
       <c r="X38" s="18" t="n">
-        <v>148.07</v>
+        <v>497.7</v>
       </c>
       <c r="Y38" s="18" t="n">
-        <v>58.2</v>
+        <v>636.16</v>
       </c>
       <c r="Z38" s="37" t="n">
-        <v>58.2</v>
+        <v>636.16</v>
       </c>
       <c r="AA38" s="18" t="n">
-        <v>75.34</v>
+        <v>631.11</v>
       </c>
       <c r="AB38" s="19" t="n">
-        <v>96.64</v>
+        <v>585.23</v>
       </c>
       <c r="AC38" s="10" t="n"/>
       <c r="AD38" s="10" t="n"/>
@@ -22365,80 +22372,80 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>이연법인세부채</t>
+          <t>부채총계</t>
         </is>
       </c>
       <c r="E39" s="18" t="n">
-        <v>875.28</v>
+        <v>17946.53</v>
       </c>
       <c r="F39" s="37" t="n">
-        <v>875.28</v>
+        <v>17946.53</v>
       </c>
       <c r="G39" s="18" t="n">
-        <v>1025.97</v>
+        <v>27621.05</v>
       </c>
       <c r="H39" s="18" t="n">
-        <v>955.71</v>
+        <v>26898.68</v>
       </c>
       <c r="I39" s="18" t="n">
-        <v>1042.35</v>
+        <v>28215.93</v>
       </c>
       <c r="J39" s="18" t="n">
-        <v>841.13</v>
+        <v>25666.93</v>
       </c>
       <c r="K39" s="37" t="n">
-        <v>841.13</v>
+        <v>25666.93</v>
       </c>
       <c r="L39" s="18" t="n">
-        <v>877.73</v>
+        <v>22955.54</v>
       </c>
       <c r="M39" s="18" t="n">
-        <v>1192.51</v>
+        <v>22082.03</v>
       </c>
       <c r="N39" s="18" t="n">
-        <v>1035.1</v>
+        <v>21698.66</v>
       </c>
       <c r="O39" s="18" t="n">
-        <v>831.08</v>
+        <v>21298.68</v>
       </c>
       <c r="P39" s="37" t="n">
-        <v>831.08</v>
+        <v>21298.68</v>
       </c>
       <c r="Q39" s="18" t="n">
-        <v>748.67</v>
+        <v>20886.82</v>
       </c>
       <c r="R39" s="18" t="n">
-        <v>711.24</v>
+        <v>17719.91</v>
       </c>
       <c r="S39" s="18" t="n">
-        <v>675.05</v>
+        <v>19007.74</v>
       </c>
       <c r="T39" s="18" t="n">
-        <v>413.81</v>
+        <v>19210.59</v>
       </c>
       <c r="U39" s="37" t="n">
-        <v>413.81</v>
+        <v>19210.59</v>
       </c>
       <c r="V39" s="18" t="n">
-        <v>418.6</v>
+        <v>17335.29</v>
       </c>
       <c r="W39" s="18" t="n">
-        <v>498.2</v>
+        <v>17889.19</v>
       </c>
       <c r="X39" s="18" t="n">
-        <v>497.7</v>
+        <v>19590.11</v>
       </c>
       <c r="Y39" s="18" t="n">
-        <v>636.16</v>
+        <v>19744.59</v>
       </c>
       <c r="Z39" s="37" t="n">
-        <v>636.16</v>
+        <v>19744.59</v>
       </c>
       <c r="AA39" s="18" t="n">
-        <v>631.11</v>
+        <v>20273.9</v>
       </c>
       <c r="AB39" s="19" t="n">
-        <v>585.23</v>
+        <v>21315.85</v>
       </c>
       <c r="AC39" s="10" t="n"/>
       <c r="AD39" s="10" t="n"/>
@@ -22460,80 +22467,80 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>부채총계</t>
+          <t>자본금</t>
         </is>
       </c>
       <c r="E40" s="18" t="n">
-        <v>17946.53</v>
+        <v>3072.67</v>
       </c>
       <c r="F40" s="37" t="n">
-        <v>17946.53</v>
+        <v>3072.67</v>
       </c>
       <c r="G40" s="18" t="n">
-        <v>27621.05</v>
+        <v>3072.67</v>
       </c>
       <c r="H40" s="18" t="n">
-        <v>26898.68</v>
+        <v>3072.67</v>
       </c>
       <c r="I40" s="18" t="n">
-        <v>28215.93</v>
+        <v>3072.67</v>
       </c>
       <c r="J40" s="18" t="n">
-        <v>25666.93</v>
+        <v>3072.67</v>
       </c>
       <c r="K40" s="37" t="n">
-        <v>25666.93</v>
+        <v>3072.67</v>
       </c>
       <c r="L40" s="18" t="n">
-        <v>22955.54</v>
+        <v>3072.67</v>
       </c>
       <c r="M40" s="18" t="n">
-        <v>22082.03</v>
+        <v>3072.67</v>
       </c>
       <c r="N40" s="18" t="n">
-        <v>21698.66</v>
+        <v>3072.67</v>
       </c>
       <c r="O40" s="18" t="n">
-        <v>21298.68</v>
+        <v>3072.67</v>
       </c>
       <c r="P40" s="37" t="n">
-        <v>21298.68</v>
+        <v>3072.67</v>
       </c>
       <c r="Q40" s="18" t="n">
-        <v>20886.82</v>
+        <v>3072.67</v>
       </c>
       <c r="R40" s="18" t="n">
-        <v>17719.91</v>
+        <v>3072.67</v>
       </c>
       <c r="S40" s="18" t="n">
-        <v>19007.74</v>
+        <v>3072.67</v>
       </c>
       <c r="T40" s="18" t="n">
-        <v>19210.59</v>
+        <v>3072.67</v>
       </c>
       <c r="U40" s="37" t="n">
-        <v>19210.59</v>
+        <v>3072.67</v>
       </c>
       <c r="V40" s="18" t="n">
-        <v>17335.29</v>
+        <v>3072.67</v>
       </c>
       <c r="W40" s="18" t="n">
-        <v>17889.19</v>
+        <v>3072.67</v>
       </c>
       <c r="X40" s="18" t="n">
-        <v>19590.11</v>
+        <v>3072.67</v>
       </c>
       <c r="Y40" s="18" t="n">
-        <v>19744.59</v>
+        <v>3072.67</v>
       </c>
       <c r="Z40" s="37" t="n">
-        <v>19744.59</v>
+        <v>3072.67</v>
       </c>
       <c r="AA40" s="18" t="n">
-        <v>20273.9</v>
+        <v>3072.67</v>
       </c>
       <c r="AB40" s="19" t="n">
-        <v>21315.85</v>
+        <v>3072.67</v>
       </c>
       <c r="AC40" s="10" t="n"/>
       <c r="AD40" s="10" t="n"/>
@@ -22555,80 +22562,80 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>자본금</t>
+          <t>자본잉여금</t>
         </is>
       </c>
       <c r="E41" s="18" t="n">
-        <v>3072.67</v>
+        <v>22064.38</v>
       </c>
       <c r="F41" s="37" t="n">
-        <v>3072.67</v>
+        <v>22064.38</v>
       </c>
       <c r="G41" s="18" t="n">
-        <v>3072.67</v>
+        <v>22064.38</v>
       </c>
       <c r="H41" s="18" t="n">
-        <v>3072.67</v>
+        <v>22064.38</v>
       </c>
       <c r="I41" s="18" t="n">
-        <v>3072.67</v>
+        <v>22064.38</v>
       </c>
       <c r="J41" s="18" t="n">
-        <v>3072.67</v>
+        <v>22064.38</v>
       </c>
       <c r="K41" s="37" t="n">
-        <v>3072.67</v>
+        <v>22064.38</v>
       </c>
       <c r="L41" s="18" t="n">
-        <v>3072.67</v>
+        <v>22064.38</v>
       </c>
       <c r="M41" s="18" t="n">
-        <v>3072.67</v>
+        <v>22064.38</v>
       </c>
       <c r="N41" s="18" t="n">
-        <v>3072.67</v>
+        <v>22064.38</v>
       </c>
       <c r="O41" s="18" t="n">
-        <v>3072.67</v>
+        <v>22064.38</v>
       </c>
       <c r="P41" s="37" t="n">
-        <v>3072.67</v>
+        <v>22064.38</v>
       </c>
       <c r="Q41" s="18" t="n">
-        <v>3072.67</v>
+        <v>22064.38</v>
       </c>
       <c r="R41" s="18" t="n">
-        <v>3072.67</v>
+        <v>22064.38</v>
       </c>
       <c r="S41" s="18" t="n">
-        <v>3072.67</v>
+        <v>22064.38</v>
       </c>
       <c r="T41" s="18" t="n">
-        <v>3072.67</v>
+        <v>22064.38</v>
       </c>
       <c r="U41" s="37" t="n">
-        <v>3072.67</v>
+        <v>22064.38</v>
       </c>
       <c r="V41" s="18" t="n">
-        <v>3072.67</v>
+        <v>22064.38</v>
       </c>
       <c r="W41" s="18" t="n">
-        <v>3072.67</v>
+        <v>22064.38</v>
       </c>
       <c r="X41" s="18" t="n">
-        <v>3072.67</v>
+        <v>22064.38</v>
       </c>
       <c r="Y41" s="18" t="n">
-        <v>3072.67</v>
+        <v>22033.95</v>
       </c>
       <c r="Z41" s="37" t="n">
-        <v>3072.67</v>
+        <v>22033.95</v>
       </c>
       <c r="AA41" s="18" t="n">
-        <v>3072.67</v>
+        <v>22033.95</v>
       </c>
       <c r="AB41" s="19" t="n">
-        <v>3072.67</v>
+        <v>22033.95</v>
       </c>
       <c r="AC41" s="10" t="n"/>
       <c r="AD41" s="10" t="n"/>
@@ -22650,80 +22657,80 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>자본잉여금</t>
+          <t>기타자본</t>
         </is>
       </c>
       <c r="E42" s="18" t="n">
-        <v>22064.38</v>
+        <v>0</v>
       </c>
       <c r="F42" s="37" t="n">
-        <v>22064.38</v>
+        <v>0</v>
       </c>
       <c r="G42" s="18" t="n">
-        <v>22064.38</v>
+        <v>0</v>
       </c>
       <c r="H42" s="18" t="n">
-        <v>22064.38</v>
+        <v>0</v>
       </c>
       <c r="I42" s="18" t="n">
-        <v>22064.38</v>
+        <v>0</v>
       </c>
       <c r="J42" s="18" t="n">
-        <v>22064.38</v>
+        <v>0</v>
       </c>
       <c r="K42" s="37" t="n">
-        <v>22064.38</v>
+        <v>0</v>
       </c>
       <c r="L42" s="18" t="n">
-        <v>22064.38</v>
+        <v>0</v>
       </c>
       <c r="M42" s="18" t="n">
-        <v>22064.38</v>
+        <v>0</v>
       </c>
       <c r="N42" s="18" t="n">
-        <v>22064.38</v>
+        <v>0</v>
       </c>
       <c r="O42" s="18" t="n">
-        <v>22064.38</v>
+        <v>0</v>
       </c>
       <c r="P42" s="37" t="n">
-        <v>22064.38</v>
+        <v>0</v>
       </c>
       <c r="Q42" s="18" t="n">
-        <v>22064.38</v>
+        <v>0</v>
       </c>
       <c r="R42" s="18" t="n">
-        <v>22064.38</v>
+        <v>0</v>
       </c>
       <c r="S42" s="18" t="n">
-        <v>22064.38</v>
+        <v>-141.91</v>
       </c>
       <c r="T42" s="18" t="n">
-        <v>22064.38</v>
+        <v>-141.91</v>
       </c>
       <c r="U42" s="37" t="n">
-        <v>22064.38</v>
+        <v>-141.91</v>
       </c>
       <c r="V42" s="18" t="n">
-        <v>22064.38</v>
+        <v>-141.91</v>
       </c>
       <c r="W42" s="18" t="n">
-        <v>22064.38</v>
+        <v>-141.91</v>
       </c>
       <c r="X42" s="18" t="n">
-        <v>22064.38</v>
+        <v>-141.91</v>
       </c>
       <c r="Y42" s="18" t="n">
-        <v>22033.95</v>
+        <v>-141.91</v>
       </c>
       <c r="Z42" s="37" t="n">
-        <v>22033.95</v>
+        <v>-141.91</v>
       </c>
       <c r="AA42" s="18" t="n">
-        <v>22033.95</v>
+        <v>-141.91</v>
       </c>
       <c r="AB42" s="19" t="n">
-        <v>22033.95</v>
+        <v>-141.91</v>
       </c>
       <c r="AC42" s="10" t="n"/>
       <c r="AD42" s="10" t="n"/>
@@ -22745,80 +22752,80 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>기타자본</t>
+          <t>기타포괄이익누계액</t>
         </is>
       </c>
       <c r="E43" s="18" t="n">
-        <v>0</v>
+        <v>-58.8</v>
       </c>
       <c r="F43" s="37" t="n">
-        <v>0</v>
+        <v>-58.8</v>
       </c>
       <c r="G43" s="18" t="n">
-        <v>0</v>
+        <v>426.31</v>
       </c>
       <c r="H43" s="18" t="n">
-        <v>0</v>
+        <v>143.93</v>
       </c>
       <c r="I43" s="18" t="n">
-        <v>0</v>
+        <v>574.83</v>
       </c>
       <c r="J43" s="18" t="n">
-        <v>0</v>
+        <v>84.87</v>
       </c>
       <c r="K43" s="37" t="n">
-        <v>0</v>
+        <v>84.87</v>
       </c>
       <c r="L43" s="18" t="n">
-        <v>0</v>
+        <v>284.11</v>
       </c>
       <c r="M43" s="18" t="n">
-        <v>0</v>
+        <v>1328.1</v>
       </c>
       <c r="N43" s="18" t="n">
-        <v>0</v>
+        <v>830.99</v>
       </c>
       <c r="O43" s="18" t="n">
-        <v>0</v>
+        <v>694.91</v>
       </c>
       <c r="P43" s="37" t="n">
-        <v>0</v>
+        <v>694.91</v>
       </c>
       <c r="Q43" s="18" t="n">
-        <v>0</v>
+        <v>387.93</v>
       </c>
       <c r="R43" s="18" t="n">
-        <v>0</v>
+        <v>254.48</v>
       </c>
       <c r="S43" s="18" t="n">
-        <v>-141.91</v>
+        <v>119.21</v>
       </c>
       <c r="T43" s="18" t="n">
-        <v>-141.91</v>
+        <v>-969.72</v>
       </c>
       <c r="U43" s="37" t="n">
-        <v>-141.91</v>
+        <v>-969.72</v>
       </c>
       <c r="V43" s="18" t="n">
-        <v>-141.91</v>
+        <v>-950.04</v>
       </c>
       <c r="W43" s="18" t="n">
-        <v>-141.91</v>
+        <v>-667.1900000000001</v>
       </c>
       <c r="X43" s="18" t="n">
-        <v>-141.91</v>
+        <v>-667.23</v>
       </c>
       <c r="Y43" s="18" t="n">
-        <v>-141.91</v>
+        <v>-623.74</v>
       </c>
       <c r="Z43" s="37" t="n">
-        <v>-141.91</v>
+        <v>-623.74</v>
       </c>
       <c r="AA43" s="18" t="n">
-        <v>-141.91</v>
+        <v>-640.0700000000001</v>
       </c>
       <c r="AB43" s="19" t="n">
-        <v>-141.91</v>
+        <v>-802.47</v>
       </c>
       <c r="AC43" s="10" t="n"/>
       <c r="AD43" s="10" t="n"/>
@@ -22840,80 +22847,80 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>기타포괄이익누계액</t>
+          <t>이익잉여금</t>
         </is>
       </c>
       <c r="E44" s="18" t="n">
-        <v>-58.8</v>
+        <v>5675.33</v>
       </c>
       <c r="F44" s="37" t="n">
-        <v>-58.8</v>
+        <v>5675.33</v>
       </c>
       <c r="G44" s="18" t="n">
-        <v>426.31</v>
+        <v>5892.02</v>
       </c>
       <c r="H44" s="18" t="n">
-        <v>143.93</v>
+        <v>6045.12</v>
       </c>
       <c r="I44" s="18" t="n">
-        <v>574.83</v>
+        <v>8461.700000000001</v>
       </c>
       <c r="J44" s="18" t="n">
-        <v>84.87</v>
+        <v>7697.86</v>
       </c>
       <c r="K44" s="37" t="n">
-        <v>84.87</v>
+        <v>7697.86</v>
       </c>
       <c r="L44" s="18" t="n">
-        <v>284.11</v>
+        <v>7956.17</v>
       </c>
       <c r="M44" s="18" t="n">
-        <v>1328.1</v>
+        <v>8425.280000000001</v>
       </c>
       <c r="N44" s="18" t="n">
-        <v>830.99</v>
+        <v>8313.77</v>
       </c>
       <c r="O44" s="18" t="n">
-        <v>694.91</v>
+        <v>10681.63</v>
       </c>
       <c r="P44" s="37" t="n">
-        <v>694.91</v>
+        <v>10681.63</v>
       </c>
       <c r="Q44" s="18" t="n">
-        <v>387.93</v>
+        <v>11149.72</v>
       </c>
       <c r="R44" s="18" t="n">
-        <v>254.48</v>
+        <v>20929.86</v>
       </c>
       <c r="S44" s="18" t="n">
-        <v>119.21</v>
+        <v>22323.55</v>
       </c>
       <c r="T44" s="18" t="n">
-        <v>-969.72</v>
+        <v>23320.1</v>
       </c>
       <c r="U44" s="37" t="n">
-        <v>-969.72</v>
+        <v>23320.1</v>
       </c>
       <c r="V44" s="18" t="n">
-        <v>-950.04</v>
+        <v>23906.82</v>
       </c>
       <c r="W44" s="18" t="n">
-        <v>-667.1900000000001</v>
+        <v>24281.74</v>
       </c>
       <c r="X44" s="18" t="n">
-        <v>-667.23</v>
+        <v>25095.65</v>
       </c>
       <c r="Y44" s="18" t="n">
-        <v>-623.74</v>
+        <v>26285.42</v>
       </c>
       <c r="Z44" s="37" t="n">
-        <v>-623.74</v>
+        <v>26285.42</v>
       </c>
       <c r="AA44" s="18" t="n">
-        <v>-640.0700000000001</v>
+        <v>28393.62</v>
       </c>
       <c r="AB44" s="19" t="n">
-        <v>-802.47</v>
+        <v>32281.56</v>
       </c>
       <c r="AC44" s="10" t="n"/>
       <c r="AD44" s="10" t="n"/>
@@ -22935,80 +22942,80 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>이익잉여금</t>
+          <t>자본총계</t>
         </is>
       </c>
       <c r="E45" s="18" t="n">
-        <v>5675.33</v>
+        <v>30753.58</v>
       </c>
       <c r="F45" s="37" t="n">
-        <v>5675.33</v>
+        <v>30753.58</v>
       </c>
       <c r="G45" s="18" t="n">
-        <v>5892.02</v>
+        <v>31455.39</v>
       </c>
       <c r="H45" s="18" t="n">
-        <v>6045.12</v>
+        <v>31326.11</v>
       </c>
       <c r="I45" s="18" t="n">
-        <v>8461.700000000001</v>
+        <v>34173.58</v>
       </c>
       <c r="J45" s="18" t="n">
-        <v>7697.86</v>
+        <v>32919.78</v>
       </c>
       <c r="K45" s="37" t="n">
-        <v>7697.86</v>
+        <v>32919.78</v>
       </c>
       <c r="L45" s="18" t="n">
-        <v>7956.17</v>
+        <v>33377.33</v>
       </c>
       <c r="M45" s="18" t="n">
-        <v>8425.280000000001</v>
+        <v>34890.43</v>
       </c>
       <c r="N45" s="18" t="n">
-        <v>8313.77</v>
+        <v>34281.81</v>
       </c>
       <c r="O45" s="18" t="n">
-        <v>10681.63</v>
+        <v>36513.59</v>
       </c>
       <c r="P45" s="37" t="n">
-        <v>10681.63</v>
+        <v>36513.59</v>
       </c>
       <c r="Q45" s="18" t="n">
-        <v>11149.72</v>
+        <v>36674.7</v>
       </c>
       <c r="R45" s="18" t="n">
-        <v>20929.86</v>
+        <v>46321.4</v>
       </c>
       <c r="S45" s="18" t="n">
-        <v>22323.55</v>
+        <v>47437.9</v>
       </c>
       <c r="T45" s="18" t="n">
-        <v>23320.1</v>
+        <v>47345.52</v>
       </c>
       <c r="U45" s="37" t="n">
-        <v>23320.1</v>
+        <v>47345.52</v>
       </c>
       <c r="V45" s="18" t="n">
-        <v>23906.82</v>
+        <v>47951.92</v>
       </c>
       <c r="W45" s="18" t="n">
-        <v>24281.74</v>
+        <v>48609.69</v>
       </c>
       <c r="X45" s="18" t="n">
-        <v>25095.65</v>
+        <v>49423.56</v>
       </c>
       <c r="Y45" s="18" t="n">
-        <v>26285.42</v>
+        <v>50626.4</v>
       </c>
       <c r="Z45" s="37" t="n">
-        <v>26285.42</v>
+        <v>50626.4</v>
       </c>
       <c r="AA45" s="18" t="n">
-        <v>28393.62</v>
+        <v>52718.26</v>
       </c>
       <c r="AB45" s="19" t="n">
-        <v>32281.56</v>
+        <v>56443.79</v>
       </c>
       <c r="AC45" s="10" t="n"/>
       <c r="AD45" s="10" t="n"/>
@@ -23030,80 +23037,80 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>자본총계</t>
+          <t>부채와자본총계</t>
         </is>
       </c>
       <c r="E46" s="18" t="n">
-        <v>30753.58</v>
+        <v>48700.11</v>
       </c>
       <c r="F46" s="37" t="n">
-        <v>30753.58</v>
+        <v>48700.11</v>
       </c>
       <c r="G46" s="18" t="n">
-        <v>31455.39</v>
+        <v>59076.44</v>
       </c>
       <c r="H46" s="18" t="n">
-        <v>31326.11</v>
+        <v>58224.79</v>
       </c>
       <c r="I46" s="18" t="n">
-        <v>34173.58</v>
+        <v>62389.51</v>
       </c>
       <c r="J46" s="18" t="n">
-        <v>32919.78</v>
+        <v>58586.72</v>
       </c>
       <c r="K46" s="37" t="n">
-        <v>32919.78</v>
+        <v>58586.72</v>
       </c>
       <c r="L46" s="18" t="n">
-        <v>33377.33</v>
+        <v>56332.87</v>
       </c>
       <c r="M46" s="18" t="n">
-        <v>34890.43</v>
+        <v>56972.46</v>
       </c>
       <c r="N46" s="18" t="n">
-        <v>34281.81</v>
+        <v>55980.47</v>
       </c>
       <c r="O46" s="18" t="n">
-        <v>36513.59</v>
+        <v>57812.27</v>
       </c>
       <c r="P46" s="37" t="n">
-        <v>36513.59</v>
+        <v>57812.27</v>
       </c>
       <c r="Q46" s="18" t="n">
-        <v>36674.7</v>
+        <v>57561.52</v>
       </c>
       <c r="R46" s="18" t="n">
-        <v>46321.4</v>
+        <v>64041.3</v>
       </c>
       <c r="S46" s="18" t="n">
-        <v>47437.9</v>
+        <v>66445.64</v>
       </c>
       <c r="T46" s="18" t="n">
-        <v>47345.52</v>
+        <v>66556.11</v>
       </c>
       <c r="U46" s="37" t="n">
-        <v>47345.52</v>
+        <v>66556.11</v>
       </c>
       <c r="V46" s="18" t="n">
-        <v>47951.92</v>
+        <v>65287.21</v>
       </c>
       <c r="W46" s="18" t="n">
-        <v>48609.69</v>
+        <v>66498.89</v>
       </c>
       <c r="X46" s="18" t="n">
-        <v>49423.56</v>
+        <v>69013.67999999999</v>
       </c>
       <c r="Y46" s="18" t="n">
-        <v>50626.4</v>
+        <v>70370.99000000001</v>
       </c>
       <c r="Z46" s="37" t="n">
-        <v>50626.4</v>
+        <v>70370.99000000001</v>
       </c>
       <c r="AA46" s="18" t="n">
-        <v>52718.26</v>
+        <v>72992.16</v>
       </c>
       <c r="AB46" s="19" t="n">
-        <v>56443.79</v>
+        <v>77759.64</v>
       </c>
       <c r="AC46" s="10" t="n"/>
       <c r="AD46" s="10" t="n"/>
@@ -23125,80 +23132,80 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>부채와자본총계</t>
+          <t>지배주주지분</t>
         </is>
       </c>
       <c r="E47" s="18" t="n">
-        <v>48700.11</v>
+        <v>30753.58</v>
       </c>
       <c r="F47" s="37" t="n">
-        <v>48700.11</v>
+        <v>30753.58</v>
       </c>
       <c r="G47" s="18" t="n">
-        <v>59076.44</v>
+        <v>31455.39</v>
       </c>
       <c r="H47" s="18" t="n">
-        <v>58224.79</v>
+        <v>31326.11</v>
       </c>
       <c r="I47" s="18" t="n">
-        <v>62389.51</v>
+        <v>34173.58</v>
       </c>
       <c r="J47" s="18" t="n">
-        <v>58586.72</v>
+        <v>32919.78</v>
       </c>
       <c r="K47" s="37" t="n">
-        <v>58586.72</v>
+        <v>32919.78</v>
       </c>
       <c r="L47" s="18" t="n">
-        <v>56332.87</v>
+        <v>33377.33</v>
       </c>
       <c r="M47" s="18" t="n">
-        <v>56972.46</v>
+        <v>34890.43</v>
       </c>
       <c r="N47" s="18" t="n">
-        <v>55980.47</v>
+        <v>34281.81</v>
       </c>
       <c r="O47" s="18" t="n">
-        <v>57812.27</v>
+        <v>36513.59</v>
       </c>
       <c r="P47" s="37" t="n">
-        <v>57812.27</v>
+        <v>36513.59</v>
       </c>
       <c r="Q47" s="18" t="n">
-        <v>57561.52</v>
+        <v>36674.7</v>
       </c>
       <c r="R47" s="18" t="n">
-        <v>64041.3</v>
+        <v>46321.4</v>
       </c>
       <c r="S47" s="18" t="n">
-        <v>66445.64</v>
+        <v>47437.9</v>
       </c>
       <c r="T47" s="18" t="n">
-        <v>66556.11</v>
+        <v>47345.52</v>
       </c>
       <c r="U47" s="37" t="n">
-        <v>66556.11</v>
+        <v>47345.52</v>
       </c>
       <c r="V47" s="18" t="n">
-        <v>65287.21</v>
+        <v>47951.92</v>
       </c>
       <c r="W47" s="18" t="n">
-        <v>66498.89</v>
+        <v>48609.69</v>
       </c>
       <c r="X47" s="18" t="n">
-        <v>69013.67999999999</v>
+        <v>49423.56</v>
       </c>
       <c r="Y47" s="18" t="n">
-        <v>70370.99000000001</v>
+        <v>50626.4</v>
       </c>
       <c r="Z47" s="37" t="n">
-        <v>70370.99000000001</v>
+        <v>50626.4</v>
       </c>
       <c r="AA47" s="18" t="n">
-        <v>72992.16</v>
+        <v>52718.26</v>
       </c>
       <c r="AB47" s="19" t="n">
-        <v>77759.64</v>
+        <v>56443.79</v>
       </c>
       <c r="AC47" s="10" t="n"/>
       <c r="AD47" s="10" t="n"/>
@@ -23220,80 +23227,80 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>지배주주지분</t>
+          <t>총차입금</t>
         </is>
       </c>
       <c r="E48" s="18" t="n">
-        <v>30753.58</v>
+        <v>8814.99</v>
       </c>
       <c r="F48" s="37" t="n">
-        <v>30753.58</v>
+        <v>8814.99</v>
       </c>
       <c r="G48" s="18" t="n">
-        <v>31455.39</v>
+        <v>17186.21</v>
       </c>
       <c r="H48" s="18" t="n">
-        <v>31326.11</v>
+        <v>17100</v>
       </c>
       <c r="I48" s="18" t="n">
-        <v>34173.58</v>
+        <v>17800</v>
       </c>
       <c r="J48" s="18" t="n">
-        <v>32919.78</v>
+        <v>17800</v>
       </c>
       <c r="K48" s="37" t="n">
-        <v>32919.78</v>
+        <v>17800</v>
       </c>
       <c r="L48" s="18" t="n">
-        <v>33377.33</v>
+        <v>17800</v>
       </c>
       <c r="M48" s="18" t="n">
-        <v>34890.43</v>
+        <v>17100</v>
       </c>
       <c r="N48" s="18" t="n">
-        <v>34281.81</v>
+        <v>17100</v>
       </c>
       <c r="O48" s="18" t="n">
-        <v>36513.59</v>
+        <v>17100</v>
       </c>
       <c r="P48" s="37" t="n">
-        <v>36513.59</v>
+        <v>17100</v>
       </c>
       <c r="Q48" s="18" t="n">
-        <v>36674.7</v>
+        <v>16891.59</v>
       </c>
       <c r="R48" s="18" t="n">
-        <v>46321.4</v>
+        <v>12728.94</v>
       </c>
       <c r="S48" s="18" t="n">
-        <v>47437.9</v>
+        <v>14291.52</v>
       </c>
       <c r="T48" s="18" t="n">
-        <v>47345.52</v>
+        <v>14200</v>
       </c>
       <c r="U48" s="37" t="n">
-        <v>47345.52</v>
+        <v>14200</v>
       </c>
       <c r="V48" s="18" t="n">
-        <v>47951.92</v>
+        <v>14200</v>
       </c>
       <c r="W48" s="18" t="n">
-        <v>48609.69</v>
+        <v>16200</v>
       </c>
       <c r="X48" s="18" t="n">
-        <v>49423.56</v>
+        <v>17700</v>
       </c>
       <c r="Y48" s="18" t="n">
-        <v>50626.4</v>
+        <v>17700</v>
       </c>
       <c r="Z48" s="37" t="n">
-        <v>50626.4</v>
+        <v>17700</v>
       </c>
       <c r="AA48" s="18" t="n">
-        <v>52718.26</v>
+        <v>17700</v>
       </c>
       <c r="AB48" s="19" t="n">
-        <v>56443.79</v>
+        <v>17700</v>
       </c>
       <c r="AC48" s="10" t="n"/>
       <c r="AD48" s="10" t="n"/>
@@ -23315,80 +23322,80 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>총차입금</t>
+          <t>순차입금</t>
         </is>
       </c>
       <c r="E49" s="18" t="n">
-        <v>8814.99</v>
+        <v>916.8099999999999</v>
       </c>
       <c r="F49" s="37" t="n">
-        <v>8814.99</v>
+        <v>916.8099999999999</v>
       </c>
       <c r="G49" s="18" t="n">
-        <v>17186.21</v>
+        <v>9878.200000000001</v>
       </c>
       <c r="H49" s="18" t="n">
-        <v>17100</v>
+        <v>13776.34</v>
       </c>
       <c r="I49" s="18" t="n">
-        <v>17800</v>
+        <v>13784.67</v>
       </c>
       <c r="J49" s="18" t="n">
-        <v>17800</v>
+        <v>13943.95</v>
       </c>
       <c r="K49" s="37" t="n">
-        <v>17800</v>
+        <v>13943.95</v>
       </c>
       <c r="L49" s="18" t="n">
-        <v>17800</v>
+        <v>10402.97</v>
       </c>
       <c r="M49" s="18" t="n">
-        <v>17100</v>
+        <v>8491.620000000001</v>
       </c>
       <c r="N49" s="18" t="n">
-        <v>17100</v>
+        <v>6205.7</v>
       </c>
       <c r="O49" s="18" t="n">
-        <v>17100</v>
+        <v>6053.04</v>
       </c>
       <c r="P49" s="37" t="n">
-        <v>17100</v>
+        <v>6053.04</v>
       </c>
       <c r="Q49" s="18" t="n">
-        <v>16891.59</v>
+        <v>4578.72</v>
       </c>
       <c r="R49" s="18" t="n">
-        <v>12728.94</v>
+        <v>-11477.14</v>
       </c>
       <c r="S49" s="18" t="n">
-        <v>14291.52</v>
+        <v>-11597.53</v>
       </c>
       <c r="T49" s="18" t="n">
-        <v>14200</v>
+        <v>-14464.16</v>
       </c>
       <c r="U49" s="37" t="n">
-        <v>14200</v>
+        <v>-14464.16</v>
       </c>
       <c r="V49" s="18" t="n">
-        <v>14200</v>
+        <v>-12461.87</v>
       </c>
       <c r="W49" s="18" t="n">
-        <v>16200</v>
+        <v>-11925.64</v>
       </c>
       <c r="X49" s="18" t="n">
-        <v>17700</v>
+        <v>-13060.96</v>
       </c>
       <c r="Y49" s="18" t="n">
-        <v>17700</v>
+        <v>-12732.78</v>
       </c>
       <c r="Z49" s="37" t="n">
-        <v>17700</v>
+        <v>-12732.78</v>
       </c>
       <c r="AA49" s="18" t="n">
-        <v>17700</v>
+        <v>-14874.17</v>
       </c>
       <c r="AB49" s="19" t="n">
-        <v>17700</v>
+        <v>-17857.17</v>
       </c>
       <c r="AC49" s="10" t="n"/>
       <c r="AD49" s="10" t="n"/>
@@ -23410,80 +23417,80 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>순차입금</t>
+          <t>이자발생자산</t>
         </is>
       </c>
       <c r="E50" s="18" t="n">
-        <v>916.8099999999999</v>
+        <v>14270.76</v>
       </c>
       <c r="F50" s="37" t="n">
-        <v>916.8099999999999</v>
+        <v>14270.76</v>
       </c>
       <c r="G50" s="18" t="n">
-        <v>9878.200000000001</v>
+        <v>14302.52</v>
       </c>
       <c r="H50" s="18" t="n">
-        <v>13776.34</v>
+        <v>10956.15</v>
       </c>
       <c r="I50" s="18" t="n">
-        <v>13784.67</v>
+        <v>12200.25</v>
       </c>
       <c r="J50" s="18" t="n">
-        <v>13943.95</v>
+        <v>11411.44</v>
       </c>
       <c r="K50" s="37" t="n">
-        <v>13943.95</v>
+        <v>11411.44</v>
       </c>
       <c r="L50" s="18" t="n">
-        <v>10402.97</v>
+        <v>15204.62</v>
       </c>
       <c r="M50" s="18" t="n">
-        <v>8491.620000000001</v>
+        <v>17737.48</v>
       </c>
       <c r="N50" s="18" t="n">
-        <v>6205.7</v>
+        <v>19337.92</v>
       </c>
       <c r="O50" s="18" t="n">
-        <v>6053.04</v>
+        <v>19504.74</v>
       </c>
       <c r="P50" s="37" t="n">
-        <v>6053.04</v>
+        <v>19504.74</v>
       </c>
       <c r="Q50" s="18" t="n">
-        <v>4578.72</v>
+        <v>20460.57</v>
       </c>
       <c r="R50" s="18" t="n">
-        <v>-11477.14</v>
+        <v>31739.03</v>
       </c>
       <c r="S50" s="18" t="n">
-        <v>-11597.53</v>
+        <v>32929.34</v>
       </c>
       <c r="T50" s="18" t="n">
-        <v>-14464.16</v>
+        <v>35341.31</v>
       </c>
       <c r="U50" s="37" t="n">
-        <v>-14464.16</v>
+        <v>35341.31</v>
       </c>
       <c r="V50" s="18" t="n">
-        <v>-12461.87</v>
+        <v>33736.69</v>
       </c>
       <c r="W50" s="18" t="n">
-        <v>-11925.64</v>
+        <v>35536.26</v>
       </c>
       <c r="X50" s="18" t="n">
-        <v>-13060.96</v>
+        <v>38452.94</v>
       </c>
       <c r="Y50" s="18" t="n">
-        <v>-12732.78</v>
+        <v>38317.87</v>
       </c>
       <c r="Z50" s="37" t="n">
-        <v>-12732.78</v>
+        <v>38317.87</v>
       </c>
       <c r="AA50" s="18" t="n">
-        <v>-14874.17</v>
+        <v>41001.54</v>
       </c>
       <c r="AB50" s="19" t="n">
-        <v>-17857.17</v>
+        <v>45770.84</v>
       </c>
       <c r="AC50" s="10" t="n"/>
       <c r="AD50" s="10" t="n"/>
@@ -23505,81 +23512,66 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>이자발생자산</t>
-        </is>
-      </c>
-      <c r="E51" s="18" t="n">
-        <v>14270.76</v>
-      </c>
-      <c r="F51" s="37" t="n">
-        <v>14270.76</v>
-      </c>
+          <t>장기금융부채(face)</t>
+        </is>
+      </c>
+      <c r="F51" s="9" t="n"/>
       <c r="G51" s="18" t="n">
-        <v>14302.52</v>
+        <v>13500</v>
       </c>
       <c r="H51" s="18" t="n">
-        <v>10956.15</v>
+        <v>13500</v>
       </c>
       <c r="I51" s="18" t="n">
-        <v>12200.25</v>
+        <v>13500</v>
       </c>
       <c r="J51" s="18" t="n">
-        <v>11411.44</v>
+        <v>13500</v>
       </c>
       <c r="K51" s="37" t="n">
-        <v>11411.44</v>
+        <v>13500</v>
       </c>
       <c r="L51" s="18" t="n">
-        <v>15204.62</v>
+        <v>13291.59</v>
       </c>
       <c r="M51" s="18" t="n">
-        <v>17737.48</v>
+        <v>12728.94</v>
       </c>
       <c r="N51" s="18" t="n">
-        <v>19337.92</v>
+        <v>12166.45</v>
       </c>
       <c r="O51" s="18" t="n">
-        <v>19504.74</v>
+        <v>11603.96</v>
       </c>
       <c r="P51" s="37" t="n">
-        <v>19504.74</v>
+        <v>11603.96</v>
       </c>
       <c r="Q51" s="18" t="n">
-        <v>20460.57</v>
+        <v>11041.47</v>
       </c>
       <c r="R51" s="18" t="n">
-        <v>31739.03</v>
+        <v>10478.98</v>
       </c>
       <c r="S51" s="18" t="n">
-        <v>32929.34</v>
+        <v>12874.88</v>
       </c>
       <c r="T51" s="18" t="n">
-        <v>35341.31</v>
+        <v>14200</v>
       </c>
       <c r="U51" s="37" t="n">
-        <v>35341.31</v>
+        <v>14200</v>
       </c>
       <c r="V51" s="18" t="n">
-        <v>33736.69</v>
+        <v>14200</v>
       </c>
       <c r="W51" s="18" t="n">
-        <v>35536.26</v>
+        <v>14200</v>
       </c>
       <c r="X51" s="18" t="n">
-        <v>38452.94</v>
-      </c>
-      <c r="Y51" s="18" t="n">
-        <v>38317.87</v>
-      </c>
-      <c r="Z51" s="37" t="n">
-        <v>38317.87</v>
-      </c>
-      <c r="AA51" s="18" t="n">
-        <v>41001.54</v>
-      </c>
-      <c r="AB51" s="19" t="n">
-        <v>45770.84</v>
-      </c>
+        <v>15700</v>
+      </c>
+      <c r="Z51" s="9" t="n"/>
+      <c r="AB51" s="5" t="n"/>
       <c r="AC51" s="10" t="n"/>
       <c r="AD51" s="10" t="n"/>
       <c r="AE51" s="11" t="n"/>
@@ -23600,14 +23592,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>당기법인세자산(선급법인세)</t>
+          <t>유동성장기부채</t>
         </is>
       </c>
       <c r="F52" s="9" t="n"/>
+      <c r="H52" s="18" t="n">
+        <v>1600</v>
+      </c>
       <c r="K52" s="9" t="n"/>
-      <c r="N52" s="18" t="n">
-        <v>82.65000000000001</v>
-      </c>
       <c r="P52" s="9" t="n"/>
       <c r="U52" s="9" t="n"/>
       <c r="Z52" s="9" t="n"/>
@@ -23632,39 +23624,18 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>기타비유동부채</t>
+          <t>당기법인세자산(선급법인세)</t>
         </is>
       </c>
       <c r="F53" s="9" t="n"/>
       <c r="K53" s="9" t="n"/>
+      <c r="N53" s="18" t="n">
+        <v>82.65000000000001</v>
+      </c>
       <c r="P53" s="9" t="n"/>
-      <c r="T53" s="18" t="n">
-        <v>9.58</v>
-      </c>
-      <c r="U53" s="37" t="n">
-        <v>9.58</v>
-      </c>
-      <c r="V53" s="18" t="n">
-        <v>9.98</v>
-      </c>
-      <c r="W53" s="18" t="n">
-        <v>8.949999999999999</v>
-      </c>
-      <c r="X53" s="18" t="n">
-        <v>9.82</v>
-      </c>
-      <c r="Y53" s="18" t="n">
-        <v>6.81</v>
-      </c>
-      <c r="Z53" s="37" t="n">
-        <v>6.81</v>
-      </c>
-      <c r="AA53" s="18" t="n">
-        <v>7.51</v>
-      </c>
-      <c r="AB53" s="19" t="n">
-        <v>5.65</v>
-      </c>
+      <c r="U53" s="9" t="n"/>
+      <c r="Z53" s="9" t="n"/>
+      <c r="AB53" s="5" t="n"/>
       <c r="AC53" s="10" t="n"/>
       <c r="AD53" s="10" t="n"/>
       <c r="AE53" s="11" t="n"/>
@@ -23685,24 +23656,38 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>투자부동산</t>
+          <t>기타비유동부채</t>
         </is>
       </c>
       <c r="F54" s="9" t="n"/>
       <c r="K54" s="9" t="n"/>
       <c r="P54" s="9" t="n"/>
-      <c r="U54" s="9" t="n"/>
+      <c r="T54" s="18" t="n">
+        <v>9.58</v>
+      </c>
+      <c r="U54" s="37" t="n">
+        <v>9.58</v>
+      </c>
+      <c r="V54" s="18" t="n">
+        <v>9.98</v>
+      </c>
+      <c r="W54" s="18" t="n">
+        <v>8.949999999999999</v>
+      </c>
+      <c r="X54" s="18" t="n">
+        <v>9.82</v>
+      </c>
       <c r="Y54" s="18" t="n">
-        <v>8169.29</v>
+        <v>6.81</v>
       </c>
       <c r="Z54" s="37" t="n">
-        <v>8169.29</v>
+        <v>6.81</v>
       </c>
       <c r="AA54" s="18" t="n">
-        <v>8169.29</v>
+        <v>7.51</v>
       </c>
       <c r="AB54" s="19" t="n">
-        <v>8169.29</v>
+        <v>5.65</v>
       </c>
       <c r="AC54" s="10" t="n"/>
       <c r="AD54" s="10" t="n"/>
@@ -23724,16 +23709,24 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>매각예정비유동자산및처분자산</t>
+          <t>투자부동산</t>
         </is>
       </c>
       <c r="F55" s="9" t="n"/>
       <c r="K55" s="9" t="n"/>
       <c r="P55" s="9" t="n"/>
       <c r="U55" s="9" t="n"/>
-      <c r="Z55" s="9" t="n"/>
+      <c r="Y55" s="18" t="n">
+        <v>8169.29</v>
+      </c>
+      <c r="Z55" s="37" t="n">
+        <v>8169.29</v>
+      </c>
+      <c r="AA55" s="18" t="n">
+        <v>8169.29</v>
+      </c>
       <c r="AB55" s="19" t="n">
-        <v>986.25</v>
+        <v>8169.29</v>
       </c>
       <c r="AC55" s="10" t="n"/>
       <c r="AD55" s="10" t="n"/>
@@ -23755,78 +23748,16 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>매출액(수익)</t>
-        </is>
-      </c>
-      <c r="E56" s="18" t="n">
-        <v>13028.42</v>
+          <t>매각예정비유동자산및처분자산</t>
+        </is>
       </c>
       <c r="F56" s="9" t="n"/>
-      <c r="G56" s="18" t="n">
-        <v>9661.41</v>
-      </c>
-      <c r="H56" s="18" t="n">
-        <v>7581.21</v>
-      </c>
-      <c r="I56" s="18" t="n">
-        <v>11424.27</v>
-      </c>
-      <c r="J56" s="18" t="n">
-        <v>12123.76</v>
-      </c>
-      <c r="K56" s="37" t="n">
-        <v>40790.65</v>
-      </c>
-      <c r="L56" s="18" t="n">
-        <v>7648.6</v>
-      </c>
-      <c r="M56" s="18" t="n">
-        <v>6882.17</v>
-      </c>
-      <c r="N56" s="18" t="n">
-        <v>4143.53</v>
-      </c>
-      <c r="O56" s="18" t="n">
-        <v>6989.32</v>
-      </c>
-      <c r="P56" s="37" t="n">
-        <v>25663.62</v>
-      </c>
-      <c r="Q56" s="18" t="n">
-        <v>4256.38</v>
-      </c>
-      <c r="R56" s="18" t="n">
-        <v>2062.35</v>
-      </c>
-      <c r="S56" s="18" t="n">
-        <v>3378.91</v>
-      </c>
-      <c r="T56" s="18" t="n">
-        <v>4838.84</v>
-      </c>
-      <c r="U56" s="37" t="n">
-        <v>14536.48</v>
-      </c>
-      <c r="V56" s="18" t="n">
-        <v>1560</v>
-      </c>
-      <c r="W56" s="18" t="n">
-        <v>2719.07</v>
-      </c>
-      <c r="X56" s="18" t="n">
-        <v>2291.1</v>
-      </c>
-      <c r="Y56" s="18" t="n">
-        <v>2224.94</v>
-      </c>
-      <c r="Z56" s="37" t="n">
-        <v>8795.110000000001</v>
-      </c>
-      <c r="AA56" s="18" t="n">
-        <v>2882.21</v>
-      </c>
+      <c r="K56" s="9" t="n"/>
+      <c r="P56" s="9" t="n"/>
+      <c r="U56" s="9" t="n"/>
+      <c r="Z56" s="9" t="n"/>
       <c r="AB56" s="19" t="n">
-        <v>4568.32</v>
+        <v>986.25</v>
       </c>
       <c r="AC56" s="10" t="n"/>
       <c r="AD56" s="10" t="n"/>
@@ -23848,78 +23779,78 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>매출원가</t>
+          <t>매출액(수익)</t>
         </is>
       </c>
       <c r="E57" s="18" t="n">
-        <v>10701</v>
+        <v>13028.42</v>
       </c>
       <c r="F57" s="9" t="n"/>
       <c r="G57" s="18" t="n">
-        <v>8461.34</v>
+        <v>9661.41</v>
       </c>
       <c r="H57" s="18" t="n">
-        <v>6482.02</v>
+        <v>7581.21</v>
       </c>
       <c r="I57" s="18" t="n">
-        <v>7404.42</v>
+        <v>11424.27</v>
       </c>
       <c r="J57" s="18" t="n">
-        <v>11122.52</v>
+        <v>12123.76</v>
       </c>
       <c r="K57" s="37" t="n">
-        <v>33470.3</v>
+        <v>40790.65</v>
       </c>
       <c r="L57" s="18" t="n">
-        <v>6681.99</v>
+        <v>7648.6</v>
       </c>
       <c r="M57" s="18" t="n">
-        <v>5476.61</v>
+        <v>6882.17</v>
       </c>
       <c r="N57" s="18" t="n">
-        <v>3173.68</v>
+        <v>4143.53</v>
       </c>
       <c r="O57" s="18" t="n">
-        <v>4386.04</v>
+        <v>6989.32</v>
       </c>
       <c r="P57" s="37" t="n">
-        <v>19718.32</v>
+        <v>25663.62</v>
       </c>
       <c r="Q57" s="18" t="n">
-        <v>3373.95</v>
+        <v>4256.38</v>
       </c>
       <c r="R57" s="18" t="n">
-        <v>1498.34</v>
+        <v>2062.35</v>
       </c>
       <c r="S57" s="18" t="n">
-        <v>1436.31</v>
+        <v>3378.91</v>
       </c>
       <c r="T57" s="18" t="n">
-        <v>3741.01</v>
+        <v>4838.84</v>
       </c>
       <c r="U57" s="37" t="n">
-        <v>10049.61</v>
+        <v>14536.48</v>
       </c>
       <c r="V57" s="18" t="n">
-        <v>1065.96</v>
+        <v>1560</v>
       </c>
       <c r="W57" s="18" t="n">
-        <v>1909.47</v>
+        <v>2719.07</v>
       </c>
       <c r="X57" s="18" t="n">
-        <v>1702.97</v>
+        <v>2291.1</v>
       </c>
       <c r="Y57" s="18" t="n">
-        <v>1502.82</v>
+        <v>2224.94</v>
       </c>
       <c r="Z57" s="37" t="n">
-        <v>6181.22</v>
+        <v>8795.110000000001</v>
       </c>
       <c r="AA57" s="18" t="n">
-        <v>1886.8</v>
+        <v>2882.21</v>
       </c>
       <c r="AB57" s="19" t="n">
-        <v>2325.04</v>
+        <v>4568.32</v>
       </c>
       <c r="AC57" s="10" t="n"/>
       <c r="AD57" s="10" t="n"/>
@@ -23941,78 +23872,78 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>매출총이익</t>
+          <t>매출원가</t>
         </is>
       </c>
       <c r="E58" s="18" t="n">
-        <v>2327.4</v>
+        <v>10701</v>
       </c>
       <c r="F58" s="9" t="n"/>
       <c r="G58" s="18" t="n">
-        <v>1200.06</v>
+        <v>8461.34</v>
       </c>
       <c r="H58" s="18" t="n">
-        <v>1099.19</v>
+        <v>6482.02</v>
       </c>
       <c r="I58" s="18" t="n">
-        <v>4019.85</v>
+        <v>7404.42</v>
       </c>
       <c r="J58" s="18" t="n">
-        <v>1001.24</v>
+        <v>11122.52</v>
       </c>
       <c r="K58" s="37" t="n">
-        <v>7320.34</v>
+        <v>33470.3</v>
       </c>
       <c r="L58" s="18" t="n">
-        <v>966.61</v>
+        <v>6681.99</v>
       </c>
       <c r="M58" s="18" t="n">
-        <v>1405.56</v>
+        <v>5476.61</v>
       </c>
       <c r="N58" s="18" t="n">
-        <v>969.84</v>
+        <v>3173.68</v>
       </c>
       <c r="O58" s="18" t="n">
-        <v>2603.28</v>
+        <v>4386.04</v>
       </c>
       <c r="P58" s="37" t="n">
-        <v>5945.29</v>
+        <v>19718.32</v>
       </c>
       <c r="Q58" s="18" t="n">
-        <v>882.4299999999999</v>
+        <v>3373.95</v>
       </c>
       <c r="R58" s="18" t="n">
-        <v>564.01</v>
+        <v>1498.34</v>
       </c>
       <c r="S58" s="18" t="n">
-        <v>1942.6</v>
+        <v>1436.31</v>
       </c>
       <c r="T58" s="18" t="n">
-        <v>1097.83</v>
+        <v>3741.01</v>
       </c>
       <c r="U58" s="37" t="n">
-        <v>4486.87</v>
+        <v>10049.61</v>
       </c>
       <c r="V58" s="18" t="n">
-        <v>494.05</v>
+        <v>1065.96</v>
       </c>
       <c r="W58" s="18" t="n">
-        <v>809.6</v>
+        <v>1909.47</v>
       </c>
       <c r="X58" s="18" t="n">
-        <v>588.13</v>
+        <v>1702.97</v>
       </c>
       <c r="Y58" s="18" t="n">
-        <v>722.13</v>
+        <v>1502.82</v>
       </c>
       <c r="Z58" s="37" t="n">
-        <v>2613.91</v>
+        <v>6181.22</v>
       </c>
       <c r="AA58" s="18" t="n">
-        <v>995.41</v>
+        <v>1886.8</v>
       </c>
       <c r="AB58" s="19" t="n">
-        <v>2243.27</v>
+        <v>2325.04</v>
       </c>
       <c r="AC58" s="10" t="n"/>
       <c r="AD58" s="10" t="n"/>
@@ -24034,78 +23965,78 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>판관비</t>
+          <t>매출총이익</t>
         </is>
       </c>
       <c r="E59" s="18" t="n">
-        <v>1400.56</v>
+        <v>2327.4</v>
       </c>
       <c r="F59" s="9" t="n"/>
       <c r="G59" s="18" t="n">
-        <v>1303.26</v>
+        <v>1200.06</v>
       </c>
       <c r="H59" s="18" t="n">
-        <v>1115.73</v>
+        <v>1099.19</v>
       </c>
       <c r="I59" s="18" t="n">
-        <v>1464.12</v>
+        <v>4019.85</v>
       </c>
       <c r="J59" s="18" t="n">
-        <v>1559.72</v>
+        <v>1001.24</v>
       </c>
       <c r="K59" s="37" t="n">
-        <v>5442.83</v>
+        <v>7320.34</v>
       </c>
       <c r="L59" s="18" t="n">
-        <v>1084.6</v>
+        <v>966.61</v>
       </c>
       <c r="M59" s="18" t="n">
-        <v>863.01</v>
+        <v>1405.56</v>
       </c>
       <c r="N59" s="18" t="n">
-        <v>1485.81</v>
+        <v>969.84</v>
       </c>
       <c r="O59" s="18" t="n">
-        <v>959.59</v>
+        <v>2603.28</v>
       </c>
       <c r="P59" s="37" t="n">
-        <v>4393.01</v>
+        <v>5945.29</v>
       </c>
       <c r="Q59" s="18" t="n">
-        <v>915.4400000000001</v>
+        <v>882.4299999999999</v>
       </c>
       <c r="R59" s="18" t="n">
-        <v>495.36</v>
+        <v>564.01</v>
       </c>
       <c r="S59" s="18" t="n">
-        <v>485.91</v>
+        <v>1942.6</v>
       </c>
       <c r="T59" s="18" t="n">
-        <v>502.08</v>
+        <v>1097.83</v>
       </c>
       <c r="U59" s="37" t="n">
-        <v>2398.79</v>
+        <v>4486.87</v>
       </c>
       <c r="V59" s="18" t="n">
-        <v>420.69</v>
+        <v>494.05</v>
       </c>
       <c r="W59" s="18" t="n">
-        <v>420.4</v>
+        <v>809.6</v>
       </c>
       <c r="X59" s="18" t="n">
-        <v>477.05</v>
+        <v>588.13</v>
       </c>
       <c r="Y59" s="18" t="n">
-        <v>540.51</v>
+        <v>722.13</v>
       </c>
       <c r="Z59" s="37" t="n">
-        <v>1858.65</v>
+        <v>2613.91</v>
       </c>
       <c r="AA59" s="18" t="n">
-        <v>451.59</v>
+        <v>995.41</v>
       </c>
       <c r="AB59" s="19" t="n">
-        <v>420.18</v>
+        <v>2243.27</v>
       </c>
       <c r="AC59" s="10" t="n"/>
       <c r="AD59" s="10" t="n"/>
@@ -24127,78 +24058,78 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>영업이익</t>
+          <t>판관비</t>
         </is>
       </c>
       <c r="E60" s="18" t="n">
-        <v>926.84</v>
+        <v>1400.56</v>
       </c>
       <c r="F60" s="9" t="n"/>
       <c r="G60" s="18" t="n">
-        <v>-103.2</v>
+        <v>1303.26</v>
       </c>
       <c r="H60" s="18" t="n">
-        <v>-16.54</v>
+        <v>1115.73</v>
       </c>
       <c r="I60" s="18" t="n">
-        <v>2555.73</v>
+        <v>1464.12</v>
       </c>
       <c r="J60" s="18" t="n">
-        <v>-558.49</v>
+        <v>1559.72</v>
       </c>
       <c r="K60" s="37" t="n">
-        <v>1877.5</v>
+        <v>5442.83</v>
       </c>
       <c r="L60" s="18" t="n">
-        <v>-117.99</v>
+        <v>1084.6</v>
       </c>
       <c r="M60" s="18" t="n">
-        <v>542.5599999999999</v>
+        <v>863.01</v>
       </c>
       <c r="N60" s="18" t="n">
-        <v>-515.97</v>
+        <v>1485.81</v>
       </c>
       <c r="O60" s="18" t="n">
-        <v>1643.69</v>
+        <v>959.59</v>
       </c>
       <c r="P60" s="37" t="n">
-        <v>1552.29</v>
+        <v>4393.01</v>
       </c>
       <c r="Q60" s="18" t="n">
-        <v>-33</v>
+        <v>915.4400000000001</v>
       </c>
       <c r="R60" s="18" t="n">
-        <v>68.65000000000001</v>
+        <v>495.36</v>
       </c>
       <c r="S60" s="18" t="n">
-        <v>1456.69</v>
+        <v>485.91</v>
       </c>
       <c r="T60" s="18" t="n">
-        <v>595.75</v>
+        <v>502.08</v>
       </c>
       <c r="U60" s="37" t="n">
-        <v>2088.09</v>
+        <v>2398.79</v>
       </c>
       <c r="V60" s="18" t="n">
-        <v>73.36</v>
+        <v>420.69</v>
       </c>
       <c r="W60" s="18" t="n">
-        <v>389.2</v>
+        <v>420.4</v>
       </c>
       <c r="X60" s="18" t="n">
-        <v>111.08</v>
+        <v>477.05</v>
       </c>
       <c r="Y60" s="18" t="n">
-        <v>181.61</v>
+        <v>540.51</v>
       </c>
       <c r="Z60" s="37" t="n">
-        <v>755.25</v>
+        <v>1858.65</v>
       </c>
       <c r="AA60" s="18" t="n">
-        <v>543.8200000000001</v>
+        <v>451.59</v>
       </c>
       <c r="AB60" s="19" t="n">
-        <v>1823.09</v>
+        <v>420.18</v>
       </c>
       <c r="AC60" s="10" t="n"/>
       <c r="AD60" s="10" t="n"/>
@@ -24220,78 +24151,78 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>기타영업외손익</t>
+          <t>영업이익</t>
         </is>
       </c>
       <c r="E61" s="18" t="n">
-        <v>17.53</v>
+        <v>926.84</v>
       </c>
       <c r="F61" s="9" t="n"/>
       <c r="G61" s="18" t="n">
-        <v>12.41</v>
+        <v>-103.2</v>
       </c>
       <c r="H61" s="18" t="n">
-        <v>20.87</v>
+        <v>-16.54</v>
       </c>
       <c r="I61" s="18" t="n">
-        <v>18.1</v>
+        <v>2555.73</v>
       </c>
       <c r="J61" s="18" t="n">
-        <v>63.24</v>
+        <v>-558.49</v>
       </c>
       <c r="K61" s="37" t="n">
-        <v>114.62</v>
+        <v>1877.5</v>
       </c>
       <c r="L61" s="18" t="n">
-        <v>123.38</v>
+        <v>-117.99</v>
       </c>
       <c r="M61" s="18" t="n">
-        <v>110.59</v>
+        <v>542.5599999999999</v>
       </c>
       <c r="N61" s="18" t="n">
-        <v>115.16</v>
+        <v>-515.97</v>
       </c>
       <c r="O61" s="18" t="n">
-        <v>432.45</v>
+        <v>1643.69</v>
       </c>
       <c r="P61" s="37" t="n">
-        <v>781.58</v>
+        <v>1552.29</v>
       </c>
       <c r="Q61" s="18" t="n">
-        <v>144.55</v>
+        <v>-33</v>
       </c>
       <c r="R61" s="18" t="n">
-        <v>112.75</v>
+        <v>68.65000000000001</v>
       </c>
       <c r="S61" s="18" t="n">
-        <v>312.94</v>
+        <v>1456.69</v>
       </c>
       <c r="T61" s="18" t="n">
-        <v>121.92</v>
+        <v>595.75</v>
       </c>
       <c r="U61" s="37" t="n">
-        <v>692.16</v>
+        <v>2088.09</v>
       </c>
       <c r="V61" s="18" t="n">
-        <v>89.63</v>
+        <v>73.36</v>
       </c>
       <c r="W61" s="18" t="n">
-        <v>101.53</v>
+        <v>389.2</v>
       </c>
       <c r="X61" s="18" t="n">
-        <v>104.03</v>
+        <v>111.08</v>
       </c>
       <c r="Y61" s="18" t="n">
-        <v>109.46</v>
+        <v>181.61</v>
       </c>
       <c r="Z61" s="37" t="n">
-        <v>404.65</v>
+        <v>755.25</v>
       </c>
       <c r="AA61" s="18" t="n">
-        <v>99.88</v>
+        <v>543.8200000000001</v>
       </c>
       <c r="AB61" s="19" t="n">
-        <v>263.32</v>
+        <v>1823.09</v>
       </c>
       <c r="AC61" s="10" t="n"/>
       <c r="AD61" s="10" t="n"/>
@@ -24313,27 +24244,27 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>기타영업외수익</t>
+          <t>기타영업외손익</t>
         </is>
       </c>
       <c r="E62" s="18" t="n">
-        <v>23.1</v>
+        <v>17.53</v>
       </c>
       <c r="F62" s="9" t="n"/>
       <c r="G62" s="18" t="n">
-        <v>12.44</v>
+        <v>12.41</v>
       </c>
       <c r="H62" s="18" t="n">
         <v>20.87</v>
       </c>
       <c r="I62" s="18" t="n">
-        <v>18.85</v>
+        <v>18.1</v>
       </c>
       <c r="J62" s="18" t="n">
         <v>63.24</v>
       </c>
       <c r="K62" s="37" t="n">
-        <v>115.4</v>
+        <v>114.62</v>
       </c>
       <c r="L62" s="18" t="n">
         <v>123.38</v>
@@ -24345,31 +24276,31 @@
         <v>115.16</v>
       </c>
       <c r="O62" s="18" t="n">
-        <v>433.23</v>
+        <v>432.45</v>
       </c>
       <c r="P62" s="37" t="n">
-        <v>782.36</v>
+        <v>781.58</v>
       </c>
       <c r="Q62" s="18" t="n">
         <v>144.55</v>
       </c>
       <c r="R62" s="18" t="n">
-        <v>113.05</v>
+        <v>112.75</v>
       </c>
       <c r="S62" s="18" t="n">
-        <v>313.03</v>
+        <v>312.94</v>
       </c>
       <c r="T62" s="18" t="n">
         <v>121.92</v>
       </c>
       <c r="U62" s="37" t="n">
-        <v>692.55</v>
+        <v>692.16</v>
       </c>
       <c r="V62" s="18" t="n">
-        <v>103.95</v>
+        <v>89.63</v>
       </c>
       <c r="W62" s="18" t="n">
-        <v>101.66</v>
+        <v>101.53</v>
       </c>
       <c r="X62" s="18" t="n">
         <v>104.03</v>
@@ -24378,13 +24309,13 @@
         <v>109.46</v>
       </c>
       <c r="Z62" s="37" t="n">
-        <v>419.1</v>
+        <v>404.65</v>
       </c>
       <c r="AA62" s="18" t="n">
         <v>99.88</v>
       </c>
       <c r="AB62" s="19" t="n">
-        <v>266.23</v>
+        <v>263.32</v>
       </c>
       <c r="AC62" s="10" t="n"/>
       <c r="AD62" s="10" t="n"/>
@@ -24406,78 +24337,78 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>기타영업외비용</t>
+          <t>기타영업외수익</t>
         </is>
       </c>
       <c r="E63" s="18" t="n">
-        <v>5.58</v>
+        <v>23.1</v>
       </c>
       <c r="F63" s="9" t="n"/>
       <c r="G63" s="18" t="n">
-        <v>0.03</v>
+        <v>12.44</v>
       </c>
       <c r="H63" s="18" t="n">
-        <v>0</v>
+        <v>20.87</v>
       </c>
       <c r="I63" s="18" t="n">
-        <v>0.75</v>
+        <v>18.85</v>
       </c>
       <c r="J63" s="18" t="n">
-        <v>0</v>
+        <v>63.24</v>
       </c>
       <c r="K63" s="37" t="n">
-        <v>0.78</v>
+        <v>115.4</v>
       </c>
       <c r="L63" s="18" t="n">
-        <v>0</v>
+        <v>123.38</v>
       </c>
       <c r="M63" s="18" t="n">
-        <v>0</v>
+        <v>110.59</v>
       </c>
       <c r="N63" s="18" t="n">
-        <v>0</v>
+        <v>115.16</v>
       </c>
       <c r="O63" s="18" t="n">
-        <v>0.78</v>
+        <v>433.23</v>
       </c>
       <c r="P63" s="37" t="n">
-        <v>0.78</v>
+        <v>782.36</v>
       </c>
       <c r="Q63" s="18" t="n">
-        <v>0</v>
+        <v>144.55</v>
       </c>
       <c r="R63" s="18" t="n">
-        <v>0.3</v>
+        <v>113.05</v>
       </c>
       <c r="S63" s="18" t="n">
-        <v>0.09</v>
+        <v>313.03</v>
       </c>
       <c r="T63" s="18" t="n">
-        <v>0</v>
+        <v>121.92</v>
       </c>
       <c r="U63" s="37" t="n">
-        <v>0.39</v>
+        <v>692.55</v>
       </c>
       <c r="V63" s="18" t="n">
-        <v>14.32</v>
+        <v>103.95</v>
       </c>
       <c r="W63" s="18" t="n">
-        <v>0.13</v>
+        <v>101.66</v>
       </c>
       <c r="X63" s="18" t="n">
-        <v>0</v>
+        <v>104.03</v>
       </c>
       <c r="Y63" s="18" t="n">
-        <v>0</v>
+        <v>109.46</v>
       </c>
       <c r="Z63" s="37" t="n">
-        <v>14.45</v>
+        <v>419.1</v>
       </c>
       <c r="AA63" s="18" t="n">
-        <v>0</v>
+        <v>99.88</v>
       </c>
       <c r="AB63" s="19" t="n">
-        <v>2.91</v>
+        <v>266.23</v>
       </c>
       <c r="AC63" s="10" t="n"/>
       <c r="AD63" s="10" t="n"/>
@@ -24499,78 +24430,78 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>금융손익</t>
+          <t>기타영업외비용</t>
         </is>
       </c>
       <c r="E64" s="18" t="n">
-        <v>396.33</v>
+        <v>5.58</v>
       </c>
       <c r="F64" s="9" t="n"/>
       <c r="G64" s="18" t="n">
-        <v>291.59</v>
+        <v>0.03</v>
       </c>
       <c r="H64" s="18" t="n">
-        <v>127.28</v>
+        <v>0</v>
       </c>
       <c r="I64" s="18" t="n">
-        <v>594.13</v>
+        <v>0.75</v>
       </c>
       <c r="J64" s="18" t="n">
-        <v>-565.59</v>
+        <v>0</v>
       </c>
       <c r="K64" s="37" t="n">
-        <v>447.41</v>
+        <v>0.78</v>
       </c>
       <c r="L64" s="18" t="n">
-        <v>252.45</v>
+        <v>0</v>
       </c>
       <c r="M64" s="18" t="n">
-        <v>-69.29000000000001</v>
+        <v>0</v>
       </c>
       <c r="N64" s="18" t="n">
-        <v>205.17</v>
+        <v>0</v>
       </c>
       <c r="O64" s="18" t="n">
-        <v>340.46</v>
+        <v>0.78</v>
       </c>
       <c r="P64" s="37" t="n">
-        <v>728.79</v>
+        <v>0.78</v>
       </c>
       <c r="Q64" s="18" t="n">
-        <v>433.18</v>
+        <v>0</v>
       </c>
       <c r="R64" s="18" t="n">
-        <v>-531.83</v>
+        <v>0.3</v>
       </c>
       <c r="S64" s="18" t="n">
-        <v>-15.58</v>
+        <v>0.09</v>
       </c>
       <c r="T64" s="18" t="n">
-        <v>648.67</v>
+        <v>0</v>
       </c>
       <c r="U64" s="37" t="n">
-        <v>534.4400000000001</v>
+        <v>0.39</v>
       </c>
       <c r="V64" s="18" t="n">
-        <v>591.63</v>
+        <v>14.32</v>
       </c>
       <c r="W64" s="18" t="n">
-        <v>-22.99</v>
+        <v>0.13</v>
       </c>
       <c r="X64" s="18" t="n">
-        <v>865.05</v>
+        <v>0</v>
       </c>
       <c r="Y64" s="18" t="n">
-        <v>848.63</v>
+        <v>0</v>
       </c>
       <c r="Z64" s="37" t="n">
-        <v>2282.32</v>
+        <v>14.45</v>
       </c>
       <c r="AA64" s="18" t="n">
-        <v>2047.93</v>
+        <v>0</v>
       </c>
       <c r="AB64" s="19" t="n">
-        <v>2824.66</v>
+        <v>2.91</v>
       </c>
       <c r="AC64" s="10" t="n"/>
       <c r="AD64" s="10" t="n"/>
@@ -24592,78 +24523,78 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>금융수익</t>
+          <t>금융손익</t>
         </is>
       </c>
       <c r="E65" s="18" t="n">
-        <v>619.9</v>
+        <v>396.33</v>
       </c>
       <c r="F65" s="9" t="n"/>
       <c r="G65" s="18" t="n">
-        <v>422.25</v>
+        <v>291.59</v>
       </c>
       <c r="H65" s="18" t="n">
-        <v>280.4</v>
+        <v>127.28</v>
       </c>
       <c r="I65" s="18" t="n">
-        <v>768.95</v>
+        <v>594.13</v>
       </c>
       <c r="J65" s="18" t="n">
-        <v>-110.92</v>
+        <v>-565.59</v>
       </c>
       <c r="K65" s="37" t="n">
-        <v>1360.68</v>
+        <v>447.41</v>
       </c>
       <c r="L65" s="18" t="n">
-        <v>494.41</v>
+        <v>252.45</v>
       </c>
       <c r="M65" s="18" t="n">
-        <v>152.45</v>
+        <v>-69.29000000000001</v>
       </c>
       <c r="N65" s="18" t="n">
-        <v>470.51</v>
+        <v>205.17</v>
       </c>
       <c r="O65" s="18" t="n">
-        <v>565.97</v>
+        <v>340.46</v>
       </c>
       <c r="P65" s="37" t="n">
-        <v>1683.34</v>
+        <v>728.79</v>
       </c>
       <c r="Q65" s="18" t="n">
-        <v>634.25</v>
+        <v>433.18</v>
       </c>
       <c r="R65" s="18" t="n">
-        <v>32.2</v>
+        <v>-531.83</v>
       </c>
       <c r="S65" s="18" t="n">
-        <v>419.54</v>
+        <v>-15.58</v>
       </c>
       <c r="T65" s="18" t="n">
-        <v>972.3</v>
+        <v>648.67</v>
       </c>
       <c r="U65" s="37" t="n">
-        <v>2058.29</v>
+        <v>534.4400000000001</v>
       </c>
       <c r="V65" s="18" t="n">
-        <v>736.9</v>
+        <v>591.63</v>
       </c>
       <c r="W65" s="18" t="n">
-        <v>145.79</v>
+        <v>-22.99</v>
       </c>
       <c r="X65" s="18" t="n">
-        <v>1022.57</v>
+        <v>865.05</v>
       </c>
       <c r="Y65" s="18" t="n">
-        <v>1552.65</v>
+        <v>848.63</v>
       </c>
       <c r="Z65" s="37" t="n">
-        <v>3457.91</v>
+        <v>2282.32</v>
       </c>
       <c r="AA65" s="18" t="n">
-        <v>3907.86</v>
+        <v>2047.93</v>
       </c>
       <c r="AB65" s="19" t="n">
-        <v>2929.37</v>
+        <v>2824.66</v>
       </c>
       <c r="AC65" s="10" t="n"/>
       <c r="AD65" s="10" t="n"/>
@@ -24685,78 +24616,78 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>금융비용</t>
+          <t>금융수익</t>
         </is>
       </c>
       <c r="E66" s="18" t="n">
-        <v>223.57</v>
+        <v>619.9</v>
       </c>
       <c r="F66" s="9" t="n"/>
       <c r="G66" s="18" t="n">
-        <v>130.66</v>
+        <v>422.25</v>
       </c>
       <c r="H66" s="18" t="n">
-        <v>153.12</v>
+        <v>280.4</v>
       </c>
       <c r="I66" s="18" t="n">
-        <v>174.82</v>
+        <v>768.95</v>
       </c>
       <c r="J66" s="18" t="n">
-        <v>454.67</v>
+        <v>-110.92</v>
       </c>
       <c r="K66" s="37" t="n">
-        <v>913.27</v>
+        <v>1360.68</v>
       </c>
       <c r="L66" s="18" t="n">
-        <v>241.96</v>
+        <v>494.41</v>
       </c>
       <c r="M66" s="18" t="n">
-        <v>221.74</v>
+        <v>152.45</v>
       </c>
       <c r="N66" s="18" t="n">
-        <v>265.34</v>
+        <v>470.51</v>
       </c>
       <c r="O66" s="18" t="n">
-        <v>225.5</v>
+        <v>565.97</v>
       </c>
       <c r="P66" s="37" t="n">
-        <v>954.54</v>
+        <v>1683.34</v>
       </c>
       <c r="Q66" s="18" t="n">
-        <v>201.07</v>
+        <v>634.25</v>
       </c>
       <c r="R66" s="18" t="n">
-        <v>564.03</v>
+        <v>32.2</v>
       </c>
       <c r="S66" s="18" t="n">
-        <v>435.12</v>
+        <v>419.54</v>
       </c>
       <c r="T66" s="18" t="n">
-        <v>323.63</v>
+        <v>972.3</v>
       </c>
       <c r="U66" s="37" t="n">
-        <v>1523.85</v>
+        <v>2058.29</v>
       </c>
       <c r="V66" s="18" t="n">
-        <v>145.27</v>
+        <v>736.9</v>
       </c>
       <c r="W66" s="18" t="n">
-        <v>168.78</v>
+        <v>145.79</v>
       </c>
       <c r="X66" s="18" t="n">
-        <v>157.52</v>
+        <v>1022.57</v>
       </c>
       <c r="Y66" s="18" t="n">
-        <v>704.02</v>
+        <v>1552.65</v>
       </c>
       <c r="Z66" s="37" t="n">
-        <v>1175.59</v>
+        <v>3457.91</v>
       </c>
       <c r="AA66" s="18" t="n">
-        <v>1859.93</v>
+        <v>3907.86</v>
       </c>
       <c r="AB66" s="19" t="n">
-        <v>104.71</v>
+        <v>2929.37</v>
       </c>
       <c r="AC66" s="10" t="n"/>
       <c r="AD66" s="10" t="n"/>
@@ -24778,78 +24709,78 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>법인세비용차감전계속사업이익</t>
+          <t>금융비용</t>
         </is>
       </c>
       <c r="E67" s="18" t="n">
-        <v>1340.7</v>
+        <v>223.57</v>
       </c>
       <c r="F67" s="9" t="n"/>
       <c r="G67" s="18" t="n">
-        <v>200.8</v>
+        <v>130.66</v>
       </c>
       <c r="H67" s="18" t="n">
-        <v>131.6</v>
+        <v>153.12</v>
       </c>
       <c r="I67" s="18" t="n">
-        <v>3167.95</v>
+        <v>174.82</v>
       </c>
       <c r="J67" s="18" t="n">
-        <v>-1060.83</v>
+        <v>454.67</v>
       </c>
       <c r="K67" s="37" t="n">
-        <v>2439.52</v>
+        <v>913.27</v>
       </c>
       <c r="L67" s="18" t="n">
-        <v>257.84</v>
+        <v>241.96</v>
       </c>
       <c r="M67" s="18" t="n">
-        <v>583.86</v>
+        <v>221.74</v>
       </c>
       <c r="N67" s="18" t="n">
-        <v>-195.63</v>
+        <v>265.34</v>
       </c>
       <c r="O67" s="18" t="n">
-        <v>2416.6</v>
+        <v>225.5</v>
       </c>
       <c r="P67" s="37" t="n">
-        <v>3062.67</v>
+        <v>954.54</v>
       </c>
       <c r="Q67" s="18" t="n">
-        <v>544.73</v>
+        <v>201.07</v>
       </c>
       <c r="R67" s="18" t="n">
-        <v>-350.44</v>
+        <v>564.03</v>
       </c>
       <c r="S67" s="18" t="n">
-        <v>1754.05</v>
+        <v>435.12</v>
       </c>
       <c r="T67" s="18" t="n">
-        <v>1366.35</v>
+        <v>323.63</v>
       </c>
       <c r="U67" s="37" t="n">
-        <v>3314.69</v>
+        <v>1523.85</v>
       </c>
       <c r="V67" s="18" t="n">
-        <v>754.63</v>
+        <v>145.27</v>
       </c>
       <c r="W67" s="18" t="n">
-        <v>467.74</v>
+        <v>168.78</v>
       </c>
       <c r="X67" s="18" t="n">
-        <v>1080.16</v>
+        <v>157.52</v>
       </c>
       <c r="Y67" s="18" t="n">
-        <v>1139.7</v>
+        <v>704.02</v>
       </c>
       <c r="Z67" s="37" t="n">
-        <v>3442.23</v>
+        <v>1175.59</v>
       </c>
       <c r="AA67" s="18" t="n">
-        <v>2691.64</v>
+        <v>1859.93</v>
       </c>
       <c r="AB67" s="19" t="n">
-        <v>4911.07</v>
+        <v>104.71</v>
       </c>
       <c r="AC67" s="10" t="n"/>
       <c r="AD67" s="10" t="n"/>
@@ -24871,78 +24802,78 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>법인세비용</t>
+          <t>법인세비용차감전계속사업이익</t>
         </is>
       </c>
       <c r="E68" s="18" t="n">
-        <v>441.05</v>
+        <v>1340.7</v>
       </c>
       <c r="F68" s="9" t="n"/>
       <c r="G68" s="18" t="n">
-        <v>28.86</v>
+        <v>200.8</v>
       </c>
       <c r="H68" s="18" t="n">
-        <v>39.86</v>
+        <v>131.6</v>
       </c>
       <c r="I68" s="18" t="n">
-        <v>699.27</v>
+        <v>3167.95</v>
       </c>
       <c r="J68" s="18" t="n">
-        <v>-405.62</v>
+        <v>-1060.83</v>
       </c>
       <c r="K68" s="37" t="n">
-        <v>362.37</v>
+        <v>2439.52</v>
       </c>
       <c r="L68" s="18" t="n">
-        <v>0.48</v>
+        <v>257.84</v>
       </c>
       <c r="M68" s="18" t="n">
-        <v>108.92</v>
+        <v>583.86</v>
       </c>
       <c r="N68" s="18" t="n">
-        <v>-84.12</v>
+        <v>-195.63</v>
       </c>
       <c r="O68" s="18" t="n">
-        <v>111.39</v>
+        <v>2416.6</v>
       </c>
       <c r="P68" s="37" t="n">
-        <v>136.67</v>
+        <v>3062.67</v>
       </c>
       <c r="Q68" s="18" t="n">
-        <v>71.73</v>
+        <v>544.73</v>
       </c>
       <c r="R68" s="18" t="n">
-        <v>-192.66</v>
+        <v>-350.44</v>
       </c>
       <c r="S68" s="18" t="n">
-        <v>358.65</v>
+        <v>1754.05</v>
       </c>
       <c r="T68" s="18" t="n">
-        <v>368.83</v>
+        <v>1366.35</v>
       </c>
       <c r="U68" s="37" t="n">
-        <v>606.55</v>
+        <v>3314.69</v>
       </c>
       <c r="V68" s="18" t="n">
-        <v>166.36</v>
+        <v>754.63</v>
       </c>
       <c r="W68" s="18" t="n">
-        <v>111.23</v>
+        <v>467.74</v>
       </c>
       <c r="X68" s="18" t="n">
-        <v>264.39</v>
+        <v>1080.16</v>
       </c>
       <c r="Y68" s="18" t="n">
-        <v>36.69</v>
+        <v>1139.7</v>
       </c>
       <c r="Z68" s="37" t="n">
-        <v>578.67</v>
+        <v>3442.23</v>
       </c>
       <c r="AA68" s="18" t="n">
-        <v>581.84</v>
+        <v>2691.64</v>
       </c>
       <c r="AB68" s="19" t="n">
-        <v>1022.88</v>
+        <v>4911.07</v>
       </c>
       <c r="AC68" s="10" t="n"/>
       <c r="AD68" s="10" t="n"/>
@@ -24964,78 +24895,78 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>당기순이익</t>
+          <t>법인세비용</t>
         </is>
       </c>
       <c r="E69" s="18" t="n">
-        <v>899.66</v>
+        <v>441.05</v>
       </c>
       <c r="F69" s="9" t="n"/>
       <c r="G69" s="18" t="n">
-        <v>171.93</v>
+        <v>28.86</v>
       </c>
       <c r="H69" s="18" t="n">
-        <v>91.75</v>
+        <v>39.86</v>
       </c>
       <c r="I69" s="18" t="n">
-        <v>2468.68</v>
+        <v>699.27</v>
       </c>
       <c r="J69" s="18" t="n">
-        <v>-655.21</v>
+        <v>-405.62</v>
       </c>
       <c r="K69" s="37" t="n">
-        <v>2077.15</v>
+        <v>362.37</v>
       </c>
       <c r="L69" s="18" t="n">
-        <v>258.32</v>
+        <v>0.48</v>
       </c>
       <c r="M69" s="18" t="n">
-        <v>474.94</v>
+        <v>108.92</v>
       </c>
       <c r="N69" s="18" t="n">
-        <v>-111.51</v>
+        <v>-84.12</v>
       </c>
       <c r="O69" s="18" t="n">
-        <v>2305.22</v>
+        <v>111.39</v>
       </c>
       <c r="P69" s="37" t="n">
-        <v>2926.97</v>
+        <v>136.67</v>
       </c>
       <c r="Q69" s="18" t="n">
-        <v>473</v>
+        <v>71.73</v>
       </c>
       <c r="R69" s="18" t="n">
-        <v>9661.48</v>
+        <v>-192.66</v>
       </c>
       <c r="S69" s="18" t="n">
-        <v>1395.4</v>
+        <v>358.65</v>
       </c>
       <c r="T69" s="18" t="n">
-        <v>997.51</v>
+        <v>368.83</v>
       </c>
       <c r="U69" s="37" t="n">
-        <v>12527.39</v>
+        <v>606.55</v>
       </c>
       <c r="V69" s="18" t="n">
-        <v>588.27</v>
+        <v>166.36</v>
       </c>
       <c r="W69" s="18" t="n">
-        <v>356.52</v>
+        <v>111.23</v>
       </c>
       <c r="X69" s="18" t="n">
-        <v>815.77</v>
+        <v>264.39</v>
       </c>
       <c r="Y69" s="18" t="n">
-        <v>1103.01</v>
+        <v>36.69</v>
       </c>
       <c r="Z69" s="37" t="n">
-        <v>2863.57</v>
+        <v>578.67</v>
       </c>
       <c r="AA69" s="18" t="n">
-        <v>2109.8</v>
+        <v>581.84</v>
       </c>
       <c r="AB69" s="19" t="n">
-        <v>3888.19</v>
+        <v>1022.88</v>
       </c>
       <c r="AC69" s="10" t="n"/>
       <c r="AD69" s="10" t="n"/>
@@ -25057,78 +24988,78 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>총포괄손익</t>
+          <t>당기순이익</t>
         </is>
       </c>
       <c r="E70" s="18" t="n">
-        <v>894.97</v>
+        <v>899.66</v>
       </c>
       <c r="F70" s="9" t="n"/>
       <c r="G70" s="18" t="n">
-        <v>701.8</v>
+        <v>171.93</v>
       </c>
       <c r="H70" s="18" t="n">
-        <v>-129.28</v>
+        <v>91.75</v>
       </c>
       <c r="I70" s="18" t="n">
-        <v>2847.47</v>
+        <v>2468.68</v>
       </c>
       <c r="J70" s="18" t="n">
-        <v>-1253.8</v>
+        <v>-655.21</v>
       </c>
       <c r="K70" s="37" t="n">
-        <v>2166.19</v>
+        <v>2077.15</v>
       </c>
       <c r="L70" s="18" t="n">
-        <v>457.55</v>
+        <v>258.32</v>
       </c>
       <c r="M70" s="18" t="n">
-        <v>1513.09</v>
+        <v>474.94</v>
       </c>
       <c r="N70" s="18" t="n">
-        <v>-608.62</v>
+        <v>-111.51</v>
       </c>
       <c r="O70" s="18" t="n">
-        <v>2231.78</v>
+        <v>2305.22</v>
       </c>
       <c r="P70" s="37" t="n">
-        <v>3593.8</v>
+        <v>2926.97</v>
       </c>
       <c r="Q70" s="18" t="n">
-        <v>161.11</v>
+        <v>473</v>
       </c>
       <c r="R70" s="18" t="n">
-        <v>9646.700000000001</v>
+        <v>9661.48</v>
       </c>
       <c r="S70" s="18" t="n">
-        <v>1258.42</v>
+        <v>1395.4</v>
       </c>
       <c r="T70" s="18" t="n">
-        <v>-92.37</v>
+        <v>997.51</v>
       </c>
       <c r="U70" s="37" t="n">
-        <v>10973.86</v>
+        <v>12527.39</v>
       </c>
       <c r="V70" s="18" t="n">
-        <v>606.4</v>
+        <v>588.27</v>
       </c>
       <c r="W70" s="18" t="n">
-        <v>657.77</v>
+        <v>356.52</v>
       </c>
       <c r="X70" s="18" t="n">
-        <v>813.87</v>
+        <v>815.77</v>
       </c>
       <c r="Y70" s="18" t="n">
-        <v>1233.27</v>
+        <v>1103.01</v>
       </c>
       <c r="Z70" s="37" t="n">
-        <v>3311.31</v>
+        <v>2863.57</v>
       </c>
       <c r="AA70" s="18" t="n">
-        <v>2091.86</v>
+        <v>2109.8</v>
       </c>
       <c r="AB70" s="19" t="n">
-        <v>3725.53</v>
+        <v>3888.19</v>
       </c>
       <c r="AC70" s="10" t="n"/>
       <c r="AD70" s="10" t="n"/>
@@ -25150,78 +25081,78 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>(지배주주지분)당기순이익</t>
+          <t>총포괄손익</t>
         </is>
       </c>
       <c r="E71" s="18" t="n">
-        <v>899.66</v>
+        <v>894.97</v>
       </c>
       <c r="F71" s="9" t="n"/>
       <c r="G71" s="18" t="n">
-        <v>171.93</v>
+        <v>701.8</v>
       </c>
       <c r="H71" s="18" t="n">
-        <v>91.75</v>
+        <v>-129.28</v>
       </c>
       <c r="I71" s="18" t="n">
-        <v>2468.68</v>
+        <v>2847.47</v>
       </c>
       <c r="J71" s="18" t="n">
-        <v>-655.21</v>
+        <v>-1253.8</v>
       </c>
       <c r="K71" s="37" t="n">
-        <v>2077.15</v>
+        <v>2166.19</v>
       </c>
       <c r="L71" s="18" t="n">
-        <v>258.32</v>
+        <v>457.55</v>
       </c>
       <c r="M71" s="18" t="n">
-        <v>474.94</v>
+        <v>1513.09</v>
       </c>
       <c r="N71" s="18" t="n">
-        <v>-111.51</v>
+        <v>-608.62</v>
       </c>
       <c r="O71" s="18" t="n">
-        <v>2305.22</v>
+        <v>2231.78</v>
       </c>
       <c r="P71" s="37" t="n">
-        <v>2926.97</v>
+        <v>3593.8</v>
       </c>
       <c r="Q71" s="18" t="n">
-        <v>473</v>
+        <v>161.11</v>
       </c>
       <c r="R71" s="18" t="n">
-        <v>9661.48</v>
+        <v>9646.700000000001</v>
       </c>
       <c r="S71" s="18" t="n">
-        <v>1395.4</v>
+        <v>1258.42</v>
       </c>
       <c r="T71" s="18" t="n">
-        <v>997.51</v>
+        <v>-92.37</v>
       </c>
       <c r="U71" s="37" t="n">
-        <v>12527.39</v>
+        <v>10973.86</v>
       </c>
       <c r="V71" s="18" t="n">
-        <v>588.27</v>
+        <v>606.4</v>
       </c>
       <c r="W71" s="18" t="n">
-        <v>356.52</v>
+        <v>657.77</v>
       </c>
       <c r="X71" s="18" t="n">
-        <v>815.77</v>
+        <v>813.87</v>
       </c>
       <c r="Y71" s="18" t="n">
-        <v>1103.01</v>
+        <v>1233.27</v>
       </c>
       <c r="Z71" s="37" t="n">
-        <v>2863.57</v>
+        <v>3311.31</v>
       </c>
       <c r="AA71" s="18" t="n">
-        <v>2109.8</v>
+        <v>2091.86</v>
       </c>
       <c r="AB71" s="19" t="n">
-        <v>3888.19</v>
+        <v>3725.53</v>
       </c>
       <c r="AC71" s="10" t="n"/>
       <c r="AD71" s="10" t="n"/>
@@ -25243,7 +25174,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>계속사업이익</t>
+          <t>(지배주주지분)당기순이익</t>
         </is>
       </c>
       <c r="E72" s="18" t="n">
@@ -25284,7 +25215,7 @@
         <v>473</v>
       </c>
       <c r="R72" s="18" t="n">
-        <v>-157.78</v>
+        <v>9661.48</v>
       </c>
       <c r="S72" s="18" t="n">
         <v>1395.4</v>
@@ -25293,7 +25224,7 @@
         <v>997.51</v>
       </c>
       <c r="U72" s="37" t="n">
-        <v>2708.13</v>
+        <v>12527.39</v>
       </c>
       <c r="V72" s="18" t="n">
         <v>588.27</v>
@@ -25336,38 +25267,79 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>중단사업이익</t>
-        </is>
+          <t>계속사업이익</t>
+        </is>
+      </c>
+      <c r="E73" s="18" t="n">
+        <v>899.66</v>
       </c>
       <c r="F73" s="9" t="n"/>
-      <c r="K73" s="9" t="n"/>
-      <c r="P73" s="9" t="n"/>
+      <c r="G73" s="18" t="n">
+        <v>171.93</v>
+      </c>
+      <c r="H73" s="18" t="n">
+        <v>91.75</v>
+      </c>
+      <c r="I73" s="18" t="n">
+        <v>2468.68</v>
+      </c>
+      <c r="J73" s="18" t="n">
+        <v>-655.21</v>
+      </c>
+      <c r="K73" s="37" t="n">
+        <v>2077.15</v>
+      </c>
+      <c r="L73" s="18" t="n">
+        <v>258.32</v>
+      </c>
+      <c r="M73" s="18" t="n">
+        <v>474.94</v>
+      </c>
+      <c r="N73" s="18" t="n">
+        <v>-111.51</v>
+      </c>
+      <c r="O73" s="18" t="n">
+        <v>2305.22</v>
+      </c>
+      <c r="P73" s="37" t="n">
+        <v>2926.97</v>
+      </c>
+      <c r="Q73" s="18" t="n">
+        <v>473</v>
+      </c>
       <c r="R73" s="18" t="n">
-        <v>9819.26</v>
+        <v>-157.78</v>
       </c>
       <c r="S73" s="18" t="n">
-        <v>0</v>
+        <v>1395.4</v>
       </c>
       <c r="T73" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U73" s="9" t="n"/>
+        <v>997.51</v>
+      </c>
+      <c r="U73" s="37" t="n">
+        <v>2708.13</v>
+      </c>
       <c r="V73" s="18" t="n">
-        <v>0</v>
+        <v>588.27</v>
       </c>
       <c r="W73" s="18" t="n">
-        <v>0</v>
+        <v>356.52</v>
       </c>
       <c r="X73" s="18" t="n">
-        <v>0</v>
+        <v>815.77</v>
       </c>
       <c r="Y73" s="18" t="n">
-        <v>0</v>
+        <v>1103.01</v>
       </c>
       <c r="Z73" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB73" s="5" t="n"/>
+        <v>2863.57</v>
+      </c>
+      <c r="AA73" s="18" t="n">
+        <v>2109.8</v>
+      </c>
+      <c r="AB73" s="19" t="n">
+        <v>3888.19</v>
+      </c>
       <c r="AC73" s="10" t="n"/>
       <c r="AD73" s="10" t="n"/>
       <c r="AE73" s="11" t="n"/>
@@ -25388,79 +25360,38 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>영업활동으로인한현금흐름</t>
-        </is>
-      </c>
-      <c r="E74" s="18" t="n">
-        <v>2321</v>
+          <t>이자수익</t>
+        </is>
       </c>
       <c r="F74" s="9" t="n"/>
       <c r="G74" s="18" t="n">
-        <v>-412.48</v>
+        <v>290.96</v>
       </c>
       <c r="H74" s="18" t="n">
-        <v>-1721.65</v>
+        <v>8.59</v>
       </c>
       <c r="I74" s="18" t="n">
-        <v>663.91</v>
+        <v>327.9</v>
       </c>
       <c r="J74" s="18" t="n">
-        <v>173.06</v>
+        <v>43.26</v>
       </c>
       <c r="K74" s="37" t="n">
-        <v>-1297.16</v>
+        <v>670.71</v>
       </c>
       <c r="L74" s="18" t="n">
-        <v>3487.06</v>
+        <v>306.96</v>
       </c>
       <c r="M74" s="18" t="n">
-        <v>1968.24</v>
+        <v>19.84</v>
       </c>
       <c r="N74" s="18" t="n">
-        <v>2172</v>
-      </c>
-      <c r="O74" s="18" t="n">
-        <v>-225.58</v>
-      </c>
-      <c r="P74" s="37" t="n">
-        <v>7401.72</v>
-      </c>
-      <c r="Q74" s="18" t="n">
-        <v>1531.45</v>
-      </c>
-      <c r="R74" s="18" t="n">
-        <v>99.58</v>
-      </c>
-      <c r="S74" s="18" t="n">
-        <v>175.05</v>
-      </c>
-      <c r="T74" s="18" t="n">
-        <v>3188.89</v>
-      </c>
-      <c r="U74" s="37" t="n">
-        <v>4994.97</v>
-      </c>
-      <c r="V74" s="18" t="n">
-        <v>-1993.48</v>
-      </c>
-      <c r="W74" s="18" t="n">
-        <v>-566.6900000000001</v>
-      </c>
-      <c r="X74" s="18" t="n">
-        <v>732.96</v>
-      </c>
-      <c r="Y74" s="18" t="n">
-        <v>-1156.94</v>
-      </c>
-      <c r="Z74" s="37" t="n">
-        <v>-2984.15</v>
-      </c>
-      <c r="AA74" s="18" t="n">
-        <v>893.5599999999999</v>
-      </c>
-      <c r="AB74" s="19" t="n">
-        <v>2185.69</v>
-      </c>
+        <v>375.53</v>
+      </c>
+      <c r="P74" s="9" t="n"/>
+      <c r="U74" s="9" t="n"/>
+      <c r="Z74" s="9" t="n"/>
+      <c r="AB74" s="5" t="n"/>
       <c r="AC74" s="10" t="n"/>
       <c r="AD74" s="10" t="n"/>
       <c r="AE74" s="11" t="n"/>
@@ -25481,79 +25412,38 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>법인세납부(CF)</t>
-        </is>
-      </c>
-      <c r="E75" s="18" t="n">
-        <v>3.47</v>
+          <t>이자비용</t>
+        </is>
       </c>
       <c r="F75" s="9" t="n"/>
       <c r="G75" s="18" t="n">
-        <v>-223.48</v>
+        <v>119.87</v>
       </c>
       <c r="H75" s="18" t="n">
-        <v>-223.35</v>
+        <v>128.62</v>
       </c>
       <c r="I75" s="18" t="n">
-        <v>-190.36</v>
+        <v>137.06</v>
       </c>
       <c r="J75" s="18" t="n">
-        <v>-3.89</v>
+        <v>188.19</v>
       </c>
       <c r="K75" s="37" t="n">
-        <v>-641.08</v>
+        <v>573.74</v>
       </c>
       <c r="L75" s="18" t="n">
-        <v>-98.59999999999999</v>
+        <v>210.24</v>
       </c>
       <c r="M75" s="18" t="n">
-        <v>-137.38</v>
+        <v>212.08</v>
       </c>
       <c r="N75" s="18" t="n">
-        <v>-96.91</v>
-      </c>
-      <c r="O75" s="18" t="n">
-        <v>-109.66</v>
-      </c>
-      <c r="P75" s="37" t="n">
-        <v>-442.55</v>
-      </c>
-      <c r="Q75" s="18" t="n">
-        <v>-38.48</v>
-      </c>
-      <c r="R75" s="18" t="n">
-        <v>-66.68000000000001</v>
-      </c>
-      <c r="S75" s="18" t="n">
-        <v>-78.53</v>
-      </c>
-      <c r="T75" s="18" t="n">
-        <v>-94.28</v>
-      </c>
-      <c r="U75" s="37" t="n">
-        <v>-277.97</v>
-      </c>
-      <c r="V75" s="18" t="n">
-        <v>-1365.97</v>
-      </c>
-      <c r="W75" s="18" t="n">
-        <v>-1653.54</v>
-      </c>
-      <c r="X75" s="18" t="n">
-        <v>-158.62</v>
-      </c>
-      <c r="Y75" s="18" t="n">
-        <v>-5.86</v>
-      </c>
-      <c r="Z75" s="37" t="n">
-        <v>-3183.99</v>
-      </c>
-      <c r="AA75" s="18" t="n">
-        <v>-4.41</v>
-      </c>
-      <c r="AB75" s="19" t="n">
-        <v>-181.89</v>
-      </c>
+        <v>197.09</v>
+      </c>
+      <c r="P75" s="9" t="n"/>
+      <c r="U75" s="9" t="n"/>
+      <c r="Z75" s="9" t="n"/>
+      <c r="AB75" s="5" t="n"/>
       <c r="AC75" s="10" t="n"/>
       <c r="AD75" s="10" t="n"/>
       <c r="AE75" s="11" t="n"/>
@@ -25574,79 +25464,38 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>투자활동으로인한현금흐름</t>
-        </is>
-      </c>
-      <c r="E76" s="18" t="n">
-        <v>-4084.14</v>
+          <t>외환차익</t>
+        </is>
       </c>
       <c r="F76" s="9" t="n"/>
       <c r="G76" s="18" t="n">
-        <v>-8356.459999999999</v>
+        <v>66.47</v>
       </c>
       <c r="H76" s="18" t="n">
-        <v>-2005.49</v>
+        <v>74.64</v>
       </c>
       <c r="I76" s="18" t="n">
-        <v>-461.31</v>
+        <v>471.82</v>
       </c>
       <c r="J76" s="18" t="n">
-        <v>-121.99</v>
+        <v>70.03</v>
       </c>
       <c r="K76" s="37" t="n">
-        <v>-10945.25</v>
+        <v>682.96</v>
       </c>
       <c r="L76" s="18" t="n">
-        <v>1.18</v>
+        <v>74.52</v>
       </c>
       <c r="M76" s="18" t="n">
-        <v>10.15</v>
+        <v>110.91</v>
       </c>
       <c r="N76" s="18" t="n">
-        <v>27.85</v>
-      </c>
-      <c r="O76" s="18" t="n">
-        <v>535.66</v>
-      </c>
-      <c r="P76" s="37" t="n">
-        <v>574.84</v>
-      </c>
-      <c r="Q76" s="18" t="n">
-        <v>-62.75</v>
-      </c>
-      <c r="R76" s="18" t="n">
-        <v>12380.62</v>
-      </c>
-      <c r="S76" s="18" t="n">
-        <v>108.33</v>
-      </c>
-      <c r="T76" s="18" t="n">
-        <v>1673.19</v>
-      </c>
-      <c r="U76" s="37" t="n">
-        <v>14099.39</v>
-      </c>
-      <c r="V76" s="18" t="n">
-        <v>-3.73</v>
-      </c>
-      <c r="W76" s="18" t="n">
-        <v>-870.0700000000001</v>
-      </c>
-      <c r="X76" s="18" t="n">
-        <v>-5954.62</v>
-      </c>
-      <c r="Y76" s="18" t="n">
-        <v>-4217.95</v>
-      </c>
-      <c r="Z76" s="37" t="n">
-        <v>-11046.37</v>
-      </c>
-      <c r="AA76" s="18" t="n">
-        <v>-4409.66</v>
-      </c>
-      <c r="AB76" s="19" t="n">
-        <v>-8327.719999999999</v>
-      </c>
+        <v>57.86</v>
+      </c>
+      <c r="P76" s="9" t="n"/>
+      <c r="U76" s="9" t="n"/>
+      <c r="Z76" s="9" t="n"/>
+      <c r="AB76" s="5" t="n"/>
       <c r="AC76" s="10" t="n"/>
       <c r="AD76" s="10" t="n"/>
       <c r="AE76" s="11" t="n"/>
@@ -25667,73 +25516,37 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>유형자산의증가</t>
-        </is>
-      </c>
-      <c r="E77" s="18" t="n">
-        <v>88.58</v>
+          <t>외환차손</t>
+        </is>
       </c>
       <c r="F77" s="9" t="n"/>
       <c r="G77" s="18" t="n">
-        <v>8979.09</v>
+        <v>3.96</v>
       </c>
       <c r="H77" s="18" t="n">
-        <v>1440.99</v>
+        <v>21.49</v>
       </c>
       <c r="I77" s="18" t="n">
-        <v>564.11</v>
+        <v>23.99</v>
       </c>
       <c r="J77" s="18" t="n">
-        <v>96.54000000000001</v>
+        <v>75.83</v>
       </c>
       <c r="K77" s="37" t="n">
-        <v>11080.73</v>
+        <v>125.27</v>
       </c>
       <c r="L77" s="18" t="n">
-        <v>1.8</v>
+        <v>26.49</v>
       </c>
       <c r="M77" s="18" t="n">
-        <v>36.57</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="N77" s="18" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="O77" s="18" t="n">
-        <v>5.37</v>
-      </c>
-      <c r="P77" s="37" t="n">
-        <v>47.14</v>
-      </c>
-      <c r="Q77" s="18" t="n">
-        <v>10.05</v>
-      </c>
-      <c r="R77" s="18" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="S77" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T77" s="18" t="n">
-        <v>9.81</v>
-      </c>
-      <c r="U77" s="37" t="n">
-        <v>20.76</v>
-      </c>
-      <c r="V77" s="18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W77" s="18" t="n">
-        <v>3.81</v>
-      </c>
-      <c r="X77" s="18" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="Y77" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z77" s="37" t="n">
-        <v>7.63</v>
-      </c>
+        <v>12.45</v>
+      </c>
+      <c r="P77" s="9" t="n"/>
+      <c r="U77" s="9" t="n"/>
+      <c r="Z77" s="9" t="n"/>
       <c r="AB77" s="5" t="n"/>
       <c r="AC77" s="10" t="n"/>
       <c r="AD77" s="10" t="n"/>
@@ -25755,73 +25568,37 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>CAPEX</t>
-        </is>
-      </c>
-      <c r="E78" s="18" t="n">
-        <v>138.08</v>
+          <t>외화환산이익</t>
+        </is>
       </c>
       <c r="F78" s="9" t="n"/>
       <c r="G78" s="18" t="n">
-        <v>8979.09</v>
+        <v>64.81999999999999</v>
       </c>
       <c r="H78" s="18" t="n">
-        <v>1446.49</v>
+        <v>196.66</v>
       </c>
       <c r="I78" s="18" t="n">
-        <v>564.11</v>
+        <v>-30.78</v>
       </c>
       <c r="J78" s="18" t="n">
-        <v>125.29</v>
+        <v>-224.21</v>
       </c>
       <c r="K78" s="37" t="n">
-        <v>11114.98</v>
+        <v>6.49</v>
       </c>
       <c r="L78" s="18" t="n">
-        <v>1.8</v>
+        <v>112.93</v>
       </c>
       <c r="M78" s="18" t="n">
-        <v>36.57</v>
+        <v>-36.1</v>
       </c>
       <c r="N78" s="18" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="O78" s="18" t="n">
-        <v>5.37</v>
-      </c>
-      <c r="P78" s="37" t="n">
-        <v>47.14</v>
-      </c>
-      <c r="Q78" s="18" t="n">
-        <v>10.05</v>
-      </c>
-      <c r="R78" s="18" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="S78" s="18" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="T78" s="18" t="n">
-        <v>9.81</v>
-      </c>
-      <c r="U78" s="37" t="n">
-        <v>27.36</v>
-      </c>
-      <c r="V78" s="18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W78" s="18" t="n">
-        <v>3.81</v>
-      </c>
-      <c r="X78" s="18" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="Y78" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z78" s="37" t="n">
-        <v>7.63</v>
-      </c>
+        <v>37.12</v>
+      </c>
+      <c r="P78" s="9" t="n"/>
+      <c r="U78" s="9" t="n"/>
+      <c r="Z78" s="9" t="n"/>
       <c r="AB78" s="5" t="n"/>
       <c r="AC78" s="10" t="n"/>
       <c r="AD78" s="10" t="n"/>
@@ -25843,50 +25620,36 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>무형자산의증가</t>
-        </is>
-      </c>
-      <c r="E79" s="18" t="n">
-        <v>49.5</v>
+          <t>외화환산손실</t>
+        </is>
       </c>
       <c r="F79" s="9" t="n"/>
       <c r="G79" s="18" t="n">
-        <v>0</v>
+        <v>6.83</v>
       </c>
       <c r="H79" s="18" t="n">
-        <v>5.5</v>
+        <v>3</v>
       </c>
       <c r="I79" s="18" t="n">
-        <v>0</v>
+        <v>13.78</v>
       </c>
       <c r="J79" s="18" t="n">
-        <v>28.75</v>
+        <v>190.65</v>
       </c>
       <c r="K79" s="37" t="n">
-        <v>34.25</v>
+        <v>214.26</v>
       </c>
       <c r="L79" s="18" t="n">
-        <v>0</v>
+        <v>5.24</v>
       </c>
       <c r="M79" s="18" t="n">
-        <v>0</v>
+        <v>0.28</v>
       </c>
       <c r="N79" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O79" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P79" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="T79" s="18" t="n">
-        <v>0</v>
-      </c>
+        <v>0.91</v>
+      </c>
+      <c r="P79" s="9" t="n"/>
       <c r="U79" s="9" t="n"/>
-      <c r="Y79" s="18" t="n">
-        <v>0</v>
-      </c>
       <c r="Z79" s="9" t="n"/>
       <c r="AB79" s="5" t="n"/>
       <c r="AC79" s="10" t="n"/>
@@ -25909,79 +25672,38 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>재무활동으로인한현금흐름</t>
-        </is>
-      </c>
-      <c r="E80" s="18" t="n">
-        <v>4429.12</v>
+          <t>이자손익</t>
+        </is>
       </c>
       <c r="F80" s="9" t="n"/>
       <c r="G80" s="18" t="n">
-        <v>8184.3</v>
+        <v>171.09</v>
       </c>
       <c r="H80" s="18" t="n">
-        <v>-280.37</v>
+        <v>-120.03</v>
       </c>
       <c r="I80" s="18" t="n">
-        <v>502.48</v>
+        <v>190.84</v>
       </c>
       <c r="J80" s="18" t="n">
-        <v>-200.14</v>
+        <v>-144.93</v>
       </c>
       <c r="K80" s="37" t="n">
-        <v>8206.27</v>
+        <v>96.97</v>
       </c>
       <c r="L80" s="18" t="n">
-        <v>-8.92</v>
+        <v>96.72</v>
       </c>
       <c r="M80" s="18" t="n">
-        <v>-708.3</v>
+        <v>-192.24</v>
       </c>
       <c r="N80" s="18" t="n">
-        <v>-8.51</v>
-      </c>
-      <c r="O80" s="18" t="n">
-        <v>-8.74</v>
-      </c>
-      <c r="P80" s="37" t="n">
-        <v>-734.47</v>
-      </c>
-      <c r="Q80" s="18" t="n">
-        <v>-217.37</v>
-      </c>
-      <c r="R80" s="18" t="n">
-        <v>-570.87</v>
-      </c>
-      <c r="S80" s="18" t="n">
-        <v>1413.06</v>
-      </c>
-      <c r="T80" s="18" t="n">
-        <v>-99.08</v>
-      </c>
-      <c r="U80" s="37" t="n">
-        <v>525.74</v>
-      </c>
-      <c r="V80" s="18" t="n">
-        <v>-7.87</v>
-      </c>
-      <c r="W80" s="18" t="n">
-        <v>1995.35</v>
-      </c>
-      <c r="X80" s="18" t="n">
-        <v>1495.46</v>
-      </c>
-      <c r="Y80" s="18" t="n">
-        <v>-4.19</v>
-      </c>
-      <c r="Z80" s="37" t="n">
-        <v>3478.75</v>
-      </c>
-      <c r="AA80" s="18" t="n">
-        <v>-4.28</v>
-      </c>
-      <c r="AB80" s="19" t="n">
-        <v>-3.31</v>
-      </c>
+        <v>178.44</v>
+      </c>
+      <c r="P80" s="9" t="n"/>
+      <c r="U80" s="9" t="n"/>
+      <c r="Z80" s="9" t="n"/>
+      <c r="AB80" s="5" t="n"/>
       <c r="AC80" s="10" t="n"/>
       <c r="AD80" s="10" t="n"/>
       <c r="AE80" s="11" t="n"/>
@@ -26002,79 +25724,30 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>리스부채의상환</t>
-        </is>
-      </c>
-      <c r="E81" s="18" t="n">
-        <v>440.69</v>
+          <t>배당금수익</t>
+        </is>
       </c>
       <c r="F81" s="9" t="n"/>
-      <c r="G81" s="18" t="n">
-        <v>186.92</v>
-      </c>
       <c r="H81" s="18" t="n">
-        <v>194.16</v>
+        <v>0.51</v>
       </c>
       <c r="I81" s="18" t="n">
-        <v>197.52</v>
+        <v>0</v>
       </c>
       <c r="J81" s="18" t="n">
-        <v>200.14</v>
-      </c>
-      <c r="K81" s="37" t="n">
-        <v>778.74</v>
-      </c>
-      <c r="L81" s="18" t="n">
-        <v>8.92</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K81" s="9" t="n"/>
       <c r="M81" s="18" t="n">
-        <v>8.300000000000001</v>
+        <v>57.81</v>
       </c>
       <c r="N81" s="18" t="n">
-        <v>8.51</v>
-      </c>
-      <c r="O81" s="18" t="n">
-        <v>8.74</v>
-      </c>
-      <c r="P81" s="37" t="n">
-        <v>34.47</v>
-      </c>
-      <c r="Q81" s="18" t="n">
-        <v>8.960000000000001</v>
-      </c>
-      <c r="R81" s="18" t="n">
-        <v>8.220000000000001</v>
-      </c>
-      <c r="S81" s="18" t="n">
-        <v>7.61</v>
-      </c>
-      <c r="T81" s="18" t="n">
-        <v>7.56</v>
-      </c>
-      <c r="U81" s="37" t="n">
-        <v>32.35</v>
-      </c>
-      <c r="V81" s="18" t="n">
-        <v>7.87</v>
-      </c>
-      <c r="W81" s="18" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="X81" s="18" t="n">
-        <v>4.54</v>
-      </c>
-      <c r="Y81" s="18" t="n">
-        <v>4.19</v>
-      </c>
-      <c r="Z81" s="37" t="n">
-        <v>21.25</v>
-      </c>
-      <c r="AA81" s="18" t="n">
-        <v>4.28</v>
-      </c>
-      <c r="AB81" s="19" t="n">
-        <v>3.31</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P81" s="9" t="n"/>
+      <c r="U81" s="9" t="n"/>
+      <c r="Z81" s="9" t="n"/>
+      <c r="AB81" s="5" t="n"/>
       <c r="AC81" s="10" t="n"/>
       <c r="AD81" s="10" t="n"/>
       <c r="AE81" s="11" t="n"/>
@@ -26095,42 +25768,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>단기차입금의감소</t>
-        </is>
-      </c>
-      <c r="E82" s="18" t="n">
-        <v>0</v>
+          <t>중단사업이익</t>
+        </is>
       </c>
       <c r="F82" s="9" t="n"/>
-      <c r="G82" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H82" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I82" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J82" s="18" t="n">
-        <v>1200</v>
-      </c>
-      <c r="K82" s="37" t="n">
-        <v>1200</v>
-      </c>
-      <c r="L82" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M82" s="18" t="n">
-        <v>700</v>
-      </c>
-      <c r="N82" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O82" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P82" s="37" t="n">
-        <v>700</v>
+      <c r="K82" s="9" t="n"/>
+      <c r="P82" s="9" t="n"/>
+      <c r="R82" s="18" t="n">
+        <v>9819.26</v>
       </c>
       <c r="S82" s="18" t="n">
         <v>0</v>
@@ -26139,13 +25784,22 @@
         <v>0</v>
       </c>
       <c r="U82" s="9" t="n"/>
-      <c r="Z82" s="9" t="n"/>
-      <c r="AA82" s="18" t="n">
-        <v>2000</v>
-      </c>
-      <c r="AB82" s="19" t="n">
+      <c r="V82" s="18" t="n">
         <v>0</v>
       </c>
+      <c r="W82" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X82" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y82" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z82" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB82" s="5" t="n"/>
       <c r="AC82" s="10" t="n"/>
       <c r="AD82" s="10" t="n"/>
       <c r="AE82" s="11" t="n"/>
@@ -26166,52 +25820,79 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>유동성장기부채의감소</t>
+          <t>영업활동으로인한현금흐름</t>
         </is>
       </c>
       <c r="E83" s="18" t="n">
-        <v>128.13</v>
+        <v>2321</v>
       </c>
       <c r="F83" s="9" t="n"/>
       <c r="G83" s="18" t="n">
-        <v>128.78</v>
+        <v>-412.48</v>
       </c>
       <c r="H83" s="18" t="n">
-        <v>86.20999999999999</v>
+        <v>-1721.65</v>
       </c>
       <c r="I83" s="18" t="n">
-        <v>0</v>
+        <v>663.91</v>
       </c>
       <c r="J83" s="18" t="n">
-        <v>0</v>
+        <v>173.06</v>
       </c>
       <c r="K83" s="37" t="n">
-        <v>214.99</v>
+        <v>-1297.16</v>
       </c>
       <c r="L83" s="18" t="n">
-        <v>0</v>
+        <v>3487.06</v>
       </c>
       <c r="M83" s="18" t="n">
-        <v>1600</v>
+        <v>1968.24</v>
       </c>
       <c r="N83" s="18" t="n">
-        <v>0</v>
+        <v>2172</v>
       </c>
       <c r="O83" s="18" t="n">
-        <v>0</v>
+        <v>-225.58</v>
       </c>
       <c r="P83" s="37" t="n">
-        <v>1600</v>
+        <v>7401.72</v>
+      </c>
+      <c r="Q83" s="18" t="n">
+        <v>1531.45</v>
+      </c>
+      <c r="R83" s="18" t="n">
+        <v>99.58</v>
       </c>
       <c r="S83" s="18" t="n">
-        <v>0</v>
+        <v>175.05</v>
       </c>
       <c r="T83" s="18" t="n">
-        <v>1896.04</v>
-      </c>
-      <c r="U83" s="9" t="n"/>
-      <c r="Z83" s="9" t="n"/>
-      <c r="AB83" s="5" t="n"/>
+        <v>3188.89</v>
+      </c>
+      <c r="U83" s="37" t="n">
+        <v>4994.97</v>
+      </c>
+      <c r="V83" s="18" t="n">
+        <v>-1993.48</v>
+      </c>
+      <c r="W83" s="18" t="n">
+        <v>-566.6900000000001</v>
+      </c>
+      <c r="X83" s="18" t="n">
+        <v>732.96</v>
+      </c>
+      <c r="Y83" s="18" t="n">
+        <v>-1156.94</v>
+      </c>
+      <c r="Z83" s="37" t="n">
+        <v>-2984.15</v>
+      </c>
+      <c r="AA83" s="18" t="n">
+        <v>893.5599999999999</v>
+      </c>
+      <c r="AB83" s="19" t="n">
+        <v>2185.69</v>
+      </c>
       <c r="AC83" s="10" t="n"/>
       <c r="AD83" s="10" t="n"/>
       <c r="AE83" s="11" t="n"/>
@@ -26232,66 +25913,79 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>장기차입금의감소</t>
+          <t>법인세납부(CF)</t>
         </is>
       </c>
       <c r="E84" s="18" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="F84" s="9" t="n"/>
       <c r="G84" s="18" t="n">
-        <v>0</v>
+        <v>-223.48</v>
       </c>
       <c r="H84" s="18" t="n">
-        <v>0</v>
+        <v>-223.35</v>
       </c>
       <c r="I84" s="18" t="n">
-        <v>0</v>
+        <v>-190.36</v>
       </c>
       <c r="J84" s="18" t="n">
-        <v>0</v>
+        <v>-3.89</v>
       </c>
       <c r="K84" s="37" t="n">
-        <v>0</v>
+        <v>-641.08</v>
       </c>
       <c r="L84" s="18" t="n">
-        <v>0</v>
+        <v>-98.59999999999999</v>
       </c>
       <c r="M84" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P84" s="9" t="n"/>
+        <v>-137.38</v>
+      </c>
+      <c r="N84" s="18" t="n">
+        <v>-96.91</v>
+      </c>
+      <c r="O84" s="18" t="n">
+        <v>-109.66</v>
+      </c>
+      <c r="P84" s="37" t="n">
+        <v>-442.55</v>
+      </c>
       <c r="Q84" s="18" t="n">
-        <v>208.41</v>
+        <v>-38.48</v>
       </c>
       <c r="R84" s="18" t="n">
-        <v>562.65</v>
+        <v>-66.68000000000001</v>
       </c>
       <c r="S84" s="18" t="n">
-        <v>4937.42</v>
+        <v>-78.53</v>
       </c>
       <c r="T84" s="18" t="n">
-        <v>5895.48</v>
+        <v>-94.28</v>
       </c>
       <c r="U84" s="37" t="n">
-        <v>11603.96</v>
+        <v>-277.97</v>
       </c>
       <c r="V84" s="18" t="n">
-        <v>0</v>
+        <v>-1365.97</v>
       </c>
       <c r="W84" s="18" t="n">
-        <v>0</v>
+        <v>-1653.54</v>
       </c>
       <c r="X84" s="18" t="n">
-        <v>0</v>
+        <v>-158.62</v>
       </c>
       <c r="Y84" s="18" t="n">
-        <v>0</v>
+        <v>-5.86</v>
       </c>
       <c r="Z84" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB84" s="5" t="n"/>
+        <v>-3183.99</v>
+      </c>
+      <c r="AA84" s="18" t="n">
+        <v>-4.41</v>
+      </c>
+      <c r="AB84" s="19" t="n">
+        <v>-181.89</v>
+      </c>
       <c r="AC84" s="10" t="n"/>
       <c r="AD84" s="10" t="n"/>
       <c r="AE84" s="11" t="n"/>
@@ -26312,78 +26006,78 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>현금및현금성자산의증감</t>
+          <t>투자활동으로인한현금흐름</t>
         </is>
       </c>
       <c r="E85" s="18" t="n">
-        <v>2659.61</v>
+        <v>-4084.14</v>
       </c>
       <c r="F85" s="9" t="n"/>
       <c r="G85" s="18" t="n">
-        <v>-588.76</v>
+        <v>-8356.459999999999</v>
       </c>
       <c r="H85" s="18" t="n">
-        <v>-3984.35</v>
+        <v>-2005.49</v>
       </c>
       <c r="I85" s="18" t="n">
-        <v>686.47</v>
+        <v>-461.31</v>
       </c>
       <c r="J85" s="18" t="n">
-        <v>-157.62</v>
+        <v>-121.99</v>
       </c>
       <c r="K85" s="37" t="n">
-        <v>-4044.26</v>
+        <v>-10945.25</v>
       </c>
       <c r="L85" s="18" t="n">
-        <v>3535.35</v>
+        <v>1.18</v>
       </c>
       <c r="M85" s="18" t="n">
-        <v>1218.95</v>
+        <v>10.15</v>
       </c>
       <c r="N85" s="18" t="n">
-        <v>2287.49</v>
+        <v>27.85</v>
       </c>
       <c r="O85" s="18" t="n">
-        <v>151.12</v>
+        <v>535.66</v>
       </c>
       <c r="P85" s="37" t="n">
-        <v>7192.91</v>
+        <v>574.84</v>
       </c>
       <c r="Q85" s="18" t="n">
-        <v>1265.84</v>
+        <v>-62.75</v>
       </c>
       <c r="R85" s="18" t="n">
-        <v>11894.81</v>
+        <v>12380.62</v>
       </c>
       <c r="S85" s="18" t="n">
-        <v>1682.98</v>
+        <v>108.33</v>
       </c>
       <c r="T85" s="18" t="n">
-        <v>4775.1</v>
+        <v>1673.19</v>
       </c>
       <c r="U85" s="37" t="n">
-        <v>19618.73</v>
+        <v>14099.39</v>
       </c>
       <c r="V85" s="18" t="n">
-        <v>-2002.29</v>
+        <v>-3.73</v>
       </c>
       <c r="W85" s="18" t="n">
-        <v>534.91</v>
+        <v>-870.0700000000001</v>
       </c>
       <c r="X85" s="18" t="n">
-        <v>-3705.3</v>
+        <v>-5954.62</v>
       </c>
       <c r="Y85" s="18" t="n">
-        <v>-5379.09</v>
+        <v>-4217.95</v>
       </c>
       <c r="Z85" s="37" t="n">
-        <v>-10551.77</v>
+        <v>-11046.37</v>
       </c>
       <c r="AA85" s="18" t="n">
-        <v>-3520.38</v>
+        <v>-4409.66</v>
       </c>
       <c r="AB85" s="19" t="n">
-        <v>-6145.34</v>
+        <v>-8327.719999999999</v>
       </c>
       <c r="AC85" s="10" t="n"/>
       <c r="AD85" s="10" t="n"/>
@@ -26405,79 +26099,74 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>기말현금및현금성자산</t>
+          <t>유형자산의증가</t>
         </is>
       </c>
       <c r="E86" s="18" t="n">
-        <v>2659.61</v>
+        <v>88.58</v>
       </c>
       <c r="F86" s="9" t="n"/>
       <c r="G86" s="18" t="n">
-        <v>5308.01</v>
+        <v>8979.09</v>
       </c>
       <c r="H86" s="18" t="n">
-        <v>-3984.35</v>
+        <v>1440.99</v>
       </c>
       <c r="I86" s="18" t="n">
-        <v>686.47</v>
+        <v>564.11</v>
       </c>
       <c r="J86" s="18" t="n">
-        <v>-157.62</v>
+        <v>96.54000000000001</v>
       </c>
       <c r="K86" s="37" t="n">
-        <v>1852.51</v>
+        <v>11080.73</v>
       </c>
       <c r="L86" s="18" t="n">
-        <v>5387.86</v>
+        <v>1.8</v>
       </c>
       <c r="M86" s="18" t="n">
-        <v>1218.96</v>
+        <v>36.57</v>
       </c>
       <c r="N86" s="18" t="n">
-        <v>2287.48</v>
+        <v>3.4</v>
       </c>
       <c r="O86" s="18" t="n">
-        <v>151.13</v>
+        <v>5.37</v>
       </c>
       <c r="P86" s="37" t="n">
-        <v>9045.43</v>
+        <v>47.14</v>
       </c>
       <c r="Q86" s="18" t="n">
-        <v>10311.27</v>
+        <v>10.05</v>
       </c>
       <c r="R86" s="18" t="n">
-        <v>11894.81</v>
+        <v>0.9</v>
       </c>
       <c r="S86" s="18" t="n">
-        <v>1682.97</v>
+        <v>0</v>
       </c>
       <c r="T86" s="18" t="n">
-        <v>4775.11</v>
+        <v>9.81</v>
       </c>
       <c r="U86" s="37" t="n">
-        <v>28664.16</v>
+        <v>20.76</v>
       </c>
       <c r="V86" s="18" t="n">
-        <v>26661.87</v>
+        <v>1.5</v>
       </c>
       <c r="W86" s="18" t="n">
-        <v>534.91</v>
+        <v>3.81</v>
       </c>
       <c r="X86" s="18" t="n">
-        <v>-3705.3</v>
+        <v>2.32</v>
       </c>
       <c r="Y86" s="18" t="n">
-        <v>-5379.09</v>
+        <v>0</v>
       </c>
       <c r="Z86" s="37" t="n">
-        <v>18112.39</v>
-      </c>
-      <c r="AA86" s="18" t="n">
-        <v>14592.01</v>
-      </c>
-      <c r="AB86" s="19" t="n">
-        <v>-6145.34</v>
-      </c>
+        <v>7.63</v>
+      </c>
+      <c r="AB86" s="5" t="n"/>
       <c r="AC86" s="10" t="n"/>
       <c r="AD86" s="10" t="n"/>
       <c r="AE86" s="11" t="n"/>
@@ -26498,54 +26187,73 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>배당금수취(CF)</t>
-        </is>
+          <t>CAPEX</t>
+        </is>
+      </c>
+      <c r="E87" s="18" t="n">
+        <v>138.08</v>
       </c>
       <c r="F87" s="9" t="n"/>
       <c r="G87" s="18" t="n">
+        <v>8979.09</v>
+      </c>
+      <c r="H87" s="18" t="n">
+        <v>1446.49</v>
+      </c>
+      <c r="I87" s="18" t="n">
+        <v>564.11</v>
+      </c>
+      <c r="J87" s="18" t="n">
+        <v>125.29</v>
+      </c>
+      <c r="K87" s="37" t="n">
+        <v>11114.98</v>
+      </c>
+      <c r="L87" s="18" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M87" s="18" t="n">
+        <v>36.57</v>
+      </c>
+      <c r="N87" s="18" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O87" s="18" t="n">
+        <v>5.37</v>
+      </c>
+      <c r="P87" s="37" t="n">
+        <v>47.14</v>
+      </c>
+      <c r="Q87" s="18" t="n">
+        <v>10.05</v>
+      </c>
+      <c r="R87" s="18" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="S87" s="18" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="T87" s="18" t="n">
+        <v>9.81</v>
+      </c>
+      <c r="U87" s="37" t="n">
+        <v>27.36</v>
+      </c>
+      <c r="V87" s="18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W87" s="18" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="X87" s="18" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Y87" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="H87" s="18" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="I87" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J87" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K87" s="37" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="L87" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M87" s="18" t="n">
-        <v>57.81</v>
-      </c>
-      <c r="N87" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O87" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P87" s="37" t="n">
-        <v>57.81</v>
-      </c>
-      <c r="S87" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T87" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U87" s="9" t="n"/>
-      <c r="X87" s="18" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="Y87" s="18" t="n">
-        <v>9.57</v>
-      </c>
-      <c r="Z87" s="9" t="n"/>
+      <c r="Z87" s="37" t="n">
+        <v>7.63</v>
+      </c>
       <c r="AB87" s="5" t="n"/>
       <c r="AC87" s="10" t="n"/>
       <c r="AD87" s="10" t="n"/>
@@ -26567,30 +26275,33 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>유형자산의감소</t>
-        </is>
+          <t>무형자산의증가</t>
+        </is>
+      </c>
+      <c r="E88" s="18" t="n">
+        <v>49.5</v>
       </c>
       <c r="F88" s="9" t="n"/>
       <c r="G88" s="18" t="n">
-        <v>624.4299999999999</v>
+        <v>0</v>
       </c>
       <c r="H88" s="18" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="I88" s="18" t="n">
         <v>0</v>
       </c>
       <c r="J88" s="18" t="n">
-        <v>1.75</v>
+        <v>28.75</v>
       </c>
       <c r="K88" s="37" t="n">
-        <v>626.1799999999999</v>
+        <v>34.25</v>
       </c>
       <c r="L88" s="18" t="n">
         <v>0</v>
       </c>
       <c r="M88" s="18" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N88" s="18" t="n">
         <v>0</v>
@@ -26599,28 +26310,17 @@
         <v>0</v>
       </c>
       <c r="P88" s="37" t="n">
-        <v>4</v>
-      </c>
-      <c r="S88" s="18" t="n">
         <v>0</v>
       </c>
       <c r="T88" s="18" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="U88" s="9" t="n"/>
-      <c r="X88" s="18" t="n">
+      <c r="Y88" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="Y88" s="18" t="n">
-        <v>8.699999999999999</v>
-      </c>
       <c r="Z88" s="9" t="n"/>
-      <c r="AA88" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB88" s="19" t="n">
-        <v>0</v>
-      </c>
+      <c r="AB88" s="5" t="n"/>
       <c r="AC88" s="10" t="n"/>
       <c r="AD88" s="10" t="n"/>
       <c r="AE88" s="11" t="n"/>
@@ -26641,55 +26341,79 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>단기차입금의증가</t>
-        </is>
+          <t>재무활동으로인한현금흐름</t>
+        </is>
+      </c>
+      <c r="E89" s="18" t="n">
+        <v>4429.12</v>
       </c>
       <c r="F89" s="9" t="n"/>
       <c r="G89" s="18" t="n">
-        <v>0</v>
+        <v>8184.3</v>
       </c>
       <c r="H89" s="18" t="n">
-        <v>0</v>
+        <v>-280.37</v>
       </c>
       <c r="I89" s="18" t="n">
-        <v>700</v>
+        <v>502.48</v>
       </c>
       <c r="J89" s="18" t="n">
-        <v>1200</v>
+        <v>-200.14</v>
       </c>
       <c r="K89" s="37" t="n">
-        <v>1900</v>
+        <v>8206.27</v>
       </c>
       <c r="L89" s="18" t="n">
-        <v>0</v>
+        <v>-8.92</v>
       </c>
       <c r="M89" s="18" t="n">
-        <v>1600</v>
+        <v>-708.3</v>
       </c>
       <c r="N89" s="18" t="n">
-        <v>0</v>
+        <v>-8.51</v>
       </c>
       <c r="O89" s="18" t="n">
-        <v>0</v>
+        <v>-8.74</v>
       </c>
       <c r="P89" s="37" t="n">
-        <v>1600</v>
+        <v>-734.47</v>
+      </c>
+      <c r="Q89" s="18" t="n">
+        <v>-217.37</v>
+      </c>
+      <c r="R89" s="18" t="n">
+        <v>-570.87</v>
       </c>
       <c r="S89" s="18" t="n">
-        <v>0</v>
+        <v>1413.06</v>
       </c>
       <c r="T89" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U89" s="9" t="n"/>
+        <v>-99.08</v>
+      </c>
+      <c r="U89" s="37" t="n">
+        <v>525.74</v>
+      </c>
+      <c r="V89" s="18" t="n">
+        <v>-7.87</v>
+      </c>
+      <c r="W89" s="18" t="n">
+        <v>1995.35</v>
+      </c>
       <c r="X89" s="18" t="n">
-        <v>0</v>
+        <v>1495.46</v>
       </c>
       <c r="Y89" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z89" s="9" t="n"/>
-      <c r="AB89" s="5" t="n"/>
+        <v>-4.19</v>
+      </c>
+      <c r="Z89" s="37" t="n">
+        <v>3478.75</v>
+      </c>
+      <c r="AA89" s="18" t="n">
+        <v>-4.28</v>
+      </c>
+      <c r="AB89" s="19" t="n">
+        <v>-3.31</v>
+      </c>
       <c r="AC89" s="10" t="n"/>
       <c r="AD89" s="10" t="n"/>
       <c r="AE89" s="11" t="n"/>
@@ -26710,53 +26434,78 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>장기차입금의증가</t>
-        </is>
+          <t>리스부채의상환</t>
+        </is>
+      </c>
+      <c r="E90" s="18" t="n">
+        <v>440.69</v>
       </c>
       <c r="F90" s="9" t="n"/>
       <c r="G90" s="18" t="n">
-        <v>8500</v>
+        <v>186.92</v>
       </c>
       <c r="H90" s="18" t="n">
-        <v>0</v>
+        <v>194.16</v>
       </c>
       <c r="I90" s="18" t="n">
-        <v>0</v>
+        <v>197.52</v>
       </c>
       <c r="J90" s="18" t="n">
-        <v>0</v>
+        <v>200.14</v>
       </c>
       <c r="K90" s="37" t="n">
-        <v>8500</v>
+        <v>778.74</v>
       </c>
       <c r="L90" s="18" t="n">
-        <v>0</v>
+        <v>8.92</v>
       </c>
       <c r="M90" s="18" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="N90" s="18" t="n">
-        <v>0</v>
+        <v>8.51</v>
       </c>
       <c r="O90" s="18" t="n">
-        <v>0</v>
+        <v>8.74</v>
       </c>
       <c r="P90" s="37" t="n">
-        <v>0</v>
+        <v>34.47</v>
+      </c>
+      <c r="Q90" s="18" t="n">
+        <v>8.960000000000001</v>
+      </c>
+      <c r="R90" s="18" t="n">
+        <v>8.220000000000001</v>
+      </c>
+      <c r="S90" s="18" t="n">
+        <v>7.61</v>
       </c>
       <c r="T90" s="18" t="n">
-        <v>7700</v>
-      </c>
-      <c r="U90" s="9" t="n"/>
+        <v>7.56</v>
+      </c>
+      <c r="U90" s="37" t="n">
+        <v>32.35</v>
+      </c>
+      <c r="V90" s="18" t="n">
+        <v>7.87</v>
+      </c>
+      <c r="W90" s="18" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="X90" s="18" t="n">
+        <v>4.54</v>
+      </c>
       <c r="Y90" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z90" s="9" t="n"/>
+        <v>4.19</v>
+      </c>
+      <c r="Z90" s="37" t="n">
+        <v>21.25</v>
+      </c>
       <c r="AA90" s="18" t="n">
-        <v>2000</v>
+        <v>4.28</v>
       </c>
       <c r="AB90" s="19" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="AC90" s="10" t="n"/>
       <c r="AD90" s="10" t="n"/>
@@ -26778,36 +26527,56 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>이자수취(CF)</t>
-        </is>
+          <t>단기차입금의감소</t>
+        </is>
+      </c>
+      <c r="E91" s="18" t="n">
+        <v>0</v>
       </c>
       <c r="F91" s="9" t="n"/>
-      <c r="K91" s="9" t="n"/>
-      <c r="P91" s="9" t="n"/>
-      <c r="Q91" s="18" t="n">
-        <v>351.33</v>
+      <c r="G91" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H91" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I91" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J91" s="18" t="n">
+        <v>1200</v>
+      </c>
+      <c r="K91" s="37" t="n">
+        <v>1200</v>
+      </c>
+      <c r="L91" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M91" s="18" t="n">
+        <v>700</v>
+      </c>
+      <c r="N91" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O91" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P91" s="37" t="n">
+        <v>700</v>
+      </c>
+      <c r="S91" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T91" s="18" t="n">
+        <v>0</v>
       </c>
       <c r="U91" s="9" t="n"/>
-      <c r="V91" s="18" t="n">
-        <v>378.24</v>
-      </c>
-      <c r="W91" s="18" t="n">
-        <v>71.48</v>
-      </c>
-      <c r="X91" s="18" t="n">
-        <v>367.67</v>
-      </c>
-      <c r="Y91" s="18" t="n">
-        <v>38.09</v>
-      </c>
-      <c r="Z91" s="37" t="n">
-        <v>855.48</v>
-      </c>
+      <c r="Z91" s="9" t="n"/>
       <c r="AA91" s="18" t="n">
-        <v>397.06</v>
+        <v>2000</v>
       </c>
       <c r="AB91" s="19" t="n">
-        <v>21.56</v>
+        <v>0</v>
       </c>
       <c r="AC91" s="10" t="n"/>
       <c r="AD91" s="10" t="n"/>
@@ -26829,19 +26598,50 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>자기주식의취득</t>
-        </is>
+          <t>유동성장기부채의감소</t>
+        </is>
+      </c>
+      <c r="E92" s="18" t="n">
+        <v>128.13</v>
       </c>
       <c r="F92" s="9" t="n"/>
-      <c r="K92" s="9" t="n"/>
-      <c r="P92" s="9" t="n"/>
+      <c r="G92" s="18" t="n">
+        <v>128.78</v>
+      </c>
+      <c r="H92" s="18" t="n">
+        <v>86.20999999999999</v>
+      </c>
+      <c r="I92" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K92" s="37" t="n">
+        <v>214.99</v>
+      </c>
+      <c r="L92" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M92" s="18" t="n">
+        <v>1600</v>
+      </c>
+      <c r="N92" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O92" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P92" s="37" t="n">
+        <v>1600</v>
+      </c>
+      <c r="S92" s="18" t="n">
+        <v>0</v>
+      </c>
       <c r="T92" s="18" t="n">
-        <v>0</v>
+        <v>1896.04</v>
       </c>
       <c r="U92" s="9" t="n"/>
-      <c r="Y92" s="18" t="n">
-        <v>0</v>
-      </c>
       <c r="Z92" s="9" t="n"/>
       <c r="AB92" s="5" t="n"/>
       <c r="AC92" s="10" t="n"/>
@@ -26857,6 +26657,638 @@
       <c r="AM92" s="10" t="n"/>
       <c r="AN92" s="10" t="n"/>
       <c r="AO92" s="11" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>1</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>장기차입금의감소</t>
+        </is>
+      </c>
+      <c r="E93" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F93" s="9" t="n"/>
+      <c r="G93" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H93" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I93" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J93" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K93" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L93" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M93" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P93" s="9" t="n"/>
+      <c r="Q93" s="18" t="n">
+        <v>208.41</v>
+      </c>
+      <c r="R93" s="18" t="n">
+        <v>562.65</v>
+      </c>
+      <c r="S93" s="18" t="n">
+        <v>4937.42</v>
+      </c>
+      <c r="T93" s="18" t="n">
+        <v>5895.48</v>
+      </c>
+      <c r="U93" s="37" t="n">
+        <v>11603.96</v>
+      </c>
+      <c r="V93" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W93" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X93" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y93" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z93" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB93" s="5" t="n"/>
+      <c r="AC93" s="10" t="n"/>
+      <c r="AD93" s="10" t="n"/>
+      <c r="AE93" s="11" t="n"/>
+      <c r="AF93" s="10" t="n"/>
+      <c r="AG93" s="10" t="n"/>
+      <c r="AH93" s="10" t="n"/>
+      <c r="AI93" s="10" t="n"/>
+      <c r="AJ93" s="11" t="n"/>
+      <c r="AK93" s="10" t="n"/>
+      <c r="AL93" s="10" t="n"/>
+      <c r="AM93" s="10" t="n"/>
+      <c r="AN93" s="10" t="n"/>
+      <c r="AO93" s="11" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>1</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>현금및현금성자산의증감</t>
+        </is>
+      </c>
+      <c r="E94" s="18" t="n">
+        <v>2659.61</v>
+      </c>
+      <c r="F94" s="9" t="n"/>
+      <c r="G94" s="18" t="n">
+        <v>-588.76</v>
+      </c>
+      <c r="H94" s="18" t="n">
+        <v>-3984.35</v>
+      </c>
+      <c r="I94" s="18" t="n">
+        <v>686.47</v>
+      </c>
+      <c r="J94" s="18" t="n">
+        <v>-157.62</v>
+      </c>
+      <c r="K94" s="37" t="n">
+        <v>-4044.26</v>
+      </c>
+      <c r="L94" s="18" t="n">
+        <v>3535.35</v>
+      </c>
+      <c r="M94" s="18" t="n">
+        <v>1218.95</v>
+      </c>
+      <c r="N94" s="18" t="n">
+        <v>2287.49</v>
+      </c>
+      <c r="O94" s="18" t="n">
+        <v>151.12</v>
+      </c>
+      <c r="P94" s="37" t="n">
+        <v>7192.91</v>
+      </c>
+      <c r="Q94" s="18" t="n">
+        <v>1265.84</v>
+      </c>
+      <c r="R94" s="18" t="n">
+        <v>11894.81</v>
+      </c>
+      <c r="S94" s="18" t="n">
+        <v>1682.98</v>
+      </c>
+      <c r="T94" s="18" t="n">
+        <v>4775.1</v>
+      </c>
+      <c r="U94" s="37" t="n">
+        <v>19618.73</v>
+      </c>
+      <c r="V94" s="18" t="n">
+        <v>-2002.29</v>
+      </c>
+      <c r="W94" s="18" t="n">
+        <v>534.91</v>
+      </c>
+      <c r="X94" s="18" t="n">
+        <v>-3705.3</v>
+      </c>
+      <c r="Y94" s="18" t="n">
+        <v>-5379.09</v>
+      </c>
+      <c r="Z94" s="37" t="n">
+        <v>-10551.77</v>
+      </c>
+      <c r="AA94" s="18" t="n">
+        <v>-3520.38</v>
+      </c>
+      <c r="AB94" s="19" t="n">
+        <v>-6145.34</v>
+      </c>
+      <c r="AC94" s="10" t="n"/>
+      <c r="AD94" s="10" t="n"/>
+      <c r="AE94" s="11" t="n"/>
+      <c r="AF94" s="10" t="n"/>
+      <c r="AG94" s="10" t="n"/>
+      <c r="AH94" s="10" t="n"/>
+      <c r="AI94" s="10" t="n"/>
+      <c r="AJ94" s="11" t="n"/>
+      <c r="AK94" s="10" t="n"/>
+      <c r="AL94" s="10" t="n"/>
+      <c r="AM94" s="10" t="n"/>
+      <c r="AN94" s="10" t="n"/>
+      <c r="AO94" s="11" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>1</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>기말현금및현금성자산</t>
+        </is>
+      </c>
+      <c r="E95" s="18" t="n">
+        <v>2659.61</v>
+      </c>
+      <c r="F95" s="9" t="n"/>
+      <c r="G95" s="18" t="n">
+        <v>5308.01</v>
+      </c>
+      <c r="H95" s="18" t="n">
+        <v>-3984.35</v>
+      </c>
+      <c r="I95" s="18" t="n">
+        <v>686.47</v>
+      </c>
+      <c r="J95" s="18" t="n">
+        <v>-157.62</v>
+      </c>
+      <c r="K95" s="37" t="n">
+        <v>1852.51</v>
+      </c>
+      <c r="L95" s="18" t="n">
+        <v>5387.86</v>
+      </c>
+      <c r="M95" s="18" t="n">
+        <v>1218.96</v>
+      </c>
+      <c r="N95" s="18" t="n">
+        <v>2287.48</v>
+      </c>
+      <c r="O95" s="18" t="n">
+        <v>151.13</v>
+      </c>
+      <c r="P95" s="37" t="n">
+        <v>9045.43</v>
+      </c>
+      <c r="Q95" s="18" t="n">
+        <v>10311.27</v>
+      </c>
+      <c r="R95" s="18" t="n">
+        <v>11894.81</v>
+      </c>
+      <c r="S95" s="18" t="n">
+        <v>1682.97</v>
+      </c>
+      <c r="T95" s="18" t="n">
+        <v>4775.11</v>
+      </c>
+      <c r="U95" s="37" t="n">
+        <v>28664.16</v>
+      </c>
+      <c r="V95" s="18" t="n">
+        <v>26661.87</v>
+      </c>
+      <c r="W95" s="18" t="n">
+        <v>534.91</v>
+      </c>
+      <c r="X95" s="18" t="n">
+        <v>-3705.3</v>
+      </c>
+      <c r="Y95" s="18" t="n">
+        <v>-5379.09</v>
+      </c>
+      <c r="Z95" s="37" t="n">
+        <v>18112.39</v>
+      </c>
+      <c r="AA95" s="18" t="n">
+        <v>14592.01</v>
+      </c>
+      <c r="AB95" s="19" t="n">
+        <v>-6145.34</v>
+      </c>
+      <c r="AC95" s="10" t="n"/>
+      <c r="AD95" s="10" t="n"/>
+      <c r="AE95" s="11" t="n"/>
+      <c r="AF95" s="10" t="n"/>
+      <c r="AG95" s="10" t="n"/>
+      <c r="AH95" s="10" t="n"/>
+      <c r="AI95" s="10" t="n"/>
+      <c r="AJ95" s="11" t="n"/>
+      <c r="AK95" s="10" t="n"/>
+      <c r="AL95" s="10" t="n"/>
+      <c r="AM95" s="10" t="n"/>
+      <c r="AN95" s="10" t="n"/>
+      <c r="AO95" s="11" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>1</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>배당금수취(CF)</t>
+        </is>
+      </c>
+      <c r="F96" s="9" t="n"/>
+      <c r="G96" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" s="18" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="I96" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K96" s="37" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="L96" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M96" s="18" t="n">
+        <v>57.81</v>
+      </c>
+      <c r="N96" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O96" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P96" s="37" t="n">
+        <v>57.81</v>
+      </c>
+      <c r="S96" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T96" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U96" s="9" t="n"/>
+      <c r="X96" s="18" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="Y96" s="18" t="n">
+        <v>9.57</v>
+      </c>
+      <c r="Z96" s="9" t="n"/>
+      <c r="AB96" s="5" t="n"/>
+      <c r="AC96" s="10" t="n"/>
+      <c r="AD96" s="10" t="n"/>
+      <c r="AE96" s="11" t="n"/>
+      <c r="AF96" s="10" t="n"/>
+      <c r="AG96" s="10" t="n"/>
+      <c r="AH96" s="10" t="n"/>
+      <c r="AI96" s="10" t="n"/>
+      <c r="AJ96" s="11" t="n"/>
+      <c r="AK96" s="10" t="n"/>
+      <c r="AL96" s="10" t="n"/>
+      <c r="AM96" s="10" t="n"/>
+      <c r="AN96" s="10" t="n"/>
+      <c r="AO96" s="11" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>1</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>유형자산의감소</t>
+        </is>
+      </c>
+      <c r="F97" s="9" t="n"/>
+      <c r="G97" s="18" t="n">
+        <v>624.4299999999999</v>
+      </c>
+      <c r="H97" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" s="18" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="K97" s="37" t="n">
+        <v>626.1799999999999</v>
+      </c>
+      <c r="L97" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M97" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="N97" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O97" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P97" s="37" t="n">
+        <v>4</v>
+      </c>
+      <c r="S97" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T97" s="18" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="U97" s="9" t="n"/>
+      <c r="X97" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y97" s="18" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="Z97" s="9" t="n"/>
+      <c r="AA97" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB97" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC97" s="10" t="n"/>
+      <c r="AD97" s="10" t="n"/>
+      <c r="AE97" s="11" t="n"/>
+      <c r="AF97" s="10" t="n"/>
+      <c r="AG97" s="10" t="n"/>
+      <c r="AH97" s="10" t="n"/>
+      <c r="AI97" s="10" t="n"/>
+      <c r="AJ97" s="11" t="n"/>
+      <c r="AK97" s="10" t="n"/>
+      <c r="AL97" s="10" t="n"/>
+      <c r="AM97" s="10" t="n"/>
+      <c r="AN97" s="10" t="n"/>
+      <c r="AO97" s="11" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>1</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>단기차입금의증가</t>
+        </is>
+      </c>
+      <c r="F98" s="9" t="n"/>
+      <c r="G98" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I98" s="18" t="n">
+        <v>700</v>
+      </c>
+      <c r="J98" s="18" t="n">
+        <v>1200</v>
+      </c>
+      <c r="K98" s="37" t="n">
+        <v>1900</v>
+      </c>
+      <c r="L98" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M98" s="18" t="n">
+        <v>1600</v>
+      </c>
+      <c r="N98" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O98" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P98" s="37" t="n">
+        <v>1600</v>
+      </c>
+      <c r="S98" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T98" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U98" s="9" t="n"/>
+      <c r="X98" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y98" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z98" s="9" t="n"/>
+      <c r="AB98" s="5" t="n"/>
+      <c r="AC98" s="10" t="n"/>
+      <c r="AD98" s="10" t="n"/>
+      <c r="AE98" s="11" t="n"/>
+      <c r="AF98" s="10" t="n"/>
+      <c r="AG98" s="10" t="n"/>
+      <c r="AH98" s="10" t="n"/>
+      <c r="AI98" s="10" t="n"/>
+      <c r="AJ98" s="11" t="n"/>
+      <c r="AK98" s="10" t="n"/>
+      <c r="AL98" s="10" t="n"/>
+      <c r="AM98" s="10" t="n"/>
+      <c r="AN98" s="10" t="n"/>
+      <c r="AO98" s="11" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>1</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>장기차입금의증가</t>
+        </is>
+      </c>
+      <c r="F99" s="9" t="n"/>
+      <c r="G99" s="18" t="n">
+        <v>8500</v>
+      </c>
+      <c r="H99" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I99" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K99" s="37" t="n">
+        <v>8500</v>
+      </c>
+      <c r="L99" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M99" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N99" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O99" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P99" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T99" s="18" t="n">
+        <v>7700</v>
+      </c>
+      <c r="U99" s="9" t="n"/>
+      <c r="Y99" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z99" s="9" t="n"/>
+      <c r="AA99" s="18" t="n">
+        <v>2000</v>
+      </c>
+      <c r="AB99" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC99" s="10" t="n"/>
+      <c r="AD99" s="10" t="n"/>
+      <c r="AE99" s="11" t="n"/>
+      <c r="AF99" s="10" t="n"/>
+      <c r="AG99" s="10" t="n"/>
+      <c r="AH99" s="10" t="n"/>
+      <c r="AI99" s="10" t="n"/>
+      <c r="AJ99" s="11" t="n"/>
+      <c r="AK99" s="10" t="n"/>
+      <c r="AL99" s="10" t="n"/>
+      <c r="AM99" s="10" t="n"/>
+      <c r="AN99" s="10" t="n"/>
+      <c r="AO99" s="11" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>1</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>이자수취(CF)</t>
+        </is>
+      </c>
+      <c r="F100" s="9" t="n"/>
+      <c r="K100" s="9" t="n"/>
+      <c r="P100" s="9" t="n"/>
+      <c r="Q100" s="18" t="n">
+        <v>351.33</v>
+      </c>
+      <c r="U100" s="9" t="n"/>
+      <c r="V100" s="18" t="n">
+        <v>378.24</v>
+      </c>
+      <c r="W100" s="18" t="n">
+        <v>71.48</v>
+      </c>
+      <c r="X100" s="18" t="n">
+        <v>367.67</v>
+      </c>
+      <c r="Y100" s="18" t="n">
+        <v>38.09</v>
+      </c>
+      <c r="Z100" s="37" t="n">
+        <v>855.48</v>
+      </c>
+      <c r="AA100" s="18" t="n">
+        <v>397.06</v>
+      </c>
+      <c r="AB100" s="19" t="n">
+        <v>21.56</v>
+      </c>
+      <c r="AC100" s="10" t="n"/>
+      <c r="AD100" s="10" t="n"/>
+      <c r="AE100" s="11" t="n"/>
+      <c r="AF100" s="10" t="n"/>
+      <c r="AG100" s="10" t="n"/>
+      <c r="AH100" s="10" t="n"/>
+      <c r="AI100" s="10" t="n"/>
+      <c r="AJ100" s="11" t="n"/>
+      <c r="AK100" s="10" t="n"/>
+      <c r="AL100" s="10" t="n"/>
+      <c r="AM100" s="10" t="n"/>
+      <c r="AN100" s="10" t="n"/>
+      <c r="AO100" s="11" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>1</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>자기주식의취득</t>
+        </is>
+      </c>
+      <c r="F101" s="9" t="n"/>
+      <c r="K101" s="9" t="n"/>
+      <c r="P101" s="9" t="n"/>
+      <c r="T101" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U101" s="9" t="n"/>
+      <c r="Y101" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z101" s="9" t="n"/>
+      <c r="AB101" s="5" t="n"/>
+      <c r="AC101" s="10" t="n"/>
+      <c r="AD101" s="10" t="n"/>
+      <c r="AE101" s="11" t="n"/>
+      <c r="AF101" s="10" t="n"/>
+      <c r="AG101" s="10" t="n"/>
+      <c r="AH101" s="10" t="n"/>
+      <c r="AI101" s="10" t="n"/>
+      <c r="AJ101" s="11" t="n"/>
+      <c r="AK101" s="10" t="n"/>
+      <c r="AL101" s="10" t="n"/>
+      <c r="AM101" s="10" t="n"/>
+      <c r="AN101" s="10" t="n"/>
+      <c r="AO101" s="11" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -40241,7 +40673,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>209.7</v>
+        <v>210.7</v>
       </c>
     </row>
     <row r="30">
@@ -40261,7 +40693,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>17.48</v>
+        <v>17.39</v>
       </c>
     </row>
     <row r="32">
@@ -40281,7 +40713,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.1221</v>
+        <v>0.1226</v>
       </c>
     </row>
     <row r="34">

--- a/argus/kship/models/333430_model.xlsx
+++ b/argus/kship/models/333430_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -23,7 +23,7 @@
     <definedName name="BS연결H">BS연결!$C$1:$AO$1</definedName>
     <definedName name="BS연결">BS연결!$C$5:$AO$102</definedName>
     <definedName name="BS별도H">BS별도!$C$1:$AO$1</definedName>
-    <definedName name="BS별도">BS별도!$C$5:$AO$101</definedName>
+    <definedName name="BS별도">BS별도!$C$5:$AO$92</definedName>
     <definedName name="SUBQH">subQ!$A$1:$AO$1</definedName>
     <definedName name="subQ">subQ!$A$5:$AO$40</definedName>
   </definedNames>
@@ -663,55 +663,55 @@
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 85183억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 85182억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 88307억 × 비례계수 0.0076 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 88314억 × 비례계수 0.0076 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 91228억 × 비례계수 0.0076 × 계절비중 Q2 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 91241억 × 비례계수 0.0076 × 계절비중 Q2 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 94600억 × 비례계수 0.0076 × 계절비중 Q3 0.233(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 94620억 × 비례계수 0.0076 × 계절비중 Q3 0.233(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 99289억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 99317억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 105070억 × 비례계수 0.0076 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 105097억 × 비례계수 0.0076 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 111421억 × 비례계수 0.0076 × 계절비중 Q2 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 111447억 × 비례계수 0.0076 × 계절비중 Q2 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 117844억 × 비례계수 0.0076 × 계절비중 Q3 0.233(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 117868억 × 비례계수 0.0076 × 계절비중 Q3 0.233(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 123670억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 123693억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1590,55 +1590,55 @@
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 85183억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 85182억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 88307억 × 비례계수 0.0076 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 88314억 × 비례계수 0.0076 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 91228억 × 비례계수 0.0076 × 계절비중 Q2 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 91241억 × 비례계수 0.0076 × 계절비중 Q2 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 94600억 × 비례계수 0.0076 × 계절비중 Q3 0.233(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 94620억 × 비례계수 0.0076 × 계절비중 Q3 0.233(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 99289억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 99317억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 105070억 × 비례계수 0.0076 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 105097억 × 비례계수 0.0076 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 111421억 × 비례계수 0.0076 × 계절비중 Q2 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 111447억 × 비례계수 0.0076 × 계절비중 Q2 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 117844억 × 비례계수 0.0076 × 계절비중 Q3 0.233(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 117868억 × 비례계수 0.0076 × 계절비중 Q3 0.233(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 123670억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 123693억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -4208,7 +4208,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>· 이자율 자산 1.66% / 부채 3.63% — 이자손익 = (전분기 이자발생자산 × 자산이자율 − 전분기 총차입금 × 부채이자율)/4, 최소자승 역산(모델 assumptions [0.0166, 0.0362] 는 4자리 반올림이라 그대로 쓰면 ±1억 어긋남) · 출처: {"asset": "주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)", "debt": "주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)"}</t>
+          <t>· 이자율 자산 1.66% / 부채 3.62% — 이자손익 = (전분기 이자발생자산 × 자산이자율 − 전분기 총차입금 × 부채이자율)/4, 최소자승 역산(모델 assumptions [0.0166, 0.0362] 는 4자리 반올림이라 그대로 쓰면 ±1억 어긋남) · 출처: {"asset": "주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)", "debt": "주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)"}</t>
         </is>
       </c>
     </row>
@@ -4930,35 +4930,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1346.2</v>
+        <v>1345.74</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1458.38</v>
+        <v>1457.79</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5049,35 +5049,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5168,35 +5168,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>851.8099999999999</v>
+        <v>851.3099999999999</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.9299999999999</v>
+        <v>919.5700000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5287,35 +5287,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5406,35 +5406,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1512.43</v>
+        <v>1510.82</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1691.86</v>
+        <v>1690.9</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5525,35 +5525,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5644,35 +5644,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.79</v>
+        <v>200.73</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.89</v>
+        <v>213.82</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5763,35 +5763,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5898,7 +5898,7 @@
         <v>3790</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>3665</v>
+        <v>3680</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6171,7 +6171,7 @@
         <v>3675.7</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>3832</v>
+        <v>3835</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6330,29 +6330,29 @@
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.229013833</v>
+        <v>0.229096623</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.007838539</v>
+        <v>0.007961777</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.179216018</v>
+        <v>0.179427524</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.165579728</v>
+        <v>0.165928212</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.189828225</v>
+        <v>0.190017513</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.221325507</v>
+        <v>0.221481844</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.245665431</v>
+        <v>0.245740929</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.245547345</v>
+        <v>0.245431255</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6644,32 +6644,32 @@
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.195621421</v>
+        <v>0.195608245</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.195646857</v>
+        <v>0.195622937</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.19562358</v>
+        <v>0.195648275</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.19566053</v>
+        <v>0.195644748</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.195663251</v>
+        <v>0.195618951</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.195634762</v>
+        <v>0.195635854</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.195632349</v>
+        <v>0.195633397</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.195631301</v>
+        <v>0.195625343</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7539,36 +7539,36 @@
         <v/>
       </c>
       <c r="AC29" s="30" t="n">
-        <v>0.001370794</v>
+        <v>0.001116851</v>
       </c>
       <c r="AD29" s="30" t="n">
-        <v>-0.003342852</v>
+        <v>-0.00373285</v>
       </c>
       <c r="AE29" s="31" t="n"/>
       <c r="AF29" s="30" t="n">
-        <v>0.007680666</v>
+        <v>-0.002629252</v>
       </c>
       <c r="AG29" s="30" t="n">
-        <v>-0.007328564</v>
+        <v>0.002312495</v>
       </c>
       <c r="AH29" s="30" t="n">
-        <v>-0.000800383</v>
+        <v>-0.002364124</v>
       </c>
       <c r="AI29" s="30" t="n">
-        <v>0.007922452</v>
+        <v>0.006203543</v>
       </c>
       <c r="AJ29" s="31" t="n"/>
       <c r="AK29" s="30" t="n">
-        <v>0.001487675</v>
+        <v>-0.008859482</v>
       </c>
       <c r="AL29" s="30" t="n">
-        <v>0.006596532</v>
+        <v>0.004967321</v>
       </c>
       <c r="AM29" s="30" t="n">
-        <v>0.001134992</v>
+        <v>-0.000500382</v>
       </c>
       <c r="AN29" s="30" t="n">
-        <v>-0.000708558</v>
+        <v>-0.002500987</v>
       </c>
       <c r="AO29" s="31" t="n"/>
     </row>
@@ -7667,36 +7667,36 @@
         <v/>
       </c>
       <c r="AC30" s="30" t="n">
-        <v>0.00361582</v>
+        <v>0.00357668</v>
       </c>
       <c r="AD30" s="30" t="n">
-        <v>-0.005528254</v>
+        <v>-0.005600673</v>
       </c>
       <c r="AE30" s="31" t="n"/>
       <c r="AF30" s="30" t="n">
-        <v>0.001116082</v>
+        <v>0.001050841</v>
       </c>
       <c r="AG30" s="30" t="n">
-        <v>-0.000726324</v>
+        <v>-0.000807864</v>
       </c>
       <c r="AH30" s="30" t="n">
-        <v>-0.000355157</v>
+        <v>-0.005413632</v>
       </c>
       <c r="AI30" s="30" t="n">
-        <v>0.005287276</v>
+        <v>0.000190554</v>
       </c>
       <c r="AJ30" s="31" t="n"/>
       <c r="AK30" s="30" t="n">
-        <v>-0.001752575</v>
+        <v>-0.001816081</v>
       </c>
       <c r="AL30" s="30" t="n">
-        <v>-0.000189406</v>
+        <v>0.004740572</v>
       </c>
       <c r="AM30" s="30" t="n">
-        <v>-0.004404074</v>
+        <v>0.000529342</v>
       </c>
       <c r="AN30" s="30" t="n">
-        <v>0.001836257</v>
+        <v>-0.003257342</v>
       </c>
       <c r="AO30" s="31" t="n"/>
     </row>
@@ -7933,26 +7933,26 @@
         <v>0.08418850899999999</v>
       </c>
       <c r="AG32" s="24" t="n">
-        <v>0.085759932</v>
+        <v>0.08579007700000001</v>
       </c>
       <c r="AH32" s="24" t="n">
-        <v>0.081040562</v>
+        <v>0.081038312</v>
       </c>
       <c r="AI32" s="24" t="n">
-        <v>0.104781961</v>
+        <v>0.104804951</v>
       </c>
       <c r="AJ32" s="25" t="n"/>
       <c r="AK32" s="24" t="n">
-        <v>0.072179088</v>
+        <v>0.072198977</v>
       </c>
       <c r="AL32" s="24" t="n">
-        <v>0.076209267</v>
+        <v>0.07622598999999999</v>
       </c>
       <c r="AM32" s="24" t="n">
-        <v>0.07403602099999999</v>
+        <v>0.074050199</v>
       </c>
       <c r="AN32" s="24" t="n">
-        <v>0.09603661400000001</v>
+        <v>0.096046363</v>
       </c>
       <c r="AO32" s="25" t="n"/>
     </row>
@@ -8061,26 +8061,26 @@
         <v>0.036881667</v>
       </c>
       <c r="AG33" s="24" t="n">
-        <v>0.039284186</v>
+        <v>0.039297994</v>
       </c>
       <c r="AH33" s="24" t="n">
-        <v>0.038782452</v>
+        <v>0.038781936</v>
       </c>
       <c r="AI33" s="24" t="n">
-        <v>0.052171133</v>
+        <v>0.052196045</v>
       </c>
       <c r="AJ33" s="25" t="n"/>
       <c r="AK33" s="24" t="n">
-        <v>0.037756491</v>
+        <v>0.037755114</v>
       </c>
       <c r="AL33" s="24" t="n">
-        <v>0.041173714</v>
+        <v>0.041183981</v>
       </c>
       <c r="AM33" s="24" t="n">
-        <v>0.041345559</v>
+        <v>0.041354948</v>
       </c>
       <c r="AN33" s="24" t="n">
-        <v>0.055315471</v>
+        <v>0.055312483</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -8743,11 +8743,11 @@
         </is>
       </c>
       <c r="D41" s="34" t="n">
-        <v>3665</v>
+        <v>3680</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 3,860원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 3,755원)</t>
         </is>
       </c>
       <c r="F41" s="9" t="n"/>
@@ -9018,7 +9018,7 @@
         </is>
       </c>
       <c r="D48" s="36" t="n">
-        <v>0.1213020833333333</v>
+        <v>0.121312329123812</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
@@ -9057,7 +9057,7 @@
         </is>
       </c>
       <c r="D49" s="36" t="n">
-        <v>0.1230963481968672</v>
+        <v>0.1231063741721854</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -9096,7 +9096,7 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.5707468879668049</v>
+        <v>0.570751222403319</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -9135,7 +9135,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.01661919388857396</v>
+        <v>0.01661608399237282</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -9174,7 +9174,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.03625453639493557</v>
+        <v>0.03624719825973411</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -18592,7 +18592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO101"/>
+  <dimension ref="A1:AO92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -21248,7 +21248,7 @@
         <v>3686.21</v>
       </c>
       <c r="H27" s="18" t="n">
-        <v>2000</v>
+        <v>3600</v>
       </c>
       <c r="I27" s="18" t="n">
         <v>4300</v>
@@ -21342,6 +21342,9 @@
       <c r="G28" s="18" t="n">
         <v>3686.21</v>
       </c>
+      <c r="H28" s="18" t="n">
+        <v>3600</v>
+      </c>
       <c r="I28" s="18" t="n">
         <v>4300</v>
       </c>
@@ -21992,81 +21995,71 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>비유동리스부채</t>
+          <t>장기금융부채(face)</t>
         </is>
       </c>
       <c r="E35" s="18" t="n">
-        <v>22.71</v>
+        <v>5000</v>
       </c>
       <c r="F35" s="37" t="n">
-        <v>22.71</v>
+        <v>5000</v>
       </c>
       <c r="G35" s="18" t="n">
-        <v>19.33</v>
+        <v>13500</v>
       </c>
       <c r="H35" s="18" t="n">
-        <v>59.32</v>
+        <v>13500</v>
       </c>
       <c r="I35" s="18" t="n">
-        <v>53.33</v>
+        <v>13500</v>
       </c>
       <c r="J35" s="18" t="n">
-        <v>47.18</v>
+        <v>13500</v>
       </c>
       <c r="K35" s="37" t="n">
-        <v>47.18</v>
+        <v>13500</v>
       </c>
       <c r="L35" s="18" t="n">
-        <v>40.85</v>
+        <v>13291.59</v>
       </c>
       <c r="M35" s="18" t="n">
-        <v>34.34</v>
+        <v>12728.94</v>
       </c>
       <c r="N35" s="18" t="n">
-        <v>30.99</v>
+        <v>12166.45</v>
       </c>
       <c r="O35" s="18" t="n">
-        <v>28.32</v>
+        <v>11603.96</v>
       </c>
       <c r="P35" s="37" t="n">
-        <v>28.32</v>
+        <v>11603.96</v>
       </c>
       <c r="Q35" s="18" t="n">
-        <v>25.58</v>
+        <v>11041.47</v>
       </c>
       <c r="R35" s="18" t="n">
-        <v>22.77</v>
+        <v>10478.98</v>
       </c>
       <c r="S35" s="18" t="n">
-        <v>19.91</v>
+        <v>12874.88</v>
       </c>
       <c r="T35" s="18" t="n">
-        <v>16.97</v>
+        <v>14200</v>
       </c>
       <c r="U35" s="37" t="n">
-        <v>16.97</v>
+        <v>14200</v>
       </c>
       <c r="V35" s="18" t="n">
-        <v>13.97</v>
+        <v>14200</v>
       </c>
       <c r="W35" s="18" t="n">
-        <v>10.89</v>
+        <v>14200</v>
       </c>
       <c r="X35" s="18" t="n">
-        <v>7.75</v>
-      </c>
-      <c r="Y35" s="18" t="n">
-        <v>4.53</v>
-      </c>
-      <c r="Z35" s="37" t="n">
-        <v>4.53</v>
-      </c>
-      <c r="AA35" s="18" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AB35" s="19" t="n">
-        <v>0</v>
-      </c>
+        <v>15700</v>
+      </c>
+      <c r="Z35" s="9" t="n"/>
+      <c r="AB35" s="5" t="n"/>
       <c r="AC35" s="10" t="n"/>
       <c r="AD35" s="10" t="n"/>
       <c r="AE35" s="11" t="n"/>
@@ -22087,7 +22080,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>장기금융부채</t>
+          <t>비유동리스부채</t>
         </is>
       </c>
       <c r="E36" s="18" t="n">
@@ -22182,80 +22175,80 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>확정급여부채</t>
+          <t>장기금융부채</t>
         </is>
       </c>
       <c r="E37" s="18" t="n">
-        <v>225.15</v>
+        <v>22.71</v>
       </c>
       <c r="F37" s="37" t="n">
-        <v>225.15</v>
+        <v>22.71</v>
       </c>
       <c r="G37" s="18" t="n">
-        <v>221.68</v>
+        <v>19.33</v>
       </c>
       <c r="H37" s="18" t="n">
-        <v>193.02</v>
+        <v>59.32</v>
       </c>
       <c r="I37" s="18" t="n">
-        <v>308.8</v>
+        <v>53.33</v>
       </c>
       <c r="J37" s="18" t="n">
-        <v>466.97</v>
+        <v>47.18</v>
       </c>
       <c r="K37" s="37" t="n">
-        <v>466.97</v>
+        <v>47.18</v>
       </c>
       <c r="L37" s="18" t="n">
-        <v>523.5700000000001</v>
+        <v>40.85</v>
       </c>
       <c r="M37" s="18" t="n">
-        <v>408.56</v>
+        <v>34.34</v>
       </c>
       <c r="N37" s="18" t="n">
-        <v>402.9</v>
+        <v>30.99</v>
       </c>
       <c r="O37" s="18" t="n">
-        <v>86.92</v>
+        <v>28.32</v>
       </c>
       <c r="P37" s="37" t="n">
-        <v>86.92</v>
+        <v>28.32</v>
       </c>
       <c r="Q37" s="18" t="n">
-        <v>218.97</v>
+        <v>25.58</v>
       </c>
       <c r="R37" s="18" t="n">
-        <v>8.23</v>
+        <v>22.77</v>
       </c>
       <c r="S37" s="18" t="n">
-        <v>37.94</v>
+        <v>19.91</v>
       </c>
       <c r="T37" s="18" t="n">
-        <v>67.19</v>
+        <v>16.97</v>
       </c>
       <c r="U37" s="37" t="n">
-        <v>67.19</v>
+        <v>16.97</v>
       </c>
       <c r="V37" s="18" t="n">
-        <v>101.5</v>
+        <v>13.97</v>
       </c>
       <c r="W37" s="18" t="n">
-        <v>113.11</v>
+        <v>10.89</v>
       </c>
       <c r="X37" s="18" t="n">
-        <v>148.07</v>
+        <v>7.75</v>
       </c>
       <c r="Y37" s="18" t="n">
-        <v>58.2</v>
+        <v>4.53</v>
       </c>
       <c r="Z37" s="37" t="n">
-        <v>58.2</v>
+        <v>4.53</v>
       </c>
       <c r="AA37" s="18" t="n">
-        <v>75.34</v>
+        <v>1.23</v>
       </c>
       <c r="AB37" s="19" t="n">
-        <v>96.64</v>
+        <v>0</v>
       </c>
       <c r="AC37" s="10" t="n"/>
       <c r="AD37" s="10" t="n"/>
@@ -22277,80 +22270,80 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>이연법인세부채</t>
+          <t>확정급여부채</t>
         </is>
       </c>
       <c r="E38" s="18" t="n">
-        <v>875.28</v>
+        <v>225.15</v>
       </c>
       <c r="F38" s="37" t="n">
-        <v>875.28</v>
+        <v>225.15</v>
       </c>
       <c r="G38" s="18" t="n">
-        <v>1025.97</v>
+        <v>221.68</v>
       </c>
       <c r="H38" s="18" t="n">
-        <v>955.71</v>
+        <v>193.02</v>
       </c>
       <c r="I38" s="18" t="n">
-        <v>1042.35</v>
+        <v>308.8</v>
       </c>
       <c r="J38" s="18" t="n">
-        <v>841.13</v>
+        <v>466.97</v>
       </c>
       <c r="K38" s="37" t="n">
-        <v>841.13</v>
+        <v>466.97</v>
       </c>
       <c r="L38" s="18" t="n">
-        <v>877.73</v>
+        <v>523.5700000000001</v>
       </c>
       <c r="M38" s="18" t="n">
-        <v>1192.51</v>
+        <v>408.56</v>
       </c>
       <c r="N38" s="18" t="n">
-        <v>1035.1</v>
+        <v>402.9</v>
       </c>
       <c r="O38" s="18" t="n">
-        <v>831.08</v>
+        <v>86.92</v>
       </c>
       <c r="P38" s="37" t="n">
-        <v>831.08</v>
+        <v>86.92</v>
       </c>
       <c r="Q38" s="18" t="n">
-        <v>748.67</v>
+        <v>218.97</v>
       </c>
       <c r="R38" s="18" t="n">
-        <v>711.24</v>
+        <v>8.23</v>
       </c>
       <c r="S38" s="18" t="n">
-        <v>675.05</v>
+        <v>37.94</v>
       </c>
       <c r="T38" s="18" t="n">
-        <v>413.81</v>
+        <v>67.19</v>
       </c>
       <c r="U38" s="37" t="n">
-        <v>413.81</v>
+        <v>67.19</v>
       </c>
       <c r="V38" s="18" t="n">
-        <v>418.6</v>
+        <v>101.5</v>
       </c>
       <c r="W38" s="18" t="n">
-        <v>498.2</v>
+        <v>113.11</v>
       </c>
       <c r="X38" s="18" t="n">
-        <v>497.7</v>
+        <v>148.07</v>
       </c>
       <c r="Y38" s="18" t="n">
-        <v>636.16</v>
+        <v>58.2</v>
       </c>
       <c r="Z38" s="37" t="n">
-        <v>636.16</v>
+        <v>58.2</v>
       </c>
       <c r="AA38" s="18" t="n">
-        <v>631.11</v>
+        <v>75.34</v>
       </c>
       <c r="AB38" s="19" t="n">
-        <v>585.23</v>
+        <v>96.64</v>
       </c>
       <c r="AC38" s="10" t="n"/>
       <c r="AD38" s="10" t="n"/>
@@ -22372,80 +22365,80 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>부채총계</t>
+          <t>이연법인세부채</t>
         </is>
       </c>
       <c r="E39" s="18" t="n">
-        <v>17946.53</v>
+        <v>875.28</v>
       </c>
       <c r="F39" s="37" t="n">
-        <v>17946.53</v>
+        <v>875.28</v>
       </c>
       <c r="G39" s="18" t="n">
-        <v>27621.05</v>
+        <v>1025.97</v>
       </c>
       <c r="H39" s="18" t="n">
-        <v>26898.68</v>
+        <v>955.71</v>
       </c>
       <c r="I39" s="18" t="n">
-        <v>28215.93</v>
+        <v>1042.35</v>
       </c>
       <c r="J39" s="18" t="n">
-        <v>25666.93</v>
+        <v>841.13</v>
       </c>
       <c r="K39" s="37" t="n">
-        <v>25666.93</v>
+        <v>841.13</v>
       </c>
       <c r="L39" s="18" t="n">
-        <v>22955.54</v>
+        <v>877.73</v>
       </c>
       <c r="M39" s="18" t="n">
-        <v>22082.03</v>
+        <v>1192.51</v>
       </c>
       <c r="N39" s="18" t="n">
-        <v>21698.66</v>
+        <v>1035.1</v>
       </c>
       <c r="O39" s="18" t="n">
-        <v>21298.68</v>
+        <v>831.08</v>
       </c>
       <c r="P39" s="37" t="n">
-        <v>21298.68</v>
+        <v>831.08</v>
       </c>
       <c r="Q39" s="18" t="n">
-        <v>20886.82</v>
+        <v>748.67</v>
       </c>
       <c r="R39" s="18" t="n">
-        <v>17719.91</v>
+        <v>711.24</v>
       </c>
       <c r="S39" s="18" t="n">
-        <v>19007.74</v>
+        <v>675.05</v>
       </c>
       <c r="T39" s="18" t="n">
-        <v>19210.59</v>
+        <v>413.81</v>
       </c>
       <c r="U39" s="37" t="n">
-        <v>19210.59</v>
+        <v>413.81</v>
       </c>
       <c r="V39" s="18" t="n">
-        <v>17335.29</v>
+        <v>418.6</v>
       </c>
       <c r="W39" s="18" t="n">
-        <v>17889.19</v>
+        <v>498.2</v>
       </c>
       <c r="X39" s="18" t="n">
-        <v>19590.11</v>
+        <v>497.7</v>
       </c>
       <c r="Y39" s="18" t="n">
-        <v>19744.59</v>
+        <v>636.16</v>
       </c>
       <c r="Z39" s="37" t="n">
-        <v>19744.59</v>
+        <v>636.16</v>
       </c>
       <c r="AA39" s="18" t="n">
-        <v>20273.9</v>
+        <v>631.11</v>
       </c>
       <c r="AB39" s="19" t="n">
-        <v>21315.85</v>
+        <v>585.23</v>
       </c>
       <c r="AC39" s="10" t="n"/>
       <c r="AD39" s="10" t="n"/>
@@ -22467,80 +22460,80 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>자본금</t>
+          <t>부채총계</t>
         </is>
       </c>
       <c r="E40" s="18" t="n">
-        <v>3072.67</v>
+        <v>17946.53</v>
       </c>
       <c r="F40" s="37" t="n">
-        <v>3072.67</v>
+        <v>17946.53</v>
       </c>
       <c r="G40" s="18" t="n">
-        <v>3072.67</v>
+        <v>27621.05</v>
       </c>
       <c r="H40" s="18" t="n">
-        <v>3072.67</v>
+        <v>26898.68</v>
       </c>
       <c r="I40" s="18" t="n">
-        <v>3072.67</v>
+        <v>28215.93</v>
       </c>
       <c r="J40" s="18" t="n">
-        <v>3072.67</v>
+        <v>25666.93</v>
       </c>
       <c r="K40" s="37" t="n">
-        <v>3072.67</v>
+        <v>25666.93</v>
       </c>
       <c r="L40" s="18" t="n">
-        <v>3072.67</v>
+        <v>22955.54</v>
       </c>
       <c r="M40" s="18" t="n">
-        <v>3072.67</v>
+        <v>22082.03</v>
       </c>
       <c r="N40" s="18" t="n">
-        <v>3072.67</v>
+        <v>21698.66</v>
       </c>
       <c r="O40" s="18" t="n">
-        <v>3072.67</v>
+        <v>21298.68</v>
       </c>
       <c r="P40" s="37" t="n">
-        <v>3072.67</v>
+        <v>21298.68</v>
       </c>
       <c r="Q40" s="18" t="n">
-        <v>3072.67</v>
+        <v>20886.82</v>
       </c>
       <c r="R40" s="18" t="n">
-        <v>3072.67</v>
+        <v>17719.91</v>
       </c>
       <c r="S40" s="18" t="n">
-        <v>3072.67</v>
+        <v>19007.74</v>
       </c>
       <c r="T40" s="18" t="n">
-        <v>3072.67</v>
+        <v>19210.59</v>
       </c>
       <c r="U40" s="37" t="n">
-        <v>3072.67</v>
+        <v>19210.59</v>
       </c>
       <c r="V40" s="18" t="n">
-        <v>3072.67</v>
+        <v>17335.29</v>
       </c>
       <c r="W40" s="18" t="n">
-        <v>3072.67</v>
+        <v>17889.19</v>
       </c>
       <c r="X40" s="18" t="n">
-        <v>3072.67</v>
+        <v>19590.11</v>
       </c>
       <c r="Y40" s="18" t="n">
-        <v>3072.67</v>
+        <v>19744.59</v>
       </c>
       <c r="Z40" s="37" t="n">
-        <v>3072.67</v>
+        <v>19744.59</v>
       </c>
       <c r="AA40" s="18" t="n">
-        <v>3072.67</v>
+        <v>20273.9</v>
       </c>
       <c r="AB40" s="19" t="n">
-        <v>3072.67</v>
+        <v>21315.85</v>
       </c>
       <c r="AC40" s="10" t="n"/>
       <c r="AD40" s="10" t="n"/>
@@ -22562,80 +22555,80 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>자본잉여금</t>
+          <t>자본금</t>
         </is>
       </c>
       <c r="E41" s="18" t="n">
-        <v>22064.38</v>
+        <v>3072.67</v>
       </c>
       <c r="F41" s="37" t="n">
-        <v>22064.38</v>
+        <v>3072.67</v>
       </c>
       <c r="G41" s="18" t="n">
-        <v>22064.38</v>
+        <v>3072.67</v>
       </c>
       <c r="H41" s="18" t="n">
-        <v>22064.38</v>
+        <v>3072.67</v>
       </c>
       <c r="I41" s="18" t="n">
-        <v>22064.38</v>
+        <v>3072.67</v>
       </c>
       <c r="J41" s="18" t="n">
-        <v>22064.38</v>
+        <v>3072.67</v>
       </c>
       <c r="K41" s="37" t="n">
-        <v>22064.38</v>
+        <v>3072.67</v>
       </c>
       <c r="L41" s="18" t="n">
-        <v>22064.38</v>
+        <v>3072.67</v>
       </c>
       <c r="M41" s="18" t="n">
-        <v>22064.38</v>
+        <v>3072.67</v>
       </c>
       <c r="N41" s="18" t="n">
-        <v>22064.38</v>
+        <v>3072.67</v>
       </c>
       <c r="O41" s="18" t="n">
-        <v>22064.38</v>
+        <v>3072.67</v>
       </c>
       <c r="P41" s="37" t="n">
-        <v>22064.38</v>
+        <v>3072.67</v>
       </c>
       <c r="Q41" s="18" t="n">
-        <v>22064.38</v>
+        <v>3072.67</v>
       </c>
       <c r="R41" s="18" t="n">
-        <v>22064.38</v>
+        <v>3072.67</v>
       </c>
       <c r="S41" s="18" t="n">
-        <v>22064.38</v>
+        <v>3072.67</v>
       </c>
       <c r="T41" s="18" t="n">
-        <v>22064.38</v>
+        <v>3072.67</v>
       </c>
       <c r="U41" s="37" t="n">
-        <v>22064.38</v>
+        <v>3072.67</v>
       </c>
       <c r="V41" s="18" t="n">
-        <v>22064.38</v>
+        <v>3072.67</v>
       </c>
       <c r="W41" s="18" t="n">
-        <v>22064.38</v>
+        <v>3072.67</v>
       </c>
       <c r="X41" s="18" t="n">
-        <v>22064.38</v>
+        <v>3072.67</v>
       </c>
       <c r="Y41" s="18" t="n">
-        <v>22033.95</v>
+        <v>3072.67</v>
       </c>
       <c r="Z41" s="37" t="n">
-        <v>22033.95</v>
+        <v>3072.67</v>
       </c>
       <c r="AA41" s="18" t="n">
-        <v>22033.95</v>
+        <v>3072.67</v>
       </c>
       <c r="AB41" s="19" t="n">
-        <v>22033.95</v>
+        <v>3072.67</v>
       </c>
       <c r="AC41" s="10" t="n"/>
       <c r="AD41" s="10" t="n"/>
@@ -22657,80 +22650,80 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>기타자본</t>
+          <t>자본잉여금</t>
         </is>
       </c>
       <c r="E42" s="18" t="n">
-        <v>0</v>
+        <v>22064.38</v>
       </c>
       <c r="F42" s="37" t="n">
-        <v>0</v>
+        <v>22064.38</v>
       </c>
       <c r="G42" s="18" t="n">
-        <v>0</v>
+        <v>22064.38</v>
       </c>
       <c r="H42" s="18" t="n">
-        <v>0</v>
+        <v>22064.38</v>
       </c>
       <c r="I42" s="18" t="n">
-        <v>0</v>
+        <v>22064.38</v>
       </c>
       <c r="J42" s="18" t="n">
-        <v>0</v>
+        <v>22064.38</v>
       </c>
       <c r="K42" s="37" t="n">
-        <v>0</v>
+        <v>22064.38</v>
       </c>
       <c r="L42" s="18" t="n">
-        <v>0</v>
+        <v>22064.38</v>
       </c>
       <c r="M42" s="18" t="n">
-        <v>0</v>
+        <v>22064.38</v>
       </c>
       <c r="N42" s="18" t="n">
-        <v>0</v>
+        <v>22064.38</v>
       </c>
       <c r="O42" s="18" t="n">
-        <v>0</v>
+        <v>22064.38</v>
       </c>
       <c r="P42" s="37" t="n">
-        <v>0</v>
+        <v>22064.38</v>
       </c>
       <c r="Q42" s="18" t="n">
-        <v>0</v>
+        <v>22064.38</v>
       </c>
       <c r="R42" s="18" t="n">
-        <v>0</v>
+        <v>22064.38</v>
       </c>
       <c r="S42" s="18" t="n">
-        <v>-141.91</v>
+        <v>22064.38</v>
       </c>
       <c r="T42" s="18" t="n">
-        <v>-141.91</v>
+        <v>22064.38</v>
       </c>
       <c r="U42" s="37" t="n">
-        <v>-141.91</v>
+        <v>22064.38</v>
       </c>
       <c r="V42" s="18" t="n">
-        <v>-141.91</v>
+        <v>22064.38</v>
       </c>
       <c r="W42" s="18" t="n">
-        <v>-141.91</v>
+        <v>22064.38</v>
       </c>
       <c r="X42" s="18" t="n">
-        <v>-141.91</v>
+        <v>22064.38</v>
       </c>
       <c r="Y42" s="18" t="n">
-        <v>-141.91</v>
+        <v>22033.95</v>
       </c>
       <c r="Z42" s="37" t="n">
-        <v>-141.91</v>
+        <v>22033.95</v>
       </c>
       <c r="AA42" s="18" t="n">
-        <v>-141.91</v>
+        <v>22033.95</v>
       </c>
       <c r="AB42" s="19" t="n">
-        <v>-141.91</v>
+        <v>22033.95</v>
       </c>
       <c r="AC42" s="10" t="n"/>
       <c r="AD42" s="10" t="n"/>
@@ -22752,80 +22745,80 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>기타포괄이익누계액</t>
+          <t>기타자본</t>
         </is>
       </c>
       <c r="E43" s="18" t="n">
-        <v>-58.8</v>
+        <v>0</v>
       </c>
       <c r="F43" s="37" t="n">
-        <v>-58.8</v>
+        <v>0</v>
       </c>
       <c r="G43" s="18" t="n">
-        <v>426.31</v>
+        <v>0</v>
       </c>
       <c r="H43" s="18" t="n">
-        <v>143.93</v>
+        <v>0</v>
       </c>
       <c r="I43" s="18" t="n">
-        <v>574.83</v>
+        <v>0</v>
       </c>
       <c r="J43" s="18" t="n">
-        <v>84.87</v>
+        <v>0</v>
       </c>
       <c r="K43" s="37" t="n">
-        <v>84.87</v>
+        <v>0</v>
       </c>
       <c r="L43" s="18" t="n">
-        <v>284.11</v>
+        <v>0</v>
       </c>
       <c r="M43" s="18" t="n">
-        <v>1328.1</v>
+        <v>0</v>
       </c>
       <c r="N43" s="18" t="n">
-        <v>830.99</v>
+        <v>0</v>
       </c>
       <c r="O43" s="18" t="n">
-        <v>694.91</v>
+        <v>0</v>
       </c>
       <c r="P43" s="37" t="n">
-        <v>694.91</v>
+        <v>0</v>
       </c>
       <c r="Q43" s="18" t="n">
-        <v>387.93</v>
+        <v>0</v>
       </c>
       <c r="R43" s="18" t="n">
-        <v>254.48</v>
+        <v>0</v>
       </c>
       <c r="S43" s="18" t="n">
-        <v>119.21</v>
+        <v>-141.91</v>
       </c>
       <c r="T43" s="18" t="n">
-        <v>-969.72</v>
+        <v>-141.91</v>
       </c>
       <c r="U43" s="37" t="n">
-        <v>-969.72</v>
+        <v>-141.91</v>
       </c>
       <c r="V43" s="18" t="n">
-        <v>-950.04</v>
+        <v>-141.91</v>
       </c>
       <c r="W43" s="18" t="n">
-        <v>-667.1900000000001</v>
+        <v>-141.91</v>
       </c>
       <c r="X43" s="18" t="n">
-        <v>-667.23</v>
+        <v>-141.91</v>
       </c>
       <c r="Y43" s="18" t="n">
-        <v>-623.74</v>
+        <v>-141.91</v>
       </c>
       <c r="Z43" s="37" t="n">
-        <v>-623.74</v>
+        <v>-141.91</v>
       </c>
       <c r="AA43" s="18" t="n">
-        <v>-640.0700000000001</v>
+        <v>-141.91</v>
       </c>
       <c r="AB43" s="19" t="n">
-        <v>-802.47</v>
+        <v>-141.91</v>
       </c>
       <c r="AC43" s="10" t="n"/>
       <c r="AD43" s="10" t="n"/>
@@ -22847,80 +22840,80 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>이익잉여금</t>
+          <t>기타포괄이익누계액</t>
         </is>
       </c>
       <c r="E44" s="18" t="n">
-        <v>5675.33</v>
+        <v>-58.8</v>
       </c>
       <c r="F44" s="37" t="n">
-        <v>5675.33</v>
+        <v>-58.8</v>
       </c>
       <c r="G44" s="18" t="n">
-        <v>5892.02</v>
+        <v>426.31</v>
       </c>
       <c r="H44" s="18" t="n">
-        <v>6045.12</v>
+        <v>143.93</v>
       </c>
       <c r="I44" s="18" t="n">
-        <v>8461.700000000001</v>
+        <v>574.83</v>
       </c>
       <c r="J44" s="18" t="n">
-        <v>7697.86</v>
+        <v>84.87</v>
       </c>
       <c r="K44" s="37" t="n">
-        <v>7697.86</v>
+        <v>84.87</v>
       </c>
       <c r="L44" s="18" t="n">
-        <v>7956.17</v>
+        <v>284.11</v>
       </c>
       <c r="M44" s="18" t="n">
-        <v>8425.280000000001</v>
+        <v>1328.1</v>
       </c>
       <c r="N44" s="18" t="n">
-        <v>8313.77</v>
+        <v>830.99</v>
       </c>
       <c r="O44" s="18" t="n">
-        <v>10681.63</v>
+        <v>694.91</v>
       </c>
       <c r="P44" s="37" t="n">
-        <v>10681.63</v>
+        <v>694.91</v>
       </c>
       <c r="Q44" s="18" t="n">
-        <v>11149.72</v>
+        <v>387.93</v>
       </c>
       <c r="R44" s="18" t="n">
-        <v>20929.86</v>
+        <v>254.48</v>
       </c>
       <c r="S44" s="18" t="n">
-        <v>22323.55</v>
+        <v>119.21</v>
       </c>
       <c r="T44" s="18" t="n">
-        <v>23320.1</v>
+        <v>-969.72</v>
       </c>
       <c r="U44" s="37" t="n">
-        <v>23320.1</v>
+        <v>-969.72</v>
       </c>
       <c r="V44" s="18" t="n">
-        <v>23906.82</v>
+        <v>-950.04</v>
       </c>
       <c r="W44" s="18" t="n">
-        <v>24281.74</v>
+        <v>-667.1900000000001</v>
       </c>
       <c r="X44" s="18" t="n">
-        <v>25095.65</v>
+        <v>-667.23</v>
       </c>
       <c r="Y44" s="18" t="n">
-        <v>26285.42</v>
+        <v>-623.74</v>
       </c>
       <c r="Z44" s="37" t="n">
-        <v>26285.42</v>
+        <v>-623.74</v>
       </c>
       <c r="AA44" s="18" t="n">
-        <v>28393.62</v>
+        <v>-640.0700000000001</v>
       </c>
       <c r="AB44" s="19" t="n">
-        <v>32281.56</v>
+        <v>-802.47</v>
       </c>
       <c r="AC44" s="10" t="n"/>
       <c r="AD44" s="10" t="n"/>
@@ -22942,80 +22935,80 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>자본총계</t>
+          <t>이익잉여금</t>
         </is>
       </c>
       <c r="E45" s="18" t="n">
-        <v>30753.58</v>
+        <v>5675.33</v>
       </c>
       <c r="F45" s="37" t="n">
-        <v>30753.58</v>
+        <v>5675.33</v>
       </c>
       <c r="G45" s="18" t="n">
-        <v>31455.39</v>
+        <v>5892.02</v>
       </c>
       <c r="H45" s="18" t="n">
-        <v>31326.11</v>
+        <v>6045.12</v>
       </c>
       <c r="I45" s="18" t="n">
-        <v>34173.58</v>
+        <v>8461.700000000001</v>
       </c>
       <c r="J45" s="18" t="n">
-        <v>32919.78</v>
+        <v>7697.86</v>
       </c>
       <c r="K45" s="37" t="n">
-        <v>32919.78</v>
+        <v>7697.86</v>
       </c>
       <c r="L45" s="18" t="n">
-        <v>33377.33</v>
+        <v>7956.17</v>
       </c>
       <c r="M45" s="18" t="n">
-        <v>34890.43</v>
+        <v>8425.280000000001</v>
       </c>
       <c r="N45" s="18" t="n">
-        <v>34281.81</v>
+        <v>8313.77</v>
       </c>
       <c r="O45" s="18" t="n">
-        <v>36513.59</v>
+        <v>10681.63</v>
       </c>
       <c r="P45" s="37" t="n">
-        <v>36513.59</v>
+        <v>10681.63</v>
       </c>
       <c r="Q45" s="18" t="n">
-        <v>36674.7</v>
+        <v>11149.72</v>
       </c>
       <c r="R45" s="18" t="n">
-        <v>46321.4</v>
+        <v>20929.86</v>
       </c>
       <c r="S45" s="18" t="n">
-        <v>47437.9</v>
+        <v>22323.55</v>
       </c>
       <c r="T45" s="18" t="n">
-        <v>47345.52</v>
+        <v>23320.1</v>
       </c>
       <c r="U45" s="37" t="n">
-        <v>47345.52</v>
+        <v>23320.1</v>
       </c>
       <c r="V45" s="18" t="n">
-        <v>47951.92</v>
+        <v>23906.82</v>
       </c>
       <c r="W45" s="18" t="n">
-        <v>48609.69</v>
+        <v>24281.74</v>
       </c>
       <c r="X45" s="18" t="n">
-        <v>49423.56</v>
+        <v>25095.65</v>
       </c>
       <c r="Y45" s="18" t="n">
-        <v>50626.4</v>
+        <v>26285.42</v>
       </c>
       <c r="Z45" s="37" t="n">
-        <v>50626.4</v>
+        <v>26285.42</v>
       </c>
       <c r="AA45" s="18" t="n">
-        <v>52718.26</v>
+        <v>28393.62</v>
       </c>
       <c r="AB45" s="19" t="n">
-        <v>56443.79</v>
+        <v>32281.56</v>
       </c>
       <c r="AC45" s="10" t="n"/>
       <c r="AD45" s="10" t="n"/>
@@ -23037,80 +23030,80 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>부채와자본총계</t>
+          <t>자본총계</t>
         </is>
       </c>
       <c r="E46" s="18" t="n">
-        <v>48700.11</v>
+        <v>30753.58</v>
       </c>
       <c r="F46" s="37" t="n">
-        <v>48700.11</v>
+        <v>30753.58</v>
       </c>
       <c r="G46" s="18" t="n">
-        <v>59076.44</v>
+        <v>31455.39</v>
       </c>
       <c r="H46" s="18" t="n">
-        <v>58224.79</v>
+        <v>31326.11</v>
       </c>
       <c r="I46" s="18" t="n">
-        <v>62389.51</v>
+        <v>34173.58</v>
       </c>
       <c r="J46" s="18" t="n">
-        <v>58586.72</v>
+        <v>32919.78</v>
       </c>
       <c r="K46" s="37" t="n">
-        <v>58586.72</v>
+        <v>32919.78</v>
       </c>
       <c r="L46" s="18" t="n">
-        <v>56332.87</v>
+        <v>33377.33</v>
       </c>
       <c r="M46" s="18" t="n">
-        <v>56972.46</v>
+        <v>34890.43</v>
       </c>
       <c r="N46" s="18" t="n">
-        <v>55980.47</v>
+        <v>34281.81</v>
       </c>
       <c r="O46" s="18" t="n">
-        <v>57812.27</v>
+        <v>36513.59</v>
       </c>
       <c r="P46" s="37" t="n">
-        <v>57812.27</v>
+        <v>36513.59</v>
       </c>
       <c r="Q46" s="18" t="n">
-        <v>57561.52</v>
+        <v>36674.7</v>
       </c>
       <c r="R46" s="18" t="n">
-        <v>64041.3</v>
+        <v>46321.4</v>
       </c>
       <c r="S46" s="18" t="n">
-        <v>66445.64</v>
+        <v>47437.9</v>
       </c>
       <c r="T46" s="18" t="n">
-        <v>66556.11</v>
+        <v>47345.52</v>
       </c>
       <c r="U46" s="37" t="n">
-        <v>66556.11</v>
+        <v>47345.52</v>
       </c>
       <c r="V46" s="18" t="n">
-        <v>65287.21</v>
+        <v>47951.92</v>
       </c>
       <c r="W46" s="18" t="n">
-        <v>66498.89</v>
+        <v>48609.69</v>
       </c>
       <c r="X46" s="18" t="n">
-        <v>69013.67999999999</v>
+        <v>49423.56</v>
       </c>
       <c r="Y46" s="18" t="n">
-        <v>70370.99000000001</v>
+        <v>50626.4</v>
       </c>
       <c r="Z46" s="37" t="n">
-        <v>70370.99000000001</v>
+        <v>50626.4</v>
       </c>
       <c r="AA46" s="18" t="n">
-        <v>72992.16</v>
+        <v>52718.26</v>
       </c>
       <c r="AB46" s="19" t="n">
-        <v>77759.64</v>
+        <v>56443.79</v>
       </c>
       <c r="AC46" s="10" t="n"/>
       <c r="AD46" s="10" t="n"/>
@@ -23132,80 +23125,80 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>지배주주지분</t>
+          <t>부채와자본총계</t>
         </is>
       </c>
       <c r="E47" s="18" t="n">
-        <v>30753.58</v>
+        <v>48700.11</v>
       </c>
       <c r="F47" s="37" t="n">
-        <v>30753.58</v>
+        <v>48700.11</v>
       </c>
       <c r="G47" s="18" t="n">
-        <v>31455.39</v>
+        <v>59076.44</v>
       </c>
       <c r="H47" s="18" t="n">
-        <v>31326.11</v>
+        <v>58224.79</v>
       </c>
       <c r="I47" s="18" t="n">
-        <v>34173.58</v>
+        <v>62389.51</v>
       </c>
       <c r="J47" s="18" t="n">
-        <v>32919.78</v>
+        <v>58586.72</v>
       </c>
       <c r="K47" s="37" t="n">
-        <v>32919.78</v>
+        <v>58586.72</v>
       </c>
       <c r="L47" s="18" t="n">
-        <v>33377.33</v>
+        <v>56332.87</v>
       </c>
       <c r="M47" s="18" t="n">
-        <v>34890.43</v>
+        <v>56972.46</v>
       </c>
       <c r="N47" s="18" t="n">
-        <v>34281.81</v>
+        <v>55980.47</v>
       </c>
       <c r="O47" s="18" t="n">
-        <v>36513.59</v>
+        <v>57812.27</v>
       </c>
       <c r="P47" s="37" t="n">
-        <v>36513.59</v>
+        <v>57812.27</v>
       </c>
       <c r="Q47" s="18" t="n">
-        <v>36674.7</v>
+        <v>57561.52</v>
       </c>
       <c r="R47" s="18" t="n">
-        <v>46321.4</v>
+        <v>64041.3</v>
       </c>
       <c r="S47" s="18" t="n">
-        <v>47437.9</v>
+        <v>66445.64</v>
       </c>
       <c r="T47" s="18" t="n">
-        <v>47345.52</v>
+        <v>66556.11</v>
       </c>
       <c r="U47" s="37" t="n">
-        <v>47345.52</v>
+        <v>66556.11</v>
       </c>
       <c r="V47" s="18" t="n">
-        <v>47951.92</v>
+        <v>65287.21</v>
       </c>
       <c r="W47" s="18" t="n">
-        <v>48609.69</v>
+        <v>66498.89</v>
       </c>
       <c r="X47" s="18" t="n">
-        <v>49423.56</v>
+        <v>69013.67999999999</v>
       </c>
       <c r="Y47" s="18" t="n">
-        <v>50626.4</v>
+        <v>70370.99000000001</v>
       </c>
       <c r="Z47" s="37" t="n">
-        <v>50626.4</v>
+        <v>70370.99000000001</v>
       </c>
       <c r="AA47" s="18" t="n">
-        <v>52718.26</v>
+        <v>72992.16</v>
       </c>
       <c r="AB47" s="19" t="n">
-        <v>56443.79</v>
+        <v>77759.64</v>
       </c>
       <c r="AC47" s="10" t="n"/>
       <c r="AD47" s="10" t="n"/>
@@ -23227,80 +23220,80 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>총차입금</t>
+          <t>지배주주지분</t>
         </is>
       </c>
       <c r="E48" s="18" t="n">
-        <v>8814.99</v>
+        <v>30753.58</v>
       </c>
       <c r="F48" s="37" t="n">
-        <v>8814.99</v>
+        <v>30753.58</v>
       </c>
       <c r="G48" s="18" t="n">
-        <v>17186.21</v>
+        <v>31455.39</v>
       </c>
       <c r="H48" s="18" t="n">
-        <v>17100</v>
+        <v>31326.11</v>
       </c>
       <c r="I48" s="18" t="n">
-        <v>17800</v>
+        <v>34173.58</v>
       </c>
       <c r="J48" s="18" t="n">
-        <v>17800</v>
+        <v>32919.78</v>
       </c>
       <c r="K48" s="37" t="n">
-        <v>17800</v>
+        <v>32919.78</v>
       </c>
       <c r="L48" s="18" t="n">
-        <v>17800</v>
+        <v>33377.33</v>
       </c>
       <c r="M48" s="18" t="n">
-        <v>17100</v>
+        <v>34890.43</v>
       </c>
       <c r="N48" s="18" t="n">
-        <v>17100</v>
+        <v>34281.81</v>
       </c>
       <c r="O48" s="18" t="n">
-        <v>17100</v>
+        <v>36513.59</v>
       </c>
       <c r="P48" s="37" t="n">
-        <v>17100</v>
+        <v>36513.59</v>
       </c>
       <c r="Q48" s="18" t="n">
-        <v>16891.59</v>
+        <v>36674.7</v>
       </c>
       <c r="R48" s="18" t="n">
-        <v>12728.94</v>
+        <v>46321.4</v>
       </c>
       <c r="S48" s="18" t="n">
-        <v>14291.52</v>
+        <v>47437.9</v>
       </c>
       <c r="T48" s="18" t="n">
-        <v>14200</v>
+        <v>47345.52</v>
       </c>
       <c r="U48" s="37" t="n">
-        <v>14200</v>
+        <v>47345.52</v>
       </c>
       <c r="V48" s="18" t="n">
-        <v>14200</v>
+        <v>47951.92</v>
       </c>
       <c r="W48" s="18" t="n">
-        <v>16200</v>
+        <v>48609.69</v>
       </c>
       <c r="X48" s="18" t="n">
-        <v>17700</v>
+        <v>49423.56</v>
       </c>
       <c r="Y48" s="18" t="n">
-        <v>17700</v>
+        <v>50626.4</v>
       </c>
       <c r="Z48" s="37" t="n">
-        <v>17700</v>
+        <v>50626.4</v>
       </c>
       <c r="AA48" s="18" t="n">
-        <v>17700</v>
+        <v>52718.26</v>
       </c>
       <c r="AB48" s="19" t="n">
-        <v>17700</v>
+        <v>56443.79</v>
       </c>
       <c r="AC48" s="10" t="n"/>
       <c r="AD48" s="10" t="n"/>
@@ -23322,80 +23315,80 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>순차입금</t>
+          <t>총차입금</t>
         </is>
       </c>
       <c r="E49" s="18" t="n">
-        <v>916.8099999999999</v>
+        <v>8814.99</v>
       </c>
       <c r="F49" s="37" t="n">
-        <v>916.8099999999999</v>
+        <v>8814.99</v>
       </c>
       <c r="G49" s="18" t="n">
-        <v>9878.200000000001</v>
+        <v>17186.21</v>
       </c>
       <c r="H49" s="18" t="n">
-        <v>13776.34</v>
+        <v>17100</v>
       </c>
       <c r="I49" s="18" t="n">
-        <v>13784.67</v>
+        <v>17800</v>
       </c>
       <c r="J49" s="18" t="n">
-        <v>13943.95</v>
+        <v>17800</v>
       </c>
       <c r="K49" s="37" t="n">
-        <v>13943.95</v>
+        <v>17800</v>
       </c>
       <c r="L49" s="18" t="n">
-        <v>10402.97</v>
+        <v>17800</v>
       </c>
       <c r="M49" s="18" t="n">
-        <v>8491.620000000001</v>
+        <v>17100</v>
       </c>
       <c r="N49" s="18" t="n">
-        <v>6205.7</v>
+        <v>17100</v>
       </c>
       <c r="O49" s="18" t="n">
-        <v>6053.04</v>
+        <v>17100</v>
       </c>
       <c r="P49" s="37" t="n">
-        <v>6053.04</v>
+        <v>17100</v>
       </c>
       <c r="Q49" s="18" t="n">
-        <v>4578.72</v>
+        <v>16891.59</v>
       </c>
       <c r="R49" s="18" t="n">
-        <v>-11477.14</v>
+        <v>12728.94</v>
       </c>
       <c r="S49" s="18" t="n">
-        <v>-11597.53</v>
+        <v>14291.52</v>
       </c>
       <c r="T49" s="18" t="n">
-        <v>-14464.16</v>
+        <v>14200</v>
       </c>
       <c r="U49" s="37" t="n">
-        <v>-14464.16</v>
+        <v>14200</v>
       </c>
       <c r="V49" s="18" t="n">
-        <v>-12461.87</v>
+        <v>14200</v>
       </c>
       <c r="W49" s="18" t="n">
-        <v>-11925.64</v>
+        <v>16200</v>
       </c>
       <c r="X49" s="18" t="n">
-        <v>-13060.96</v>
+        <v>17700</v>
       </c>
       <c r="Y49" s="18" t="n">
-        <v>-12732.78</v>
+        <v>17700</v>
       </c>
       <c r="Z49" s="37" t="n">
-        <v>-12732.78</v>
+        <v>17700</v>
       </c>
       <c r="AA49" s="18" t="n">
-        <v>-14874.17</v>
+        <v>17700</v>
       </c>
       <c r="AB49" s="19" t="n">
-        <v>-17857.17</v>
+        <v>17700</v>
       </c>
       <c r="AC49" s="10" t="n"/>
       <c r="AD49" s="10" t="n"/>
@@ -23417,80 +23410,80 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>이자발생자산</t>
+          <t>순차입금</t>
         </is>
       </c>
       <c r="E50" s="18" t="n">
-        <v>14270.76</v>
+        <v>916.8099999999999</v>
       </c>
       <c r="F50" s="37" t="n">
-        <v>14270.76</v>
+        <v>916.8099999999999</v>
       </c>
       <c r="G50" s="18" t="n">
-        <v>14302.52</v>
+        <v>9878.200000000001</v>
       </c>
       <c r="H50" s="18" t="n">
-        <v>10956.15</v>
+        <v>13776.34</v>
       </c>
       <c r="I50" s="18" t="n">
-        <v>12200.25</v>
+        <v>13784.67</v>
       </c>
       <c r="J50" s="18" t="n">
-        <v>11411.44</v>
+        <v>13943.95</v>
       </c>
       <c r="K50" s="37" t="n">
-        <v>11411.44</v>
+        <v>13943.95</v>
       </c>
       <c r="L50" s="18" t="n">
-        <v>15204.62</v>
+        <v>10402.97</v>
       </c>
       <c r="M50" s="18" t="n">
-        <v>17737.48</v>
+        <v>8491.620000000001</v>
       </c>
       <c r="N50" s="18" t="n">
-        <v>19337.92</v>
+        <v>6205.7</v>
       </c>
       <c r="O50" s="18" t="n">
-        <v>19504.74</v>
+        <v>6053.04</v>
       </c>
       <c r="P50" s="37" t="n">
-        <v>19504.74</v>
+        <v>6053.04</v>
       </c>
       <c r="Q50" s="18" t="n">
-        <v>20460.57</v>
+        <v>4578.72</v>
       </c>
       <c r="R50" s="18" t="n">
-        <v>31739.03</v>
+        <v>-11477.14</v>
       </c>
       <c r="S50" s="18" t="n">
-        <v>32929.34</v>
+        <v>-11597.53</v>
       </c>
       <c r="T50" s="18" t="n">
-        <v>35341.31</v>
+        <v>-14464.16</v>
       </c>
       <c r="U50" s="37" t="n">
-        <v>35341.31</v>
+        <v>-14464.16</v>
       </c>
       <c r="V50" s="18" t="n">
-        <v>33736.69</v>
+        <v>-12461.87</v>
       </c>
       <c r="W50" s="18" t="n">
-        <v>35536.26</v>
+        <v>-11925.64</v>
       </c>
       <c r="X50" s="18" t="n">
-        <v>38452.94</v>
+        <v>-13060.96</v>
       </c>
       <c r="Y50" s="18" t="n">
-        <v>38317.87</v>
+        <v>-12732.78</v>
       </c>
       <c r="Z50" s="37" t="n">
-        <v>38317.87</v>
+        <v>-12732.78</v>
       </c>
       <c r="AA50" s="18" t="n">
-        <v>41001.54</v>
+        <v>-14874.17</v>
       </c>
       <c r="AB50" s="19" t="n">
-        <v>45770.84</v>
+        <v>-17857.17</v>
       </c>
       <c r="AC50" s="10" t="n"/>
       <c r="AD50" s="10" t="n"/>
@@ -23512,66 +23505,81 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>장기금융부채(face)</t>
-        </is>
-      </c>
-      <c r="F51" s="9" t="n"/>
+          <t>이자발생자산</t>
+        </is>
+      </c>
+      <c r="E51" s="18" t="n">
+        <v>14270.76</v>
+      </c>
+      <c r="F51" s="37" t="n">
+        <v>14270.76</v>
+      </c>
       <c r="G51" s="18" t="n">
-        <v>13500</v>
+        <v>14302.52</v>
       </c>
       <c r="H51" s="18" t="n">
-        <v>13500</v>
+        <v>10956.15</v>
       </c>
       <c r="I51" s="18" t="n">
-        <v>13500</v>
+        <v>12200.25</v>
       </c>
       <c r="J51" s="18" t="n">
-        <v>13500</v>
+        <v>11411.44</v>
       </c>
       <c r="K51" s="37" t="n">
-        <v>13500</v>
+        <v>11411.44</v>
       </c>
       <c r="L51" s="18" t="n">
-        <v>13291.59</v>
+        <v>15204.62</v>
       </c>
       <c r="M51" s="18" t="n">
-        <v>12728.94</v>
+        <v>17737.48</v>
       </c>
       <c r="N51" s="18" t="n">
-        <v>12166.45</v>
+        <v>19337.92</v>
       </c>
       <c r="O51" s="18" t="n">
-        <v>11603.96</v>
+        <v>19504.74</v>
       </c>
       <c r="P51" s="37" t="n">
-        <v>11603.96</v>
+        <v>19504.74</v>
       </c>
       <c r="Q51" s="18" t="n">
-        <v>11041.47</v>
+        <v>20460.57</v>
       </c>
       <c r="R51" s="18" t="n">
-        <v>10478.98</v>
+        <v>31739.03</v>
       </c>
       <c r="S51" s="18" t="n">
-        <v>12874.88</v>
+        <v>32929.34</v>
       </c>
       <c r="T51" s="18" t="n">
-        <v>14200</v>
+        <v>35341.31</v>
       </c>
       <c r="U51" s="37" t="n">
-        <v>14200</v>
+        <v>35341.31</v>
       </c>
       <c r="V51" s="18" t="n">
-        <v>14200</v>
+        <v>33736.69</v>
       </c>
       <c r="W51" s="18" t="n">
-        <v>14200</v>
+        <v>35536.26</v>
       </c>
       <c r="X51" s="18" t="n">
-        <v>15700</v>
-      </c>
-      <c r="Z51" s="9" t="n"/>
-      <c r="AB51" s="5" t="n"/>
+        <v>38452.94</v>
+      </c>
+      <c r="Y51" s="18" t="n">
+        <v>38317.87</v>
+      </c>
+      <c r="Z51" s="37" t="n">
+        <v>38317.87</v>
+      </c>
+      <c r="AA51" s="18" t="n">
+        <v>41001.54</v>
+      </c>
+      <c r="AB51" s="19" t="n">
+        <v>45770.84</v>
+      </c>
       <c r="AC51" s="10" t="n"/>
       <c r="AD51" s="10" t="n"/>
       <c r="AE51" s="11" t="n"/>
@@ -23592,14 +23600,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>유동성장기부채</t>
+          <t>당기법인세자산(선급법인세)</t>
         </is>
       </c>
       <c r="F52" s="9" t="n"/>
-      <c r="H52" s="18" t="n">
-        <v>1600</v>
-      </c>
       <c r="K52" s="9" t="n"/>
+      <c r="N52" s="18" t="n">
+        <v>82.65000000000001</v>
+      </c>
       <c r="P52" s="9" t="n"/>
       <c r="U52" s="9" t="n"/>
       <c r="Z52" s="9" t="n"/>
@@ -23624,18 +23632,39 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>당기법인세자산(선급법인세)</t>
+          <t>기타비유동부채</t>
         </is>
       </c>
       <c r="F53" s="9" t="n"/>
       <c r="K53" s="9" t="n"/>
-      <c r="N53" s="18" t="n">
-        <v>82.65000000000001</v>
-      </c>
       <c r="P53" s="9" t="n"/>
-      <c r="U53" s="9" t="n"/>
-      <c r="Z53" s="9" t="n"/>
-      <c r="AB53" s="5" t="n"/>
+      <c r="T53" s="18" t="n">
+        <v>9.58</v>
+      </c>
+      <c r="U53" s="37" t="n">
+        <v>9.58</v>
+      </c>
+      <c r="V53" s="18" t="n">
+        <v>9.98</v>
+      </c>
+      <c r="W53" s="18" t="n">
+        <v>8.949999999999999</v>
+      </c>
+      <c r="X53" s="18" t="n">
+        <v>9.82</v>
+      </c>
+      <c r="Y53" s="18" t="n">
+        <v>6.81</v>
+      </c>
+      <c r="Z53" s="37" t="n">
+        <v>6.81</v>
+      </c>
+      <c r="AA53" s="18" t="n">
+        <v>7.51</v>
+      </c>
+      <c r="AB53" s="19" t="n">
+        <v>5.65</v>
+      </c>
       <c r="AC53" s="10" t="n"/>
       <c r="AD53" s="10" t="n"/>
       <c r="AE53" s="11" t="n"/>
@@ -23656,38 +23685,24 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>기타비유동부채</t>
+          <t>투자부동산</t>
         </is>
       </c>
       <c r="F54" s="9" t="n"/>
       <c r="K54" s="9" t="n"/>
       <c r="P54" s="9" t="n"/>
-      <c r="T54" s="18" t="n">
-        <v>9.58</v>
-      </c>
-      <c r="U54" s="37" t="n">
-        <v>9.58</v>
-      </c>
-      <c r="V54" s="18" t="n">
-        <v>9.98</v>
-      </c>
-      <c r="W54" s="18" t="n">
-        <v>8.949999999999999</v>
-      </c>
-      <c r="X54" s="18" t="n">
-        <v>9.82</v>
-      </c>
+      <c r="U54" s="9" t="n"/>
       <c r="Y54" s="18" t="n">
-        <v>6.81</v>
+        <v>8169.29</v>
       </c>
       <c r="Z54" s="37" t="n">
-        <v>6.81</v>
+        <v>8169.29</v>
       </c>
       <c r="AA54" s="18" t="n">
-        <v>7.51</v>
+        <v>8169.29</v>
       </c>
       <c r="AB54" s="19" t="n">
-        <v>5.65</v>
+        <v>8169.29</v>
       </c>
       <c r="AC54" s="10" t="n"/>
       <c r="AD54" s="10" t="n"/>
@@ -23709,24 +23724,16 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>투자부동산</t>
+          <t>매각예정비유동자산및처분자산</t>
         </is>
       </c>
       <c r="F55" s="9" t="n"/>
       <c r="K55" s="9" t="n"/>
       <c r="P55" s="9" t="n"/>
       <c r="U55" s="9" t="n"/>
-      <c r="Y55" s="18" t="n">
-        <v>8169.29</v>
-      </c>
-      <c r="Z55" s="37" t="n">
-        <v>8169.29</v>
-      </c>
-      <c r="AA55" s="18" t="n">
-        <v>8169.29</v>
-      </c>
+      <c r="Z55" s="9" t="n"/>
       <c r="AB55" s="19" t="n">
-        <v>8169.29</v>
+        <v>986.25</v>
       </c>
       <c r="AC55" s="10" t="n"/>
       <c r="AD55" s="10" t="n"/>
@@ -23748,16 +23755,78 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>매각예정비유동자산및처분자산</t>
-        </is>
+          <t>매출액(수익)</t>
+        </is>
+      </c>
+      <c r="E56" s="18" t="n">
+        <v>13028.42</v>
       </c>
       <c r="F56" s="9" t="n"/>
-      <c r="K56" s="9" t="n"/>
-      <c r="P56" s="9" t="n"/>
-      <c r="U56" s="9" t="n"/>
-      <c r="Z56" s="9" t="n"/>
+      <c r="G56" s="18" t="n">
+        <v>9661.41</v>
+      </c>
+      <c r="H56" s="18" t="n">
+        <v>7581.21</v>
+      </c>
+      <c r="I56" s="18" t="n">
+        <v>11424.27</v>
+      </c>
+      <c r="J56" s="18" t="n">
+        <v>12123.76</v>
+      </c>
+      <c r="K56" s="37" t="n">
+        <v>40790.65</v>
+      </c>
+      <c r="L56" s="18" t="n">
+        <v>7648.6</v>
+      </c>
+      <c r="M56" s="18" t="n">
+        <v>6882.17</v>
+      </c>
+      <c r="N56" s="18" t="n">
+        <v>4143.53</v>
+      </c>
+      <c r="O56" s="18" t="n">
+        <v>6989.32</v>
+      </c>
+      <c r="P56" s="37" t="n">
+        <v>25663.62</v>
+      </c>
+      <c r="Q56" s="18" t="n">
+        <v>4256.38</v>
+      </c>
+      <c r="R56" s="18" t="n">
+        <v>2062.35</v>
+      </c>
+      <c r="S56" s="18" t="n">
+        <v>3378.91</v>
+      </c>
+      <c r="T56" s="18" t="n">
+        <v>4838.84</v>
+      </c>
+      <c r="U56" s="37" t="n">
+        <v>14536.48</v>
+      </c>
+      <c r="V56" s="18" t="n">
+        <v>1560</v>
+      </c>
+      <c r="W56" s="18" t="n">
+        <v>2719.07</v>
+      </c>
+      <c r="X56" s="18" t="n">
+        <v>2291.1</v>
+      </c>
+      <c r="Y56" s="18" t="n">
+        <v>2224.94</v>
+      </c>
+      <c r="Z56" s="37" t="n">
+        <v>8795.110000000001</v>
+      </c>
+      <c r="AA56" s="18" t="n">
+        <v>2882.21</v>
+      </c>
       <c r="AB56" s="19" t="n">
-        <v>986.25</v>
+        <v>4568.32</v>
       </c>
       <c r="AC56" s="10" t="n"/>
       <c r="AD56" s="10" t="n"/>
@@ -23779,78 +23848,78 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>매출액(수익)</t>
+          <t>매출원가</t>
         </is>
       </c>
       <c r="E57" s="18" t="n">
-        <v>13028.42</v>
+        <v>10701</v>
       </c>
       <c r="F57" s="9" t="n"/>
       <c r="G57" s="18" t="n">
-        <v>9661.41</v>
+        <v>8461.34</v>
       </c>
       <c r="H57" s="18" t="n">
-        <v>7581.21</v>
+        <v>6482.02</v>
       </c>
       <c r="I57" s="18" t="n">
-        <v>11424.27</v>
+        <v>7404.42</v>
       </c>
       <c r="J57" s="18" t="n">
-        <v>12123.76</v>
+        <v>11122.52</v>
       </c>
       <c r="K57" s="37" t="n">
-        <v>40790.65</v>
+        <v>33470.3</v>
       </c>
       <c r="L57" s="18" t="n">
-        <v>7648.6</v>
+        <v>6681.99</v>
       </c>
       <c r="M57" s="18" t="n">
-        <v>6882.17</v>
+        <v>5476.61</v>
       </c>
       <c r="N57" s="18" t="n">
-        <v>4143.53</v>
+        <v>3173.68</v>
       </c>
       <c r="O57" s="18" t="n">
-        <v>6989.32</v>
+        <v>4386.04</v>
       </c>
       <c r="P57" s="37" t="n">
-        <v>25663.62</v>
+        <v>19718.32</v>
       </c>
       <c r="Q57" s="18" t="n">
-        <v>4256.38</v>
+        <v>3373.95</v>
       </c>
       <c r="R57" s="18" t="n">
-        <v>2062.35</v>
+        <v>1498.34</v>
       </c>
       <c r="S57" s="18" t="n">
-        <v>3378.91</v>
+        <v>1436.31</v>
       </c>
       <c r="T57" s="18" t="n">
-        <v>4838.84</v>
+        <v>3741.01</v>
       </c>
       <c r="U57" s="37" t="n">
-        <v>14536.48</v>
+        <v>10049.61</v>
       </c>
       <c r="V57" s="18" t="n">
-        <v>1560</v>
+        <v>1065.96</v>
       </c>
       <c r="W57" s="18" t="n">
-        <v>2719.07</v>
+        <v>1909.47</v>
       </c>
       <c r="X57" s="18" t="n">
-        <v>2291.1</v>
+        <v>1702.97</v>
       </c>
       <c r="Y57" s="18" t="n">
-        <v>2224.94</v>
+        <v>1502.82</v>
       </c>
       <c r="Z57" s="37" t="n">
-        <v>8795.110000000001</v>
+        <v>6181.22</v>
       </c>
       <c r="AA57" s="18" t="n">
-        <v>2882.21</v>
+        <v>1886.8</v>
       </c>
       <c r="AB57" s="19" t="n">
-        <v>4568.32</v>
+        <v>2325.04</v>
       </c>
       <c r="AC57" s="10" t="n"/>
       <c r="AD57" s="10" t="n"/>
@@ -23872,78 +23941,78 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>매출원가</t>
+          <t>매출총이익</t>
         </is>
       </c>
       <c r="E58" s="18" t="n">
-        <v>10701</v>
+        <v>2327.4</v>
       </c>
       <c r="F58" s="9" t="n"/>
       <c r="G58" s="18" t="n">
-        <v>8461.34</v>
+        <v>1200.06</v>
       </c>
       <c r="H58" s="18" t="n">
-        <v>6482.02</v>
+        <v>1099.19</v>
       </c>
       <c r="I58" s="18" t="n">
-        <v>7404.42</v>
+        <v>4019.85</v>
       </c>
       <c r="J58" s="18" t="n">
-        <v>11122.52</v>
+        <v>1001.24</v>
       </c>
       <c r="K58" s="37" t="n">
-        <v>33470.3</v>
+        <v>7320.34</v>
       </c>
       <c r="L58" s="18" t="n">
-        <v>6681.99</v>
+        <v>966.61</v>
       </c>
       <c r="M58" s="18" t="n">
-        <v>5476.61</v>
+        <v>1405.56</v>
       </c>
       <c r="N58" s="18" t="n">
-        <v>3173.68</v>
+        <v>969.84</v>
       </c>
       <c r="O58" s="18" t="n">
-        <v>4386.04</v>
+        <v>2603.28</v>
       </c>
       <c r="P58" s="37" t="n">
-        <v>19718.32</v>
+        <v>5945.29</v>
       </c>
       <c r="Q58" s="18" t="n">
-        <v>3373.95</v>
+        <v>882.4299999999999</v>
       </c>
       <c r="R58" s="18" t="n">
-        <v>1498.34</v>
+        <v>564.01</v>
       </c>
       <c r="S58" s="18" t="n">
-        <v>1436.31</v>
+        <v>1942.6</v>
       </c>
       <c r="T58" s="18" t="n">
-        <v>3741.01</v>
+        <v>1097.83</v>
       </c>
       <c r="U58" s="37" t="n">
-        <v>10049.61</v>
+        <v>4486.87</v>
       </c>
       <c r="V58" s="18" t="n">
-        <v>1065.96</v>
+        <v>494.05</v>
       </c>
       <c r="W58" s="18" t="n">
-        <v>1909.47</v>
+        <v>809.6</v>
       </c>
       <c r="X58" s="18" t="n">
-        <v>1702.97</v>
+        <v>588.13</v>
       </c>
       <c r="Y58" s="18" t="n">
-        <v>1502.82</v>
+        <v>722.13</v>
       </c>
       <c r="Z58" s="37" t="n">
-        <v>6181.22</v>
+        <v>2613.91</v>
       </c>
       <c r="AA58" s="18" t="n">
-        <v>1886.8</v>
+        <v>995.41</v>
       </c>
       <c r="AB58" s="19" t="n">
-        <v>2325.04</v>
+        <v>2243.27</v>
       </c>
       <c r="AC58" s="10" t="n"/>
       <c r="AD58" s="10" t="n"/>
@@ -23965,78 +24034,78 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>매출총이익</t>
+          <t>판관비</t>
         </is>
       </c>
       <c r="E59" s="18" t="n">
-        <v>2327.4</v>
+        <v>1400.56</v>
       </c>
       <c r="F59" s="9" t="n"/>
       <c r="G59" s="18" t="n">
-        <v>1200.06</v>
+        <v>1303.26</v>
       </c>
       <c r="H59" s="18" t="n">
-        <v>1099.19</v>
+        <v>1115.73</v>
       </c>
       <c r="I59" s="18" t="n">
-        <v>4019.85</v>
+        <v>1464.12</v>
       </c>
       <c r="J59" s="18" t="n">
-        <v>1001.24</v>
+        <v>1559.72</v>
       </c>
       <c r="K59" s="37" t="n">
-        <v>7320.34</v>
+        <v>5442.83</v>
       </c>
       <c r="L59" s="18" t="n">
-        <v>966.61</v>
+        <v>1084.6</v>
       </c>
       <c r="M59" s="18" t="n">
-        <v>1405.56</v>
+        <v>863.01</v>
       </c>
       <c r="N59" s="18" t="n">
-        <v>969.84</v>
+        <v>1485.81</v>
       </c>
       <c r="O59" s="18" t="n">
-        <v>2603.28</v>
+        <v>959.59</v>
       </c>
       <c r="P59" s="37" t="n">
-        <v>5945.29</v>
+        <v>4393.01</v>
       </c>
       <c r="Q59" s="18" t="n">
-        <v>882.4299999999999</v>
+        <v>915.4400000000001</v>
       </c>
       <c r="R59" s="18" t="n">
-        <v>564.01</v>
+        <v>495.36</v>
       </c>
       <c r="S59" s="18" t="n">
-        <v>1942.6</v>
+        <v>485.91</v>
       </c>
       <c r="T59" s="18" t="n">
-        <v>1097.83</v>
+        <v>502.08</v>
       </c>
       <c r="U59" s="37" t="n">
-        <v>4486.87</v>
+        <v>2398.79</v>
       </c>
       <c r="V59" s="18" t="n">
-        <v>494.05</v>
+        <v>420.69</v>
       </c>
       <c r="W59" s="18" t="n">
-        <v>809.6</v>
+        <v>420.4</v>
       </c>
       <c r="X59" s="18" t="n">
-        <v>588.13</v>
+        <v>477.05</v>
       </c>
       <c r="Y59" s="18" t="n">
-        <v>722.13</v>
+        <v>540.51</v>
       </c>
       <c r="Z59" s="37" t="n">
-        <v>2613.91</v>
+        <v>1858.65</v>
       </c>
       <c r="AA59" s="18" t="n">
-        <v>995.41</v>
+        <v>451.59</v>
       </c>
       <c r="AB59" s="19" t="n">
-        <v>2243.27</v>
+        <v>420.18</v>
       </c>
       <c r="AC59" s="10" t="n"/>
       <c r="AD59" s="10" t="n"/>
@@ -24058,78 +24127,78 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>판관비</t>
+          <t>영업이익</t>
         </is>
       </c>
       <c r="E60" s="18" t="n">
-        <v>1400.56</v>
+        <v>926.84</v>
       </c>
       <c r="F60" s="9" t="n"/>
       <c r="G60" s="18" t="n">
-        <v>1303.26</v>
+        <v>-103.2</v>
       </c>
       <c r="H60" s="18" t="n">
-        <v>1115.73</v>
+        <v>-16.54</v>
       </c>
       <c r="I60" s="18" t="n">
-        <v>1464.12</v>
+        <v>2555.73</v>
       </c>
       <c r="J60" s="18" t="n">
-        <v>1559.72</v>
+        <v>-558.49</v>
       </c>
       <c r="K60" s="37" t="n">
-        <v>5442.83</v>
+        <v>1877.5</v>
       </c>
       <c r="L60" s="18" t="n">
-        <v>1084.6</v>
+        <v>-117.99</v>
       </c>
       <c r="M60" s="18" t="n">
-        <v>863.01</v>
+        <v>542.5599999999999</v>
       </c>
       <c r="N60" s="18" t="n">
-        <v>1485.81</v>
+        <v>-515.97</v>
       </c>
       <c r="O60" s="18" t="n">
-        <v>959.59</v>
+        <v>1643.69</v>
       </c>
       <c r="P60" s="37" t="n">
-        <v>4393.01</v>
+        <v>1552.29</v>
       </c>
       <c r="Q60" s="18" t="n">
-        <v>915.4400000000001</v>
+        <v>-33</v>
       </c>
       <c r="R60" s="18" t="n">
-        <v>495.36</v>
+        <v>68.65000000000001</v>
       </c>
       <c r="S60" s="18" t="n">
-        <v>485.91</v>
+        <v>1456.69</v>
       </c>
       <c r="T60" s="18" t="n">
-        <v>502.08</v>
+        <v>595.75</v>
       </c>
       <c r="U60" s="37" t="n">
-        <v>2398.79</v>
+        <v>2088.09</v>
       </c>
       <c r="V60" s="18" t="n">
-        <v>420.69</v>
+        <v>73.36</v>
       </c>
       <c r="W60" s="18" t="n">
-        <v>420.4</v>
+        <v>389.2</v>
       </c>
       <c r="X60" s="18" t="n">
-        <v>477.05</v>
+        <v>111.08</v>
       </c>
       <c r="Y60" s="18" t="n">
-        <v>540.51</v>
+        <v>181.61</v>
       </c>
       <c r="Z60" s="37" t="n">
-        <v>1858.65</v>
+        <v>755.25</v>
       </c>
       <c r="AA60" s="18" t="n">
-        <v>451.59</v>
+        <v>543.8200000000001</v>
       </c>
       <c r="AB60" s="19" t="n">
-        <v>420.18</v>
+        <v>1823.09</v>
       </c>
       <c r="AC60" s="10" t="n"/>
       <c r="AD60" s="10" t="n"/>
@@ -24151,78 +24220,78 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>영업이익</t>
+          <t>기타영업외손익</t>
         </is>
       </c>
       <c r="E61" s="18" t="n">
-        <v>926.84</v>
+        <v>17.53</v>
       </c>
       <c r="F61" s="9" t="n"/>
       <c r="G61" s="18" t="n">
-        <v>-103.2</v>
+        <v>12.41</v>
       </c>
       <c r="H61" s="18" t="n">
-        <v>-16.54</v>
+        <v>20.87</v>
       </c>
       <c r="I61" s="18" t="n">
-        <v>2555.73</v>
+        <v>18.1</v>
       </c>
       <c r="J61" s="18" t="n">
-        <v>-558.49</v>
+        <v>63.24</v>
       </c>
       <c r="K61" s="37" t="n">
-        <v>1877.5</v>
+        <v>114.62</v>
       </c>
       <c r="L61" s="18" t="n">
-        <v>-117.99</v>
+        <v>123.38</v>
       </c>
       <c r="M61" s="18" t="n">
-        <v>542.5599999999999</v>
+        <v>110.59</v>
       </c>
       <c r="N61" s="18" t="n">
-        <v>-515.97</v>
+        <v>115.16</v>
       </c>
       <c r="O61" s="18" t="n">
-        <v>1643.69</v>
+        <v>432.45</v>
       </c>
       <c r="P61" s="37" t="n">
-        <v>1552.29</v>
+        <v>781.58</v>
       </c>
       <c r="Q61" s="18" t="n">
-        <v>-33</v>
+        <v>144.55</v>
       </c>
       <c r="R61" s="18" t="n">
-        <v>68.65000000000001</v>
+        <v>112.75</v>
       </c>
       <c r="S61" s="18" t="n">
-        <v>1456.69</v>
+        <v>312.94</v>
       </c>
       <c r="T61" s="18" t="n">
-        <v>595.75</v>
+        <v>121.92</v>
       </c>
       <c r="U61" s="37" t="n">
-        <v>2088.09</v>
+        <v>692.16</v>
       </c>
       <c r="V61" s="18" t="n">
-        <v>73.36</v>
+        <v>89.63</v>
       </c>
       <c r="W61" s="18" t="n">
-        <v>389.2</v>
+        <v>101.53</v>
       </c>
       <c r="X61" s="18" t="n">
-        <v>111.08</v>
+        <v>104.03</v>
       </c>
       <c r="Y61" s="18" t="n">
-        <v>181.61</v>
+        <v>109.46</v>
       </c>
       <c r="Z61" s="37" t="n">
-        <v>755.25</v>
+        <v>404.65</v>
       </c>
       <c r="AA61" s="18" t="n">
-        <v>543.8200000000001</v>
+        <v>99.88</v>
       </c>
       <c r="AB61" s="19" t="n">
-        <v>1823.09</v>
+        <v>263.32</v>
       </c>
       <c r="AC61" s="10" t="n"/>
       <c r="AD61" s="10" t="n"/>
@@ -24244,27 +24313,27 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>기타영업외손익</t>
+          <t>기타영업외수익</t>
         </is>
       </c>
       <c r="E62" s="18" t="n">
-        <v>17.53</v>
+        <v>23.1</v>
       </c>
       <c r="F62" s="9" t="n"/>
       <c r="G62" s="18" t="n">
-        <v>12.41</v>
+        <v>12.44</v>
       </c>
       <c r="H62" s="18" t="n">
         <v>20.87</v>
       </c>
       <c r="I62" s="18" t="n">
-        <v>18.1</v>
+        <v>18.85</v>
       </c>
       <c r="J62" s="18" t="n">
         <v>63.24</v>
       </c>
       <c r="K62" s="37" t="n">
-        <v>114.62</v>
+        <v>115.4</v>
       </c>
       <c r="L62" s="18" t="n">
         <v>123.38</v>
@@ -24276,31 +24345,31 @@
         <v>115.16</v>
       </c>
       <c r="O62" s="18" t="n">
-        <v>432.45</v>
+        <v>433.23</v>
       </c>
       <c r="P62" s="37" t="n">
-        <v>781.58</v>
+        <v>782.36</v>
       </c>
       <c r="Q62" s="18" t="n">
         <v>144.55</v>
       </c>
       <c r="R62" s="18" t="n">
-        <v>112.75</v>
+        <v>113.05</v>
       </c>
       <c r="S62" s="18" t="n">
-        <v>312.94</v>
+        <v>313.03</v>
       </c>
       <c r="T62" s="18" t="n">
         <v>121.92</v>
       </c>
       <c r="U62" s="37" t="n">
-        <v>692.16</v>
+        <v>692.55</v>
       </c>
       <c r="V62" s="18" t="n">
-        <v>89.63</v>
+        <v>103.95</v>
       </c>
       <c r="W62" s="18" t="n">
-        <v>101.53</v>
+        <v>101.66</v>
       </c>
       <c r="X62" s="18" t="n">
         <v>104.03</v>
@@ -24309,13 +24378,13 @@
         <v>109.46</v>
       </c>
       <c r="Z62" s="37" t="n">
-        <v>404.65</v>
+        <v>419.1</v>
       </c>
       <c r="AA62" s="18" t="n">
         <v>99.88</v>
       </c>
       <c r="AB62" s="19" t="n">
-        <v>263.32</v>
+        <v>266.23</v>
       </c>
       <c r="AC62" s="10" t="n"/>
       <c r="AD62" s="10" t="n"/>
@@ -24337,78 +24406,78 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>기타영업외수익</t>
+          <t>기타영업외비용</t>
         </is>
       </c>
       <c r="E63" s="18" t="n">
-        <v>23.1</v>
+        <v>5.58</v>
       </c>
       <c r="F63" s="9" t="n"/>
       <c r="G63" s="18" t="n">
-        <v>12.44</v>
+        <v>0.03</v>
       </c>
       <c r="H63" s="18" t="n">
-        <v>20.87</v>
+        <v>0</v>
       </c>
       <c r="I63" s="18" t="n">
-        <v>18.85</v>
+        <v>0.75</v>
       </c>
       <c r="J63" s="18" t="n">
-        <v>63.24</v>
+        <v>0</v>
       </c>
       <c r="K63" s="37" t="n">
-        <v>115.4</v>
+        <v>0.78</v>
       </c>
       <c r="L63" s="18" t="n">
-        <v>123.38</v>
+        <v>0</v>
       </c>
       <c r="M63" s="18" t="n">
-        <v>110.59</v>
+        <v>0</v>
       </c>
       <c r="N63" s="18" t="n">
-        <v>115.16</v>
+        <v>0</v>
       </c>
       <c r="O63" s="18" t="n">
-        <v>433.23</v>
+        <v>0.78</v>
       </c>
       <c r="P63" s="37" t="n">
-        <v>782.36</v>
+        <v>0.78</v>
       </c>
       <c r="Q63" s="18" t="n">
-        <v>144.55</v>
+        <v>0</v>
       </c>
       <c r="R63" s="18" t="n">
-        <v>113.05</v>
+        <v>0.3</v>
       </c>
       <c r="S63" s="18" t="n">
-        <v>313.03</v>
+        <v>0.09</v>
       </c>
       <c r="T63" s="18" t="n">
-        <v>121.92</v>
+        <v>0</v>
       </c>
       <c r="U63" s="37" t="n">
-        <v>692.55</v>
+        <v>0.39</v>
       </c>
       <c r="V63" s="18" t="n">
-        <v>103.95</v>
+        <v>14.32</v>
       </c>
       <c r="W63" s="18" t="n">
-        <v>101.66</v>
+        <v>0.13</v>
       </c>
       <c r="X63" s="18" t="n">
-        <v>104.03</v>
+        <v>0</v>
       </c>
       <c r="Y63" s="18" t="n">
-        <v>109.46</v>
+        <v>0</v>
       </c>
       <c r="Z63" s="37" t="n">
-        <v>419.1</v>
+        <v>14.45</v>
       </c>
       <c r="AA63" s="18" t="n">
-        <v>99.88</v>
+        <v>0</v>
       </c>
       <c r="AB63" s="19" t="n">
-        <v>266.23</v>
+        <v>2.91</v>
       </c>
       <c r="AC63" s="10" t="n"/>
       <c r="AD63" s="10" t="n"/>
@@ -24430,78 +24499,78 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>기타영업외비용</t>
+          <t>금융손익</t>
         </is>
       </c>
       <c r="E64" s="18" t="n">
-        <v>5.58</v>
+        <v>396.33</v>
       </c>
       <c r="F64" s="9" t="n"/>
       <c r="G64" s="18" t="n">
-        <v>0.03</v>
+        <v>291.59</v>
       </c>
       <c r="H64" s="18" t="n">
-        <v>0</v>
+        <v>127.28</v>
       </c>
       <c r="I64" s="18" t="n">
-        <v>0.75</v>
+        <v>594.13</v>
       </c>
       <c r="J64" s="18" t="n">
-        <v>0</v>
+        <v>-565.59</v>
       </c>
       <c r="K64" s="37" t="n">
-        <v>0.78</v>
+        <v>447.41</v>
       </c>
       <c r="L64" s="18" t="n">
-        <v>0</v>
+        <v>252.45</v>
       </c>
       <c r="M64" s="18" t="n">
-        <v>0</v>
+        <v>-69.29000000000001</v>
       </c>
       <c r="N64" s="18" t="n">
-        <v>0</v>
+        <v>205.17</v>
       </c>
       <c r="O64" s="18" t="n">
-        <v>0.78</v>
+        <v>340.46</v>
       </c>
       <c r="P64" s="37" t="n">
-        <v>0.78</v>
+        <v>728.79</v>
       </c>
       <c r="Q64" s="18" t="n">
-        <v>0</v>
+        <v>433.18</v>
       </c>
       <c r="R64" s="18" t="n">
-        <v>0.3</v>
+        <v>-531.83</v>
       </c>
       <c r="S64" s="18" t="n">
-        <v>0.09</v>
+        <v>-15.58</v>
       </c>
       <c r="T64" s="18" t="n">
-        <v>0</v>
+        <v>648.67</v>
       </c>
       <c r="U64" s="37" t="n">
-        <v>0.39</v>
+        <v>534.4400000000001</v>
       </c>
       <c r="V64" s="18" t="n">
-        <v>14.32</v>
+        <v>591.63</v>
       </c>
       <c r="W64" s="18" t="n">
-        <v>0.13</v>
+        <v>-22.99</v>
       </c>
       <c r="X64" s="18" t="n">
-        <v>0</v>
+        <v>865.05</v>
       </c>
       <c r="Y64" s="18" t="n">
-        <v>0</v>
+        <v>848.63</v>
       </c>
       <c r="Z64" s="37" t="n">
-        <v>14.45</v>
+        <v>2282.32</v>
       </c>
       <c r="AA64" s="18" t="n">
-        <v>0</v>
+        <v>2047.93</v>
       </c>
       <c r="AB64" s="19" t="n">
-        <v>2.91</v>
+        <v>2824.66</v>
       </c>
       <c r="AC64" s="10" t="n"/>
       <c r="AD64" s="10" t="n"/>
@@ -24523,78 +24592,78 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>금융손익</t>
+          <t>금융수익</t>
         </is>
       </c>
       <c r="E65" s="18" t="n">
-        <v>396.33</v>
+        <v>619.9</v>
       </c>
       <c r="F65" s="9" t="n"/>
       <c r="G65" s="18" t="n">
-        <v>291.59</v>
+        <v>422.25</v>
       </c>
       <c r="H65" s="18" t="n">
-        <v>127.28</v>
+        <v>280.4</v>
       </c>
       <c r="I65" s="18" t="n">
-        <v>594.13</v>
+        <v>768.95</v>
       </c>
       <c r="J65" s="18" t="n">
-        <v>-565.59</v>
+        <v>-110.92</v>
       </c>
       <c r="K65" s="37" t="n">
-        <v>447.41</v>
+        <v>1360.68</v>
       </c>
       <c r="L65" s="18" t="n">
-        <v>252.45</v>
+        <v>494.41</v>
       </c>
       <c r="M65" s="18" t="n">
-        <v>-69.29000000000001</v>
+        <v>152.45</v>
       </c>
       <c r="N65" s="18" t="n">
-        <v>205.17</v>
+        <v>470.51</v>
       </c>
       <c r="O65" s="18" t="n">
-        <v>340.46</v>
+        <v>565.97</v>
       </c>
       <c r="P65" s="37" t="n">
-        <v>728.79</v>
+        <v>1683.34</v>
       </c>
       <c r="Q65" s="18" t="n">
-        <v>433.18</v>
+        <v>634.25</v>
       </c>
       <c r="R65" s="18" t="n">
-        <v>-531.83</v>
+        <v>32.2</v>
       </c>
       <c r="S65" s="18" t="n">
-        <v>-15.58</v>
+        <v>419.54</v>
       </c>
       <c r="T65" s="18" t="n">
-        <v>648.67</v>
+        <v>972.3</v>
       </c>
       <c r="U65" s="37" t="n">
-        <v>534.4400000000001</v>
+        <v>2058.29</v>
       </c>
       <c r="V65" s="18" t="n">
-        <v>591.63</v>
+        <v>736.9</v>
       </c>
       <c r="W65" s="18" t="n">
-        <v>-22.99</v>
+        <v>145.79</v>
       </c>
       <c r="X65" s="18" t="n">
-        <v>865.05</v>
+        <v>1022.57</v>
       </c>
       <c r="Y65" s="18" t="n">
-        <v>848.63</v>
+        <v>1552.65</v>
       </c>
       <c r="Z65" s="37" t="n">
-        <v>2282.32</v>
+        <v>3457.91</v>
       </c>
       <c r="AA65" s="18" t="n">
-        <v>2047.93</v>
+        <v>3907.86</v>
       </c>
       <c r="AB65" s="19" t="n">
-        <v>2824.66</v>
+        <v>2929.37</v>
       </c>
       <c r="AC65" s="10" t="n"/>
       <c r="AD65" s="10" t="n"/>
@@ -24616,78 +24685,78 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>금융수익</t>
+          <t>금융비용</t>
         </is>
       </c>
       <c r="E66" s="18" t="n">
-        <v>619.9</v>
+        <v>223.57</v>
       </c>
       <c r="F66" s="9" t="n"/>
       <c r="G66" s="18" t="n">
-        <v>422.25</v>
+        <v>130.66</v>
       </c>
       <c r="H66" s="18" t="n">
-        <v>280.4</v>
+        <v>153.12</v>
       </c>
       <c r="I66" s="18" t="n">
-        <v>768.95</v>
+        <v>174.82</v>
       </c>
       <c r="J66" s="18" t="n">
-        <v>-110.92</v>
+        <v>454.67</v>
       </c>
       <c r="K66" s="37" t="n">
-        <v>1360.68</v>
+        <v>913.27</v>
       </c>
       <c r="L66" s="18" t="n">
-        <v>494.41</v>
+        <v>241.96</v>
       </c>
       <c r="M66" s="18" t="n">
-        <v>152.45</v>
+        <v>221.74</v>
       </c>
       <c r="N66" s="18" t="n">
-        <v>470.51</v>
+        <v>265.34</v>
       </c>
       <c r="O66" s="18" t="n">
-        <v>565.97</v>
+        <v>225.5</v>
       </c>
       <c r="P66" s="37" t="n">
-        <v>1683.34</v>
+        <v>954.54</v>
       </c>
       <c r="Q66" s="18" t="n">
-        <v>634.25</v>
+        <v>201.07</v>
       </c>
       <c r="R66" s="18" t="n">
-        <v>32.2</v>
+        <v>564.03</v>
       </c>
       <c r="S66" s="18" t="n">
-        <v>419.54</v>
+        <v>435.12</v>
       </c>
       <c r="T66" s="18" t="n">
-        <v>972.3</v>
+        <v>323.63</v>
       </c>
       <c r="U66" s="37" t="n">
-        <v>2058.29</v>
+        <v>1523.85</v>
       </c>
       <c r="V66" s="18" t="n">
-        <v>736.9</v>
+        <v>145.27</v>
       </c>
       <c r="W66" s="18" t="n">
-        <v>145.79</v>
+        <v>168.78</v>
       </c>
       <c r="X66" s="18" t="n">
-        <v>1022.57</v>
+        <v>157.52</v>
       </c>
       <c r="Y66" s="18" t="n">
-        <v>1552.65</v>
+        <v>704.02</v>
       </c>
       <c r="Z66" s="37" t="n">
-        <v>3457.91</v>
+        <v>1175.59</v>
       </c>
       <c r="AA66" s="18" t="n">
-        <v>3907.86</v>
+        <v>1859.93</v>
       </c>
       <c r="AB66" s="19" t="n">
-        <v>2929.37</v>
+        <v>104.71</v>
       </c>
       <c r="AC66" s="10" t="n"/>
       <c r="AD66" s="10" t="n"/>
@@ -24709,78 +24778,78 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>금융비용</t>
+          <t>법인세비용차감전계속사업이익</t>
         </is>
       </c>
       <c r="E67" s="18" t="n">
-        <v>223.57</v>
+        <v>1340.7</v>
       </c>
       <c r="F67" s="9" t="n"/>
       <c r="G67" s="18" t="n">
-        <v>130.66</v>
+        <v>200.8</v>
       </c>
       <c r="H67" s="18" t="n">
-        <v>153.12</v>
+        <v>131.6</v>
       </c>
       <c r="I67" s="18" t="n">
-        <v>174.82</v>
+        <v>3167.95</v>
       </c>
       <c r="J67" s="18" t="n">
-        <v>454.67</v>
+        <v>-1060.83</v>
       </c>
       <c r="K67" s="37" t="n">
-        <v>913.27</v>
+        <v>2439.52</v>
       </c>
       <c r="L67" s="18" t="n">
-        <v>241.96</v>
+        <v>257.84</v>
       </c>
       <c r="M67" s="18" t="n">
-        <v>221.74</v>
+        <v>583.86</v>
       </c>
       <c r="N67" s="18" t="n">
-        <v>265.34</v>
+        <v>-195.63</v>
       </c>
       <c r="O67" s="18" t="n">
-        <v>225.5</v>
+        <v>2416.6</v>
       </c>
       <c r="P67" s="37" t="n">
-        <v>954.54</v>
+        <v>3062.67</v>
       </c>
       <c r="Q67" s="18" t="n">
-        <v>201.07</v>
+        <v>544.73</v>
       </c>
       <c r="R67" s="18" t="n">
-        <v>564.03</v>
+        <v>-350.44</v>
       </c>
       <c r="S67" s="18" t="n">
-        <v>435.12</v>
+        <v>1754.05</v>
       </c>
       <c r="T67" s="18" t="n">
-        <v>323.63</v>
+        <v>1366.35</v>
       </c>
       <c r="U67" s="37" t="n">
-        <v>1523.85</v>
+        <v>3314.69</v>
       </c>
       <c r="V67" s="18" t="n">
-        <v>145.27</v>
+        <v>754.63</v>
       </c>
       <c r="W67" s="18" t="n">
-        <v>168.78</v>
+        <v>467.74</v>
       </c>
       <c r="X67" s="18" t="n">
-        <v>157.52</v>
+        <v>1080.16</v>
       </c>
       <c r="Y67" s="18" t="n">
-        <v>704.02</v>
+        <v>1139.7</v>
       </c>
       <c r="Z67" s="37" t="n">
-        <v>1175.59</v>
+        <v>3442.23</v>
       </c>
       <c r="AA67" s="18" t="n">
-        <v>1859.93</v>
+        <v>2691.64</v>
       </c>
       <c r="AB67" s="19" t="n">
-        <v>104.71</v>
+        <v>4911.07</v>
       </c>
       <c r="AC67" s="10" t="n"/>
       <c r="AD67" s="10" t="n"/>
@@ -24802,78 +24871,78 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>법인세비용차감전계속사업이익</t>
+          <t>법인세비용</t>
         </is>
       </c>
       <c r="E68" s="18" t="n">
-        <v>1340.7</v>
+        <v>441.05</v>
       </c>
       <c r="F68" s="9" t="n"/>
       <c r="G68" s="18" t="n">
-        <v>200.8</v>
+        <v>28.86</v>
       </c>
       <c r="H68" s="18" t="n">
-        <v>131.6</v>
+        <v>39.86</v>
       </c>
       <c r="I68" s="18" t="n">
-        <v>3167.95</v>
+        <v>699.27</v>
       </c>
       <c r="J68" s="18" t="n">
-        <v>-1060.83</v>
+        <v>-405.62</v>
       </c>
       <c r="K68" s="37" t="n">
-        <v>2439.52</v>
+        <v>362.37</v>
       </c>
       <c r="L68" s="18" t="n">
-        <v>257.84</v>
+        <v>0.48</v>
       </c>
       <c r="M68" s="18" t="n">
-        <v>583.86</v>
+        <v>108.92</v>
       </c>
       <c r="N68" s="18" t="n">
-        <v>-195.63</v>
+        <v>-84.12</v>
       </c>
       <c r="O68" s="18" t="n">
-        <v>2416.6</v>
+        <v>111.39</v>
       </c>
       <c r="P68" s="37" t="n">
-        <v>3062.67</v>
+        <v>136.67</v>
       </c>
       <c r="Q68" s="18" t="n">
-        <v>544.73</v>
+        <v>71.73</v>
       </c>
       <c r="R68" s="18" t="n">
-        <v>-350.44</v>
+        <v>-192.66</v>
       </c>
       <c r="S68" s="18" t="n">
-        <v>1754.05</v>
+        <v>358.65</v>
       </c>
       <c r="T68" s="18" t="n">
-        <v>1366.35</v>
+        <v>368.83</v>
       </c>
       <c r="U68" s="37" t="n">
-        <v>3314.69</v>
+        <v>606.55</v>
       </c>
       <c r="V68" s="18" t="n">
-        <v>754.63</v>
+        <v>166.36</v>
       </c>
       <c r="W68" s="18" t="n">
-        <v>467.74</v>
+        <v>111.23</v>
       </c>
       <c r="X68" s="18" t="n">
-        <v>1080.16</v>
+        <v>264.39</v>
       </c>
       <c r="Y68" s="18" t="n">
-        <v>1139.7</v>
+        <v>36.69</v>
       </c>
       <c r="Z68" s="37" t="n">
-        <v>3442.23</v>
+        <v>578.67</v>
       </c>
       <c r="AA68" s="18" t="n">
-        <v>2691.64</v>
+        <v>581.84</v>
       </c>
       <c r="AB68" s="19" t="n">
-        <v>4911.07</v>
+        <v>1022.88</v>
       </c>
       <c r="AC68" s="10" t="n"/>
       <c r="AD68" s="10" t="n"/>
@@ -24895,78 +24964,78 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>법인세비용</t>
+          <t>당기순이익</t>
         </is>
       </c>
       <c r="E69" s="18" t="n">
-        <v>441.05</v>
+        <v>899.66</v>
       </c>
       <c r="F69" s="9" t="n"/>
       <c r="G69" s="18" t="n">
-        <v>28.86</v>
+        <v>171.93</v>
       </c>
       <c r="H69" s="18" t="n">
-        <v>39.86</v>
+        <v>91.75</v>
       </c>
       <c r="I69" s="18" t="n">
-        <v>699.27</v>
+        <v>2468.68</v>
       </c>
       <c r="J69" s="18" t="n">
-        <v>-405.62</v>
+        <v>-655.21</v>
       </c>
       <c r="K69" s="37" t="n">
-        <v>362.37</v>
+        <v>2077.15</v>
       </c>
       <c r="L69" s="18" t="n">
-        <v>0.48</v>
+        <v>258.32</v>
       </c>
       <c r="M69" s="18" t="n">
-        <v>108.92</v>
+        <v>474.94</v>
       </c>
       <c r="N69" s="18" t="n">
-        <v>-84.12</v>
+        <v>-111.51</v>
       </c>
       <c r="O69" s="18" t="n">
-        <v>111.39</v>
+        <v>2305.22</v>
       </c>
       <c r="P69" s="37" t="n">
-        <v>136.67</v>
+        <v>2926.97</v>
       </c>
       <c r="Q69" s="18" t="n">
-        <v>71.73</v>
+        <v>473</v>
       </c>
       <c r="R69" s="18" t="n">
-        <v>-192.66</v>
+        <v>9661.48</v>
       </c>
       <c r="S69" s="18" t="n">
-        <v>358.65</v>
+        <v>1395.4</v>
       </c>
       <c r="T69" s="18" t="n">
-        <v>368.83</v>
+        <v>997.51</v>
       </c>
       <c r="U69" s="37" t="n">
-        <v>606.55</v>
+        <v>12527.39</v>
       </c>
       <c r="V69" s="18" t="n">
-        <v>166.36</v>
+        <v>588.27</v>
       </c>
       <c r="W69" s="18" t="n">
-        <v>111.23</v>
+        <v>356.52</v>
       </c>
       <c r="X69" s="18" t="n">
-        <v>264.39</v>
+        <v>815.77</v>
       </c>
       <c r="Y69" s="18" t="n">
-        <v>36.69</v>
+        <v>1103.01</v>
       </c>
       <c r="Z69" s="37" t="n">
-        <v>578.67</v>
+        <v>2863.57</v>
       </c>
       <c r="AA69" s="18" t="n">
-        <v>581.84</v>
+        <v>2109.8</v>
       </c>
       <c r="AB69" s="19" t="n">
-        <v>1022.88</v>
+        <v>3888.19</v>
       </c>
       <c r="AC69" s="10" t="n"/>
       <c r="AD69" s="10" t="n"/>
@@ -24988,78 +25057,78 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>당기순이익</t>
+          <t>총포괄손익</t>
         </is>
       </c>
       <c r="E70" s="18" t="n">
-        <v>899.66</v>
+        <v>894.97</v>
       </c>
       <c r="F70" s="9" t="n"/>
       <c r="G70" s="18" t="n">
-        <v>171.93</v>
+        <v>701.8</v>
       </c>
       <c r="H70" s="18" t="n">
-        <v>91.75</v>
+        <v>-129.28</v>
       </c>
       <c r="I70" s="18" t="n">
-        <v>2468.68</v>
+        <v>2847.47</v>
       </c>
       <c r="J70" s="18" t="n">
-        <v>-655.21</v>
+        <v>-1253.8</v>
       </c>
       <c r="K70" s="37" t="n">
-        <v>2077.15</v>
+        <v>2166.19</v>
       </c>
       <c r="L70" s="18" t="n">
-        <v>258.32</v>
+        <v>457.55</v>
       </c>
       <c r="M70" s="18" t="n">
-        <v>474.94</v>
+        <v>1513.09</v>
       </c>
       <c r="N70" s="18" t="n">
-        <v>-111.51</v>
+        <v>-608.62</v>
       </c>
       <c r="O70" s="18" t="n">
-        <v>2305.22</v>
+        <v>2231.78</v>
       </c>
       <c r="P70" s="37" t="n">
-        <v>2926.97</v>
+        <v>3593.8</v>
       </c>
       <c r="Q70" s="18" t="n">
-        <v>473</v>
+        <v>161.11</v>
       </c>
       <c r="R70" s="18" t="n">
-        <v>9661.48</v>
+        <v>9646.700000000001</v>
       </c>
       <c r="S70" s="18" t="n">
-        <v>1395.4</v>
+        <v>1258.42</v>
       </c>
       <c r="T70" s="18" t="n">
-        <v>997.51</v>
+        <v>-92.37</v>
       </c>
       <c r="U70" s="37" t="n">
-        <v>12527.39</v>
+        <v>10973.86</v>
       </c>
       <c r="V70" s="18" t="n">
-        <v>588.27</v>
+        <v>606.4</v>
       </c>
       <c r="W70" s="18" t="n">
-        <v>356.52</v>
+        <v>657.77</v>
       </c>
       <c r="X70" s="18" t="n">
-        <v>815.77</v>
+        <v>813.87</v>
       </c>
       <c r="Y70" s="18" t="n">
-        <v>1103.01</v>
+        <v>1233.27</v>
       </c>
       <c r="Z70" s="37" t="n">
-        <v>2863.57</v>
+        <v>3311.31</v>
       </c>
       <c r="AA70" s="18" t="n">
-        <v>2109.8</v>
+        <v>2091.86</v>
       </c>
       <c r="AB70" s="19" t="n">
-        <v>3888.19</v>
+        <v>3725.53</v>
       </c>
       <c r="AC70" s="10" t="n"/>
       <c r="AD70" s="10" t="n"/>
@@ -25081,78 +25150,78 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>총포괄손익</t>
+          <t>(지배주주지분)당기순이익</t>
         </is>
       </c>
       <c r="E71" s="18" t="n">
-        <v>894.97</v>
+        <v>899.66</v>
       </c>
       <c r="F71" s="9" t="n"/>
       <c r="G71" s="18" t="n">
-        <v>701.8</v>
+        <v>171.93</v>
       </c>
       <c r="H71" s="18" t="n">
-        <v>-129.28</v>
+        <v>91.75</v>
       </c>
       <c r="I71" s="18" t="n">
-        <v>2847.47</v>
+        <v>2468.68</v>
       </c>
       <c r="J71" s="18" t="n">
-        <v>-1253.8</v>
+        <v>-655.21</v>
       </c>
       <c r="K71" s="37" t="n">
-        <v>2166.19</v>
+        <v>2077.15</v>
       </c>
       <c r="L71" s="18" t="n">
-        <v>457.55</v>
+        <v>258.32</v>
       </c>
       <c r="M71" s="18" t="n">
-        <v>1513.09</v>
+        <v>474.94</v>
       </c>
       <c r="N71" s="18" t="n">
-        <v>-608.62</v>
+        <v>-111.51</v>
       </c>
       <c r="O71" s="18" t="n">
-        <v>2231.78</v>
+        <v>2305.22</v>
       </c>
       <c r="P71" s="37" t="n">
-        <v>3593.8</v>
+        <v>2926.97</v>
       </c>
       <c r="Q71" s="18" t="n">
-        <v>161.11</v>
+        <v>473</v>
       </c>
       <c r="R71" s="18" t="n">
-        <v>9646.700000000001</v>
+        <v>9661.48</v>
       </c>
       <c r="S71" s="18" t="n">
-        <v>1258.42</v>
+        <v>1395.4</v>
       </c>
       <c r="T71" s="18" t="n">
-        <v>-92.37</v>
+        <v>997.51</v>
       </c>
       <c r="U71" s="37" t="n">
-        <v>10973.86</v>
+        <v>12527.39</v>
       </c>
       <c r="V71" s="18" t="n">
-        <v>606.4</v>
+        <v>588.27</v>
       </c>
       <c r="W71" s="18" t="n">
-        <v>657.77</v>
+        <v>356.52</v>
       </c>
       <c r="X71" s="18" t="n">
-        <v>813.87</v>
+        <v>815.77</v>
       </c>
       <c r="Y71" s="18" t="n">
-        <v>1233.27</v>
+        <v>1103.01</v>
       </c>
       <c r="Z71" s="37" t="n">
-        <v>3311.31</v>
+        <v>2863.57</v>
       </c>
       <c r="AA71" s="18" t="n">
-        <v>2091.86</v>
+        <v>2109.8</v>
       </c>
       <c r="AB71" s="19" t="n">
-        <v>3725.53</v>
+        <v>3888.19</v>
       </c>
       <c r="AC71" s="10" t="n"/>
       <c r="AD71" s="10" t="n"/>
@@ -25174,7 +25243,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>(지배주주지분)당기순이익</t>
+          <t>계속사업이익</t>
         </is>
       </c>
       <c r="E72" s="18" t="n">
@@ -25215,7 +25284,7 @@
         <v>473</v>
       </c>
       <c r="R72" s="18" t="n">
-        <v>9661.48</v>
+        <v>-157.78</v>
       </c>
       <c r="S72" s="18" t="n">
         <v>1395.4</v>
@@ -25224,7 +25293,7 @@
         <v>997.51</v>
       </c>
       <c r="U72" s="37" t="n">
-        <v>12527.39</v>
+        <v>2708.13</v>
       </c>
       <c r="V72" s="18" t="n">
         <v>588.27</v>
@@ -25267,79 +25336,38 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>계속사업이익</t>
-        </is>
-      </c>
-      <c r="E73" s="18" t="n">
-        <v>899.66</v>
+          <t>중단사업이익</t>
+        </is>
       </c>
       <c r="F73" s="9" t="n"/>
-      <c r="G73" s="18" t="n">
-        <v>171.93</v>
-      </c>
-      <c r="H73" s="18" t="n">
-        <v>91.75</v>
-      </c>
-      <c r="I73" s="18" t="n">
-        <v>2468.68</v>
-      </c>
-      <c r="J73" s="18" t="n">
-        <v>-655.21</v>
-      </c>
-      <c r="K73" s="37" t="n">
-        <v>2077.15</v>
-      </c>
-      <c r="L73" s="18" t="n">
-        <v>258.32</v>
-      </c>
-      <c r="M73" s="18" t="n">
-        <v>474.94</v>
-      </c>
-      <c r="N73" s="18" t="n">
-        <v>-111.51</v>
-      </c>
-      <c r="O73" s="18" t="n">
-        <v>2305.22</v>
-      </c>
-      <c r="P73" s="37" t="n">
-        <v>2926.97</v>
-      </c>
-      <c r="Q73" s="18" t="n">
-        <v>473</v>
-      </c>
+      <c r="K73" s="9" t="n"/>
+      <c r="P73" s="9" t="n"/>
       <c r="R73" s="18" t="n">
-        <v>-157.78</v>
+        <v>9819.26</v>
       </c>
       <c r="S73" s="18" t="n">
-        <v>1395.4</v>
+        <v>0</v>
       </c>
       <c r="T73" s="18" t="n">
-        <v>997.51</v>
-      </c>
-      <c r="U73" s="37" t="n">
-        <v>2708.13</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U73" s="9" t="n"/>
       <c r="V73" s="18" t="n">
-        <v>588.27</v>
+        <v>0</v>
       </c>
       <c r="W73" s="18" t="n">
-        <v>356.52</v>
+        <v>0</v>
       </c>
       <c r="X73" s="18" t="n">
-        <v>815.77</v>
+        <v>0</v>
       </c>
       <c r="Y73" s="18" t="n">
-        <v>1103.01</v>
+        <v>0</v>
       </c>
       <c r="Z73" s="37" t="n">
-        <v>2863.57</v>
-      </c>
-      <c r="AA73" s="18" t="n">
-        <v>2109.8</v>
-      </c>
-      <c r="AB73" s="19" t="n">
-        <v>3888.19</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AB73" s="5" t="n"/>
       <c r="AC73" s="10" t="n"/>
       <c r="AD73" s="10" t="n"/>
       <c r="AE73" s="11" t="n"/>
@@ -25360,38 +25388,79 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>이자수익</t>
-        </is>
+          <t>영업활동으로인한현금흐름</t>
+        </is>
+      </c>
+      <c r="E74" s="18" t="n">
+        <v>2321</v>
       </c>
       <c r="F74" s="9" t="n"/>
       <c r="G74" s="18" t="n">
-        <v>290.96</v>
+        <v>-412.48</v>
       </c>
       <c r="H74" s="18" t="n">
-        <v>8.59</v>
+        <v>-1721.65</v>
       </c>
       <c r="I74" s="18" t="n">
-        <v>327.9</v>
+        <v>663.91</v>
       </c>
       <c r="J74" s="18" t="n">
-        <v>43.26</v>
+        <v>173.06</v>
       </c>
       <c r="K74" s="37" t="n">
-        <v>670.71</v>
+        <v>-1297.16</v>
       </c>
       <c r="L74" s="18" t="n">
-        <v>306.96</v>
+        <v>3487.06</v>
       </c>
       <c r="M74" s="18" t="n">
-        <v>19.84</v>
+        <v>1968.24</v>
       </c>
       <c r="N74" s="18" t="n">
-        <v>375.53</v>
-      </c>
-      <c r="P74" s="9" t="n"/>
-      <c r="U74" s="9" t="n"/>
-      <c r="Z74" s="9" t="n"/>
-      <c r="AB74" s="5" t="n"/>
+        <v>2172</v>
+      </c>
+      <c r="O74" s="18" t="n">
+        <v>-225.58</v>
+      </c>
+      <c r="P74" s="37" t="n">
+        <v>7401.72</v>
+      </c>
+      <c r="Q74" s="18" t="n">
+        <v>1531.45</v>
+      </c>
+      <c r="R74" s="18" t="n">
+        <v>99.58</v>
+      </c>
+      <c r="S74" s="18" t="n">
+        <v>175.05</v>
+      </c>
+      <c r="T74" s="18" t="n">
+        <v>3188.89</v>
+      </c>
+      <c r="U74" s="37" t="n">
+        <v>4994.97</v>
+      </c>
+      <c r="V74" s="18" t="n">
+        <v>-1993.48</v>
+      </c>
+      <c r="W74" s="18" t="n">
+        <v>-566.6900000000001</v>
+      </c>
+      <c r="X74" s="18" t="n">
+        <v>732.96</v>
+      </c>
+      <c r="Y74" s="18" t="n">
+        <v>-1156.94</v>
+      </c>
+      <c r="Z74" s="37" t="n">
+        <v>-2984.15</v>
+      </c>
+      <c r="AA74" s="18" t="n">
+        <v>893.5599999999999</v>
+      </c>
+      <c r="AB74" s="19" t="n">
+        <v>2185.69</v>
+      </c>
       <c r="AC74" s="10" t="n"/>
       <c r="AD74" s="10" t="n"/>
       <c r="AE74" s="11" t="n"/>
@@ -25412,38 +25481,79 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>이자비용</t>
-        </is>
+          <t>법인세납부(CF)</t>
+        </is>
+      </c>
+      <c r="E75" s="18" t="n">
+        <v>3.47</v>
       </c>
       <c r="F75" s="9" t="n"/>
       <c r="G75" s="18" t="n">
-        <v>119.87</v>
+        <v>-223.48</v>
       </c>
       <c r="H75" s="18" t="n">
-        <v>128.62</v>
+        <v>-223.35</v>
       </c>
       <c r="I75" s="18" t="n">
-        <v>137.06</v>
+        <v>-190.36</v>
       </c>
       <c r="J75" s="18" t="n">
-        <v>188.19</v>
+        <v>-3.89</v>
       </c>
       <c r="K75" s="37" t="n">
-        <v>573.74</v>
+        <v>-641.08</v>
       </c>
       <c r="L75" s="18" t="n">
-        <v>210.24</v>
+        <v>-98.59999999999999</v>
       </c>
       <c r="M75" s="18" t="n">
-        <v>212.08</v>
+        <v>-137.38</v>
       </c>
       <c r="N75" s="18" t="n">
-        <v>197.09</v>
-      </c>
-      <c r="P75" s="9" t="n"/>
-      <c r="U75" s="9" t="n"/>
-      <c r="Z75" s="9" t="n"/>
-      <c r="AB75" s="5" t="n"/>
+        <v>-96.91</v>
+      </c>
+      <c r="O75" s="18" t="n">
+        <v>-109.66</v>
+      </c>
+      <c r="P75" s="37" t="n">
+        <v>-442.55</v>
+      </c>
+      <c r="Q75" s="18" t="n">
+        <v>-38.48</v>
+      </c>
+      <c r="R75" s="18" t="n">
+        <v>-66.68000000000001</v>
+      </c>
+      <c r="S75" s="18" t="n">
+        <v>-78.53</v>
+      </c>
+      <c r="T75" s="18" t="n">
+        <v>-94.28</v>
+      </c>
+      <c r="U75" s="37" t="n">
+        <v>-277.97</v>
+      </c>
+      <c r="V75" s="18" t="n">
+        <v>-1365.97</v>
+      </c>
+      <c r="W75" s="18" t="n">
+        <v>-1653.54</v>
+      </c>
+      <c r="X75" s="18" t="n">
+        <v>-158.62</v>
+      </c>
+      <c r="Y75" s="18" t="n">
+        <v>-5.86</v>
+      </c>
+      <c r="Z75" s="37" t="n">
+        <v>-3183.99</v>
+      </c>
+      <c r="AA75" s="18" t="n">
+        <v>-4.41</v>
+      </c>
+      <c r="AB75" s="19" t="n">
+        <v>-181.89</v>
+      </c>
       <c r="AC75" s="10" t="n"/>
       <c r="AD75" s="10" t="n"/>
       <c r="AE75" s="11" t="n"/>
@@ -25464,38 +25574,79 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>외환차익</t>
-        </is>
+          <t>투자활동으로인한현금흐름</t>
+        </is>
+      </c>
+      <c r="E76" s="18" t="n">
+        <v>-4084.14</v>
       </c>
       <c r="F76" s="9" t="n"/>
       <c r="G76" s="18" t="n">
-        <v>66.47</v>
+        <v>-8356.459999999999</v>
       </c>
       <c r="H76" s="18" t="n">
-        <v>74.64</v>
+        <v>-2005.49</v>
       </c>
       <c r="I76" s="18" t="n">
-        <v>471.82</v>
+        <v>-461.31</v>
       </c>
       <c r="J76" s="18" t="n">
-        <v>70.03</v>
+        <v>-121.99</v>
       </c>
       <c r="K76" s="37" t="n">
-        <v>682.96</v>
+        <v>-10945.25</v>
       </c>
       <c r="L76" s="18" t="n">
-        <v>74.52</v>
+        <v>1.18</v>
       </c>
       <c r="M76" s="18" t="n">
-        <v>110.91</v>
+        <v>10.15</v>
       </c>
       <c r="N76" s="18" t="n">
-        <v>57.86</v>
-      </c>
-      <c r="P76" s="9" t="n"/>
-      <c r="U76" s="9" t="n"/>
-      <c r="Z76" s="9" t="n"/>
-      <c r="AB76" s="5" t="n"/>
+        <v>27.85</v>
+      </c>
+      <c r="O76" s="18" t="n">
+        <v>535.66</v>
+      </c>
+      <c r="P76" s="37" t="n">
+        <v>574.84</v>
+      </c>
+      <c r="Q76" s="18" t="n">
+        <v>-62.75</v>
+      </c>
+      <c r="R76" s="18" t="n">
+        <v>12380.62</v>
+      </c>
+      <c r="S76" s="18" t="n">
+        <v>108.33</v>
+      </c>
+      <c r="T76" s="18" t="n">
+        <v>1673.19</v>
+      </c>
+      <c r="U76" s="37" t="n">
+        <v>14099.39</v>
+      </c>
+      <c r="V76" s="18" t="n">
+        <v>-3.73</v>
+      </c>
+      <c r="W76" s="18" t="n">
+        <v>-870.0700000000001</v>
+      </c>
+      <c r="X76" s="18" t="n">
+        <v>-5954.62</v>
+      </c>
+      <c r="Y76" s="18" t="n">
+        <v>-4217.95</v>
+      </c>
+      <c r="Z76" s="37" t="n">
+        <v>-11046.37</v>
+      </c>
+      <c r="AA76" s="18" t="n">
+        <v>-4409.66</v>
+      </c>
+      <c r="AB76" s="19" t="n">
+        <v>-8327.719999999999</v>
+      </c>
       <c r="AC76" s="10" t="n"/>
       <c r="AD76" s="10" t="n"/>
       <c r="AE76" s="11" t="n"/>
@@ -25516,37 +25667,73 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>외환차손</t>
-        </is>
+          <t>유형자산의증가</t>
+        </is>
+      </c>
+      <c r="E77" s="18" t="n">
+        <v>88.58</v>
       </c>
       <c r="F77" s="9" t="n"/>
       <c r="G77" s="18" t="n">
-        <v>3.96</v>
+        <v>8979.09</v>
       </c>
       <c r="H77" s="18" t="n">
-        <v>21.49</v>
+        <v>1440.99</v>
       </c>
       <c r="I77" s="18" t="n">
-        <v>23.99</v>
+        <v>564.11</v>
       </c>
       <c r="J77" s="18" t="n">
-        <v>75.83</v>
+        <v>96.54000000000001</v>
       </c>
       <c r="K77" s="37" t="n">
-        <v>125.27</v>
+        <v>11080.73</v>
       </c>
       <c r="L77" s="18" t="n">
-        <v>26.49</v>
+        <v>1.8</v>
       </c>
       <c r="M77" s="18" t="n">
-        <v>9.390000000000001</v>
+        <v>36.57</v>
       </c>
       <c r="N77" s="18" t="n">
-        <v>12.45</v>
-      </c>
-      <c r="P77" s="9" t="n"/>
-      <c r="U77" s="9" t="n"/>
-      <c r="Z77" s="9" t="n"/>
+        <v>3.4</v>
+      </c>
+      <c r="O77" s="18" t="n">
+        <v>5.37</v>
+      </c>
+      <c r="P77" s="37" t="n">
+        <v>47.14</v>
+      </c>
+      <c r="Q77" s="18" t="n">
+        <v>10.05</v>
+      </c>
+      <c r="R77" s="18" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="S77" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T77" s="18" t="n">
+        <v>9.81</v>
+      </c>
+      <c r="U77" s="37" t="n">
+        <v>20.76</v>
+      </c>
+      <c r="V77" s="18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W77" s="18" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="X77" s="18" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Y77" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z77" s="37" t="n">
+        <v>7.63</v>
+      </c>
       <c r="AB77" s="5" t="n"/>
       <c r="AC77" s="10" t="n"/>
       <c r="AD77" s="10" t="n"/>
@@ -25568,37 +25755,73 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>외화환산이익</t>
-        </is>
+          <t>CAPEX</t>
+        </is>
+      </c>
+      <c r="E78" s="18" t="n">
+        <v>138.08</v>
       </c>
       <c r="F78" s="9" t="n"/>
       <c r="G78" s="18" t="n">
-        <v>64.81999999999999</v>
+        <v>8979.09</v>
       </c>
       <c r="H78" s="18" t="n">
-        <v>196.66</v>
+        <v>1446.49</v>
       </c>
       <c r="I78" s="18" t="n">
-        <v>-30.78</v>
+        <v>564.11</v>
       </c>
       <c r="J78" s="18" t="n">
-        <v>-224.21</v>
+        <v>125.29</v>
       </c>
       <c r="K78" s="37" t="n">
-        <v>6.49</v>
+        <v>11114.98</v>
       </c>
       <c r="L78" s="18" t="n">
-        <v>112.93</v>
+        <v>1.8</v>
       </c>
       <c r="M78" s="18" t="n">
-        <v>-36.1</v>
+        <v>36.57</v>
       </c>
       <c r="N78" s="18" t="n">
-        <v>37.12</v>
-      </c>
-      <c r="P78" s="9" t="n"/>
-      <c r="U78" s="9" t="n"/>
-      <c r="Z78" s="9" t="n"/>
+        <v>3.4</v>
+      </c>
+      <c r="O78" s="18" t="n">
+        <v>5.37</v>
+      </c>
+      <c r="P78" s="37" t="n">
+        <v>47.14</v>
+      </c>
+      <c r="Q78" s="18" t="n">
+        <v>10.05</v>
+      </c>
+      <c r="R78" s="18" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="S78" s="18" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="T78" s="18" t="n">
+        <v>9.81</v>
+      </c>
+      <c r="U78" s="37" t="n">
+        <v>27.36</v>
+      </c>
+      <c r="V78" s="18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W78" s="18" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="X78" s="18" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Y78" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z78" s="37" t="n">
+        <v>7.63</v>
+      </c>
       <c r="AB78" s="5" t="n"/>
       <c r="AC78" s="10" t="n"/>
       <c r="AD78" s="10" t="n"/>
@@ -25620,36 +25843,50 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>외화환산손실</t>
-        </is>
+          <t>무형자산의증가</t>
+        </is>
+      </c>
+      <c r="E79" s="18" t="n">
+        <v>49.5</v>
       </c>
       <c r="F79" s="9" t="n"/>
       <c r="G79" s="18" t="n">
-        <v>6.83</v>
+        <v>0</v>
       </c>
       <c r="H79" s="18" t="n">
-        <v>3</v>
+        <v>5.5</v>
       </c>
       <c r="I79" s="18" t="n">
-        <v>13.78</v>
+        <v>0</v>
       </c>
       <c r="J79" s="18" t="n">
-        <v>190.65</v>
+        <v>28.75</v>
       </c>
       <c r="K79" s="37" t="n">
-        <v>214.26</v>
+        <v>34.25</v>
       </c>
       <c r="L79" s="18" t="n">
-        <v>5.24</v>
+        <v>0</v>
       </c>
       <c r="M79" s="18" t="n">
-        <v>0.28</v>
+        <v>0</v>
       </c>
       <c r="N79" s="18" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="P79" s="9" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="O79" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P79" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T79" s="18" t="n">
+        <v>0</v>
+      </c>
       <c r="U79" s="9" t="n"/>
+      <c r="Y79" s="18" t="n">
+        <v>0</v>
+      </c>
       <c r="Z79" s="9" t="n"/>
       <c r="AB79" s="5" t="n"/>
       <c r="AC79" s="10" t="n"/>
@@ -25672,38 +25909,79 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>이자손익</t>
-        </is>
+          <t>재무활동으로인한현금흐름</t>
+        </is>
+      </c>
+      <c r="E80" s="18" t="n">
+        <v>4429.12</v>
       </c>
       <c r="F80" s="9" t="n"/>
       <c r="G80" s="18" t="n">
-        <v>171.09</v>
+        <v>8184.3</v>
       </c>
       <c r="H80" s="18" t="n">
-        <v>-120.03</v>
+        <v>-280.37</v>
       </c>
       <c r="I80" s="18" t="n">
-        <v>190.84</v>
+        <v>502.48</v>
       </c>
       <c r="J80" s="18" t="n">
-        <v>-144.93</v>
+        <v>-200.14</v>
       </c>
       <c r="K80" s="37" t="n">
-        <v>96.97</v>
+        <v>8206.27</v>
       </c>
       <c r="L80" s="18" t="n">
-        <v>96.72</v>
+        <v>-8.92</v>
       </c>
       <c r="M80" s="18" t="n">
-        <v>-192.24</v>
+        <v>-708.3</v>
       </c>
       <c r="N80" s="18" t="n">
-        <v>178.44</v>
-      </c>
-      <c r="P80" s="9" t="n"/>
-      <c r="U80" s="9" t="n"/>
-      <c r="Z80" s="9" t="n"/>
-      <c r="AB80" s="5" t="n"/>
+        <v>-8.51</v>
+      </c>
+      <c r="O80" s="18" t="n">
+        <v>-8.74</v>
+      </c>
+      <c r="P80" s="37" t="n">
+        <v>-734.47</v>
+      </c>
+      <c r="Q80" s="18" t="n">
+        <v>-217.37</v>
+      </c>
+      <c r="R80" s="18" t="n">
+        <v>-570.87</v>
+      </c>
+      <c r="S80" s="18" t="n">
+        <v>1413.06</v>
+      </c>
+      <c r="T80" s="18" t="n">
+        <v>-99.08</v>
+      </c>
+      <c r="U80" s="37" t="n">
+        <v>525.74</v>
+      </c>
+      <c r="V80" s="18" t="n">
+        <v>-7.87</v>
+      </c>
+      <c r="W80" s="18" t="n">
+        <v>1995.35</v>
+      </c>
+      <c r="X80" s="18" t="n">
+        <v>1495.46</v>
+      </c>
+      <c r="Y80" s="18" t="n">
+        <v>-4.19</v>
+      </c>
+      <c r="Z80" s="37" t="n">
+        <v>3478.75</v>
+      </c>
+      <c r="AA80" s="18" t="n">
+        <v>-4.28</v>
+      </c>
+      <c r="AB80" s="19" t="n">
+        <v>-3.31</v>
+      </c>
       <c r="AC80" s="10" t="n"/>
       <c r="AD80" s="10" t="n"/>
       <c r="AE80" s="11" t="n"/>
@@ -25724,30 +26002,79 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>배당금수익</t>
-        </is>
+          <t>리스부채의상환</t>
+        </is>
+      </c>
+      <c r="E81" s="18" t="n">
+        <v>440.69</v>
       </c>
       <c r="F81" s="9" t="n"/>
+      <c r="G81" s="18" t="n">
+        <v>186.92</v>
+      </c>
       <c r="H81" s="18" t="n">
-        <v>0.51</v>
+        <v>194.16</v>
       </c>
       <c r="I81" s="18" t="n">
-        <v>0</v>
+        <v>197.52</v>
       </c>
       <c r="J81" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K81" s="9" t="n"/>
+        <v>200.14</v>
+      </c>
+      <c r="K81" s="37" t="n">
+        <v>778.74</v>
+      </c>
+      <c r="L81" s="18" t="n">
+        <v>8.92</v>
+      </c>
       <c r="M81" s="18" t="n">
-        <v>57.81</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="N81" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P81" s="9" t="n"/>
-      <c r="U81" s="9" t="n"/>
-      <c r="Z81" s="9" t="n"/>
-      <c r="AB81" s="5" t="n"/>
+        <v>8.51</v>
+      </c>
+      <c r="O81" s="18" t="n">
+        <v>8.74</v>
+      </c>
+      <c r="P81" s="37" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="Q81" s="18" t="n">
+        <v>8.960000000000001</v>
+      </c>
+      <c r="R81" s="18" t="n">
+        <v>8.220000000000001</v>
+      </c>
+      <c r="S81" s="18" t="n">
+        <v>7.61</v>
+      </c>
+      <c r="T81" s="18" t="n">
+        <v>7.56</v>
+      </c>
+      <c r="U81" s="37" t="n">
+        <v>32.35</v>
+      </c>
+      <c r="V81" s="18" t="n">
+        <v>7.87</v>
+      </c>
+      <c r="W81" s="18" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="X81" s="18" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="Y81" s="18" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="Z81" s="37" t="n">
+        <v>21.25</v>
+      </c>
+      <c r="AA81" s="18" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="AB81" s="19" t="n">
+        <v>3.31</v>
+      </c>
       <c r="AC81" s="10" t="n"/>
       <c r="AD81" s="10" t="n"/>
       <c r="AE81" s="11" t="n"/>
@@ -25768,14 +26095,42 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>중단사업이익</t>
-        </is>
+          <t>단기차입금의감소</t>
+        </is>
+      </c>
+      <c r="E82" s="18" t="n">
+        <v>0</v>
       </c>
       <c r="F82" s="9" t="n"/>
-      <c r="K82" s="9" t="n"/>
-      <c r="P82" s="9" t="n"/>
-      <c r="R82" s="18" t="n">
-        <v>9819.26</v>
+      <c r="G82" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I82" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" s="18" t="n">
+        <v>1200</v>
+      </c>
+      <c r="K82" s="37" t="n">
+        <v>1200</v>
+      </c>
+      <c r="L82" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" s="18" t="n">
+        <v>700</v>
+      </c>
+      <c r="N82" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O82" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P82" s="37" t="n">
+        <v>700</v>
       </c>
       <c r="S82" s="18" t="n">
         <v>0</v>
@@ -25784,22 +26139,13 @@
         <v>0</v>
       </c>
       <c r="U82" s="9" t="n"/>
-      <c r="V82" s="18" t="n">
+      <c r="Z82" s="9" t="n"/>
+      <c r="AA82" s="18" t="n">
+        <v>2000</v>
+      </c>
+      <c r="AB82" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="W82" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X82" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y82" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z82" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB82" s="5" t="n"/>
       <c r="AC82" s="10" t="n"/>
       <c r="AD82" s="10" t="n"/>
       <c r="AE82" s="11" t="n"/>
@@ -25820,79 +26166,52 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>영업활동으로인한현금흐름</t>
+          <t>유동성장기부채의감소</t>
         </is>
       </c>
       <c r="E83" s="18" t="n">
-        <v>2321</v>
+        <v>128.13</v>
       </c>
       <c r="F83" s="9" t="n"/>
       <c r="G83" s="18" t="n">
-        <v>-412.48</v>
+        <v>128.78</v>
       </c>
       <c r="H83" s="18" t="n">
-        <v>-1721.65</v>
+        <v>86.20999999999999</v>
       </c>
       <c r="I83" s="18" t="n">
-        <v>663.91</v>
+        <v>0</v>
       </c>
       <c r="J83" s="18" t="n">
-        <v>173.06</v>
+        <v>0</v>
       </c>
       <c r="K83" s="37" t="n">
-        <v>-1297.16</v>
+        <v>214.99</v>
       </c>
       <c r="L83" s="18" t="n">
-        <v>3487.06</v>
+        <v>0</v>
       </c>
       <c r="M83" s="18" t="n">
-        <v>1968.24</v>
+        <v>1600</v>
       </c>
       <c r="N83" s="18" t="n">
-        <v>2172</v>
+        <v>0</v>
       </c>
       <c r="O83" s="18" t="n">
-        <v>-225.58</v>
+        <v>0</v>
       </c>
       <c r="P83" s="37" t="n">
-        <v>7401.72</v>
-      </c>
-      <c r="Q83" s="18" t="n">
-        <v>1531.45</v>
-      </c>
-      <c r="R83" s="18" t="n">
-        <v>99.58</v>
+        <v>1600</v>
       </c>
       <c r="S83" s="18" t="n">
-        <v>175.05</v>
+        <v>0</v>
       </c>
       <c r="T83" s="18" t="n">
-        <v>3188.89</v>
-      </c>
-      <c r="U83" s="37" t="n">
-        <v>4994.97</v>
-      </c>
-      <c r="V83" s="18" t="n">
-        <v>-1993.48</v>
-      </c>
-      <c r="W83" s="18" t="n">
-        <v>-566.6900000000001</v>
-      </c>
-      <c r="X83" s="18" t="n">
-        <v>732.96</v>
-      </c>
-      <c r="Y83" s="18" t="n">
-        <v>-1156.94</v>
-      </c>
-      <c r="Z83" s="37" t="n">
-        <v>-2984.15</v>
-      </c>
-      <c r="AA83" s="18" t="n">
-        <v>893.5599999999999</v>
-      </c>
-      <c r="AB83" s="19" t="n">
-        <v>2185.69</v>
-      </c>
+        <v>1896.04</v>
+      </c>
+      <c r="U83" s="9" t="n"/>
+      <c r="Z83" s="9" t="n"/>
+      <c r="AB83" s="5" t="n"/>
       <c r="AC83" s="10" t="n"/>
       <c r="AD83" s="10" t="n"/>
       <c r="AE83" s="11" t="n"/>
@@ -25913,79 +26232,66 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>법인세납부(CF)</t>
+          <t>장기차입금의감소</t>
         </is>
       </c>
       <c r="E84" s="18" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="F84" s="9" t="n"/>
       <c r="G84" s="18" t="n">
-        <v>-223.48</v>
+        <v>0</v>
       </c>
       <c r="H84" s="18" t="n">
-        <v>-223.35</v>
+        <v>0</v>
       </c>
       <c r="I84" s="18" t="n">
-        <v>-190.36</v>
+        <v>0</v>
       </c>
       <c r="J84" s="18" t="n">
-        <v>-3.89</v>
+        <v>0</v>
       </c>
       <c r="K84" s="37" t="n">
-        <v>-641.08</v>
+        <v>0</v>
       </c>
       <c r="L84" s="18" t="n">
-        <v>-98.59999999999999</v>
+        <v>0</v>
       </c>
       <c r="M84" s="18" t="n">
-        <v>-137.38</v>
-      </c>
-      <c r="N84" s="18" t="n">
-        <v>-96.91</v>
-      </c>
-      <c r="O84" s="18" t="n">
-        <v>-109.66</v>
-      </c>
-      <c r="P84" s="37" t="n">
-        <v>-442.55</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P84" s="9" t="n"/>
       <c r="Q84" s="18" t="n">
-        <v>-38.48</v>
+        <v>208.41</v>
       </c>
       <c r="R84" s="18" t="n">
-        <v>-66.68000000000001</v>
+        <v>562.65</v>
       </c>
       <c r="S84" s="18" t="n">
-        <v>-78.53</v>
+        <v>4937.42</v>
       </c>
       <c r="T84" s="18" t="n">
-        <v>-94.28</v>
+        <v>5895.48</v>
       </c>
       <c r="U84" s="37" t="n">
-        <v>-277.97</v>
+        <v>11603.96</v>
       </c>
       <c r="V84" s="18" t="n">
-        <v>-1365.97</v>
+        <v>0</v>
       </c>
       <c r="W84" s="18" t="n">
-        <v>-1653.54</v>
+        <v>0</v>
       </c>
       <c r="X84" s="18" t="n">
-        <v>-158.62</v>
+        <v>0</v>
       </c>
       <c r="Y84" s="18" t="n">
-        <v>-5.86</v>
+        <v>0</v>
       </c>
       <c r="Z84" s="37" t="n">
-        <v>-3183.99</v>
-      </c>
-      <c r="AA84" s="18" t="n">
-        <v>-4.41</v>
-      </c>
-      <c r="AB84" s="19" t="n">
-        <v>-181.89</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AB84" s="5" t="n"/>
       <c r="AC84" s="10" t="n"/>
       <c r="AD84" s="10" t="n"/>
       <c r="AE84" s="11" t="n"/>
@@ -26006,78 +26312,78 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>투자활동으로인한현금흐름</t>
+          <t>현금및현금성자산의증감</t>
         </is>
       </c>
       <c r="E85" s="18" t="n">
-        <v>-4084.14</v>
+        <v>2659.61</v>
       </c>
       <c r="F85" s="9" t="n"/>
       <c r="G85" s="18" t="n">
-        <v>-8356.459999999999</v>
+        <v>-588.76</v>
       </c>
       <c r="H85" s="18" t="n">
-        <v>-2005.49</v>
+        <v>-3984.35</v>
       </c>
       <c r="I85" s="18" t="n">
-        <v>-461.31</v>
+        <v>686.47</v>
       </c>
       <c r="J85" s="18" t="n">
-        <v>-121.99</v>
+        <v>-157.62</v>
       </c>
       <c r="K85" s="37" t="n">
-        <v>-10945.25</v>
+        <v>-4044.26</v>
       </c>
       <c r="L85" s="18" t="n">
-        <v>1.18</v>
+        <v>3535.35</v>
       </c>
       <c r="M85" s="18" t="n">
-        <v>10.15</v>
+        <v>1218.95</v>
       </c>
       <c r="N85" s="18" t="n">
-        <v>27.85</v>
+        <v>2287.49</v>
       </c>
       <c r="O85" s="18" t="n">
-        <v>535.66</v>
+        <v>151.12</v>
       </c>
       <c r="P85" s="37" t="n">
-        <v>574.84</v>
+        <v>7192.91</v>
       </c>
       <c r="Q85" s="18" t="n">
-        <v>-62.75</v>
+        <v>1265.84</v>
       </c>
       <c r="R85" s="18" t="n">
-        <v>12380.62</v>
+        <v>11894.81</v>
       </c>
       <c r="S85" s="18" t="n">
-        <v>108.33</v>
+        <v>1682.98</v>
       </c>
       <c r="T85" s="18" t="n">
-        <v>1673.19</v>
+        <v>4775.1</v>
       </c>
       <c r="U85" s="37" t="n">
-        <v>14099.39</v>
+        <v>19618.73</v>
       </c>
       <c r="V85" s="18" t="n">
-        <v>-3.73</v>
+        <v>-2002.29</v>
       </c>
       <c r="W85" s="18" t="n">
-        <v>-870.0700000000001</v>
+        <v>534.91</v>
       </c>
       <c r="X85" s="18" t="n">
-        <v>-5954.62</v>
+        <v>-3705.3</v>
       </c>
       <c r="Y85" s="18" t="n">
-        <v>-4217.95</v>
+        <v>-5379.09</v>
       </c>
       <c r="Z85" s="37" t="n">
-        <v>-11046.37</v>
+        <v>-10551.77</v>
       </c>
       <c r="AA85" s="18" t="n">
-        <v>-4409.66</v>
+        <v>-3520.38</v>
       </c>
       <c r="AB85" s="19" t="n">
-        <v>-8327.719999999999</v>
+        <v>-6145.34</v>
       </c>
       <c r="AC85" s="10" t="n"/>
       <c r="AD85" s="10" t="n"/>
@@ -26099,74 +26405,79 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>유형자산의증가</t>
+          <t>기말현금및현금성자산</t>
         </is>
       </c>
       <c r="E86" s="18" t="n">
-        <v>88.58</v>
+        <v>2659.61</v>
       </c>
       <c r="F86" s="9" t="n"/>
       <c r="G86" s="18" t="n">
-        <v>8979.09</v>
+        <v>5308.01</v>
       </c>
       <c r="H86" s="18" t="n">
-        <v>1440.99</v>
+        <v>-3984.35</v>
       </c>
       <c r="I86" s="18" t="n">
-        <v>564.11</v>
+        <v>686.47</v>
       </c>
       <c r="J86" s="18" t="n">
-        <v>96.54000000000001</v>
+        <v>-157.62</v>
       </c>
       <c r="K86" s="37" t="n">
-        <v>11080.73</v>
+        <v>1852.51</v>
       </c>
       <c r="L86" s="18" t="n">
-        <v>1.8</v>
+        <v>5387.86</v>
       </c>
       <c r="M86" s="18" t="n">
-        <v>36.57</v>
+        <v>1218.96</v>
       </c>
       <c r="N86" s="18" t="n">
-        <v>3.4</v>
+        <v>2287.48</v>
       </c>
       <c r="O86" s="18" t="n">
-        <v>5.37</v>
+        <v>151.13</v>
       </c>
       <c r="P86" s="37" t="n">
-        <v>47.14</v>
+        <v>9045.43</v>
       </c>
       <c r="Q86" s="18" t="n">
-        <v>10.05</v>
+        <v>10311.27</v>
       </c>
       <c r="R86" s="18" t="n">
-        <v>0.9</v>
+        <v>11894.81</v>
       </c>
       <c r="S86" s="18" t="n">
-        <v>0</v>
+        <v>1682.97</v>
       </c>
       <c r="T86" s="18" t="n">
-        <v>9.81</v>
+        <v>4775.11</v>
       </c>
       <c r="U86" s="37" t="n">
-        <v>20.76</v>
+        <v>28664.16</v>
       </c>
       <c r="V86" s="18" t="n">
-        <v>1.5</v>
+        <v>26661.87</v>
       </c>
       <c r="W86" s="18" t="n">
-        <v>3.81</v>
+        <v>534.91</v>
       </c>
       <c r="X86" s="18" t="n">
-        <v>2.32</v>
+        <v>-3705.3</v>
       </c>
       <c r="Y86" s="18" t="n">
-        <v>0</v>
+        <v>-5379.09</v>
       </c>
       <c r="Z86" s="37" t="n">
-        <v>7.63</v>
-      </c>
-      <c r="AB86" s="5" t="n"/>
+        <v>18112.39</v>
+      </c>
+      <c r="AA86" s="18" t="n">
+        <v>14592.01</v>
+      </c>
+      <c r="AB86" s="19" t="n">
+        <v>-6145.34</v>
+      </c>
       <c r="AC86" s="10" t="n"/>
       <c r="AD86" s="10" t="n"/>
       <c r="AE86" s="11" t="n"/>
@@ -26187,73 +26498,54 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>CAPEX</t>
-        </is>
-      </c>
-      <c r="E87" s="18" t="n">
-        <v>138.08</v>
+          <t>배당금수취(CF)</t>
+        </is>
       </c>
       <c r="F87" s="9" t="n"/>
       <c r="G87" s="18" t="n">
-        <v>8979.09</v>
+        <v>0</v>
       </c>
       <c r="H87" s="18" t="n">
-        <v>1446.49</v>
+        <v>0.51</v>
       </c>
       <c r="I87" s="18" t="n">
-        <v>564.11</v>
+        <v>0</v>
       </c>
       <c r="J87" s="18" t="n">
-        <v>125.29</v>
+        <v>0</v>
       </c>
       <c r="K87" s="37" t="n">
-        <v>11114.98</v>
+        <v>0.51</v>
       </c>
       <c r="L87" s="18" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M87" s="18" t="n">
-        <v>36.57</v>
+        <v>57.81</v>
       </c>
       <c r="N87" s="18" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O87" s="18" t="n">
-        <v>5.37</v>
+        <v>0</v>
       </c>
       <c r="P87" s="37" t="n">
-        <v>47.14</v>
-      </c>
-      <c r="Q87" s="18" t="n">
-        <v>10.05</v>
-      </c>
-      <c r="R87" s="18" t="n">
-        <v>0.9</v>
+        <v>57.81</v>
       </c>
       <c r="S87" s="18" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="T87" s="18" t="n">
-        <v>9.81</v>
-      </c>
-      <c r="U87" s="37" t="n">
-        <v>27.36</v>
-      </c>
-      <c r="V87" s="18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W87" s="18" t="n">
-        <v>3.81</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U87" s="9" t="n"/>
       <c r="X87" s="18" t="n">
-        <v>2.32</v>
+        <v>3.16</v>
       </c>
       <c r="Y87" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z87" s="37" t="n">
-        <v>7.63</v>
-      </c>
+        <v>9.57</v>
+      </c>
+      <c r="Z87" s="9" t="n"/>
       <c r="AB87" s="5" t="n"/>
       <c r="AC87" s="10" t="n"/>
       <c r="AD87" s="10" t="n"/>
@@ -26275,33 +26567,30 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>무형자산의증가</t>
-        </is>
-      </c>
-      <c r="E88" s="18" t="n">
-        <v>49.5</v>
+          <t>유형자산의감소</t>
+        </is>
       </c>
       <c r="F88" s="9" t="n"/>
       <c r="G88" s="18" t="n">
+        <v>624.4299999999999</v>
+      </c>
+      <c r="H88" s="18" t="n">
         <v>0</v>
-      </c>
-      <c r="H88" s="18" t="n">
-        <v>5.5</v>
       </c>
       <c r="I88" s="18" t="n">
         <v>0</v>
       </c>
       <c r="J88" s="18" t="n">
-        <v>28.75</v>
+        <v>1.75</v>
       </c>
       <c r="K88" s="37" t="n">
-        <v>34.25</v>
+        <v>626.1799999999999</v>
       </c>
       <c r="L88" s="18" t="n">
         <v>0</v>
       </c>
       <c r="M88" s="18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N88" s="18" t="n">
         <v>0</v>
@@ -26310,17 +26599,28 @@
         <v>0</v>
       </c>
       <c r="P88" s="37" t="n">
+        <v>4</v>
+      </c>
+      <c r="S88" s="18" t="n">
         <v>0</v>
       </c>
       <c r="T88" s="18" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="U88" s="9" t="n"/>
+      <c r="X88" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="U88" s="9" t="n"/>
       <c r="Y88" s="18" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="Z88" s="9" t="n"/>
+      <c r="AA88" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="Z88" s="9" t="n"/>
-      <c r="AB88" s="5" t="n"/>
+      <c r="AB88" s="19" t="n">
+        <v>0</v>
+      </c>
       <c r="AC88" s="10" t="n"/>
       <c r="AD88" s="10" t="n"/>
       <c r="AE88" s="11" t="n"/>
@@ -26341,79 +26641,55 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>재무활동으로인한현금흐름</t>
-        </is>
-      </c>
-      <c r="E89" s="18" t="n">
-        <v>4429.12</v>
+          <t>단기차입금의증가</t>
+        </is>
       </c>
       <c r="F89" s="9" t="n"/>
       <c r="G89" s="18" t="n">
-        <v>8184.3</v>
+        <v>0</v>
       </c>
       <c r="H89" s="18" t="n">
-        <v>-280.37</v>
+        <v>0</v>
       </c>
       <c r="I89" s="18" t="n">
-        <v>502.48</v>
+        <v>700</v>
       </c>
       <c r="J89" s="18" t="n">
-        <v>-200.14</v>
+        <v>1200</v>
       </c>
       <c r="K89" s="37" t="n">
-        <v>8206.27</v>
+        <v>1900</v>
       </c>
       <c r="L89" s="18" t="n">
-        <v>-8.92</v>
+        <v>0</v>
       </c>
       <c r="M89" s="18" t="n">
-        <v>-708.3</v>
+        <v>1600</v>
       </c>
       <c r="N89" s="18" t="n">
-        <v>-8.51</v>
+        <v>0</v>
       </c>
       <c r="O89" s="18" t="n">
-        <v>-8.74</v>
+        <v>0</v>
       </c>
       <c r="P89" s="37" t="n">
-        <v>-734.47</v>
-      </c>
-      <c r="Q89" s="18" t="n">
-        <v>-217.37</v>
-      </c>
-      <c r="R89" s="18" t="n">
-        <v>-570.87</v>
+        <v>1600</v>
       </c>
       <c r="S89" s="18" t="n">
-        <v>1413.06</v>
+        <v>0</v>
       </c>
       <c r="T89" s="18" t="n">
-        <v>-99.08</v>
-      </c>
-      <c r="U89" s="37" t="n">
-        <v>525.74</v>
-      </c>
-      <c r="V89" s="18" t="n">
-        <v>-7.87</v>
-      </c>
-      <c r="W89" s="18" t="n">
-        <v>1995.35</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U89" s="9" t="n"/>
       <c r="X89" s="18" t="n">
-        <v>1495.46</v>
+        <v>0</v>
       </c>
       <c r="Y89" s="18" t="n">
-        <v>-4.19</v>
-      </c>
-      <c r="Z89" s="37" t="n">
-        <v>3478.75</v>
-      </c>
-      <c r="AA89" s="18" t="n">
-        <v>-4.28</v>
-      </c>
-      <c r="AB89" s="19" t="n">
-        <v>-3.31</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Z89" s="9" t="n"/>
+      <c r="AB89" s="5" t="n"/>
       <c r="AC89" s="10" t="n"/>
       <c r="AD89" s="10" t="n"/>
       <c r="AE89" s="11" t="n"/>
@@ -26434,78 +26710,53 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>리스부채의상환</t>
-        </is>
-      </c>
-      <c r="E90" s="18" t="n">
-        <v>440.69</v>
+          <t>장기차입금의증가</t>
+        </is>
       </c>
       <c r="F90" s="9" t="n"/>
       <c r="G90" s="18" t="n">
-        <v>186.92</v>
+        <v>8500</v>
       </c>
       <c r="H90" s="18" t="n">
-        <v>194.16</v>
+        <v>0</v>
       </c>
       <c r="I90" s="18" t="n">
-        <v>197.52</v>
+        <v>0</v>
       </c>
       <c r="J90" s="18" t="n">
-        <v>200.14</v>
+        <v>0</v>
       </c>
       <c r="K90" s="37" t="n">
-        <v>778.74</v>
+        <v>8500</v>
       </c>
       <c r="L90" s="18" t="n">
-        <v>8.92</v>
+        <v>0</v>
       </c>
       <c r="M90" s="18" t="n">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="N90" s="18" t="n">
-        <v>8.51</v>
+        <v>0</v>
       </c>
       <c r="O90" s="18" t="n">
-        <v>8.74</v>
+        <v>0</v>
       </c>
       <c r="P90" s="37" t="n">
-        <v>34.47</v>
-      </c>
-      <c r="Q90" s="18" t="n">
-        <v>8.960000000000001</v>
-      </c>
-      <c r="R90" s="18" t="n">
-        <v>8.220000000000001</v>
-      </c>
-      <c r="S90" s="18" t="n">
-        <v>7.61</v>
+        <v>0</v>
       </c>
       <c r="T90" s="18" t="n">
-        <v>7.56</v>
-      </c>
-      <c r="U90" s="37" t="n">
-        <v>32.35</v>
-      </c>
-      <c r="V90" s="18" t="n">
-        <v>7.87</v>
-      </c>
-      <c r="W90" s="18" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="X90" s="18" t="n">
-        <v>4.54</v>
-      </c>
+        <v>7700</v>
+      </c>
+      <c r="U90" s="9" t="n"/>
       <c r="Y90" s="18" t="n">
-        <v>4.19</v>
-      </c>
-      <c r="Z90" s="37" t="n">
-        <v>21.25</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Z90" s="9" t="n"/>
       <c r="AA90" s="18" t="n">
-        <v>4.28</v>
+        <v>2000</v>
       </c>
       <c r="AB90" s="19" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="AC90" s="10" t="n"/>
       <c r="AD90" s="10" t="n"/>
@@ -26527,56 +26778,36 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>단기차입금의감소</t>
-        </is>
-      </c>
-      <c r="E91" s="18" t="n">
-        <v>0</v>
+          <t>이자수취(CF)</t>
+        </is>
       </c>
       <c r="F91" s="9" t="n"/>
-      <c r="G91" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H91" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I91" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J91" s="18" t="n">
-        <v>1200</v>
-      </c>
-      <c r="K91" s="37" t="n">
-        <v>1200</v>
-      </c>
-      <c r="L91" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M91" s="18" t="n">
-        <v>700</v>
-      </c>
-      <c r="N91" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O91" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P91" s="37" t="n">
-        <v>700</v>
-      </c>
-      <c r="S91" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T91" s="18" t="n">
-        <v>0</v>
+      <c r="K91" s="9" t="n"/>
+      <c r="P91" s="9" t="n"/>
+      <c r="Q91" s="18" t="n">
+        <v>351.33</v>
       </c>
       <c r="U91" s="9" t="n"/>
-      <c r="Z91" s="9" t="n"/>
+      <c r="V91" s="18" t="n">
+        <v>378.24</v>
+      </c>
+      <c r="W91" s="18" t="n">
+        <v>71.48</v>
+      </c>
+      <c r="X91" s="18" t="n">
+        <v>367.67</v>
+      </c>
+      <c r="Y91" s="18" t="n">
+        <v>38.09</v>
+      </c>
+      <c r="Z91" s="37" t="n">
+        <v>855.48</v>
+      </c>
       <c r="AA91" s="18" t="n">
-        <v>2000</v>
+        <v>397.06</v>
       </c>
       <c r="AB91" s="19" t="n">
-        <v>0</v>
+        <v>21.56</v>
       </c>
       <c r="AC91" s="10" t="n"/>
       <c r="AD91" s="10" t="n"/>
@@ -26598,50 +26829,19 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>유동성장기부채의감소</t>
-        </is>
-      </c>
-      <c r="E92" s="18" t="n">
-        <v>128.13</v>
+          <t>자기주식의취득</t>
+        </is>
       </c>
       <c r="F92" s="9" t="n"/>
-      <c r="G92" s="18" t="n">
-        <v>128.78</v>
-      </c>
-      <c r="H92" s="18" t="n">
-        <v>86.20999999999999</v>
-      </c>
-      <c r="I92" s="18" t="n">
+      <c r="K92" s="9" t="n"/>
+      <c r="P92" s="9" t="n"/>
+      <c r="T92" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="J92" s="18" t="n">
+      <c r="U92" s="9" t="n"/>
+      <c r="Y92" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="K92" s="37" t="n">
-        <v>214.99</v>
-      </c>
-      <c r="L92" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M92" s="18" t="n">
-        <v>1600</v>
-      </c>
-      <c r="N92" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O92" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P92" s="37" t="n">
-        <v>1600</v>
-      </c>
-      <c r="S92" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T92" s="18" t="n">
-        <v>1896.04</v>
-      </c>
-      <c r="U92" s="9" t="n"/>
       <c r="Z92" s="9" t="n"/>
       <c r="AB92" s="5" t="n"/>
       <c r="AC92" s="10" t="n"/>
@@ -26657,638 +26857,6 @@
       <c r="AM92" s="10" t="n"/>
       <c r="AN92" s="10" t="n"/>
       <c r="AO92" s="11" t="n"/>
-    </row>
-    <row r="93">
-      <c r="A93" t="n">
-        <v>1</v>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>장기차입금의감소</t>
-        </is>
-      </c>
-      <c r="E93" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F93" s="9" t="n"/>
-      <c r="G93" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H93" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I93" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J93" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K93" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L93" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M93" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P93" s="9" t="n"/>
-      <c r="Q93" s="18" t="n">
-        <v>208.41</v>
-      </c>
-      <c r="R93" s="18" t="n">
-        <v>562.65</v>
-      </c>
-      <c r="S93" s="18" t="n">
-        <v>4937.42</v>
-      </c>
-      <c r="T93" s="18" t="n">
-        <v>5895.48</v>
-      </c>
-      <c r="U93" s="37" t="n">
-        <v>11603.96</v>
-      </c>
-      <c r="V93" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W93" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X93" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y93" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z93" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB93" s="5" t="n"/>
-      <c r="AC93" s="10" t="n"/>
-      <c r="AD93" s="10" t="n"/>
-      <c r="AE93" s="11" t="n"/>
-      <c r="AF93" s="10" t="n"/>
-      <c r="AG93" s="10" t="n"/>
-      <c r="AH93" s="10" t="n"/>
-      <c r="AI93" s="10" t="n"/>
-      <c r="AJ93" s="11" t="n"/>
-      <c r="AK93" s="10" t="n"/>
-      <c r="AL93" s="10" t="n"/>
-      <c r="AM93" s="10" t="n"/>
-      <c r="AN93" s="10" t="n"/>
-      <c r="AO93" s="11" t="n"/>
-    </row>
-    <row r="94">
-      <c r="A94" t="n">
-        <v>1</v>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>현금및현금성자산의증감</t>
-        </is>
-      </c>
-      <c r="E94" s="18" t="n">
-        <v>2659.61</v>
-      </c>
-      <c r="F94" s="9" t="n"/>
-      <c r="G94" s="18" t="n">
-        <v>-588.76</v>
-      </c>
-      <c r="H94" s="18" t="n">
-        <v>-3984.35</v>
-      </c>
-      <c r="I94" s="18" t="n">
-        <v>686.47</v>
-      </c>
-      <c r="J94" s="18" t="n">
-        <v>-157.62</v>
-      </c>
-      <c r="K94" s="37" t="n">
-        <v>-4044.26</v>
-      </c>
-      <c r="L94" s="18" t="n">
-        <v>3535.35</v>
-      </c>
-      <c r="M94" s="18" t="n">
-        <v>1218.95</v>
-      </c>
-      <c r="N94" s="18" t="n">
-        <v>2287.49</v>
-      </c>
-      <c r="O94" s="18" t="n">
-        <v>151.12</v>
-      </c>
-      <c r="P94" s="37" t="n">
-        <v>7192.91</v>
-      </c>
-      <c r="Q94" s="18" t="n">
-        <v>1265.84</v>
-      </c>
-      <c r="R94" s="18" t="n">
-        <v>11894.81</v>
-      </c>
-      <c r="S94" s="18" t="n">
-        <v>1682.98</v>
-      </c>
-      <c r="T94" s="18" t="n">
-        <v>4775.1</v>
-      </c>
-      <c r="U94" s="37" t="n">
-        <v>19618.73</v>
-      </c>
-      <c r="V94" s="18" t="n">
-        <v>-2002.29</v>
-      </c>
-      <c r="W94" s="18" t="n">
-        <v>534.91</v>
-      </c>
-      <c r="X94" s="18" t="n">
-        <v>-3705.3</v>
-      </c>
-      <c r="Y94" s="18" t="n">
-        <v>-5379.09</v>
-      </c>
-      <c r="Z94" s="37" t="n">
-        <v>-10551.77</v>
-      </c>
-      <c r="AA94" s="18" t="n">
-        <v>-3520.38</v>
-      </c>
-      <c r="AB94" s="19" t="n">
-        <v>-6145.34</v>
-      </c>
-      <c r="AC94" s="10" t="n"/>
-      <c r="AD94" s="10" t="n"/>
-      <c r="AE94" s="11" t="n"/>
-      <c r="AF94" s="10" t="n"/>
-      <c r="AG94" s="10" t="n"/>
-      <c r="AH94" s="10" t="n"/>
-      <c r="AI94" s="10" t="n"/>
-      <c r="AJ94" s="11" t="n"/>
-      <c r="AK94" s="10" t="n"/>
-      <c r="AL94" s="10" t="n"/>
-      <c r="AM94" s="10" t="n"/>
-      <c r="AN94" s="10" t="n"/>
-      <c r="AO94" s="11" t="n"/>
-    </row>
-    <row r="95">
-      <c r="A95" t="n">
-        <v>1</v>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>기말현금및현금성자산</t>
-        </is>
-      </c>
-      <c r="E95" s="18" t="n">
-        <v>2659.61</v>
-      </c>
-      <c r="F95" s="9" t="n"/>
-      <c r="G95" s="18" t="n">
-        <v>5308.01</v>
-      </c>
-      <c r="H95" s="18" t="n">
-        <v>-3984.35</v>
-      </c>
-      <c r="I95" s="18" t="n">
-        <v>686.47</v>
-      </c>
-      <c r="J95" s="18" t="n">
-        <v>-157.62</v>
-      </c>
-      <c r="K95" s="37" t="n">
-        <v>1852.51</v>
-      </c>
-      <c r="L95" s="18" t="n">
-        <v>5387.86</v>
-      </c>
-      <c r="M95" s="18" t="n">
-        <v>1218.96</v>
-      </c>
-      <c r="N95" s="18" t="n">
-        <v>2287.48</v>
-      </c>
-      <c r="O95" s="18" t="n">
-        <v>151.13</v>
-      </c>
-      <c r="P95" s="37" t="n">
-        <v>9045.43</v>
-      </c>
-      <c r="Q95" s="18" t="n">
-        <v>10311.27</v>
-      </c>
-      <c r="R95" s="18" t="n">
-        <v>11894.81</v>
-      </c>
-      <c r="S95" s="18" t="n">
-        <v>1682.97</v>
-      </c>
-      <c r="T95" s="18" t="n">
-        <v>4775.11</v>
-      </c>
-      <c r="U95" s="37" t="n">
-        <v>28664.16</v>
-      </c>
-      <c r="V95" s="18" t="n">
-        <v>26661.87</v>
-      </c>
-      <c r="W95" s="18" t="n">
-        <v>534.91</v>
-      </c>
-      <c r="X95" s="18" t="n">
-        <v>-3705.3</v>
-      </c>
-      <c r="Y95" s="18" t="n">
-        <v>-5379.09</v>
-      </c>
-      <c r="Z95" s="37" t="n">
-        <v>18112.39</v>
-      </c>
-      <c r="AA95" s="18" t="n">
-        <v>14592.01</v>
-      </c>
-      <c r="AB95" s="19" t="n">
-        <v>-6145.34</v>
-      </c>
-      <c r="AC95" s="10" t="n"/>
-      <c r="AD95" s="10" t="n"/>
-      <c r="AE95" s="11" t="n"/>
-      <c r="AF95" s="10" t="n"/>
-      <c r="AG95" s="10" t="n"/>
-      <c r="AH95" s="10" t="n"/>
-      <c r="AI95" s="10" t="n"/>
-      <c r="AJ95" s="11" t="n"/>
-      <c r="AK95" s="10" t="n"/>
-      <c r="AL95" s="10" t="n"/>
-      <c r="AM95" s="10" t="n"/>
-      <c r="AN95" s="10" t="n"/>
-      <c r="AO95" s="11" t="n"/>
-    </row>
-    <row r="96">
-      <c r="A96" t="n">
-        <v>1</v>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>배당금수취(CF)</t>
-        </is>
-      </c>
-      <c r="F96" s="9" t="n"/>
-      <c r="G96" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H96" s="18" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="I96" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J96" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K96" s="37" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="L96" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M96" s="18" t="n">
-        <v>57.81</v>
-      </c>
-      <c r="N96" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O96" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P96" s="37" t="n">
-        <v>57.81</v>
-      </c>
-      <c r="S96" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T96" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U96" s="9" t="n"/>
-      <c r="X96" s="18" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="Y96" s="18" t="n">
-        <v>9.57</v>
-      </c>
-      <c r="Z96" s="9" t="n"/>
-      <c r="AB96" s="5" t="n"/>
-      <c r="AC96" s="10" t="n"/>
-      <c r="AD96" s="10" t="n"/>
-      <c r="AE96" s="11" t="n"/>
-      <c r="AF96" s="10" t="n"/>
-      <c r="AG96" s="10" t="n"/>
-      <c r="AH96" s="10" t="n"/>
-      <c r="AI96" s="10" t="n"/>
-      <c r="AJ96" s="11" t="n"/>
-      <c r="AK96" s="10" t="n"/>
-      <c r="AL96" s="10" t="n"/>
-      <c r="AM96" s="10" t="n"/>
-      <c r="AN96" s="10" t="n"/>
-      <c r="AO96" s="11" t="n"/>
-    </row>
-    <row r="97">
-      <c r="A97" t="n">
-        <v>1</v>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>유형자산의감소</t>
-        </is>
-      </c>
-      <c r="F97" s="9" t="n"/>
-      <c r="G97" s="18" t="n">
-        <v>624.4299999999999</v>
-      </c>
-      <c r="H97" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I97" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J97" s="18" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="K97" s="37" t="n">
-        <v>626.1799999999999</v>
-      </c>
-      <c r="L97" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M97" s="18" t="n">
-        <v>4</v>
-      </c>
-      <c r="N97" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O97" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P97" s="37" t="n">
-        <v>4</v>
-      </c>
-      <c r="S97" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T97" s="18" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="U97" s="9" t="n"/>
-      <c r="X97" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y97" s="18" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="Z97" s="9" t="n"/>
-      <c r="AA97" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB97" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC97" s="10" t="n"/>
-      <c r="AD97" s="10" t="n"/>
-      <c r="AE97" s="11" t="n"/>
-      <c r="AF97" s="10" t="n"/>
-      <c r="AG97" s="10" t="n"/>
-      <c r="AH97" s="10" t="n"/>
-      <c r="AI97" s="10" t="n"/>
-      <c r="AJ97" s="11" t="n"/>
-      <c r="AK97" s="10" t="n"/>
-      <c r="AL97" s="10" t="n"/>
-      <c r="AM97" s="10" t="n"/>
-      <c r="AN97" s="10" t="n"/>
-      <c r="AO97" s="11" t="n"/>
-    </row>
-    <row r="98">
-      <c r="A98" t="n">
-        <v>1</v>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>단기차입금의증가</t>
-        </is>
-      </c>
-      <c r="F98" s="9" t="n"/>
-      <c r="G98" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H98" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I98" s="18" t="n">
-        <v>700</v>
-      </c>
-      <c r="J98" s="18" t="n">
-        <v>1200</v>
-      </c>
-      <c r="K98" s="37" t="n">
-        <v>1900</v>
-      </c>
-      <c r="L98" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M98" s="18" t="n">
-        <v>1600</v>
-      </c>
-      <c r="N98" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O98" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P98" s="37" t="n">
-        <v>1600</v>
-      </c>
-      <c r="S98" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T98" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U98" s="9" t="n"/>
-      <c r="X98" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y98" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z98" s="9" t="n"/>
-      <c r="AB98" s="5" t="n"/>
-      <c r="AC98" s="10" t="n"/>
-      <c r="AD98" s="10" t="n"/>
-      <c r="AE98" s="11" t="n"/>
-      <c r="AF98" s="10" t="n"/>
-      <c r="AG98" s="10" t="n"/>
-      <c r="AH98" s="10" t="n"/>
-      <c r="AI98" s="10" t="n"/>
-      <c r="AJ98" s="11" t="n"/>
-      <c r="AK98" s="10" t="n"/>
-      <c r="AL98" s="10" t="n"/>
-      <c r="AM98" s="10" t="n"/>
-      <c r="AN98" s="10" t="n"/>
-      <c r="AO98" s="11" t="n"/>
-    </row>
-    <row r="99">
-      <c r="A99" t="n">
-        <v>1</v>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>장기차입금의증가</t>
-        </is>
-      </c>
-      <c r="F99" s="9" t="n"/>
-      <c r="G99" s="18" t="n">
-        <v>8500</v>
-      </c>
-      <c r="H99" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I99" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J99" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K99" s="37" t="n">
-        <v>8500</v>
-      </c>
-      <c r="L99" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M99" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N99" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O99" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P99" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="T99" s="18" t="n">
-        <v>7700</v>
-      </c>
-      <c r="U99" s="9" t="n"/>
-      <c r="Y99" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z99" s="9" t="n"/>
-      <c r="AA99" s="18" t="n">
-        <v>2000</v>
-      </c>
-      <c r="AB99" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC99" s="10" t="n"/>
-      <c r="AD99" s="10" t="n"/>
-      <c r="AE99" s="11" t="n"/>
-      <c r="AF99" s="10" t="n"/>
-      <c r="AG99" s="10" t="n"/>
-      <c r="AH99" s="10" t="n"/>
-      <c r="AI99" s="10" t="n"/>
-      <c r="AJ99" s="11" t="n"/>
-      <c r="AK99" s="10" t="n"/>
-      <c r="AL99" s="10" t="n"/>
-      <c r="AM99" s="10" t="n"/>
-      <c r="AN99" s="10" t="n"/>
-      <c r="AO99" s="11" t="n"/>
-    </row>
-    <row r="100">
-      <c r="A100" t="n">
-        <v>1</v>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>이자수취(CF)</t>
-        </is>
-      </c>
-      <c r="F100" s="9" t="n"/>
-      <c r="K100" s="9" t="n"/>
-      <c r="P100" s="9" t="n"/>
-      <c r="Q100" s="18" t="n">
-        <v>351.33</v>
-      </c>
-      <c r="U100" s="9" t="n"/>
-      <c r="V100" s="18" t="n">
-        <v>378.24</v>
-      </c>
-      <c r="W100" s="18" t="n">
-        <v>71.48</v>
-      </c>
-      <c r="X100" s="18" t="n">
-        <v>367.67</v>
-      </c>
-      <c r="Y100" s="18" t="n">
-        <v>38.09</v>
-      </c>
-      <c r="Z100" s="37" t="n">
-        <v>855.48</v>
-      </c>
-      <c r="AA100" s="18" t="n">
-        <v>397.06</v>
-      </c>
-      <c r="AB100" s="19" t="n">
-        <v>21.56</v>
-      </c>
-      <c r="AC100" s="10" t="n"/>
-      <c r="AD100" s="10" t="n"/>
-      <c r="AE100" s="11" t="n"/>
-      <c r="AF100" s="10" t="n"/>
-      <c r="AG100" s="10" t="n"/>
-      <c r="AH100" s="10" t="n"/>
-      <c r="AI100" s="10" t="n"/>
-      <c r="AJ100" s="11" t="n"/>
-      <c r="AK100" s="10" t="n"/>
-      <c r="AL100" s="10" t="n"/>
-      <c r="AM100" s="10" t="n"/>
-      <c r="AN100" s="10" t="n"/>
-      <c r="AO100" s="11" t="n"/>
-    </row>
-    <row r="101">
-      <c r="A101" t="n">
-        <v>1</v>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>자기주식의취득</t>
-        </is>
-      </c>
-      <c r="F101" s="9" t="n"/>
-      <c r="K101" s="9" t="n"/>
-      <c r="P101" s="9" t="n"/>
-      <c r="T101" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U101" s="9" t="n"/>
-      <c r="Y101" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z101" s="9" t="n"/>
-      <c r="AB101" s="5" t="n"/>
-      <c r="AC101" s="10" t="n"/>
-      <c r="AD101" s="10" t="n"/>
-      <c r="AE101" s="11" t="n"/>
-      <c r="AF101" s="10" t="n"/>
-      <c r="AG101" s="10" t="n"/>
-      <c r="AH101" s="10" t="n"/>
-      <c r="AI101" s="10" t="n"/>
-      <c r="AJ101" s="11" t="n"/>
-      <c r="AK101" s="10" t="n"/>
-      <c r="AL101" s="10" t="n"/>
-      <c r="AM101" s="10" t="n"/>
-      <c r="AN101" s="10" t="n"/>
-      <c r="AO101" s="11" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -40693,7 +40261,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>17.39</v>
+        <v>17.47</v>
       </c>
     </row>
     <row r="32">
@@ -40703,7 +40271,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/333430_model.xlsx
+++ b/argus/kship/models/333430_model.xlsx
@@ -663,55 +663,55 @@
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 85182억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 85181억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 88314억 × 비례계수 0.0076 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 88310억 × 비례계수 0.0076 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 91241억 × 비례계수 0.0076 × 계절비중 Q2 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 91234억 × 비례계수 0.0076 × 계절비중 Q2 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 94620억 × 비례계수 0.0076 × 계절비중 Q3 0.233(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 94611억 × 비례계수 0.0076 × 계절비중 Q3 0.233(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 99317억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 99305억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 105097억 × 비례계수 0.0076 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 105085억 × 비례계수 0.0076 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 111447억 × 비례계수 0.0076 × 계절비중 Q2 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 111436억 × 비례계수 0.0076 × 계절비중 Q2 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 117868억 × 비례계수 0.0076 × 계절비중 Q3 0.233(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 117858억 × 비례계수 0.0076 × 계절비중 Q3 0.233(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 123693억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 123684억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1590,55 +1590,55 @@
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 85182억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 85181억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 88314억 × 비례계수 0.0076 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 88310억 × 비례계수 0.0076 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 91241억 × 비례계수 0.0076 × 계절비중 Q2 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 91234억 × 비례계수 0.0076 × 계절비중 Q2 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 94620억 × 비례계수 0.0076 × 계절비중 Q3 0.233(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 94611억 × 비례계수 0.0076 × 계절비중 Q3 0.233(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 99317억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 99305억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 105097억 × 비례계수 0.0076 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 105085억 × 비례계수 0.0076 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 111447억 × 비례계수 0.0076 × 계절비중 Q2 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 111436억 × 비례계수 0.0076 × 계절비중 Q2 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 117868억 × 비례계수 0.0076 × 계절비중 Q3 0.233(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 117858억 × 비례계수 0.0076 × 계절비중 Q3 0.233(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 123693억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 123684억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -4059,7 +4059,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
         </is>
       </c>
     </row>
@@ -4208,7 +4208,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>· 이자율 자산 1.66% / 부채 3.62% — 이자손익 = (전분기 이자발생자산 × 자산이자율 − 전분기 총차입금 × 부채이자율)/4, 최소자승 역산(모델 assumptions [0.0166, 0.0362] 는 4자리 반올림이라 그대로 쓰면 ±1억 어긋남) · 출처: {"asset": "주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)", "debt": "주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)"}</t>
+          <t>· 이자율 자산 1.66% / 부채 3.63% — 이자손익 = (전분기 이자발생자산 × 자산이자율 − 전분기 총차입금 × 부채이자율)/4, 최소자승 역산(모델 assumptions [0.0166, 0.0362] 는 4자리 반올림이라 그대로 쓰면 ±1억 어긋남) · 출처: {"asset": "주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)", "debt": "주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)"}</t>
         </is>
       </c>
     </row>
@@ -4930,35 +4930,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1345.74</v>
+        <v>1345.14</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1457.79</v>
+        <v>1457.21</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5049,35 +5049,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5168,35 +5168,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>851.3099999999999</v>
+        <v>850.79</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.5700000000001</v>
+        <v>919.21</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5287,35 +5287,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5406,35 +5406,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1510.82</v>
+        <v>1509.74</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1690.9</v>
+        <v>1689.95</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5525,35 +5525,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5644,35 +5644,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.73</v>
+        <v>200.69</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.82</v>
+        <v>213.75</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5763,35 +5763,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6326,33 +6326,33 @@
         <v>0.02799295</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.316349948</v>
+        <v>0.316284416</v>
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.229096623</v>
+        <v>0.229013833</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.007961777</v>
+        <v>0.007900157999999999</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.179427524</v>
+        <v>0.179357022</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.165928212</v>
+        <v>0.165836901</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.190017513</v>
+        <v>0.18996295</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.221481844</v>
+        <v>0.221434248</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.245740929</v>
+        <v>0.245695839</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.245431255</v>
+        <v>0.245462698</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6637,39 +6637,39 @@
         <v>0.195642978</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>0.195648927</v>
+        <v>0.195658668</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.195608245</v>
+        <v>0.195621421</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.195622937</v>
+        <v>0.195634896</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.195648275</v>
+        <v>0.195659971</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.195644748</v>
+        <v>0.195627109</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.195618951</v>
+        <v>0.195641098</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.195635854</v>
+        <v>0.195655438</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.195633397</v>
+        <v>0.195652174</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.195625343</v>
+        <v>0.195645465</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7539,36 +7539,36 @@
         <v/>
       </c>
       <c r="AC29" s="30" t="n">
-        <v>0.001116851</v>
+        <v>0.001012104</v>
       </c>
       <c r="AD29" s="30" t="n">
-        <v>-0.00373285</v>
+        <v>0.006133997</v>
       </c>
       <c r="AE29" s="31" t="n"/>
       <c r="AF29" s="30" t="n">
-        <v>-0.002629252</v>
+        <v>-0.012718846</v>
       </c>
       <c r="AG29" s="30" t="n">
-        <v>0.002312495</v>
+        <v>0.002221991</v>
       </c>
       <c r="AH29" s="30" t="n">
-        <v>-0.002364124</v>
+        <v>0.007515986</v>
       </c>
       <c r="AI29" s="30" t="n">
-        <v>0.006203543</v>
+        <v>-0.002698375</v>
       </c>
       <c r="AJ29" s="31" t="n"/>
       <c r="AK29" s="30" t="n">
-        <v>-0.008859482</v>
+        <v>0.001037622</v>
       </c>
       <c r="AL29" s="30" t="n">
-        <v>0.004967321</v>
+        <v>0.004860349</v>
       </c>
       <c r="AM29" s="30" t="n">
-        <v>-0.000500382</v>
+        <v>-0.00063755</v>
       </c>
       <c r="AN29" s="30" t="n">
-        <v>-0.002500987</v>
+        <v>0.007285724</v>
       </c>
       <c r="AO29" s="31" t="n"/>
     </row>
@@ -7667,36 +7667,36 @@
         <v/>
       </c>
       <c r="AC30" s="30" t="n">
-        <v>0.00357668</v>
+        <v>0.003619252</v>
       </c>
       <c r="AD30" s="30" t="n">
-        <v>-0.005600673</v>
+        <v>-0.00553138</v>
       </c>
       <c r="AE30" s="31" t="n"/>
       <c r="AF30" s="30" t="n">
-        <v>0.001050841</v>
+        <v>0.001107718</v>
       </c>
       <c r="AG30" s="30" t="n">
-        <v>-0.000807864</v>
+        <v>-0.000740203</v>
       </c>
       <c r="AH30" s="30" t="n">
-        <v>-0.005413632</v>
+        <v>0.004640381</v>
       </c>
       <c r="AI30" s="30" t="n">
-        <v>0.000190554</v>
+        <v>-0.004719142</v>
       </c>
       <c r="AJ30" s="31" t="n"/>
       <c r="AK30" s="30" t="n">
-        <v>-0.001816081</v>
+        <v>-0.001744552</v>
       </c>
       <c r="AL30" s="30" t="n">
-        <v>0.004740572</v>
+        <v>0.00482694</v>
       </c>
       <c r="AM30" s="30" t="n">
-        <v>0.000529342</v>
+        <v>0.000605205</v>
       </c>
       <c r="AN30" s="30" t="n">
-        <v>-0.003257342</v>
+        <v>-0.003164337</v>
       </c>
       <c r="AO30" s="31" t="n"/>
     </row>
@@ -7933,26 +7933,26 @@
         <v>0.08418850899999999</v>
       </c>
       <c r="AG32" s="24" t="n">
-        <v>0.08579007700000001</v>
+        <v>0.085759932</v>
       </c>
       <c r="AH32" s="24" t="n">
-        <v>0.081038312</v>
+        <v>0.081068325</v>
       </c>
       <c r="AI32" s="24" t="n">
-        <v>0.104804951</v>
+        <v>0.10477927</v>
       </c>
       <c r="AJ32" s="25" t="n"/>
       <c r="AK32" s="24" t="n">
-        <v>0.072198977</v>
+        <v>0.072200656</v>
       </c>
       <c r="AL32" s="24" t="n">
-        <v>0.07622598999999999</v>
+        <v>0.076205962</v>
       </c>
       <c r="AM32" s="24" t="n">
-        <v>0.074050199</v>
+        <v>0.07405318299999999</v>
       </c>
       <c r="AN32" s="24" t="n">
-        <v>0.096046363</v>
+        <v>0.09603121000000001</v>
       </c>
       <c r="AO32" s="25" t="n"/>
     </row>
@@ -8061,26 +8061,26 @@
         <v>0.036881667</v>
       </c>
       <c r="AG33" s="24" t="n">
-        <v>0.039297994</v>
+        <v>0.039284186</v>
       </c>
       <c r="AH33" s="24" t="n">
-        <v>0.038781936</v>
+        <v>0.038795738</v>
       </c>
       <c r="AI33" s="24" t="n">
-        <v>0.052196045</v>
+        <v>0.052183255</v>
       </c>
       <c r="AJ33" s="25" t="n"/>
       <c r="AK33" s="24" t="n">
-        <v>0.037755114</v>
+        <v>0.037755573</v>
       </c>
       <c r="AL33" s="24" t="n">
-        <v>0.041183981</v>
+        <v>0.04117275</v>
       </c>
       <c r="AM33" s="24" t="n">
-        <v>0.041354948</v>
+        <v>0.041344629</v>
       </c>
       <c r="AN33" s="24" t="n">
-        <v>0.055312483</v>
+        <v>0.055325079</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -9018,7 +9018,7 @@
         </is>
       </c>
       <c r="D48" s="36" t="n">
-        <v>0.121312329123812</v>
+        <v>0.1213154879700031</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
@@ -9057,7 +9057,7 @@
         </is>
       </c>
       <c r="D49" s="36" t="n">
-        <v>0.1231063741721854</v>
+        <v>0.1231010431327096</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -9096,7 +9096,7 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.570751222403319</v>
+        <v>0.5707554159381204</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -9135,7 +9135,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.01661608399237282</v>
+        <v>0.01661763354585222</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -9174,7 +9174,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.03624719825973411</v>
+        <v>0.03625088160501328</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -9611,7 +9611,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18840,7 +18840,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -40241,7 +40241,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>210.7</v>
+        <v>210.6</v>
       </c>
     </row>
     <row r="30">

--- a/argus/kship/models/333430_model.xlsx
+++ b/argus/kship/models/333430_model.xlsx
@@ -4059,7 +4059,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
         </is>
       </c>
     </row>
@@ -9611,7 +9611,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18840,7 +18840,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/333430_model.xlsx
+++ b/argus/kship/models/333430_model.xlsx
@@ -4059,7 +4059,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
         </is>
       </c>
     </row>
@@ -5898,7 +5898,7 @@
         <v>3790</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>3680</v>
+        <v>3440</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6080,7 +6080,7 @@
         <v>2850</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>3645</v>
+        <v>3420</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6171,7 +6171,7 @@
         <v>3675.7</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>3835</v>
+        <v>3769.2</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -8743,7 +8743,7 @@
         </is>
       </c>
       <c r="D41" s="34" t="n">
-        <v>3680</v>
+        <v>3440</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
@@ -8783,7 +8783,7 @@
       </c>
       <c r="D42" s="35" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -9611,7 +9611,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18840,7 +18840,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -33332,7 +33332,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -38209,7 +38209,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -40261,7 +40261,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>17.47</v>
+        <v>16.33</v>
       </c>
     </row>
     <row r="32">
@@ -40271,7 +40271,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/333430_model.xlsx
+++ b/argus/kship/models/333430_model.xlsx
@@ -663,55 +663,55 @@
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 85181억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 85179억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 88310억 × 비례계수 0.0076 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 88295억 × 비례계수 0.0076 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 91234억 × 비례계수 0.0076 × 계절비중 Q2 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 91206억 × 비례계수 0.0076 × 계절비중 Q2 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 94611억 × 비례계수 0.0076 × 계절비중 Q3 0.233(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 94568억 × 비례계수 0.0076 × 계절비중 Q3 0.233(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 99305억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 99251억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 105085억 × 비례계수 0.0076 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 105030억 × 비례계수 0.0076 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 111436억 × 비례계수 0.0076 × 계절비중 Q2 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 111381억 × 비례계수 0.0076 × 계절비중 Q2 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 117858억 × 비례계수 0.0076 × 계절비중 Q3 0.233(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 117805억 × 비례계수 0.0076 × 계절비중 Q3 0.233(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 123684억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 123634억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1590,55 +1590,55 @@
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 85181억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 85179억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 88310억 × 비례계수 0.0076 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 88295억 × 비례계수 0.0076 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 91234억 × 비례계수 0.0076 × 계절비중 Q2 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 91206억 × 비례계수 0.0076 × 계절비중 Q2 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 94611억 × 비례계수 0.0076 × 계절비중 Q3 0.233(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 94568억 × 비례계수 0.0076 × 계절비중 Q3 0.233(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 99305억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 99251억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 105085억 × 비례계수 0.0076 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 105030억 × 비례계수 0.0076 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 111436억 × 비례계수 0.0076 × 계절비중 Q2 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 111381억 × 비례계수 0.0076 × 계절비중 Q2 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 117858억 × 비례계수 0.0076 × 계절비중 Q3 0.233(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 117805억 × 비례계수 0.0076 × 계절비중 Q3 0.233(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 123684억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 123634억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -4059,7 +4059,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
         </is>
       </c>
     </row>
@@ -4930,35 +4930,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1345.14</v>
+        <v>1343.63</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1457.21</v>
+        <v>1456.58</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5049,35 +5049,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5168,35 +5168,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>850.79</v>
+        <v>849.51</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.21</v>
+        <v>918.8099999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5287,35 +5287,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5406,35 +5406,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1509.74</v>
+        <v>1507.34</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1689.95</v>
+        <v>1688.95</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5525,35 +5525,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5644,35 +5644,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.69</v>
+        <v>200.5</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.75</v>
+        <v>213.68</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5763,35 +5763,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5898,7 +5898,7 @@
         <v>3790</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>3440</v>
+        <v>3405</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6080,7 +6080,7 @@
         <v>2850</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>3420</v>
+        <v>3220</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6171,7 +6171,7 @@
         <v>3675.7</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>3769.2</v>
+        <v>3717.9</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6330,29 +6330,29 @@
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.229013833</v>
+        <v>0.228848254</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.007900157999999999</v>
+        <v>0.007592063</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.179357022</v>
+        <v>0.178793006</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.165836901</v>
+        <v>0.165189684</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.18996295</v>
+        <v>0.189516944</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.221434248</v>
+        <v>0.221196184</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.245695839</v>
+        <v>0.245753589</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.245462698</v>
+        <v>0.245684498</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6644,32 +6644,32 @@
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.195621421</v>
+        <v>0.19564778</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.195634896</v>
+        <v>0.195633562</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.195659971</v>
+        <v>0.195633971</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.195627109</v>
+        <v>0.195650316</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.195641098</v>
+        <v>0.195627549</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.195655438</v>
+        <v>0.195653263</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.195652174</v>
+        <v>0.195640693</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.195645465</v>
+        <v>0.195650683</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7539,36 +7539,36 @@
         <v/>
       </c>
       <c r="AC29" s="30" t="n">
-        <v>0.001012104</v>
+        <v>0.000360688</v>
       </c>
       <c r="AD29" s="30" t="n">
-        <v>0.006133997</v>
+        <v>0.005267252</v>
       </c>
       <c r="AE29" s="31" t="n"/>
       <c r="AF29" s="30" t="n">
-        <v>-0.012718846</v>
+        <v>-0.003322047</v>
       </c>
       <c r="AG29" s="30" t="n">
-        <v>0.002221991</v>
+        <v>0.00276551</v>
       </c>
       <c r="AH29" s="30" t="n">
-        <v>0.007515986</v>
+        <v>-0.000706331</v>
       </c>
       <c r="AI29" s="30" t="n">
-        <v>-0.002698375</v>
+        <v>-0.001235727</v>
       </c>
       <c r="AJ29" s="31" t="n"/>
       <c r="AK29" s="30" t="n">
-        <v>0.001037622</v>
+        <v>-0.007279979</v>
       </c>
       <c r="AL29" s="30" t="n">
-        <v>0.004860349</v>
+        <v>0.00641281</v>
       </c>
       <c r="AM29" s="30" t="n">
-        <v>-0.00063755</v>
+        <v>0.000887435</v>
       </c>
       <c r="AN29" s="30" t="n">
-        <v>0.007285724</v>
+        <v>0.008437208</v>
       </c>
       <c r="AO29" s="31" t="n"/>
     </row>
@@ -7667,36 +7667,36 @@
         <v/>
       </c>
       <c r="AC30" s="30" t="n">
-        <v>0.003619252</v>
+        <v>0.003551241</v>
       </c>
       <c r="AD30" s="30" t="n">
-        <v>-0.00553138</v>
+        <v>-0.005594867</v>
       </c>
       <c r="AE30" s="31" t="n"/>
       <c r="AF30" s="30" t="n">
-        <v>0.001107718</v>
+        <v>0.001084019</v>
       </c>
       <c r="AG30" s="30" t="n">
-        <v>-0.000740203</v>
+        <v>0.004216472</v>
       </c>
       <c r="AH30" s="30" t="n">
-        <v>0.004640381</v>
+        <v>-0.005396926</v>
       </c>
       <c r="AI30" s="30" t="n">
-        <v>-0.004719142</v>
+        <v>0.005208118</v>
       </c>
       <c r="AJ30" s="31" t="n"/>
       <c r="AK30" s="30" t="n">
-        <v>-0.001744552</v>
+        <v>-0.00181305</v>
       </c>
       <c r="AL30" s="30" t="n">
-        <v>0.00482694</v>
+        <v>0.004735233</v>
       </c>
       <c r="AM30" s="30" t="n">
-        <v>0.000605205</v>
+        <v>0.000517786</v>
       </c>
       <c r="AN30" s="30" t="n">
-        <v>-0.003164337</v>
+        <v>-0.003285113</v>
       </c>
       <c r="AO30" s="31" t="n"/>
     </row>
@@ -7933,26 +7933,26 @@
         <v>0.08418850899999999</v>
       </c>
       <c r="AG32" s="24" t="n">
-        <v>0.085759932</v>
+        <v>0.085729788</v>
       </c>
       <c r="AH32" s="24" t="n">
-        <v>0.081068325</v>
+        <v>0.08101504800000001</v>
       </c>
       <c r="AI32" s="24" t="n">
-        <v>0.10477927</v>
+        <v>0.104735977</v>
       </c>
       <c r="AJ32" s="25" t="n"/>
       <c r="AK32" s="24" t="n">
-        <v>0.072200656</v>
+        <v>0.072162552</v>
       </c>
       <c r="AL32" s="24" t="n">
-        <v>0.076205962</v>
+        <v>0.076195845</v>
       </c>
       <c r="AM32" s="24" t="n">
-        <v>0.07405318299999999</v>
+        <v>0.074024823</v>
       </c>
       <c r="AN32" s="24" t="n">
-        <v>0.09603121000000001</v>
+        <v>0.096011706</v>
       </c>
       <c r="AO32" s="25" t="n"/>
     </row>
@@ -8058,29 +8058,29 @@
       </c>
       <c r="AE33" s="25" t="n"/>
       <c r="AF33" s="24" t="n">
-        <v>0.036881667</v>
+        <v>0.036867349</v>
       </c>
       <c r="AG33" s="24" t="n">
-        <v>0.039284186</v>
+        <v>0.039284728</v>
       </c>
       <c r="AH33" s="24" t="n">
-        <v>0.038795738</v>
+        <v>0.03876968</v>
       </c>
       <c r="AI33" s="24" t="n">
-        <v>0.052183255</v>
+        <v>0.052159677</v>
       </c>
       <c r="AJ33" s="25" t="n"/>
       <c r="AK33" s="24" t="n">
-        <v>0.037755573</v>
+        <v>0.037733555</v>
       </c>
       <c r="AL33" s="24" t="n">
-        <v>0.04117275</v>
+        <v>0.041164412</v>
       </c>
       <c r="AM33" s="24" t="n">
-        <v>0.041344629</v>
+        <v>0.041325848</v>
       </c>
       <c r="AN33" s="24" t="n">
-        <v>0.055325079</v>
+        <v>0.055309448</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -8743,11 +8743,11 @@
         </is>
       </c>
       <c r="D41" s="34" t="n">
-        <v>3440</v>
+        <v>3405</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 3,755원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 3,710원)</t>
         </is>
       </c>
       <c r="F41" s="9" t="n"/>
@@ -8783,7 +8783,7 @@
       </c>
       <c r="D42" s="35" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -9018,7 +9018,7 @@
         </is>
       </c>
       <c r="D48" s="36" t="n">
-        <v>0.1213154879700031</v>
+        <v>0.1213368412826591</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
@@ -9057,7 +9057,7 @@
         </is>
       </c>
       <c r="D49" s="36" t="n">
-        <v>0.1231010431327096</v>
+        <v>0.1230971495416595</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -9096,7 +9096,7 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.5707554159381204</v>
+        <v>0.5707678624369997</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -9135,7 +9135,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.01661763354585222</v>
+        <v>0.01662387439116117</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -9174,7 +9174,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.03625088160501328</v>
+        <v>0.03626555610258933</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -9611,7 +9611,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18840,7 +18840,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -33332,7 +33332,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -38209,7 +38209,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -40261,7 +40261,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>16.33</v>
+        <v>16.17</v>
       </c>
     </row>
     <row r="32">
@@ -40271,7 +40271,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/333430_model.xlsx
+++ b/argus/kship/models/333430_model.xlsx
@@ -669,49 +669,49 @@
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 88295억 × 비례계수 0.0076 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 88307억 × 비례계수 0.0076 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 91206억 × 비례계수 0.0076 × 계절비중 Q2 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 91230억 × 비례계수 0.0076 × 계절비중 Q2 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 94568억 × 비례계수 0.0076 × 계절비중 Q3 0.233(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 94604억 × 비례계수 0.0076 × 계절비중 Q3 0.233(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 99251억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 99299억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 105030억 × 비례계수 0.0076 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 105077억 × 비례계수 0.0076 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 111381억 × 비례계수 0.0076 × 계절비중 Q2 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 111427억 × 비례계수 0.0076 × 계절비중 Q2 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 117805억 × 비례계수 0.0076 × 계절비중 Q3 0.233(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 117848억 × 비례계수 0.0076 × 계절비중 Q3 0.233(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 123634억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 123674억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1596,49 +1596,49 @@
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 88295억 × 비례계수 0.0076 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 88307억 × 비례계수 0.0076 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 91206억 × 비례계수 0.0076 × 계절비중 Q2 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 91230억 × 비례계수 0.0076 × 계절비중 Q2 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 94568억 × 비례계수 0.0076 × 계절비중 Q3 0.233(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 94604억 × 비례계수 0.0076 × 계절비중 Q3 0.233(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 99251억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 99299억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 105030억 × 비례계수 0.0076 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 105077억 × 비례계수 0.0076 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 111381억 × 비례계수 0.0076 × 계절비중 Q2 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 111427억 × 비례계수 0.0076 × 계절비중 Q2 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 117805억 × 비례계수 0.0076 × 계절비중 Q3 0.233(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 117848억 × 비례계수 0.0076 × 계절비중 Q3 0.233(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 123634억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 123674억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -4059,7 +4059,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
         </is>
       </c>
     </row>
@@ -4930,35 +4930,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1343.63</v>
+        <v>1343.39</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1456.58</v>
+        <v>1456.01</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5049,35 +5049,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5168,35 +5168,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>849.51</v>
+        <v>849.39</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>918.8099999999999</v>
+        <v>918.46</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5287,35 +5287,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5406,35 +5406,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1507.34</v>
+        <v>1506.62</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1688.95</v>
+        <v>1688.01</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5525,35 +5525,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5644,35 +5644,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.5</v>
+        <v>200.49</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.68</v>
+        <v>213.61</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5763,35 +5763,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5898,7 +5898,7 @@
         <v>3790</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>3405</v>
+        <v>3505</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6171,7 +6171,7 @@
         <v>3675.7</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>3717.9</v>
+        <v>3692.5</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6330,29 +6330,29 @@
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.228848254</v>
+        <v>0.229013833</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.007592063</v>
+        <v>0.007838539</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.178793006</v>
+        <v>0.17928652</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.165189684</v>
+        <v>0.165737329</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.189516944</v>
+        <v>0.189895588</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.221196184</v>
+        <v>0.221386647</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.245753589</v>
+        <v>0.245650744</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.245684498</v>
+        <v>0.245483664</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6644,32 +6644,32 @@
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.19564778</v>
+        <v>0.195621421</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.195633562</v>
+        <v>0.195646857</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.195633971</v>
+        <v>0.195611885</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.195650316</v>
+        <v>0.195643818</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.195627549</v>
+        <v>0.195652174</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.195653263</v>
+        <v>0.195624969</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.195640693</v>
+        <v>0.19562296</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.195650683</v>
+        <v>0.195658883</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7539,36 +7539,36 @@
         <v/>
       </c>
       <c r="AC29" s="30" t="n">
-        <v>0.000360688</v>
+        <v>0.001467</v>
       </c>
       <c r="AD29" s="30" t="n">
-        <v>0.005267252</v>
+        <v>0.0067861</v>
       </c>
       <c r="AE29" s="31" t="n"/>
       <c r="AF29" s="30" t="n">
-        <v>-0.003322047</v>
+        <v>-0.002228313</v>
       </c>
       <c r="AG29" s="30" t="n">
-        <v>0.00276551</v>
+        <v>-0.007232233</v>
       </c>
       <c r="AH29" s="30" t="n">
-        <v>-0.000706331</v>
+        <v>-0.000706225</v>
       </c>
       <c r="AI29" s="30" t="n">
-        <v>-0.001235727</v>
+        <v>0.008053457</v>
       </c>
       <c r="AJ29" s="31" t="n"/>
       <c r="AK29" s="30" t="n">
-        <v>-0.007279979</v>
+        <v>0.001613164</v>
       </c>
       <c r="AL29" s="30" t="n">
-        <v>0.00641281</v>
+        <v>-0.003268559</v>
       </c>
       <c r="AM29" s="30" t="n">
-        <v>0.000887435</v>
+        <v>0.001269707</v>
       </c>
       <c r="AN29" s="30" t="n">
-        <v>0.008437208</v>
+        <v>0.008258898000000001</v>
       </c>
       <c r="AO29" s="31" t="n"/>
     </row>
@@ -7667,36 +7667,36 @@
         <v/>
       </c>
       <c r="AC30" s="30" t="n">
-        <v>0.003551241</v>
+        <v>0.003981257</v>
       </c>
       <c r="AD30" s="30" t="n">
-        <v>-0.005594867</v>
+        <v>-0.005013879</v>
       </c>
       <c r="AE30" s="31" t="n"/>
       <c r="AF30" s="30" t="n">
-        <v>0.001084019</v>
+        <v>0.001495722</v>
       </c>
       <c r="AG30" s="30" t="n">
-        <v>0.004216472</v>
+        <v>-0.000309367</v>
       </c>
       <c r="AH30" s="30" t="n">
-        <v>-0.005396926</v>
+        <v>6.993e-05</v>
       </c>
       <c r="AI30" s="30" t="n">
-        <v>0.005208118</v>
+        <v>-0.004118921</v>
       </c>
       <c r="AJ30" s="31" t="n"/>
       <c r="AK30" s="30" t="n">
-        <v>-0.00181305</v>
+        <v>0.008714214</v>
       </c>
       <c r="AL30" s="30" t="n">
-        <v>0.004735233</v>
+        <v>0.000334729</v>
       </c>
       <c r="AM30" s="30" t="n">
-        <v>0.000517786</v>
+        <v>-0.003859636</v>
       </c>
       <c r="AN30" s="30" t="n">
-        <v>-0.003285113</v>
+        <v>-0.002394124</v>
       </c>
       <c r="AO30" s="31" t="n"/>
     </row>
@@ -7933,26 +7933,26 @@
         <v>0.08418850899999999</v>
       </c>
       <c r="AG32" s="24" t="n">
-        <v>0.085729788</v>
+        <v>0.085759932</v>
       </c>
       <c r="AH32" s="24" t="n">
-        <v>0.08101504800000001</v>
+        <v>0.081040562</v>
       </c>
       <c r="AI32" s="24" t="n">
-        <v>0.104735977</v>
+        <v>0.104781961</v>
       </c>
       <c r="AJ32" s="25" t="n"/>
       <c r="AK32" s="24" t="n">
-        <v>0.072162552</v>
+        <v>0.07220233400000001</v>
       </c>
       <c r="AL32" s="24" t="n">
-        <v>0.076195845</v>
+        <v>0.07620761400000001</v>
       </c>
       <c r="AM32" s="24" t="n">
-        <v>0.074024823</v>
+        <v>0.074034529</v>
       </c>
       <c r="AN32" s="24" t="n">
-        <v>0.096011706</v>
+        <v>0.096034813</v>
       </c>
       <c r="AO32" s="25" t="n"/>
     </row>
@@ -8058,29 +8058,29 @@
       </c>
       <c r="AE33" s="25" t="n"/>
       <c r="AF33" s="24" t="n">
-        <v>0.036867349</v>
+        <v>0.036881667</v>
       </c>
       <c r="AG33" s="24" t="n">
-        <v>0.039284728</v>
+        <v>0.039284186</v>
       </c>
       <c r="AH33" s="24" t="n">
-        <v>0.03876968</v>
+        <v>0.038782452</v>
       </c>
       <c r="AI33" s="24" t="n">
-        <v>0.052159677</v>
+        <v>0.052183923</v>
       </c>
       <c r="AJ33" s="25" t="n"/>
       <c r="AK33" s="24" t="n">
-        <v>0.037733555</v>
+        <v>0.037756032</v>
       </c>
       <c r="AL33" s="24" t="n">
-        <v>0.041164412</v>
+        <v>0.041173232</v>
       </c>
       <c r="AM33" s="24" t="n">
-        <v>0.041325848</v>
+        <v>0.041345094</v>
       </c>
       <c r="AN33" s="24" t="n">
-        <v>0.055309448</v>
+        <v>0.055314873</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -8743,11 +8743,11 @@
         </is>
       </c>
       <c r="D41" s="34" t="n">
-        <v>3405</v>
+        <v>3505</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 3,710원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 3,475원)</t>
         </is>
       </c>
       <c r="F41" s="9" t="n"/>
@@ -8783,7 +8783,7 @@
       </c>
       <c r="D42" s="35" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -9018,7 +9018,7 @@
         </is>
       </c>
       <c r="D48" s="36" t="n">
-        <v>0.1213368412826591</v>
+        <v>0.1212989245071743</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
@@ -9057,7 +9057,7 @@
         </is>
       </c>
       <c r="D49" s="36" t="n">
-        <v>0.1230971495416595</v>
+        <v>0.1230977009412532</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -9096,7 +9096,7 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.5707678624369997</v>
+        <v>0.570759609970066</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -9135,7 +9135,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.01662387439116117</v>
+        <v>0.01661842035076801</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -9174,7 +9174,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.03626555610258933</v>
+        <v>0.03625269809000879</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -9611,7 +9611,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18840,7 +18840,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -33332,7 +33332,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -38209,7 +38209,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -40261,7 +40261,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>16.17</v>
+        <v>16.64</v>
       </c>
     </row>
     <row r="32">
@@ -40271,7 +40271,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/333430_model.xlsx
+++ b/argus/kship/models/333430_model.xlsx
@@ -663,55 +663,55 @@
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 85179억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 85298억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 88307억 × 비례계수 0.0076 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 88507억 × 비례계수 0.0076 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 91230억 × 비례계수 0.0076 × 계절비중 Q2 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 91437억 × 비례계수 0.0076 × 계절비중 Q2 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 94604억 × 비례계수 0.0076 × 계절비중 Q3 0.233(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 94759억 × 비례계수 0.0076 × 계절비중 Q3 0.233(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 99299억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 99239억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 105077억 × 비례계수 0.0076 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 104812억 × 비례계수 0.0076 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 111427억 × 비례계수 0.0076 × 계절비중 Q2 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 111021억 × 비례계수 0.0076 × 계절비중 Q2 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 117848억 × 비례계수 0.0076 × 계절비중 Q3 0.233(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 117367억 × 비례계수 0.0076 × 계절비중 Q3 0.233(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 123674억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 123182억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1590,55 +1590,55 @@
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 85179억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 85298억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 88307억 × 비례계수 0.0076 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 88507억 × 비례계수 0.0076 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 91230억 × 비례계수 0.0076 × 계절비중 Q2 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 91437억 × 비례계수 0.0076 × 계절비중 Q2 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 94604억 × 비례계수 0.0076 × 계절비중 Q3 0.233(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 94759억 × 비례계수 0.0076 × 계절비중 Q3 0.233(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 99299억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 99239억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 105077억 × 비례계수 0.0076 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 104812억 × 비례계수 0.0076 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 111427억 × 비례계수 0.0076 × 계절비중 Q2 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 111021억 × 비례계수 0.0076 × 계절비중 Q2 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 117848억 × 비례계수 0.0076 × 계절비중 Q3 0.233(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 117367억 × 비례계수 0.0076 × 계절비중 Q3 0.233(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 123674억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 123182억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -1998,7 +1998,7 @@
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 926억 × 1.66%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 290억 × 3.62%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 925억 × 1.66%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 290억 × 3.62%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2058,7 +2058,7 @@
     </comment>
     <comment ref="AN12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 926억 × 1.66%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 290억 × 3.62%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 925억 × 1.66%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 290억 × 3.62%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -4059,7 +4059,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
         </is>
       </c>
     </row>
@@ -4930,35 +4930,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1343.39</v>
+        <v>1342.11</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1456.01</v>
+        <v>1454.27</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5049,35 +5049,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5168,35 +5168,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>849.39</v>
+        <v>848.59</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>918.46</v>
+        <v>917.39</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5287,35 +5287,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5406,35 +5406,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1506.62</v>
+        <v>1505.3</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1688.01</v>
+        <v>1685.25</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5525,35 +5525,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5644,35 +5644,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.49</v>
+        <v>200.38</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.61</v>
+        <v>213.41</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5763,35 +5763,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5898,7 +5898,7 @@
         <v>3790</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>3505</v>
+        <v>3445</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6080,7 +6080,7 @@
         <v>2850</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>3220</v>
+        <v>3200</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6171,7 +6171,7 @@
         <v>3675.7</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>3692.5</v>
+        <v>3599.1</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6326,33 +6326,33 @@
         <v>0.02799295</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.316284416</v>
+        <v>0.318119324</v>
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.229013833</v>
+        <v>0.231745895</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.007838539</v>
+        <v>0.010118438</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.17928652</v>
+        <v>0.181190073</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.165737329</v>
+        <v>0.163418514</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.189895588</v>
+        <v>0.184231752</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.221386647</v>
+        <v>0.214176783</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.245650744</v>
+        <v>0.238569894</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.245483664</v>
+        <v>0.241271741</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6637,39 +6637,39 @@
         <v>0.195642978</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>0.195658668</v>
+        <v>0.195634881</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.195621421</v>
+        <v>0.195658019</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.195646857</v>
+        <v>0.195632282</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.195611885</v>
+        <v>0.195654769</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.195643818</v>
+        <v>0.195632665</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.195652174</v>
+        <v>0.195641069</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.195624969</v>
+        <v>0.195639068</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.19562296</v>
+        <v>0.195653222</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.195658883</v>
+        <v>0.195648432</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7539,36 +7539,36 @@
         <v/>
       </c>
       <c r="AC29" s="30" t="n">
-        <v>0.001467</v>
+        <v>0.000325616</v>
       </c>
       <c r="AD29" s="30" t="n">
-        <v>0.0067861</v>
+        <v>-0.000736792</v>
       </c>
       <c r="AE29" s="31" t="n"/>
       <c r="AF29" s="30" t="n">
-        <v>-0.002228313</v>
+        <v>-0.001681633</v>
       </c>
       <c r="AG29" s="30" t="n">
-        <v>-0.007232233</v>
+        <v>-0.006572189</v>
       </c>
       <c r="AH29" s="30" t="n">
-        <v>-0.000706225</v>
+        <v>0.001418989</v>
       </c>
       <c r="AI29" s="30" t="n">
-        <v>0.008053457</v>
+        <v>0.000924517</v>
       </c>
       <c r="AJ29" s="31" t="n"/>
       <c r="AK29" s="30" t="n">
-        <v>0.001613164</v>
+        <v>0.001999606</v>
       </c>
       <c r="AL29" s="30" t="n">
-        <v>-0.003268559</v>
+        <v>0.002818262</v>
       </c>
       <c r="AM29" s="30" t="n">
-        <v>0.001269707</v>
+        <v>-0.000718524</v>
       </c>
       <c r="AN29" s="30" t="n">
-        <v>0.008258898000000001</v>
+        <v>0.003809042</v>
       </c>
       <c r="AO29" s="31" t="n"/>
     </row>
@@ -7667,36 +7667,36 @@
         <v/>
       </c>
       <c r="AC30" s="30" t="n">
-        <v>0.003981257</v>
+        <v>0.003312846</v>
       </c>
       <c r="AD30" s="30" t="n">
-        <v>-0.005013879</v>
+        <v>-0.000793757</v>
       </c>
       <c r="AE30" s="31" t="n"/>
       <c r="AF30" s="30" t="n">
-        <v>0.001495722</v>
+        <v>-0.003964614</v>
       </c>
       <c r="AG30" s="30" t="n">
-        <v>-0.000309367</v>
+        <v>-0.00570687</v>
       </c>
       <c r="AH30" s="30" t="n">
-        <v>6.993e-05</v>
+        <v>-0.000199415</v>
       </c>
       <c r="AI30" s="30" t="n">
-        <v>-0.004118921</v>
+        <v>0.000368654</v>
       </c>
       <c r="AJ30" s="31" t="n"/>
       <c r="AK30" s="30" t="n">
-        <v>0.008714214</v>
+        <v>0.00325249</v>
       </c>
       <c r="AL30" s="30" t="n">
-        <v>0.000334729</v>
+        <v>-0.000414237</v>
       </c>
       <c r="AM30" s="30" t="n">
-        <v>-0.003859636</v>
+        <v>-0.004926214</v>
       </c>
       <c r="AN30" s="30" t="n">
-        <v>-0.002394124</v>
+        <v>0.000878726</v>
       </c>
       <c r="AO30" s="31" t="n"/>
     </row>
@@ -7926,33 +7926,33 @@
         <v>0.098859266</v>
       </c>
       <c r="AD32" s="24" t="n">
-        <v>0.127662711</v>
+        <v>0.127846982</v>
       </c>
       <c r="AE32" s="25" t="n"/>
       <c r="AF32" s="24" t="n">
-        <v>0.08418850899999999</v>
+        <v>0.084370813</v>
       </c>
       <c r="AG32" s="24" t="n">
-        <v>0.085759932</v>
+        <v>0.08591231000000001</v>
       </c>
       <c r="AH32" s="24" t="n">
-        <v>0.081040562</v>
+        <v>0.081141081</v>
       </c>
       <c r="AI32" s="24" t="n">
-        <v>0.104781961</v>
+        <v>0.104645791</v>
       </c>
       <c r="AJ32" s="25" t="n"/>
       <c r="AK32" s="24" t="n">
-        <v>0.07220233400000001</v>
+        <v>0.07200780699999999</v>
       </c>
       <c r="AL32" s="24" t="n">
-        <v>0.07620761400000001</v>
+        <v>0.07590601700000001</v>
       </c>
       <c r="AM32" s="24" t="n">
-        <v>0.074034529</v>
+        <v>0.073753979</v>
       </c>
       <c r="AN32" s="24" t="n">
-        <v>0.096034813</v>
+        <v>0.095686598</v>
       </c>
       <c r="AO32" s="25" t="n"/>
     </row>
@@ -8054,33 +8054,33 @@
         <v>0.038180475</v>
       </c>
       <c r="AD33" s="24" t="n">
-        <v>0.052183607</v>
+        <v>0.05225893</v>
       </c>
       <c r="AE33" s="25" t="n"/>
       <c r="AF33" s="24" t="n">
-        <v>0.036881667</v>
+        <v>0.036950608</v>
       </c>
       <c r="AG33" s="24" t="n">
-        <v>0.039284186</v>
+        <v>0.039375406</v>
       </c>
       <c r="AH33" s="24" t="n">
-        <v>0.038782452</v>
+        <v>0.03884011</v>
       </c>
       <c r="AI33" s="24" t="n">
-        <v>0.052183923</v>
+        <v>0.052130883</v>
       </c>
       <c r="AJ33" s="25" t="n"/>
       <c r="AK33" s="24" t="n">
-        <v>0.037756032</v>
+        <v>0.037662243</v>
       </c>
       <c r="AL33" s="24" t="n">
-        <v>0.041173232</v>
+        <v>0.04101519</v>
       </c>
       <c r="AM33" s="24" t="n">
-        <v>0.041345094</v>
+        <v>0.041188052</v>
       </c>
       <c r="AN33" s="24" t="n">
-        <v>0.055314873</v>
+        <v>0.05510773</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -8743,11 +8743,11 @@
         </is>
       </c>
       <c r="D41" s="34" t="n">
-        <v>3505</v>
+        <v>3445</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 3,475원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 3,295원)</t>
         </is>
       </c>
       <c r="F41" s="9" t="n"/>
@@ -8783,7 +8783,7 @@
       </c>
       <c r="D42" s="35" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -9018,7 +9018,7 @@
         </is>
       </c>
       <c r="D48" s="36" t="n">
-        <v>0.1212989245071743</v>
+        <v>0.1213274590057092</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
@@ -9057,7 +9057,7 @@
         </is>
       </c>
       <c r="D49" s="36" t="n">
-        <v>0.1230977009412532</v>
+        <v>0.123100831412365</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -9096,7 +9096,7 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.570759609970066</v>
+        <v>0.570758915326648</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -9135,7 +9135,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.01661842035076801</v>
+        <v>0.01662166756093186</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -9174,7 +9174,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.03625269809000879</v>
+        <v>0.03626533214186858</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -9611,7 +9611,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18840,7 +18840,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -33332,7 +33332,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -38209,7 +38209,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -40241,7 +40241,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>210.6</v>
+        <v>210.9</v>
       </c>
     </row>
     <row r="30">
@@ -40261,7 +40261,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>16.64</v>
+        <v>16.33</v>
       </c>
     </row>
     <row r="32">
@@ -40271,7 +40271,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2.04</v>
+        <v>2.01</v>
       </c>
     </row>
     <row r="33">
@@ -40281,7 +40281,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.1226</v>
+        <v>0.1228</v>
       </c>
     </row>
     <row r="34">

--- a/argus/kship/models/333430_model.xlsx
+++ b/argus/kship/models/333430_model.xlsx
@@ -663,55 +663,55 @@
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 85298억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 85391억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 88507억 × 비례계수 0.0076 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 88678억 × 비례계수 0.0076 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 91437억 × 비례계수 0.0076 × 계절비중 Q2 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 91629억 × 비례계수 0.0076 × 계절비중 Q2 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 94759억 × 비례계수 0.0076 × 계절비중 Q3 0.233(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 94927억 × 비례계수 0.0076 × 계절비중 Q3 0.233(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 99239억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 99258억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 104812억 × 비례계수 0.0076 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 104675억 × 비례계수 0.0076 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 111021억 × 비례계수 0.0076 × 계절비중 Q2 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 110775억 × 비례계수 0.0076 × 계절비중 Q2 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 117367억 × 비례계수 0.0076 × 계절비중 Q3 0.233(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 117063억 × 비례계수 0.0076 × 계절비중 Q3 0.233(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 123182억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−0) 122870억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1590,55 +1590,55 @@
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 85298억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 85391억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 88507억 × 비례계수 0.0076 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 88678억 × 비례계수 0.0076 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 91437억 × 비례계수 0.0076 × 계절비중 Q2 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 91629억 × 비례계수 0.0076 × 계절비중 Q2 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 94759억 × 비례계수 0.0076 × 계절비중 Q3 0.233(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 94927억 × 비례계수 0.0076 × 계절비중 Q3 0.233(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 99239억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 99258억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 104812억 × 비례계수 0.0076 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 104675억 × 비례계수 0.0076 × 계절비중 Q1 0.221(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 111021억 × 비례계수 0.0076 × 계절비중 Q2 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 110775억 × 비례계수 0.0076 × 계절비중 Q2 0.236(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 117367억 × 비례계수 0.0076 × 계절비중 Q3 0.233(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 117063억 × 비례계수 0.0076 × 계절비중 Q3 0.233(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 123182억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 122870억 × 비례계수 0.0076 × 계절비중 Q4 0.310(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.84, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -1956,7 +1956,7 @@
     </comment>
     <comment ref="AF11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 698억 × 1.66%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 290억 × 3.62%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 699억 × 1.66%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 290억 × 3.62%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2016,7 +2016,7 @@
     </comment>
     <comment ref="AF12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 698억 × 1.66%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 290억 × 3.62%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 699억 × 1.66%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 290억 × 3.62%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -4059,7 +4059,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-26</t>
         </is>
       </c>
     </row>
@@ -4930,35 +4930,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1342.11</v>
+        <v>1337.49</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1454.27</v>
+        <v>1451.19</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5049,35 +5049,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5168,35 +5168,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>848.59</v>
+        <v>846.51</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>917.39</v>
+        <v>915.5700000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5287,35 +5287,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5406,35 +5406,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1505.3</v>
+        <v>1500.06</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1685.25</v>
+        <v>1680.5</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5525,35 +5525,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5644,35 +5644,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.38</v>
+        <v>199.88</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.41</v>
+        <v>213.06</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5763,35 +5763,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5898,7 +5898,7 @@
         <v>3790</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>3445</v>
+        <v>2975</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6080,7 +6080,7 @@
         <v>2850</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>3200</v>
+        <v>2955</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6171,7 +6171,7 @@
         <v>3675.7</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>3599.1</v>
+        <v>3455.9</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6326,33 +6326,33 @@
         <v>0.02799295</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.318119324</v>
+        <v>0.319561038</v>
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.231745895</v>
+        <v>0.234146798</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.010118438</v>
+        <v>0.012275099</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.181190073</v>
+        <v>0.183305133</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.163418514</v>
+        <v>0.162395709</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.184231752</v>
+        <v>0.180385054</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.214176783</v>
+        <v>0.208911614</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.238569894</v>
+        <v>0.233138704</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.241271741</v>
+        <v>0.237887721</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6637,39 +6637,39 @@
         <v>0.195642978</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>0.195634881</v>
+        <v>0.195619785</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.195658019</v>
+        <v>0.195612799</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.195632282</v>
+        <v>0.195641588</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.195654769</v>
+        <v>0.195662536</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.195632665</v>
+        <v>0.195633598</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.195641069</v>
+        <v>0.19566947</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.195639068</v>
+        <v>0.195669688</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.195653222</v>
+        <v>0.195632217</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.195648432</v>
+        <v>0.195623663</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7539,36 +7539,36 @@
         <v/>
       </c>
       <c r="AC29" s="30" t="n">
-        <v>0.000325616</v>
+        <v>0.00043487</v>
       </c>
       <c r="AD29" s="30" t="n">
-        <v>-0.000736792</v>
+        <v>-0.005376847</v>
       </c>
       <c r="AE29" s="31" t="n"/>
       <c r="AF29" s="30" t="n">
-        <v>-0.001681633</v>
+        <v>-0.007573113</v>
       </c>
       <c r="AG29" s="30" t="n">
-        <v>-0.006572189</v>
+        <v>0.005335923</v>
       </c>
       <c r="AH29" s="30" t="n">
-        <v>0.001418989</v>
+        <v>0.004738471</v>
       </c>
       <c r="AI29" s="30" t="n">
-        <v>0.000924517</v>
+        <v>-0.009393715</v>
       </c>
       <c r="AJ29" s="31" t="n"/>
       <c r="AK29" s="30" t="n">
-        <v>0.001999606</v>
+        <v>0.007618054</v>
       </c>
       <c r="AL29" s="30" t="n">
-        <v>0.002818262</v>
+        <v>0.003124976</v>
       </c>
       <c r="AM29" s="30" t="n">
-        <v>-0.000718524</v>
+        <v>0.002955297</v>
       </c>
       <c r="AN29" s="30" t="n">
-        <v>0.003809042</v>
+        <v>-0.007850642999999999</v>
       </c>
       <c r="AO29" s="31" t="n"/>
     </row>
@@ -7667,36 +7667,36 @@
         <v/>
       </c>
       <c r="AC30" s="30" t="n">
-        <v>0.003312846</v>
+        <v>0.003265899</v>
       </c>
       <c r="AD30" s="30" t="n">
-        <v>-0.000793757</v>
+        <v>-0.010767263</v>
       </c>
       <c r="AE30" s="31" t="n"/>
       <c r="AF30" s="30" t="n">
-        <v>-0.003964614</v>
+        <v>0.001094897</v>
       </c>
       <c r="AG30" s="30" t="n">
-        <v>-0.00570687</v>
+        <v>-0.000500233</v>
       </c>
       <c r="AH30" s="30" t="n">
-        <v>-0.000199415</v>
+        <v>0.000101962</v>
       </c>
       <c r="AI30" s="30" t="n">
-        <v>0.000368654</v>
+        <v>-0.004288019</v>
       </c>
       <c r="AJ30" s="31" t="n"/>
       <c r="AK30" s="30" t="n">
-        <v>0.00325249</v>
+        <v>0.003490319</v>
       </c>
       <c r="AL30" s="30" t="n">
-        <v>-0.000414237</v>
+        <v>0.009651167</v>
       </c>
       <c r="AM30" s="30" t="n">
-        <v>-0.004926214</v>
+        <v>-0.010068757</v>
       </c>
       <c r="AN30" s="30" t="n">
-        <v>0.000878726</v>
+        <v>0.005504965</v>
       </c>
       <c r="AO30" s="31" t="n"/>
     </row>
@@ -7926,33 +7926,33 @@
         <v>0.098859266</v>
       </c>
       <c r="AD32" s="24" t="n">
-        <v>0.127846982</v>
+        <v>0.127994398</v>
       </c>
       <c r="AE32" s="25" t="n"/>
       <c r="AF32" s="24" t="n">
-        <v>0.084370813</v>
+        <v>0.08449047599999999</v>
       </c>
       <c r="AG32" s="24" t="n">
-        <v>0.08591231000000001</v>
+        <v>0.086102491</v>
       </c>
       <c r="AH32" s="24" t="n">
-        <v>0.081141081</v>
+        <v>0.08124601300000001</v>
       </c>
       <c r="AI32" s="24" t="n">
-        <v>0.104645791</v>
+        <v>0.104617753</v>
       </c>
       <c r="AJ32" s="25" t="n"/>
       <c r="AK32" s="24" t="n">
-        <v>0.07200780699999999</v>
+        <v>0.071856566</v>
       </c>
       <c r="AL32" s="24" t="n">
-        <v>0.07590601700000001</v>
+        <v>0.075728029</v>
       </c>
       <c r="AM32" s="24" t="n">
-        <v>0.073753979</v>
+        <v>0.07355932900000001</v>
       </c>
       <c r="AN32" s="24" t="n">
-        <v>0.095686598</v>
+        <v>0.095442691</v>
       </c>
       <c r="AO32" s="25" t="n"/>
     </row>
@@ -8054,33 +8054,33 @@
         <v>0.038180475</v>
       </c>
       <c r="AD33" s="24" t="n">
-        <v>0.05225893</v>
+        <v>0.052304123</v>
       </c>
       <c r="AE33" s="25" t="n"/>
       <c r="AF33" s="24" t="n">
-        <v>0.036950608</v>
+        <v>0.037034916</v>
       </c>
       <c r="AG33" s="24" t="n">
-        <v>0.039375406</v>
+        <v>0.039453341</v>
       </c>
       <c r="AH33" s="24" t="n">
-        <v>0.03884011</v>
+        <v>0.038898776</v>
       </c>
       <c r="AI33" s="24" t="n">
-        <v>0.052130883</v>
+        <v>0.052130339</v>
       </c>
       <c r="AJ33" s="25" t="n"/>
       <c r="AK33" s="24" t="n">
-        <v>0.037662243</v>
+        <v>0.037591884</v>
       </c>
       <c r="AL33" s="24" t="n">
-        <v>0.04101519</v>
+        <v>0.040925538</v>
       </c>
       <c r="AM33" s="24" t="n">
-        <v>0.041188052</v>
+        <v>0.041082638</v>
       </c>
       <c r="AN33" s="24" t="n">
-        <v>0.05510773</v>
+        <v>0.05496726</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -8743,11 +8743,11 @@
         </is>
       </c>
       <c r="D41" s="34" t="n">
-        <v>3445</v>
+        <v>2975</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 3,295원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 3,220원)</t>
         </is>
       </c>
       <c r="F41" s="9" t="n"/>
@@ -8783,7 +8783,7 @@
       </c>
       <c r="D42" s="35" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -9018,7 +9018,7 @@
         </is>
       </c>
       <c r="D48" s="36" t="n">
-        <v>0.1213274590057092</v>
+        <v>0.1213164345694466</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
@@ -9057,7 +9057,7 @@
         </is>
       </c>
       <c r="D49" s="36" t="n">
-        <v>0.123100831412365</v>
+        <v>0.1231007607321269</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -9096,7 +9096,7 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.570758915326648</v>
+        <v>0.5707544369917492</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -9135,7 +9135,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.01662166756093186</v>
+        <v>0.01661689065158593</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -9174,7 +9174,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.03626533214186858</v>
+        <v>0.03625789200279597</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -9611,7 +9611,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18840,7 +18840,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -33332,7 +33332,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -38209,7 +38209,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -40241,7 +40241,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>210.9</v>
+        <v>211.3</v>
       </c>
     </row>
     <row r="30">
@@ -40261,7 +40261,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>16.33</v>
+        <v>14.08</v>
       </c>
     </row>
     <row r="32">
@@ -40271,7 +40271,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2.01</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="33">
@@ -40281,7 +40281,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.1228</v>
+        <v>0.123</v>
       </c>
     </row>
     <row r="34">
@@ -40291,7 +40291,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="35">
@@ -40301,7 +40301,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>2300</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="36">
